--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,150 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>South Korean K1 League</t>
+  </si>
+  <si>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
+    <t>Dutch Eredivisie</t>
+  </si>
+  <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>English Sky Bet Championship</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>15:55:00</t>
+  </si>
+  <si>
+    <t>16:45:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:45:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>Emelec</t>
+  </si>
+  <si>
+    <t>Mushuc Runa</t>
+  </si>
+  <si>
+    <t>Orense Sporting Club</t>
+  </si>
+  <si>
+    <t>Union Santa Fe</t>
+  </si>
+  <si>
+    <t>Ulsan Hyundai Horang-i</t>
+  </si>
+  <si>
+    <t>Incheon Utd</t>
+  </si>
+  <si>
+    <t>Al-Hazm (KSA)</t>
+  </si>
+  <si>
+    <t>NEC Nijmegen</t>
+  </si>
+  <si>
+    <t>Smouha</t>
+  </si>
+  <si>
+    <t>Al-Ittihad</t>
+  </si>
+  <si>
+    <t>Al-Quadisiya (KSA)</t>
+  </si>
+  <si>
+    <t>Southampton</t>
+  </si>
+  <si>
+    <t>Watford</t>
+  </si>
+  <si>
+    <t>Blackburn</t>
+  </si>
+  <si>
+    <t>Bolton</t>
+  </si>
+  <si>
+    <t>Manta FC</t>
+  </si>
+  <si>
+    <t>CD Leones del Norte</t>
+  </si>
+  <si>
+    <t>Guayaquil City</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
+    <t>Bucheon FC 1995</t>
+  </si>
+  <si>
+    <t>Al-Taawoun Buraidah</t>
+  </si>
+  <si>
+    <t>Excelsior</t>
+  </si>
+  <si>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Al-Feiha</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Swansea</t>
+  </si>
+  <si>
+    <t>Preston</t>
+  </si>
+  <si>
+    <t>Sheff Utd</t>
+  </si>
+  <si>
+    <t>West Ham</t>
+  </si>
+  <si>
+    <t>2026-09-06 01:56:42</t>
   </si>
 </sst>
 </file>
@@ -585,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +972,3636 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2">
+        <v>1.49</v>
+      </c>
+      <c r="G2">
+        <v>1.64</v>
+      </c>
+      <c r="H2">
+        <v>1.1</v>
+      </c>
+      <c r="I2">
+        <v>10.5</v>
+      </c>
+      <c r="J2">
+        <v>3.9</v>
+      </c>
+      <c r="K2">
+        <v>5.1</v>
+      </c>
+      <c r="L2">
+        <v>1.35</v>
+      </c>
+      <c r="M2">
+        <v>1.07</v>
+      </c>
+      <c r="N2">
+        <v>3.2</v>
+      </c>
+      <c r="O2">
+        <v>1.35</v>
+      </c>
+      <c r="P2">
+        <v>1.76</v>
+      </c>
+      <c r="Q2">
+        <v>2.04</v>
+      </c>
+      <c r="R2">
+        <v>1.26</v>
+      </c>
+      <c r="S2">
+        <v>3.2</v>
+      </c>
+      <c r="T2">
+        <v>2.14</v>
+      </c>
+      <c r="U2">
+        <v>1.7</v>
+      </c>
+      <c r="V2">
+        <v>1.12</v>
+      </c>
+      <c r="W2">
+        <v>2.56</v>
+      </c>
+      <c r="X2">
+        <v>15</v>
+      </c>
+      <c r="Y2">
+        <v>26</v>
+      </c>
+      <c r="Z2">
+        <v>940</v>
+      </c>
+      <c r="AA2">
+        <v>970</v>
+      </c>
+      <c r="AB2">
+        <v>7.8</v>
+      </c>
+      <c r="AC2">
+        <v>11.5</v>
+      </c>
+      <c r="AD2">
+        <v>38</v>
+      </c>
+      <c r="AE2">
+        <v>970</v>
+      </c>
+      <c r="AF2">
+        <v>9.4</v>
+      </c>
+      <c r="AG2">
+        <v>12</v>
+      </c>
+      <c r="AH2">
+        <v>34</v>
+      </c>
+      <c r="AI2">
+        <v>970</v>
+      </c>
+      <c r="AJ2">
+        <v>16.5</v>
+      </c>
+      <c r="AK2">
+        <v>22</v>
+      </c>
+      <c r="AL2">
+        <v>55</v>
+      </c>
+      <c r="AM2">
+        <v>970</v>
+      </c>
+      <c r="AN2">
+        <v>12</v>
+      </c>
+      <c r="AO2">
+        <v>970</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>1.01</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>1.01</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3">
+        <v>1.73</v>
+      </c>
+      <c r="G3">
+        <v>2.14</v>
+      </c>
+      <c r="H3">
+        <v>4.1</v>
+      </c>
+      <c r="I3">
+        <v>6.4</v>
+      </c>
+      <c r="J3">
+        <v>1.1</v>
+      </c>
+      <c r="K3">
+        <v>3.85</v>
+      </c>
+      <c r="L3">
+        <v>1.37</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>2.66</v>
+      </c>
+      <c r="O3">
+        <v>1.38</v>
+      </c>
+      <c r="P3">
+        <v>1.64</v>
+      </c>
+      <c r="Q3">
+        <v>2.02</v>
+      </c>
+      <c r="R3">
+        <v>1.2</v>
+      </c>
+      <c r="S3">
+        <v>3.5</v>
+      </c>
+      <c r="T3">
+        <v>1.01</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
+        <v>1.19</v>
+      </c>
+      <c r="W3">
+        <v>1.87</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3">
+        <v>1.01</v>
+      </c>
+      <c r="AR3">
+        <v>1.01</v>
+      </c>
+      <c r="AS3">
+        <v>1.01</v>
+      </c>
+      <c r="AT3">
+        <v>1.01</v>
+      </c>
+      <c r="AU3">
+        <v>1.01</v>
+      </c>
+      <c r="AV3">
+        <v>1.01</v>
+      </c>
+      <c r="AW3">
+        <v>1.01</v>
+      </c>
+      <c r="AX3">
+        <v>1.01</v>
+      </c>
+      <c r="AY3">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3">
+        <v>1.01</v>
+      </c>
+      <c r="BA3">
+        <v>1.01</v>
+      </c>
+      <c r="BB3">
+        <v>1.01</v>
+      </c>
+      <c r="BC3">
+        <v>1.01</v>
+      </c>
+      <c r="BD3">
+        <v>1.01</v>
+      </c>
+      <c r="BE3">
+        <v>1.01</v>
+      </c>
+      <c r="BF3">
+        <v>1.01</v>
+      </c>
+      <c r="BG3">
+        <v>1.01</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>2.44</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4">
+        <v>1.88</v>
+      </c>
+      <c r="G4">
+        <v>2.08</v>
+      </c>
+      <c r="H4">
+        <v>4.2</v>
+      </c>
+      <c r="I4">
+        <v>5.5</v>
+      </c>
+      <c r="J4">
+        <v>3.35</v>
+      </c>
+      <c r="K4">
+        <v>3.8</v>
+      </c>
+      <c r="L4">
+        <v>1.35</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>2.82</v>
+      </c>
+      <c r="O4">
+        <v>1.36</v>
+      </c>
+      <c r="P4">
+        <v>1.71</v>
+      </c>
+      <c r="Q4">
+        <v>2.08</v>
+      </c>
+      <c r="R4">
+        <v>1.08</v>
+      </c>
+      <c r="S4">
+        <v>2.38</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.22</v>
+      </c>
+      <c r="W4">
+        <v>1.92</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4">
+        <v>1.01</v>
+      </c>
+      <c r="AR4">
+        <v>1.01</v>
+      </c>
+      <c r="AS4">
+        <v>1.01</v>
+      </c>
+      <c r="AT4">
+        <v>1.01</v>
+      </c>
+      <c r="AU4">
+        <v>1.01</v>
+      </c>
+      <c r="AV4">
+        <v>1.01</v>
+      </c>
+      <c r="AW4">
+        <v>1.01</v>
+      </c>
+      <c r="AX4">
+        <v>1.01</v>
+      </c>
+      <c r="AY4">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4">
+        <v>1.01</v>
+      </c>
+      <c r="BA4">
+        <v>1.01</v>
+      </c>
+      <c r="BB4">
+        <v>1.01</v>
+      </c>
+      <c r="BC4">
+        <v>1.01</v>
+      </c>
+      <c r="BD4">
+        <v>1.01</v>
+      </c>
+      <c r="BE4">
+        <v>1.01</v>
+      </c>
+      <c r="BF4">
+        <v>1.01</v>
+      </c>
+      <c r="BG4">
+        <v>1.01</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5">
+        <v>2.68</v>
+      </c>
+      <c r="G5">
+        <v>2.92</v>
+      </c>
+      <c r="H5">
+        <v>3.05</v>
+      </c>
+      <c r="I5">
+        <v>3.45</v>
+      </c>
+      <c r="J5">
+        <v>2.94</v>
+      </c>
+      <c r="K5">
+        <v>3.2</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.11</v>
+      </c>
+      <c r="N5">
+        <v>2.58</v>
+      </c>
+      <c r="O5">
+        <v>1.56</v>
+      </c>
+      <c r="P5">
+        <v>1.53</v>
+      </c>
+      <c r="Q5">
+        <v>2.68</v>
+      </c>
+      <c r="R5">
+        <v>1.19</v>
+      </c>
+      <c r="S5">
+        <v>4.9</v>
+      </c>
+      <c r="T5">
+        <v>2.1</v>
+      </c>
+      <c r="U5">
+        <v>1.8</v>
+      </c>
+      <c r="V5">
+        <v>1.41</v>
+      </c>
+      <c r="W5">
+        <v>1.52</v>
+      </c>
+      <c r="X5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y5">
+        <v>10.5</v>
+      </c>
+      <c r="Z5">
+        <v>23</v>
+      </c>
+      <c r="AA5">
+        <v>75</v>
+      </c>
+      <c r="AB5">
+        <v>9.4</v>
+      </c>
+      <c r="AC5">
+        <v>8</v>
+      </c>
+      <c r="AD5">
+        <v>17</v>
+      </c>
+      <c r="AE5">
+        <v>60</v>
+      </c>
+      <c r="AF5">
+        <v>19.5</v>
+      </c>
+      <c r="AG5">
+        <v>15.5</v>
+      </c>
+      <c r="AH5">
+        <v>26</v>
+      </c>
+      <c r="AI5">
+        <v>85</v>
+      </c>
+      <c r="AJ5">
+        <v>60</v>
+      </c>
+      <c r="AK5">
+        <v>48</v>
+      </c>
+      <c r="AL5">
+        <v>80</v>
+      </c>
+      <c r="AM5">
+        <v>210</v>
+      </c>
+      <c r="AN5">
+        <v>60</v>
+      </c>
+      <c r="AO5">
+        <v>75</v>
+      </c>
+      <c r="AP5">
+        <v>7.6</v>
+      </c>
+      <c r="AQ5">
+        <v>7.8</v>
+      </c>
+      <c r="AR5">
+        <v>17.5</v>
+      </c>
+      <c r="AS5">
+        <v>5</v>
+      </c>
+      <c r="AT5">
+        <v>7.2</v>
+      </c>
+      <c r="AU5">
+        <v>6.2</v>
+      </c>
+      <c r="AV5">
+        <v>13</v>
+      </c>
+      <c r="AW5">
+        <v>4.9</v>
+      </c>
+      <c r="AX5">
+        <v>14.5</v>
+      </c>
+      <c r="AY5">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5">
+        <v>20</v>
+      </c>
+      <c r="BA5">
+        <v>5.1</v>
+      </c>
+      <c r="BB5">
+        <v>4.9</v>
+      </c>
+      <c r="BC5">
+        <v>4.8</v>
+      </c>
+      <c r="BD5">
+        <v>5.1</v>
+      </c>
+      <c r="BE5">
+        <v>5.3</v>
+      </c>
+      <c r="BF5">
+        <v>4.9</v>
+      </c>
+      <c r="BG5">
+        <v>5</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.07</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.07</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8">
+        <v>3.35</v>
+      </c>
+      <c r="G8">
+        <v>4.3</v>
+      </c>
+      <c r="H8">
+        <v>2.02</v>
+      </c>
+      <c r="I8">
+        <v>2.3</v>
+      </c>
+      <c r="J8">
+        <v>3.55</v>
+      </c>
+      <c r="K8">
+        <v>4.9</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>2</v>
+      </c>
+      <c r="Q8">
+        <v>1.77</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9">
+        <v>1.53</v>
+      </c>
+      <c r="G9">
+        <v>1.59</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
+        <v>6.2</v>
+      </c>
+      <c r="J9">
+        <v>4.9</v>
+      </c>
+      <c r="K9">
+        <v>5.4</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>3.1</v>
+      </c>
+      <c r="Q9">
+        <v>1.31</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10">
+        <v>3.5</v>
+      </c>
+      <c r="G10">
+        <v>3.85</v>
+      </c>
+      <c r="H10">
+        <v>2.46</v>
+      </c>
+      <c r="I10">
+        <v>2.74</v>
+      </c>
+      <c r="J10">
+        <v>2.82</v>
+      </c>
+      <c r="K10">
+        <v>3.05</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>1.45</v>
+      </c>
+      <c r="Q10">
+        <v>2.8</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>2.16</v>
+      </c>
+      <c r="U10">
+        <v>1.7</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>8.6</v>
+      </c>
+      <c r="Y10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z10">
+        <v>18</v>
+      </c>
+      <c r="AA10">
+        <v>55</v>
+      </c>
+      <c r="AB10">
+        <v>11.5</v>
+      </c>
+      <c r="AC10">
+        <v>8.4</v>
+      </c>
+      <c r="AD10">
+        <v>16</v>
+      </c>
+      <c r="AE10">
+        <v>50</v>
+      </c>
+      <c r="AF10">
+        <v>28</v>
+      </c>
+      <c r="AG10">
+        <v>21</v>
+      </c>
+      <c r="AH10">
+        <v>30</v>
+      </c>
+      <c r="AI10">
+        <v>90</v>
+      </c>
+      <c r="AJ10">
+        <v>100</v>
+      </c>
+      <c r="AK10">
+        <v>80</v>
+      </c>
+      <c r="AL10">
+        <v>110</v>
+      </c>
+      <c r="AM10">
+        <v>270</v>
+      </c>
+      <c r="AN10">
+        <v>110</v>
+      </c>
+      <c r="AO10">
+        <v>60</v>
+      </c>
+      <c r="AP10">
+        <v>5.8</v>
+      </c>
+      <c r="AQ10">
+        <v>5.5</v>
+      </c>
+      <c r="AR10">
+        <v>11</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>6.8</v>
+      </c>
+      <c r="AU10">
+        <v>5.3</v>
+      </c>
+      <c r="AV10">
+        <v>9.6</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>16.5</v>
+      </c>
+      <c r="AY10">
+        <v>12</v>
+      </c>
+      <c r="AZ10">
+        <v>18</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11">
+        <v>1.46</v>
+      </c>
+      <c r="G11">
+        <v>1.61</v>
+      </c>
+      <c r="H11">
+        <v>5.4</v>
+      </c>
+      <c r="I11">
+        <v>1000</v>
+      </c>
+      <c r="J11">
+        <v>2.62</v>
+      </c>
+      <c r="K11">
+        <v>7.8</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>2.56</v>
+      </c>
+      <c r="Q11">
+        <v>1.47</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12">
+        <v>1.75</v>
+      </c>
+      <c r="G12">
+        <v>2.22</v>
+      </c>
+      <c r="H12">
+        <v>3.65</v>
+      </c>
+      <c r="I12">
+        <v>5.4</v>
+      </c>
+      <c r="J12">
+        <v>3.5</v>
+      </c>
+      <c r="K12">
+        <v>6.6</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>2.36</v>
+      </c>
+      <c r="Q12">
+        <v>1.41</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13">
+        <v>1.96</v>
+      </c>
+      <c r="G13">
+        <v>2.08</v>
+      </c>
+      <c r="H13">
+        <v>3.9</v>
+      </c>
+      <c r="I13">
+        <v>4.4</v>
+      </c>
+      <c r="J13">
+        <v>3.65</v>
+      </c>
+      <c r="K13">
+        <v>4</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>2.06</v>
+      </c>
+      <c r="Q13">
+        <v>1.76</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14">
+        <v>2.2</v>
+      </c>
+      <c r="G14">
+        <v>2.36</v>
+      </c>
+      <c r="H14">
+        <v>3.35</v>
+      </c>
+      <c r="I14">
+        <v>3.65</v>
+      </c>
+      <c r="J14">
+        <v>3.45</v>
+      </c>
+      <c r="K14">
+        <v>3.8</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1.94</v>
+      </c>
+      <c r="Q14">
+        <v>1.93</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15">
+        <v>1.65</v>
+      </c>
+      <c r="G15">
+        <v>3.55</v>
+      </c>
+      <c r="H15">
+        <v>1.35</v>
+      </c>
+      <c r="I15">
+        <v>2.52</v>
+      </c>
+      <c r="J15">
+        <v>1.65</v>
+      </c>
+      <c r="K15">
+        <v>4.4</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>1.12</v>
+      </c>
+      <c r="Q15">
+        <v>1.01</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+      <c r="BA15">
+        <v>0</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>0</v>
+      </c>
+      <c r="BD15">
+        <v>0</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15">
+        <v>0</v>
+      </c>
+      <c r="BH15">
+        <v>0</v>
+      </c>
+      <c r="BI15">
+        <v>0</v>
+      </c>
+      <c r="BJ15">
+        <v>0</v>
+      </c>
+      <c r="BK15">
+        <v>0</v>
+      </c>
+      <c r="BL15">
+        <v>0</v>
+      </c>
+      <c r="BM15">
+        <v>0</v>
+      </c>
+      <c r="BN15">
+        <v>0</v>
+      </c>
+      <c r="BO15">
+        <v>0</v>
+      </c>
+      <c r="BP15">
+        <v>0</v>
+      </c>
+      <c r="BQ15">
+        <v>0</v>
+      </c>
+      <c r="BR15">
+        <v>0</v>
+      </c>
+      <c r="BS15">
+        <v>0</v>
+      </c>
+      <c r="BT15">
+        <v>0</v>
+      </c>
+      <c r="BU15">
+        <v>0</v>
+      </c>
+      <c r="BV15">
+        <v>0</v>
+      </c>
+      <c r="BW15">
+        <v>0</v>
+      </c>
+      <c r="BX15">
+        <v>0</v>
+      </c>
+      <c r="BY15">
+        <v>0</v>
+      </c>
+      <c r="BZ15">
+        <v>0</v>
+      </c>
+      <c r="CA15">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16">
+        <v>4.5</v>
+      </c>
+      <c r="G16">
+        <v>12</v>
+      </c>
+      <c r="H16">
+        <v>1.65</v>
+      </c>
+      <c r="I16">
+        <v>1.79</v>
+      </c>
+      <c r="J16">
+        <v>3.15</v>
+      </c>
+      <c r="K16">
+        <v>5.4</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.1</v>
+      </c>
+      <c r="Q16">
+        <v>1.01</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="132">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>South Korean K1 League</t>
   </si>
   <si>
+    <t>Estonian Premier League</t>
+  </si>
+  <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
@@ -289,6 +292,9 @@
     <t>10:30:00</t>
   </si>
   <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
     <t>15:55:00</t>
   </si>
   <si>
@@ -325,6 +331,9 @@
     <t>Incheon Utd</t>
   </si>
   <si>
+    <t>Trans Narva</t>
+  </si>
+  <si>
     <t>Al-Hazm (KSA)</t>
   </si>
   <si>
@@ -370,6 +379,9 @@
     <t>Bucheon FC 1995</t>
   </si>
   <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
     <t>Al-Taawoun Buraidah</t>
   </si>
   <si>
@@ -397,7 +409,7 @@
     <t>West Ham</t>
   </si>
   <si>
-    <t>2026-09-06 01:56:42</t>
+    <t>2026-09-06 04:17:41</t>
   </si>
 </sst>
 </file>
@@ -729,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -979,64 +991,64 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F2">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="G2">
         <v>1.64</v>
       </c>
       <c r="H2">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K2">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="L2">
         <v>1.35</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="O2">
         <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="T2">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
         <v>1.12</v>
@@ -1045,58 +1057,58 @@
         <v>2.56</v>
       </c>
       <c r="X2">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z2">
+        <v>910</v>
+      </c>
+      <c r="AA2">
         <v>940</v>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <v>970</v>
       </c>
-      <c r="AB2">
-        <v>7.8</v>
-      </c>
       <c r="AC2">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD2">
         <v>38</v>
       </c>
       <c r="AE2">
+        <v>940</v>
+      </c>
+      <c r="AF2">
         <v>970</v>
       </c>
-      <c r="AF2">
-        <v>9.4</v>
-      </c>
       <c r="AG2">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH2">
         <v>34</v>
       </c>
       <c r="AI2">
+        <v>940</v>
+      </c>
+      <c r="AJ2">
         <v>970</v>
       </c>
-      <c r="AJ2">
-        <v>16.5</v>
-      </c>
       <c r="AK2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL2">
         <v>55</v>
       </c>
       <c r="AM2">
+        <v>950</v>
+      </c>
+      <c r="AN2">
         <v>970</v>
       </c>
-      <c r="AN2">
-        <v>12</v>
-      </c>
       <c r="AO2">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AP2">
         <v>1.01</v>
@@ -1213,7 +1225,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1221,16 +1233,16 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F3">
         <v>1.73</v>
@@ -1260,7 +1272,7 @@
         <v>2.66</v>
       </c>
       <c r="O3">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
         <v>1.64</v>
@@ -1455,7 +1467,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1463,16 +1475,16 @@
         <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F4">
         <v>1.88</v>
@@ -1487,10 +1499,10 @@
         <v>5.5</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
         <v>1.35</v>
@@ -1499,7 +1511,7 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
         <v>1.36</v>
@@ -1511,7 +1523,7 @@
         <v>2.08</v>
       </c>
       <c r="R4">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
         <v>2.38</v>
@@ -1697,7 +1709,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1705,16 +1717,16 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F5">
         <v>2.68</v>
@@ -1726,13 +1738,13 @@
         <v>3.05</v>
       </c>
       <c r="I5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J5">
         <v>2.94</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1753,31 +1765,31 @@
         <v>2.68</v>
       </c>
       <c r="R5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="T5">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="U5">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="V5">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
         <v>1.52</v>
       </c>
       <c r="X5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y5">
         <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA5">
         <v>75</v>
@@ -1801,7 +1813,7 @@
         <v>15.5</v>
       </c>
       <c r="AH5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI5">
         <v>85</v>
@@ -1810,13 +1822,13 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL5">
         <v>80</v>
       </c>
       <c r="AM5">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN5">
         <v>60</v>
@@ -1825,7 +1837,7 @@
         <v>75</v>
       </c>
       <c r="AP5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5">
         <v>7.8</v>
@@ -1861,7 +1873,7 @@
         <v>5.1</v>
       </c>
       <c r="BB5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC5">
         <v>4.8</v>
@@ -1873,7 +1885,7 @@
         <v>5.3</v>
       </c>
       <c r="BF5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG5">
         <v>5</v>
@@ -1939,7 +1951,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1947,16 +1959,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2181,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2189,16 +2201,16 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2423,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2431,34 +2443,34 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F8">
-        <v>3.35</v>
+        <v>1.08</v>
       </c>
       <c r="G8">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="I8">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>1.08</v>
       </c>
       <c r="K8">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2473,10 +2485,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="Q8">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2665,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2673,35 +2685,35 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F9">
-        <v>1.53</v>
+        <v>3.35</v>
       </c>
       <c r="G9">
-        <v>1.59</v>
+        <v>4.3</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>2.02</v>
       </c>
       <c r="I9">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J9">
+        <v>3.55</v>
+      </c>
+      <c r="K9">
         <v>4.9</v>
       </c>
-      <c r="K9">
-        <v>5.4</v>
-      </c>
       <c r="L9">
         <v>0</v>
       </c>
@@ -2715,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.31</v>
+        <v>1.77</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2907,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2915,34 +2927,34 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F10">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="G10">
-        <v>3.85</v>
+        <v>1.59</v>
       </c>
       <c r="H10">
-        <v>2.46</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>2.74</v>
+        <v>6.2</v>
       </c>
       <c r="J10">
-        <v>2.82</v>
+        <v>4.9</v>
       </c>
       <c r="K10">
-        <v>3.05</v>
+        <v>5.4</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2957,10 +2969,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2969,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2981,112 +2993,112 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH10">
         <v>0</v>
@@ -3149,186 +3161,186 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F11">
-        <v>1.46</v>
+        <v>3.55</v>
       </c>
       <c r="G11">
-        <v>1.61</v>
+        <v>3.95</v>
       </c>
       <c r="H11">
+        <v>2.44</v>
+      </c>
+      <c r="I11">
+        <v>2.58</v>
+      </c>
+      <c r="J11">
+        <v>2.88</v>
+      </c>
+      <c r="K11">
+        <v>3.05</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.48</v>
+      </c>
+      <c r="Q11">
+        <v>2.8</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>2.18</v>
+      </c>
+      <c r="U11">
+        <v>1.72</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>8.6</v>
+      </c>
+      <c r="Y11">
+        <v>8.6</v>
+      </c>
+      <c r="Z11">
+        <v>17.5</v>
+      </c>
+      <c r="AA11">
+        <v>48</v>
+      </c>
+      <c r="AB11">
+        <v>12</v>
+      </c>
+      <c r="AC11">
+        <v>8.4</v>
+      </c>
+      <c r="AD11">
+        <v>15.5</v>
+      </c>
+      <c r="AE11">
+        <v>46</v>
+      </c>
+      <c r="AF11">
+        <v>30</v>
+      </c>
+      <c r="AG11">
+        <v>21</v>
+      </c>
+      <c r="AH11">
+        <v>30</v>
+      </c>
+      <c r="AI11">
+        <v>85</v>
+      </c>
+      <c r="AJ11">
+        <v>110</v>
+      </c>
+      <c r="AK11">
+        <v>80</v>
+      </c>
+      <c r="AL11">
+        <v>120</v>
+      </c>
+      <c r="AM11">
+        <v>260</v>
+      </c>
+      <c r="AN11">
+        <v>120</v>
+      </c>
+      <c r="AO11">
+        <v>55</v>
+      </c>
+      <c r="AP11">
+        <v>5.9</v>
+      </c>
+      <c r="AQ11">
         <v>5.4</v>
       </c>
-      <c r="I11">
-        <v>1000</v>
-      </c>
-      <c r="J11">
-        <v>2.62</v>
-      </c>
-      <c r="K11">
-        <v>7.8</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>2.56</v>
-      </c>
-      <c r="Q11">
-        <v>1.47</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>0</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
       <c r="AR11">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
         <v>0</v>
@@ -3391,42 +3403,42 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F12">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="G12">
-        <v>2.22</v>
+        <v>1.61</v>
       </c>
       <c r="H12">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="I12">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="K12">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3441,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="Q12">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3633,42 +3645,42 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F13">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="G13">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="H13">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="I13">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="J13">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3683,10 +3695,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="Q13">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3875,42 +3887,42 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F14">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="G14">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="H14">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="I14">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="J14">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K14">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3925,10 +3937,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="Q14">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4117,42 +4129,42 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F15">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="G15">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="H15">
-        <v>1.35</v>
+        <v>3.75</v>
       </c>
       <c r="I15">
-        <v>2.52</v>
+        <v>4.1</v>
       </c>
       <c r="J15">
-        <v>1.65</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4167,10 +4179,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1.12</v>
+        <v>1.96</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4359,249 +4371,491 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" t="s">
+        <v>129</v>
+      </c>
+      <c r="F16">
+        <v>3.1</v>
+      </c>
+      <c r="G16">
+        <v>3.65</v>
+      </c>
+      <c r="H16">
+        <v>1.37</v>
+      </c>
+      <c r="I16">
+        <v>13.5</v>
+      </c>
+      <c r="J16">
+        <v>1.37</v>
+      </c>
+      <c r="K16">
+        <v>4.2</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>1.96</v>
+      </c>
+      <c r="Q16">
+        <v>1.86</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>0</v>
+      </c>
+      <c r="BH16">
+        <v>0</v>
+      </c>
+      <c r="BI16">
+        <v>0</v>
+      </c>
+      <c r="BJ16">
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <v>0</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+      <c r="BM16">
+        <v>0</v>
+      </c>
+      <c r="BN16">
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <v>0</v>
+      </c>
+      <c r="BP16">
+        <v>0</v>
+      </c>
+      <c r="BQ16">
+        <v>0</v>
+      </c>
+      <c r="BR16">
+        <v>0</v>
+      </c>
+      <c r="BS16">
+        <v>0</v>
+      </c>
+      <c r="BT16">
+        <v>0</v>
+      </c>
+      <c r="BU16">
+        <v>0</v>
+      </c>
+      <c r="BV16">
+        <v>0</v>
+      </c>
+      <c r="BW16">
+        <v>0</v>
+      </c>
+      <c r="BX16">
+        <v>0</v>
+      </c>
+      <c r="BY16">
+        <v>0</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
         <v>87</v>
       </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" t="s">
-        <v>126</v>
-      </c>
-      <c r="F16">
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17">
         <v>4.5</v>
       </c>
-      <c r="G16">
+      <c r="G17">
+        <v>5.9</v>
+      </c>
+      <c r="H17">
+        <v>1.65</v>
+      </c>
+      <c r="I17">
+        <v>1.79</v>
+      </c>
+      <c r="J17">
+        <v>3.75</v>
+      </c>
+      <c r="K17">
+        <v>5.4</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>4.2</v>
+      </c>
+      <c r="O17">
+        <v>1.21</v>
+      </c>
+      <c r="P17">
+        <v>1.99</v>
+      </c>
+      <c r="Q17">
+        <v>1.21</v>
+      </c>
+      <c r="R17">
+        <v>1.08</v>
+      </c>
+      <c r="S17">
+        <v>1.77</v>
+      </c>
+      <c r="T17">
+        <v>1.01</v>
+      </c>
+      <c r="U17">
+        <v>1.01</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>1000</v>
+      </c>
+      <c r="AD17">
         <v>12</v>
       </c>
-      <c r="H16">
-        <v>1.65</v>
-      </c>
-      <c r="I16">
-        <v>1.79</v>
-      </c>
-      <c r="J16">
-        <v>3.15</v>
-      </c>
-      <c r="K16">
-        <v>5.4</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>1.1</v>
-      </c>
-      <c r="Q16">
-        <v>1.01</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>0</v>
-      </c>
-      <c r="AJ16">
-        <v>0</v>
-      </c>
-      <c r="AK16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>0</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>0</v>
-      </c>
-      <c r="BC16">
-        <v>0</v>
-      </c>
-      <c r="BD16">
-        <v>0</v>
-      </c>
-      <c r="BE16">
-        <v>0</v>
-      </c>
-      <c r="BF16">
-        <v>0</v>
-      </c>
-      <c r="BG16">
-        <v>0</v>
-      </c>
-      <c r="BH16">
-        <v>0</v>
-      </c>
-      <c r="BI16">
-        <v>0</v>
-      </c>
-      <c r="BJ16">
-        <v>0</v>
-      </c>
-      <c r="BK16">
-        <v>0</v>
-      </c>
-      <c r="BL16">
-        <v>0</v>
-      </c>
-      <c r="BM16">
-        <v>0</v>
-      </c>
-      <c r="BN16">
-        <v>0</v>
-      </c>
-      <c r="BO16">
-        <v>0</v>
-      </c>
-      <c r="BP16">
-        <v>0</v>
-      </c>
-      <c r="BQ16">
-        <v>0</v>
-      </c>
-      <c r="BR16">
-        <v>0</v>
-      </c>
-      <c r="BS16">
-        <v>0</v>
-      </c>
-      <c r="BT16">
-        <v>0</v>
-      </c>
-      <c r="BU16">
-        <v>0</v>
-      </c>
-      <c r="BV16">
-        <v>0</v>
-      </c>
-      <c r="BW16">
-        <v>0</v>
-      </c>
-      <c r="BX16">
-        <v>0</v>
-      </c>
-      <c r="BY16">
-        <v>0</v>
-      </c>
-      <c r="BZ16">
-        <v>0</v>
-      </c>
-      <c r="CA16">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>127</v>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.09</v>
+      </c>
+      <c r="AQ17">
+        <v>1.09</v>
+      </c>
+      <c r="AR17">
+        <v>1.09</v>
+      </c>
+      <c r="AS17">
+        <v>1.09</v>
+      </c>
+      <c r="AT17">
+        <v>1.09</v>
+      </c>
+      <c r="AU17">
+        <v>1.09</v>
+      </c>
+      <c r="AV17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW17">
+        <v>1.09</v>
+      </c>
+      <c r="AX17">
+        <v>1.09</v>
+      </c>
+      <c r="AY17">
+        <v>1.09</v>
+      </c>
+      <c r="AZ17">
+        <v>1.09</v>
+      </c>
+      <c r="BA17">
+        <v>1.09</v>
+      </c>
+      <c r="BB17">
+        <v>1.09</v>
+      </c>
+      <c r="BC17">
+        <v>1.09</v>
+      </c>
+      <c r="BD17">
+        <v>1.09</v>
+      </c>
+      <c r="BE17">
+        <v>1.09</v>
+      </c>
+      <c r="BF17">
+        <v>1.09</v>
+      </c>
+      <c r="BG17">
+        <v>1.09</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.01</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.01</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.01</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.01</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="137">
   <si>
     <t>League</t>
   </si>
@@ -295,6 +295,9 @@
     <t>14:30:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
     <t>15:55:00</t>
   </si>
   <si>
@@ -334,6 +337,9 @@
     <t>Trans Narva</t>
   </si>
   <si>
+    <t>Nomme Kalju</t>
+  </si>
+  <si>
     <t>Al-Hazm (KSA)</t>
   </si>
   <si>
@@ -358,6 +364,9 @@
     <t>Blackburn</t>
   </si>
   <si>
+    <t>Cardiff</t>
+  </si>
+  <si>
     <t>Bolton</t>
   </si>
   <si>
@@ -382,6 +391,9 @@
     <t>Tallinna FC Flora</t>
   </si>
   <si>
+    <t>Nomme Utd</t>
+  </si>
+  <si>
     <t>Al-Taawoun Buraidah</t>
   </si>
   <si>
@@ -406,10 +418,13 @@
     <t>Sheff Utd</t>
   </si>
   <si>
+    <t>Stoke</t>
+  </si>
+  <si>
     <t>West Ham</t>
   </si>
   <si>
-    <t>2026-09-06 04:17:41</t>
+    <t>2026-09-06 06:38:24</t>
   </si>
 </sst>
 </file>
@@ -741,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -997,10 +1012,10 @@
         <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F2">
         <v>1.44</v>
@@ -1012,10 +1027,10 @@
         <v>5.9</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
         <v>7.8</v>
@@ -1039,7 +1054,7 @@
         <v>2.02</v>
       </c>
       <c r="R2">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="S2">
         <v>2.16</v>
@@ -1225,7 +1240,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1239,10 +1254,10 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F3">
         <v>1.73</v>
@@ -1251,7 +1266,7 @@
         <v>2.14</v>
       </c>
       <c r="H3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I3">
         <v>6.4</v>
@@ -1290,7 +1305,7 @@
         <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V3">
         <v>1.19</v>
@@ -1467,7 +1482,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1481,28 +1496,28 @@
         <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F4">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G4">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I4">
         <v>5.5</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L4">
         <v>1.35</v>
@@ -1511,7 +1526,7 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="O4">
         <v>1.36</v>
@@ -1520,7 +1535,7 @@
         <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
         <v>1.25</v>
@@ -1538,61 +1553,61 @@
         <v>1.22</v>
       </c>
       <c r="W4">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP4">
         <v>1.01</v>
@@ -1709,7 +1724,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1723,10 +1738,10 @@
         <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F5">
         <v>2.68</v>
@@ -1738,7 +1753,7 @@
         <v>3.05</v>
       </c>
       <c r="I5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J5">
         <v>2.94</v>
@@ -1771,13 +1786,13 @@
         <v>5.5</v>
       </c>
       <c r="T5">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
         <v>1.52</v>
@@ -1951,7 +1966,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1965,10 +1980,10 @@
         <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2193,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2207,10 +2222,10 @@
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2435,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2449,10 +2464,10 @@
         <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F8">
         <v>1.08</v>
@@ -2470,7 +2485,7 @@
         <v>1.08</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2677,12 +2692,12 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
         <v>88</v>
@@ -2691,28 +2706,28 @@
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F9">
-        <v>3.35</v>
+        <v>1.08</v>
       </c>
       <c r="G9">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
       <c r="I9">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>1.08</v>
       </c>
       <c r="K9">
-        <v>4.9</v>
+        <v>310</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2727,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="Q9">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2919,12 +2934,12 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
         <v>88</v>
@@ -2933,28 +2948,28 @@
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F10">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="G10">
-        <v>1.59</v>
+        <v>3.5</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>2.24</v>
       </c>
       <c r="I10">
-        <v>6.2</v>
+        <v>2.44</v>
       </c>
       <c r="J10">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="K10">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2969,10 +2984,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="Q10">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3161,12 +3176,12 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
         <v>88</v>
@@ -3175,28 +3190,28 @@
         <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F11">
-        <v>3.55</v>
+        <v>1.52</v>
       </c>
       <c r="G11">
-        <v>3.95</v>
+        <v>1.64</v>
       </c>
       <c r="H11">
-        <v>2.44</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>2.58</v>
+        <v>6.4</v>
       </c>
       <c r="J11">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="K11">
-        <v>3.05</v>
+        <v>5.4</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3211,10 +3226,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="Q11">
-        <v>2.8</v>
+        <v>1.02</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3223,10 +3238,10 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -3235,112 +3250,112 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AL11">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AQ11">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AR11">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU11">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AV11">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX11">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AY11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AZ11">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH11">
         <v>0</v>
@@ -3403,12 +3418,12 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
@@ -3417,172 +3432,172 @@
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F12">
-        <v>1.46</v>
+        <v>3.5</v>
       </c>
       <c r="G12">
-        <v>1.61</v>
+        <v>4.2</v>
       </c>
       <c r="H12">
+        <v>2.46</v>
+      </c>
+      <c r="I12">
+        <v>2.82</v>
+      </c>
+      <c r="J12">
+        <v>2.68</v>
+      </c>
+      <c r="K12">
+        <v>3.1</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.44</v>
+      </c>
+      <c r="Q12">
+        <v>2.8</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>2.18</v>
+      </c>
+      <c r="U12">
+        <v>1.69</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>8.6</v>
+      </c>
+      <c r="Y12">
+        <v>8.6</v>
+      </c>
+      <c r="Z12">
+        <v>17.5</v>
+      </c>
+      <c r="AA12">
+        <v>48</v>
+      </c>
+      <c r="AB12">
+        <v>12</v>
+      </c>
+      <c r="AC12">
+        <v>8.4</v>
+      </c>
+      <c r="AD12">
+        <v>15.5</v>
+      </c>
+      <c r="AE12">
+        <v>46</v>
+      </c>
+      <c r="AF12">
+        <v>30</v>
+      </c>
+      <c r="AG12">
+        <v>21</v>
+      </c>
+      <c r="AH12">
+        <v>30</v>
+      </c>
+      <c r="AI12">
+        <v>85</v>
+      </c>
+      <c r="AJ12">
+        <v>110</v>
+      </c>
+      <c r="AK12">
+        <v>80</v>
+      </c>
+      <c r="AL12">
+        <v>120</v>
+      </c>
+      <c r="AM12">
+        <v>260</v>
+      </c>
+      <c r="AN12">
+        <v>120</v>
+      </c>
+      <c r="AO12">
+        <v>55</v>
+      </c>
+      <c r="AP12">
+        <v>5.9</v>
+      </c>
+      <c r="AQ12">
         <v>5.4</v>
       </c>
-      <c r="I12">
-        <v>1000</v>
-      </c>
-      <c r="J12">
-        <v>2.66</v>
-      </c>
-      <c r="K12">
-        <v>7.8</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>2.56</v>
-      </c>
-      <c r="Q12">
-        <v>1.47</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
       <c r="AR12">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
         <v>0</v>
@@ -3645,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3656,31 +3671,31 @@
         <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F13">
-        <v>1.75</v>
+        <v>1.08</v>
       </c>
       <c r="G13">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="H13">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="I13">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J13">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="K13">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3695,10 +3710,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="Q13">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3887,12 +3902,12 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
         <v>88</v>
@@ -3901,28 +3916,28 @@
         <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F14">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="G14">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="H14">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="I14">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="J14">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K14">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3937,10 +3952,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4129,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4140,31 +4155,31 @@
         <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F15">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="G15">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="H15">
+        <v>4.2</v>
+      </c>
+      <c r="I15">
+        <v>4.5</v>
+      </c>
+      <c r="J15">
         <v>3.75</v>
       </c>
-      <c r="I15">
-        <v>4.1</v>
-      </c>
-      <c r="J15">
-        <v>3.6</v>
-      </c>
       <c r="K15">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4179,10 +4194,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q15">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4371,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4382,31 +4397,31 @@
         <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F16">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="G16">
+        <v>2.14</v>
+      </c>
+      <c r="H16">
+        <v>3.75</v>
+      </c>
+      <c r="I16">
+        <v>3.9</v>
+      </c>
+      <c r="J16">
         <v>3.65</v>
       </c>
-      <c r="H16">
-        <v>1.37</v>
-      </c>
-      <c r="I16">
-        <v>13.5</v>
-      </c>
-      <c r="J16">
-        <v>1.37</v>
-      </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4421,10 +4436,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q16">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4613,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4627,235 +4642,719 @@
         <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F17">
+        <v>3.15</v>
+      </c>
+      <c r="G17">
+        <v>3.35</v>
+      </c>
+      <c r="H17">
+        <v>2.34</v>
+      </c>
+      <c r="I17">
+        <v>2.5</v>
+      </c>
+      <c r="J17">
+        <v>3.45</v>
+      </c>
+      <c r="K17">
+        <v>3.7</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1.98</v>
+      </c>
+      <c r="Q17">
+        <v>1.92</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18">
+        <v>1.1</v>
+      </c>
+      <c r="G18">
+        <v>2.48</v>
+      </c>
+      <c r="H18">
+        <v>1.1</v>
+      </c>
+      <c r="I18">
+        <v>3.5</v>
+      </c>
+      <c r="J18">
+        <v>1.1</v>
+      </c>
+      <c r="K18">
+        <v>4.7</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.12</v>
+      </c>
+      <c r="Q18">
+        <v>1.02</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19">
+        <v>5.4</v>
+      </c>
+      <c r="G19">
+        <v>6.2</v>
+      </c>
+      <c r="H19">
+        <v>1.66</v>
+      </c>
+      <c r="I19">
+        <v>1.73</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+      <c r="K19">
         <v>4.5</v>
       </c>
-      <c r="G17">
-        <v>5.9</v>
-      </c>
-      <c r="H17">
-        <v>1.65</v>
-      </c>
-      <c r="I17">
-        <v>1.79</v>
-      </c>
-      <c r="J17">
-        <v>3.75</v>
-      </c>
-      <c r="K17">
-        <v>5.4</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>4.2</v>
-      </c>
-      <c r="O17">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1.03</v>
+      </c>
+      <c r="N19">
+        <v>4.8</v>
+      </c>
+      <c r="O19">
         <v>1.21</v>
       </c>
-      <c r="P17">
-        <v>1.99</v>
-      </c>
-      <c r="Q17">
-        <v>1.21</v>
-      </c>
-      <c r="R17">
-        <v>1.08</v>
-      </c>
-      <c r="S17">
-        <v>1.77</v>
-      </c>
-      <c r="T17">
-        <v>1.01</v>
-      </c>
-      <c r="U17">
-        <v>1.01</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>1000</v>
-      </c>
-      <c r="Y17">
-        <v>1000</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>1000</v>
-      </c>
-      <c r="AC17">
-        <v>1000</v>
-      </c>
-      <c r="AD17">
+      <c r="P19">
+        <v>2.3</v>
+      </c>
+      <c r="Q19">
+        <v>1.69</v>
+      </c>
+      <c r="R19">
+        <v>1.52</v>
+      </c>
+      <c r="S19">
+        <v>2.62</v>
+      </c>
+      <c r="T19">
+        <v>1.66</v>
+      </c>
+      <c r="U19">
+        <v>2.24</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>30</v>
+      </c>
+      <c r="Y19">
+        <v>12.5</v>
+      </c>
+      <c r="Z19">
         <v>12</v>
       </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.09</v>
-      </c>
-      <c r="AQ17">
-        <v>1.09</v>
-      </c>
-      <c r="AR17">
-        <v>1.09</v>
-      </c>
-      <c r="AS17">
-        <v>1.09</v>
-      </c>
-      <c r="AT17">
-        <v>1.09</v>
-      </c>
-      <c r="AU17">
-        <v>1.09</v>
-      </c>
-      <c r="AV17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW17">
-        <v>1.09</v>
-      </c>
-      <c r="AX17">
-        <v>1.09</v>
-      </c>
-      <c r="AY17">
-        <v>1.09</v>
-      </c>
-      <c r="AZ17">
-        <v>1.09</v>
-      </c>
-      <c r="BA17">
-        <v>1.09</v>
-      </c>
-      <c r="BB17">
-        <v>1.09</v>
-      </c>
-      <c r="BC17">
-        <v>1.09</v>
-      </c>
-      <c r="BD17">
-        <v>1.09</v>
-      </c>
-      <c r="BE17">
-        <v>1.09</v>
-      </c>
-      <c r="BF17">
-        <v>1.09</v>
-      </c>
-      <c r="BG17">
-        <v>1.09</v>
-      </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
-        <v>1.01</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
-        <v>1.01</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.01</v>
-      </c>
-      <c r="BN17">
-        <v>1000</v>
-      </c>
-      <c r="BO17">
-        <v>1.01</v>
-      </c>
-      <c r="BP17">
-        <v>1000</v>
-      </c>
-      <c r="BQ17">
-        <v>1.01</v>
-      </c>
-      <c r="BR17">
-        <v>1000</v>
-      </c>
-      <c r="BS17">
-        <v>1.01</v>
-      </c>
-      <c r="BT17">
-        <v>1000</v>
-      </c>
-      <c r="BU17">
-        <v>1.01</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>1.01</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>1.01</v>
-      </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
-      <c r="CA17">
-        <v>1.01</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>131</v>
+      <c r="AA19">
+        <v>22</v>
+      </c>
+      <c r="AB19">
+        <v>38</v>
+      </c>
+      <c r="AC19">
+        <v>10</v>
+      </c>
+      <c r="AD19">
+        <v>11</v>
+      </c>
+      <c r="AE19">
+        <v>18.5</v>
+      </c>
+      <c r="AF19">
+        <v>140</v>
+      </c>
+      <c r="AG19">
+        <v>32</v>
+      </c>
+      <c r="AH19">
+        <v>23</v>
+      </c>
+      <c r="AI19">
+        <v>48</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>800</v>
+      </c>
+      <c r="AO19">
+        <v>9</v>
+      </c>
+      <c r="AP19">
+        <v>15.5</v>
+      </c>
+      <c r="AQ19">
+        <v>9</v>
+      </c>
+      <c r="AR19">
+        <v>9</v>
+      </c>
+      <c r="AS19">
+        <v>13.5</v>
+      </c>
+      <c r="AT19">
+        <v>17</v>
+      </c>
+      <c r="AU19">
+        <v>7.8</v>
+      </c>
+      <c r="AV19">
+        <v>8.4</v>
+      </c>
+      <c r="AW19">
+        <v>12</v>
+      </c>
+      <c r="AX19">
+        <v>34</v>
+      </c>
+      <c r="AY19">
+        <v>16</v>
+      </c>
+      <c r="AZ19">
+        <v>13.5</v>
+      </c>
+      <c r="BA19">
+        <v>21</v>
+      </c>
+      <c r="BB19">
+        <v>40</v>
+      </c>
+      <c r="BC19">
+        <v>30</v>
+      </c>
+      <c r="BD19">
+        <v>32</v>
+      </c>
+      <c r="BE19">
+        <v>34</v>
+      </c>
+      <c r="BF19">
+        <v>30</v>
+      </c>
+      <c r="BG19">
+        <v>7</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.01</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.01</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="140">
   <si>
     <t>League</t>
   </si>
@@ -298,6 +298,9 @@
     <t>15:00:00</t>
   </si>
   <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
     <t>15:55:00</t>
   </si>
   <si>
@@ -340,6 +343,9 @@
     <t>Nomme Kalju</t>
   </si>
   <si>
+    <t>Al-Ettifaq</t>
+  </si>
+  <si>
     <t>Al-Hazm (KSA)</t>
   </si>
   <si>
@@ -394,6 +400,9 @@
     <t>Nomme Utd</t>
   </si>
   <si>
+    <t>Al Faisaly ( KSA )</t>
+  </si>
+  <si>
     <t>Al-Taawoun Buraidah</t>
   </si>
   <si>
@@ -424,7 +433,7 @@
     <t>West Ham</t>
   </si>
   <si>
-    <t>2026-09-06 06:38:24</t>
+    <t>2026-09-06 08:58:47</t>
   </si>
 </sst>
 </file>
@@ -756,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB19"/>
+  <dimension ref="A1:CB20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1012,10 +1021,10 @@
         <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F2">
         <v>1.44</v>
@@ -1078,13 +1087,13 @@
         <v>23</v>
       </c>
       <c r="Z2">
-        <v>910</v>
+        <v>830</v>
       </c>
       <c r="AA2">
         <v>940</v>
       </c>
       <c r="AB2">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2">
         <v>970</v>
@@ -1240,7 +1249,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1254,10 +1263,10 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F3">
         <v>1.73</v>
@@ -1293,7 +1302,7 @@
         <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
         <v>1.2</v>
@@ -1482,7 +1491,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1496,10 +1505,10 @@
         <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F4">
         <v>1.87</v>
@@ -1511,7 +1520,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J4">
         <v>3.35</v>
@@ -1541,7 +1550,7 @@
         <v>1.25</v>
       </c>
       <c r="S4">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1724,7 +1733,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1738,10 +1747,10 @@
         <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F5">
         <v>2.68</v>
@@ -1756,7 +1765,7 @@
         <v>3.45</v>
       </c>
       <c r="J5">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="K5">
         <v>3.15</v>
@@ -1792,7 +1801,7 @@
         <v>1.79</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W5">
         <v>1.52</v>
@@ -1966,7 +1975,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1980,235 +1989,235 @@
         <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P6">
-        <v>1.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2222,235 +2231,235 @@
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.07</v>
+        <v>1.77</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2464,10 +2473,10 @@
         <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F8">
         <v>1.08</v>
@@ -2692,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2706,10 +2715,10 @@
         <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F9">
         <v>1.08</v>
@@ -2934,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2948,28 +2957,28 @@
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F10">
-        <v>3.1</v>
+        <v>1.71</v>
       </c>
       <c r="G10">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="H10">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="I10">
-        <v>2.44</v>
+        <v>5.7</v>
       </c>
       <c r="J10">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K10">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2984,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q10">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3176,12 +3185,12 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>88</v>
@@ -3190,28 +3199,28 @@
         <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F11">
-        <v>1.52</v>
+        <v>3.15</v>
       </c>
       <c r="G11">
-        <v>1.64</v>
+        <v>3.5</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="I11">
-        <v>6.4</v>
+        <v>2.44</v>
       </c>
       <c r="J11">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3226,10 +3235,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="Q11">
-        <v>1.02</v>
+        <v>1.78</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3418,12 +3427,12 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
@@ -3432,28 +3441,28 @@
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F12">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="G12">
-        <v>4.2</v>
+        <v>1.61</v>
       </c>
       <c r="H12">
-        <v>2.46</v>
+        <v>5.6</v>
       </c>
       <c r="I12">
-        <v>2.82</v>
+        <v>6.2</v>
       </c>
       <c r="J12">
-        <v>2.68</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3468,10 +3477,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="Q12">
-        <v>2.8</v>
+        <v>1.32</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3480,10 +3489,10 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3492,112 +3501,112 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AL12">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AQ12">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AR12">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU12">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AV12">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX12">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AY12">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AZ12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH12">
         <v>0</v>
@@ -3660,12 +3669,12 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
         <v>88</v>
@@ -3674,172 +3683,172 @@
         <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F13">
-        <v>1.08</v>
+        <v>3.5</v>
       </c>
       <c r="G13">
-        <v>1.59</v>
+        <v>3.8</v>
       </c>
       <c r="H13">
+        <v>2.46</v>
+      </c>
+      <c r="I13">
+        <v>2.82</v>
+      </c>
+      <c r="J13">
+        <v>2.7</v>
+      </c>
+      <c r="K13">
+        <v>3.1</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.44</v>
+      </c>
+      <c r="Q13">
+        <v>2.8</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>2.18</v>
+      </c>
+      <c r="U13">
+        <v>1.73</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>8.6</v>
+      </c>
+      <c r="Y13">
+        <v>8.6</v>
+      </c>
+      <c r="Z13">
+        <v>17.5</v>
+      </c>
+      <c r="AA13">
+        <v>48</v>
+      </c>
+      <c r="AB13">
+        <v>12</v>
+      </c>
+      <c r="AC13">
+        <v>8.4</v>
+      </c>
+      <c r="AD13">
+        <v>15.5</v>
+      </c>
+      <c r="AE13">
+        <v>46</v>
+      </c>
+      <c r="AF13">
+        <v>30</v>
+      </c>
+      <c r="AG13">
+        <v>21</v>
+      </c>
+      <c r="AH13">
+        <v>30</v>
+      </c>
+      <c r="AI13">
+        <v>85</v>
+      </c>
+      <c r="AJ13">
+        <v>110</v>
+      </c>
+      <c r="AK13">
+        <v>80</v>
+      </c>
+      <c r="AL13">
+        <v>120</v>
+      </c>
+      <c r="AM13">
+        <v>260</v>
+      </c>
+      <c r="AN13">
+        <v>120</v>
+      </c>
+      <c r="AO13">
+        <v>55</v>
+      </c>
+      <c r="AP13">
+        <v>5.9</v>
+      </c>
+      <c r="AQ13">
         <v>5.4</v>
       </c>
-      <c r="I13">
-        <v>1000</v>
-      </c>
-      <c r="J13">
-        <v>2.68</v>
-      </c>
-      <c r="K13">
-        <v>1000</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>2.56</v>
-      </c>
-      <c r="Q13">
-        <v>1.46</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
       <c r="AR13">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
         <v>0</v>
@@ -3902,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3913,31 +3922,31 @@
         <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F14">
-        <v>1.75</v>
+        <v>1.26</v>
       </c>
       <c r="G14">
-        <v>2.22</v>
+        <v>1.61</v>
       </c>
       <c r="H14">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="I14">
-        <v>5.4</v>
+        <v>75</v>
       </c>
       <c r="J14">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="K14">
-        <v>6.6</v>
+        <v>48</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3952,10 +3961,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="Q14">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4144,12 +4153,12 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
         <v>88</v>
@@ -4158,28 +4167,28 @@
         <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F15">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="H15">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="I15">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="J15">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K15">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4194,10 +4203,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="Q15">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -4386,7 +4395,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4397,32 +4406,32 @@
         <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F16">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="G16">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="H16">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="I16">
+        <v>4.5</v>
+      </c>
+      <c r="J16">
+        <v>3.7</v>
+      </c>
+      <c r="K16">
         <v>3.9</v>
       </c>
-      <c r="J16">
-        <v>3.65</v>
-      </c>
-      <c r="K16">
-        <v>3.85</v>
-      </c>
       <c r="L16">
         <v>0</v>
       </c>
@@ -4436,10 +4445,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q16">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4628,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4639,31 +4648,31 @@
         <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F17">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="G17">
-        <v>3.35</v>
+        <v>2.14</v>
       </c>
       <c r="H17">
-        <v>2.34</v>
+        <v>3.75</v>
       </c>
       <c r="I17">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="J17">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K17">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4681,7 +4690,7 @@
         <v>1.98</v>
       </c>
       <c r="Q17">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4870,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4881,31 +4890,31 @@
         <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F18">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="G18">
-        <v>2.48</v>
+        <v>3.35</v>
       </c>
       <c r="H18">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="I18">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="J18">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="K18">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4920,10 +4929,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.12</v>
+        <v>1.98</v>
       </c>
       <c r="Q18">
-        <v>1.02</v>
+        <v>1.92</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5112,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5126,58 +5135,58 @@
         <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F19">
-        <v>5.4</v>
+        <v>2.22</v>
       </c>
       <c r="G19">
-        <v>6.2</v>
+        <v>2.26</v>
       </c>
       <c r="H19">
-        <v>1.66</v>
+        <v>3.3</v>
       </c>
       <c r="I19">
-        <v>1.73</v>
+        <v>3.45</v>
       </c>
       <c r="J19">
+        <v>3.9</v>
+      </c>
+      <c r="K19">
         <v>4</v>
       </c>
-      <c r="K19">
-        <v>4.5</v>
-      </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R19">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -5186,175 +5195,417 @@
         <v>0</v>
       </c>
       <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19">
+        <v>0</v>
+      </c>
+      <c r="BI19">
+        <v>0</v>
+      </c>
+      <c r="BJ19">
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <v>0</v>
+      </c>
+      <c r="BL19">
+        <v>0</v>
+      </c>
+      <c r="BM19">
+        <v>0</v>
+      </c>
+      <c r="BN19">
+        <v>0</v>
+      </c>
+      <c r="BO19">
+        <v>0</v>
+      </c>
+      <c r="BP19">
+        <v>0</v>
+      </c>
+      <c r="BQ19">
+        <v>0</v>
+      </c>
+      <c r="BR19">
+        <v>0</v>
+      </c>
+      <c r="BS19">
+        <v>0</v>
+      </c>
+      <c r="BT19">
+        <v>0</v>
+      </c>
+      <c r="BU19">
+        <v>0</v>
+      </c>
+      <c r="BV19">
+        <v>0</v>
+      </c>
+      <c r="BW19">
+        <v>0</v>
+      </c>
+      <c r="BX19">
+        <v>0</v>
+      </c>
+      <c r="BY19">
+        <v>0</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F20">
+        <v>5.3</v>
+      </c>
+      <c r="G20">
+        <v>5.7</v>
+      </c>
+      <c r="H20">
+        <v>1.7</v>
+      </c>
+      <c r="I20">
+        <v>1.77</v>
+      </c>
+      <c r="J20">
+        <v>4</v>
+      </c>
+      <c r="K20">
+        <v>4.4</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1.05</v>
+      </c>
+      <c r="N20">
+        <v>4.9</v>
+      </c>
+      <c r="O20">
+        <v>1.23</v>
+      </c>
+      <c r="P20">
+        <v>2.32</v>
+      </c>
+      <c r="Q20">
+        <v>1.68</v>
+      </c>
+      <c r="R20">
+        <v>1.53</v>
+      </c>
+      <c r="S20">
+        <v>2.68</v>
+      </c>
+      <c r="T20">
+        <v>1.7</v>
+      </c>
+      <c r="U20">
+        <v>2.28</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>21</v>
+      </c>
+      <c r="Y20">
+        <v>11</v>
+      </c>
+      <c r="Z20">
+        <v>12.5</v>
+      </c>
+      <c r="AA20">
+        <v>17.5</v>
+      </c>
+      <c r="AB20">
+        <v>23</v>
+      </c>
+      <c r="AC20">
+        <v>9.6</v>
+      </c>
+      <c r="AD20">
+        <v>10.5</v>
+      </c>
+      <c r="AE20">
+        <v>16.5</v>
+      </c>
+      <c r="AF20">
+        <v>140</v>
+      </c>
+      <c r="AG20">
+        <v>22</v>
+      </c>
+      <c r="AH20">
+        <v>18</v>
+      </c>
+      <c r="AI20">
+        <v>60</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>770</v>
+      </c>
+      <c r="AO20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AP20">
+        <v>16.5</v>
+      </c>
+      <c r="AQ20">
+        <v>10</v>
+      </c>
+      <c r="AR20">
+        <v>10.5</v>
+      </c>
+      <c r="AS20">
+        <v>15.5</v>
+      </c>
+      <c r="AT20">
+        <v>16.5</v>
+      </c>
+      <c r="AU20">
+        <v>8.6</v>
+      </c>
+      <c r="AV20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW20">
+        <v>14.5</v>
+      </c>
+      <c r="AX20">
+        <v>26</v>
+      </c>
+      <c r="AY20">
+        <v>17.5</v>
+      </c>
+      <c r="AZ20">
+        <v>15.5</v>
+      </c>
+      <c r="BA20">
+        <v>24</v>
+      </c>
+      <c r="BB20">
+        <v>40</v>
+      </c>
+      <c r="BC20">
         <v>30</v>
       </c>
-      <c r="Y19">
-        <v>12.5</v>
-      </c>
-      <c r="Z19">
-        <v>12</v>
-      </c>
-      <c r="AA19">
-        <v>22</v>
-      </c>
-      <c r="AB19">
-        <v>38</v>
-      </c>
-      <c r="AC19">
-        <v>10</v>
-      </c>
-      <c r="AD19">
-        <v>11</v>
-      </c>
-      <c r="AE19">
-        <v>18.5</v>
-      </c>
-      <c r="AF19">
-        <v>140</v>
-      </c>
-      <c r="AG19">
+      <c r="BD20">
         <v>32</v>
       </c>
-      <c r="AH19">
-        <v>23</v>
-      </c>
-      <c r="AI19">
-        <v>48</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>1000</v>
-      </c>
-      <c r="AL19">
-        <v>1000</v>
-      </c>
-      <c r="AM19">
-        <v>1000</v>
-      </c>
-      <c r="AN19">
-        <v>800</v>
-      </c>
-      <c r="AO19">
-        <v>9</v>
-      </c>
-      <c r="AP19">
-        <v>15.5</v>
-      </c>
-      <c r="AQ19">
-        <v>9</v>
-      </c>
-      <c r="AR19">
-        <v>9</v>
-      </c>
-      <c r="AS19">
-        <v>13.5</v>
-      </c>
-      <c r="AT19">
-        <v>17</v>
-      </c>
-      <c r="AU19">
-        <v>7.8</v>
-      </c>
-      <c r="AV19">
-        <v>8.4</v>
-      </c>
-      <c r="AW19">
-        <v>12</v>
-      </c>
-      <c r="AX19">
+      <c r="BE20">
         <v>34</v>
       </c>
-      <c r="AY19">
-        <v>16</v>
-      </c>
-      <c r="AZ19">
-        <v>13.5</v>
-      </c>
-      <c r="BA19">
-        <v>21</v>
-      </c>
-      <c r="BB19">
-        <v>40</v>
-      </c>
-      <c r="BC19">
+      <c r="BF20">
         <v>30</v>
       </c>
-      <c r="BD19">
-        <v>32</v>
-      </c>
-      <c r="BE19">
-        <v>34</v>
-      </c>
-      <c r="BF19">
-        <v>30</v>
-      </c>
-      <c r="BG19">
-        <v>7</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.01</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.01</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.01</v>
-      </c>
-      <c r="BN19">
-        <v>1000</v>
-      </c>
-      <c r="BO19">
-        <v>1.01</v>
-      </c>
-      <c r="BP19">
-        <v>1000</v>
-      </c>
-      <c r="BQ19">
-        <v>1.01</v>
-      </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
-        <v>1.01</v>
-      </c>
-      <c r="BT19">
-        <v>1000</v>
-      </c>
-      <c r="BU19">
-        <v>1.01</v>
-      </c>
-      <c r="BV19">
-        <v>1000</v>
-      </c>
-      <c r="BW19">
-        <v>1.01</v>
-      </c>
-      <c r="BX19">
-        <v>1000</v>
-      </c>
-      <c r="BY19">
-        <v>1.01</v>
-      </c>
-      <c r="BZ19">
-        <v>1000</v>
-      </c>
-      <c r="CA19">
-        <v>1.01</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>136</v>
+      <c r="BG20">
+        <v>7.2</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.01</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.01</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.01</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.01</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -571,7 +571,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-09-07 12:46:00</t>
+    <t>2026-09-07 14:58:24</t>
   </si>
 </sst>
 </file>
@@ -1165,16 +1165,16 @@
         <v>148</v>
       </c>
       <c r="F2">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="G2">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J2">
         <v>3.9</v>
@@ -1183,52 +1183,52 @@
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q2">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
         <v>1.3</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T2">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="X2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z2">
         <v>60</v>
       </c>
       <c r="AA2">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AB2">
         <v>7.2</v>
@@ -1237,22 +1237,22 @@
         <v>9</v>
       </c>
       <c r="AD2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE2">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AF2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG2">
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ2">
         <v>19</v>
@@ -1261,28 +1261,28 @@
         <v>21</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN2">
         <v>13</v>
       </c>
       <c r="AO2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR2">
         <v>38</v>
       </c>
       <c r="AS2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1294,97 +1294,97 @@
         <v>19.5</v>
       </c>
       <c r="AW2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
         <v>21</v>
       </c>
       <c r="BA2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC2">
         <v>17</v>
       </c>
       <c r="BD2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE2">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BF2">
         <v>11</v>
       </c>
       <c r="BG2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BH2">
         <v>3.2</v>
       </c>
       <c r="BI2">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN2">
         <v>4.1</v>
       </c>
       <c r="BO2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP2">
         <v>12</v>
       </c>
       <c r="BQ2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BU2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="s">
         <v>185</v>
@@ -1407,7 +1407,7 @@
         <v>149</v>
       </c>
       <c r="F3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G3">
         <v>2.26</v>
@@ -1416,13 +1416,13 @@
         <v>3.9</v>
       </c>
       <c r="I3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
         <v>1.51</v>
@@ -1440,22 +1440,22 @@
         <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R3">
         <v>1.25</v>
       </c>
       <c r="S3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U3">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
         <v>1.79</v>
@@ -1464,13 +1464,13 @@
         <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA3">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="AB3">
         <v>8</v>
@@ -1494,28 +1494,28 @@
         <v>22</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL3">
         <v>60</v>
       </c>
       <c r="AM3">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO3">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AP3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3">
         <v>10.5</v>
@@ -1527,16 +1527,16 @@
         <v>55</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX3">
         <v>11</v>
@@ -1545,7 +1545,7 @@
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA3">
         <v>46</v>
@@ -1584,25 +1584,25 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BN3">
         <v>5</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT3">
         <v>7.4</v>
@@ -1611,22 +1611,22 @@
         <v>6</v>
       </c>
       <c r="BV3">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BW3">
         <v>6.8</v>
       </c>
       <c r="BX3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY3">
         <v>7.2</v>
       </c>
       <c r="BZ3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="CA3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="s">
         <v>185</v>
@@ -1649,16 +1649,16 @@
         <v>150</v>
       </c>
       <c r="F4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J4">
         <v>3.4</v>
@@ -1673,13 +1673,13 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
         <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
         <v>2.18</v>
@@ -1691,16 +1691,16 @@
         <v>4</v>
       </c>
       <c r="T4">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U4">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X4">
         <v>12</v>
@@ -1712,7 +1712,7 @@
         <v>32</v>
       </c>
       <c r="AA4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB4">
         <v>8.6</v>
@@ -1724,7 +1724,7 @@
         <v>18</v>
       </c>
       <c r="AE4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF4">
         <v>12.5</v>
@@ -1736,7 +1736,7 @@
         <v>20</v>
       </c>
       <c r="AI4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ4">
         <v>26</v>
@@ -1751,10 +1751,10 @@
         <v>150</v>
       </c>
       <c r="AN4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
@@ -1766,10 +1766,10 @@
         <v>23</v>
       </c>
       <c r="AS4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU4">
         <v>7</v>
@@ -1781,7 +1781,7 @@
         <v>38</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY4">
         <v>9.6</v>
@@ -1802,73 +1802,73 @@
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF4">
         <v>16</v>
       </c>
       <c r="BG4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH4">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI4">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP4">
         <v>16.5</v>
       </c>
       <c r="BQ4">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT4">
         <v>7.6</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW4">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY4">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4">
         <v>32</v>
       </c>
       <c r="CA4">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="s">
         <v>185</v>
@@ -1891,19 +1891,19 @@
         <v>151</v>
       </c>
       <c r="F5">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="G5">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H5">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="I5">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="J5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K5">
         <v>3.15</v>
@@ -1915,13 +1915,13 @@
         <v>1.13</v>
       </c>
       <c r="N5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O5">
         <v>1.55</v>
       </c>
       <c r="P5">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q5">
         <v>2.7</v>
@@ -1939,106 +1939,106 @@
         <v>1.83</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W5">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="X5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z5">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AA5">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>7</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH5">
         <v>22</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK5">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AL5">
         <v>75</v>
       </c>
       <c r="AM5">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP5">
         <v>7.8</v>
       </c>
       <c r="AQ5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5">
         <v>6.4</v>
       </c>
       <c r="AV5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX5">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AY5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA5">
         <v>50</v>
       </c>
       <c r="BB5">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="BC5">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BD5">
         <v>50</v>
@@ -2047,10 +2047,10 @@
         <v>46</v>
       </c>
       <c r="BF5">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BG5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BH5">
         <v>2.66</v>
@@ -2062,55 +2062,55 @@
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BN5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BO5">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BP5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BQ5">
+        <v>13</v>
+      </c>
+      <c r="BR5">
+        <v>55</v>
+      </c>
+      <c r="BS5">
+        <v>16.5</v>
+      </c>
+      <c r="BT5">
+        <v>5.4</v>
+      </c>
+      <c r="BU5">
+        <v>5</v>
+      </c>
+      <c r="BV5">
+        <v>25</v>
+      </c>
+      <c r="BW5">
         <v>12</v>
       </c>
-      <c r="BR5">
+      <c r="BX5">
+        <v>48</v>
+      </c>
+      <c r="BY5">
+        <v>16</v>
+      </c>
+      <c r="BZ5">
         <v>50</v>
       </c>
-      <c r="BS5">
-        <v>15</v>
-      </c>
-      <c r="BT5">
-        <v>5.7</v>
-      </c>
-      <c r="BU5">
-        <v>5.2</v>
-      </c>
-      <c r="BV5">
-        <v>27</v>
-      </c>
-      <c r="BW5">
-        <v>11.5</v>
-      </c>
-      <c r="BX5">
-        <v>50</v>
-      </c>
-      <c r="BY5">
-        <v>15</v>
-      </c>
-      <c r="BZ5">
-        <v>55</v>
-      </c>
       <c r="CA5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CB5" t="s">
         <v>185</v>
@@ -2145,10 +2145,10 @@
         <v>2.18</v>
       </c>
       <c r="J6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6">
         <v>1.29</v>
@@ -2166,10 +2166,10 @@
         <v>2.28</v>
       </c>
       <c r="Q6">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S6">
         <v>2.76</v>
@@ -2217,19 +2217,19 @@
         <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ6">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AM6">
         <v>1000</v>
@@ -2250,7 +2250,7 @@
         <v>13</v>
       </c>
       <c r="AS6">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AT6">
         <v>16</v>
@@ -2274,7 +2274,7 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB6">
         <v>40</v>
@@ -2298,7 +2298,7 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.52</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
@@ -2375,16 +2375,16 @@
         <v>153</v>
       </c>
       <c r="F7">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G7">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H7">
         <v>5</v>
       </c>
       <c r="I7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J7">
         <v>3.55</v>
@@ -2417,7 +2417,7 @@
         <v>4.1</v>
       </c>
       <c r="T7">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U7">
         <v>1.87</v>
@@ -2426,7 +2426,7 @@
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X7">
         <v>12</v>
@@ -2435,7 +2435,7 @@
         <v>17.5</v>
       </c>
       <c r="Z7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA7">
         <v>180</v>
@@ -2444,7 +2444,7 @@
         <v>7.6</v>
       </c>
       <c r="AC7">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7">
         <v>24</v>
@@ -2492,7 +2492,7 @@
         <v>21</v>
       </c>
       <c r="AS7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT7">
         <v>6.8</v>
@@ -2516,7 +2516,7 @@
         <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB7">
         <v>17.5</v>
@@ -2528,13 +2528,13 @@
         <v>23</v>
       </c>
       <c r="BE7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF7">
         <v>13.5</v>
       </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH7">
         <v>3.4</v>
@@ -2620,13 +2620,13 @@
         <v>5.2</v>
       </c>
       <c r="G8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I8">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="J8">
         <v>4.2</v>
@@ -2641,7 +2641,7 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O8">
         <v>1.23</v>
@@ -2665,10 +2665,10 @@
         <v>2.2</v>
       </c>
       <c r="V8">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="W8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X8">
         <v>26</v>
@@ -2785,34 +2785,34 @@
         <v>3.2</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BN8">
         <v>11</v>
       </c>
       <c r="BO8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP8">
         <v>55</v>
       </c>
       <c r="BQ8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR8">
         <v>55</v>
       </c>
       <c r="BS8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT8">
         <v>5.2</v>
@@ -2824,7 +2824,7 @@
         <v>12.5</v>
       </c>
       <c r="BW8">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BX8">
         <v>27</v>
@@ -2836,7 +2836,7 @@
         <v>19</v>
       </c>
       <c r="CA8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="CB8" t="s">
         <v>185</v>
@@ -2889,10 +2889,10 @@
         <v>1.27</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R9">
         <v>1.45</v>
@@ -2904,7 +2904,7 @@
         <v>1.91</v>
       </c>
       <c r="U9">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V9">
         <v>1.17</v>
@@ -2919,7 +2919,7 @@
         <v>23</v>
       </c>
       <c r="Z9">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2943,7 +2943,7 @@
         <v>10.5</v>
       </c>
       <c r="AH9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI9">
         <v>1000</v>
@@ -2955,7 +2955,7 @@
         <v>17</v>
       </c>
       <c r="AL9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM9">
         <v>1000</v>
@@ -2970,7 +2970,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ9">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AR9">
         <v>32</v>
@@ -3003,16 +3003,16 @@
         <v>55</v>
       </c>
       <c r="BB9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC9">
         <v>14</v>
       </c>
       <c r="BD9">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE9">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="BF9">
         <v>7.4</v>
@@ -3036,7 +3036,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN9">
         <v>4.1</v>
@@ -3051,7 +3051,7 @@
         <v>5.9</v>
       </c>
       <c r="BR9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS9">
         <v>8.800000000000001</v>
@@ -3078,7 +3078,7 @@
         <v>18</v>
       </c>
       <c r="CA9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB9" t="s">
         <v>185</v>
@@ -3101,10 +3101,10 @@
         <v>156</v>
       </c>
       <c r="F10">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G10">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H10">
         <v>6</v>
@@ -3113,7 +3113,7 @@
         <v>6.6</v>
       </c>
       <c r="J10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K10">
         <v>4.9</v>
@@ -3137,10 +3137,10 @@
         <v>1.64</v>
       </c>
       <c r="R10">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T10">
         <v>1.78</v>
@@ -3149,19 +3149,19 @@
         <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W10">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="X10">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y10">
         <v>28</v>
       </c>
       <c r="Z10">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3179,13 +3179,13 @@
         <v>95</v>
       </c>
       <c r="AF10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG10">
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10">
         <v>80</v>
@@ -3203,22 +3203,22 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO10">
         <v>95</v>
       </c>
       <c r="AP10">
+        <v>17</v>
+      </c>
+      <c r="AQ10">
         <v>17.5</v>
-      </c>
-      <c r="AQ10">
-        <v>19.5</v>
       </c>
       <c r="AR10">
         <v>30</v>
       </c>
       <c r="AS10">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="AT10">
         <v>9.800000000000001</v>
@@ -3236,7 +3236,7 @@
         <v>9.6</v>
       </c>
       <c r="AY10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
         <v>17.5</v>
@@ -3245,19 +3245,19 @@
         <v>40</v>
       </c>
       <c r="BB10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC10">
         <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BE10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG10">
         <v>34</v>
@@ -3343,16 +3343,16 @@
         <v>157</v>
       </c>
       <c r="F11">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G11">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H11">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J11">
         <v>3.6</v>
@@ -3391,10 +3391,10 @@
         <v>2.34</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W11">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X11">
         <v>18.5</v>
@@ -3418,7 +3418,7 @@
         <v>13.5</v>
       </c>
       <c r="AE11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF11">
         <v>17.5</v>
@@ -3472,7 +3472,7 @@
         <v>12</v>
       </c>
       <c r="AW11">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AX11">
         <v>15</v>
@@ -3484,7 +3484,7 @@
         <v>14</v>
       </c>
       <c r="BA11">
-        <v>8.6</v>
+        <v>19.5</v>
       </c>
       <c r="BB11">
         <v>8.4</v>
@@ -3496,7 +3496,7 @@
         <v>8.4</v>
       </c>
       <c r="BE11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF11">
         <v>14.5</v>
@@ -3520,22 +3520,22 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS11">
         <v>10</v>
@@ -3547,22 +3547,22 @@
         <v>5.7</v>
       </c>
       <c r="BV11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW11">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX11">
         <v>32</v>
       </c>
       <c r="BY11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ11">
         <v>21</v>
       </c>
       <c r="CA11">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="s">
         <v>185</v>
@@ -3585,25 +3585,25 @@
         <v>158</v>
       </c>
       <c r="F12">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G12">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H12">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I12">
         <v>6.8</v>
       </c>
       <c r="J12">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>5.4</v>
       </c>
       <c r="L12">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M12">
         <v>1.03</v>
@@ -3621,7 +3621,7 @@
         <v>1.46</v>
       </c>
       <c r="R12">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S12">
         <v>2.12</v>
@@ -3636,7 +3636,7 @@
         <v>1.17</v>
       </c>
       <c r="W12">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X12">
         <v>36</v>
@@ -3675,7 +3675,7 @@
         <v>65</v>
       </c>
       <c r="AJ12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK12">
         <v>15.5</v>
@@ -3693,16 +3693,16 @@
         <v>65</v>
       </c>
       <c r="AP12">
+        <v>7.6</v>
+      </c>
+      <c r="AQ12">
         <v>7.2</v>
-      </c>
-      <c r="AQ12">
-        <v>7</v>
       </c>
       <c r="AR12">
         <v>8</v>
       </c>
       <c r="AS12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12">
         <v>10.5</v>
@@ -3941,10 +3941,10 @@
         <v>12.5</v>
       </c>
       <c r="AR13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS13">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AT13">
         <v>8.800000000000001</v>
@@ -3968,7 +3968,7 @@
         <v>15.5</v>
       </c>
       <c r="BA13">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB13">
         <v>14.5</v>
@@ -3977,10 +3977,10 @@
         <v>19.5</v>
       </c>
       <c r="BD13">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="BE13">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF13">
         <v>14</v>
@@ -4072,7 +4072,7 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H14">
         <v>3.6</v>
@@ -4105,7 +4105,7 @@
         <v>1.63</v>
       </c>
       <c r="R14">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S14">
         <v>2.44</v>
@@ -4123,10 +4123,10 @@
         <v>1.9</v>
       </c>
       <c r="X14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z14">
         <v>32</v>
@@ -4144,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="AE14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF14">
         <v>16</v>
@@ -4311,226 +4311,226 @@
         <v>161</v>
       </c>
       <c r="F15">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="H15">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I15">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="J15">
         <v>3.75</v>
       </c>
       <c r="K15">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O15">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P15">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q15">
         <v>2</v>
       </c>
       <c r="R15">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T15">
+        <v>2.02</v>
+      </c>
+      <c r="U15">
+        <v>1.87</v>
+      </c>
+      <c r="V15">
+        <v>2.3</v>
+      </c>
+      <c r="W15">
+        <v>1.17</v>
+      </c>
+      <c r="X15">
+        <v>13.5</v>
+      </c>
+      <c r="Y15">
+        <v>7.6</v>
+      </c>
+      <c r="Z15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA15">
+        <v>21</v>
+      </c>
+      <c r="AB15">
+        <v>22</v>
+      </c>
+      <c r="AC15">
+        <v>9</v>
+      </c>
+      <c r="AD15">
+        <v>10.5</v>
+      </c>
+      <c r="AE15">
+        <v>24</v>
+      </c>
+      <c r="AF15">
+        <v>60</v>
+      </c>
+      <c r="AG15">
+        <v>29</v>
+      </c>
+      <c r="AH15">
+        <v>28</v>
+      </c>
+      <c r="AI15">
+        <v>55</v>
+      </c>
+      <c r="AJ15">
+        <v>230</v>
+      </c>
+      <c r="AK15">
+        <v>120</v>
+      </c>
+      <c r="AL15">
+        <v>120</v>
+      </c>
+      <c r="AM15">
+        <v>190</v>
+      </c>
+      <c r="AN15">
+        <v>170</v>
+      </c>
+      <c r="AO15">
+        <v>12.5</v>
+      </c>
+      <c r="AP15">
+        <v>4.9</v>
+      </c>
+      <c r="AQ15">
+        <v>3.85</v>
+      </c>
+      <c r="AR15">
+        <v>4.3</v>
+      </c>
+      <c r="AS15">
+        <v>5.5</v>
+      </c>
+      <c r="AT15">
+        <v>5.5</v>
+      </c>
+      <c r="AU15">
+        <v>4.2</v>
+      </c>
+      <c r="AV15">
+        <v>4.5</v>
+      </c>
+      <c r="AW15">
+        <v>5.6</v>
+      </c>
+      <c r="AX15">
+        <v>6.6</v>
+      </c>
+      <c r="AY15">
+        <v>5.9</v>
+      </c>
+      <c r="AZ15">
+        <v>5.8</v>
+      </c>
+      <c r="BA15">
+        <v>6.4</v>
+      </c>
+      <c r="BB15">
+        <v>7.2</v>
+      </c>
+      <c r="BC15">
+        <v>7</v>
+      </c>
+      <c r="BD15">
+        <v>7</v>
+      </c>
+      <c r="BE15">
+        <v>7</v>
+      </c>
+      <c r="BF15">
+        <v>7</v>
+      </c>
+      <c r="BG15">
+        <v>4.7</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
         <v>1.01</v>
       </c>
-      <c r="U15">
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
         <v>1.01</v>
       </c>
-      <c r="V15">
-        <v>2.24</v>
-      </c>
-      <c r="W15">
-        <v>1.14</v>
-      </c>
-      <c r="X15">
-        <v>1000</v>
-      </c>
-      <c r="Y15">
-        <v>1000</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>1000</v>
-      </c>
-      <c r="AC15">
-        <v>1000</v>
-      </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.03</v>
-      </c>
-      <c r="AQ15">
-        <v>1.03</v>
-      </c>
-      <c r="AR15">
-        <v>1.03</v>
-      </c>
-      <c r="AS15">
-        <v>1.03</v>
-      </c>
-      <c r="AT15">
-        <v>1.03</v>
-      </c>
-      <c r="AU15">
-        <v>1.03</v>
-      </c>
-      <c r="AV15">
-        <v>1.03</v>
-      </c>
-      <c r="AW15">
-        <v>1.03</v>
-      </c>
-      <c r="AX15">
-        <v>1.03</v>
-      </c>
-      <c r="AY15">
-        <v>1.03</v>
-      </c>
-      <c r="AZ15">
-        <v>1.03</v>
-      </c>
-      <c r="BA15">
-        <v>1.03</v>
-      </c>
-      <c r="BB15">
-        <v>1.03</v>
-      </c>
-      <c r="BC15">
-        <v>1.03</v>
-      </c>
-      <c r="BD15">
-        <v>1.03</v>
-      </c>
-      <c r="BE15">
-        <v>1.03</v>
-      </c>
-      <c r="BF15">
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
         <v>1.01</v>
       </c>
-      <c r="BG15">
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
         <v>1.01</v>
       </c>
-      <c r="BH15">
-        <v>3.9</v>
-      </c>
-      <c r="BI15">
-        <v>2.54</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>1.35</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.35</v>
-      </c>
-      <c r="BN15">
-        <v>1000</v>
-      </c>
-      <c r="BO15">
-        <v>1.35</v>
-      </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
         <v>185</v>
@@ -4553,58 +4553,58 @@
         <v>162</v>
       </c>
       <c r="F16">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="H16">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I16">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J16">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K16">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="L16">
+        <v>1.37</v>
+      </c>
+      <c r="M16">
+        <v>1.08</v>
+      </c>
+      <c r="N16">
+        <v>3.15</v>
+      </c>
+      <c r="O16">
         <v>1.33</v>
       </c>
-      <c r="M16">
-        <v>1.01</v>
-      </c>
-      <c r="N16">
-        <v>2.8</v>
-      </c>
-      <c r="O16">
-        <v>1.01</v>
-      </c>
       <c r="P16">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="Q16">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="R16">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S16">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V16">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="W16">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4619,10 +4619,10 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD16">
         <v>1000</v>
@@ -4661,58 +4661,58 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4801,7 +4801,7 @@
         <v>3.65</v>
       </c>
       <c r="H17">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I17">
         <v>2.26</v>
@@ -4846,7 +4846,7 @@
         <v>1.79</v>
       </c>
       <c r="W17">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X17">
         <v>16.5</v>
@@ -4855,13 +4855,13 @@
         <v>11</v>
       </c>
       <c r="Z17">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA17">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AB17">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC17">
         <v>8.4</v>
@@ -4870,7 +4870,7 @@
         <v>11.5</v>
       </c>
       <c r="AE17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF17">
         <v>28</v>
@@ -4882,7 +4882,7 @@
         <v>18</v>
       </c>
       <c r="AI17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ17">
         <v>75</v>
@@ -4894,13 +4894,13 @@
         <v>55</v>
       </c>
       <c r="AM17">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN17">
         <v>38</v>
       </c>
       <c r="AO17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP17">
         <v>14</v>
@@ -4912,7 +4912,7 @@
         <v>13</v>
       </c>
       <c r="AS17">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AT17">
         <v>13</v>
@@ -4924,7 +4924,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW17">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AX17">
         <v>17</v>
@@ -4936,22 +4936,22 @@
         <v>14.5</v>
       </c>
       <c r="BA17">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC17">
+        <v>32</v>
+      </c>
+      <c r="BD17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE17">
+        <v>10.5</v>
+      </c>
+      <c r="BF17">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BD17">
-        <v>9.6</v>
-      </c>
-      <c r="BE17">
-        <v>10</v>
-      </c>
-      <c r="BF17">
-        <v>8.800000000000001</v>
       </c>
       <c r="BG17">
         <v>14</v>
@@ -4972,49 +4972,49 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN17">
         <v>6.8</v>
       </c>
       <c r="BO17">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT17">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU17">
         <v>4.6</v>
       </c>
       <c r="BV17">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="BW17">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
+        <v>10.5</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
-      <c r="CA17">
-        <v>9.199999999999999</v>
       </c>
       <c r="CB17" t="s">
         <v>185</v>
@@ -5040,19 +5040,19 @@
         <v>4.1</v>
       </c>
       <c r="G18">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H18">
         <v>1.9</v>
       </c>
       <c r="I18">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="J18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L18">
         <v>1.31</v>
@@ -5106,7 +5106,7 @@
         <v>21</v>
       </c>
       <c r="AC18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD18">
         <v>10.5</v>
@@ -5121,7 +5121,7 @@
         <v>17</v>
       </c>
       <c r="AH18">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI18">
         <v>28</v>
@@ -5142,7 +5142,7 @@
         <v>38</v>
       </c>
       <c r="AO18">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AP18">
         <v>19.5</v>
@@ -5154,7 +5154,7 @@
         <v>12</v>
       </c>
       <c r="AS18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT18">
         <v>18</v>
@@ -5181,10 +5181,10 @@
         <v>24</v>
       </c>
       <c r="BB18">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BC18">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BD18">
         <v>38</v>
@@ -5205,16 +5205,16 @@
         <v>3.75</v>
       </c>
       <c r="BJ18">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK18">
         <v>7.8</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM18">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN18">
         <v>7.6</v>
@@ -5223,16 +5223,16 @@
         <v>6.6</v>
       </c>
       <c r="BP18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ18">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR18">
         <v>36</v>
       </c>
       <c r="BS18">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT18">
         <v>5.1</v>
@@ -5244,19 +5244,19 @@
         <v>13</v>
       </c>
       <c r="BW18">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX18">
         <v>24</v>
       </c>
       <c r="BY18">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ18">
         <v>17.5</v>
       </c>
       <c r="CA18">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB18" t="s">
         <v>185</v>
@@ -5279,16 +5279,16 @@
         <v>165</v>
       </c>
       <c r="F19">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G19">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H19">
         <v>4.5</v>
       </c>
       <c r="I19">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -5309,22 +5309,22 @@
         <v>1.22</v>
       </c>
       <c r="P19">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q19">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R19">
         <v>1.55</v>
       </c>
       <c r="S19">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T19">
         <v>1.66</v>
       </c>
       <c r="U19">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V19">
         <v>1.27</v>
@@ -5351,10 +5351,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD19">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE19">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF19">
         <v>13</v>
@@ -5363,7 +5363,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH19">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI19">
         <v>50</v>
@@ -5372,7 +5372,7 @@
         <v>21</v>
       </c>
       <c r="AK19">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL19">
         <v>28</v>
@@ -5381,10 +5381,10 @@
         <v>70</v>
       </c>
       <c r="AN19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO19">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP19">
         <v>18</v>
@@ -5396,7 +5396,7 @@
         <v>32</v>
       </c>
       <c r="AS19">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AT19">
         <v>10.5</v>
@@ -5411,7 +5411,7 @@
         <v>42</v>
       </c>
       <c r="AX19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY19">
         <v>9.4</v>
@@ -5429,16 +5429,16 @@
         <v>16</v>
       </c>
       <c r="BD19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE19">
         <v>55</v>
       </c>
       <c r="BF19">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH19">
         <v>4</v>
@@ -5456,13 +5456,13 @@
         <v>95</v>
       </c>
       <c r="BM19">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="BN19">
         <v>4.8</v>
       </c>
       <c r="BO19">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP19">
         <v>12</v>
@@ -5474,7 +5474,7 @@
         <v>23</v>
       </c>
       <c r="BS19">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="BT19">
         <v>8</v>
@@ -5486,19 +5486,19 @@
         <v>34</v>
       </c>
       <c r="BW19">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="BX19">
         <v>38</v>
       </c>
       <c r="BY19">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="BZ19">
         <v>17</v>
       </c>
       <c r="CA19">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="CB19" t="s">
         <v>185</v>
@@ -5545,19 +5545,19 @@
         <v>1.05</v>
       </c>
       <c r="N20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O20">
         <v>1.26</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q20">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S20">
         <v>3</v>
@@ -5581,7 +5581,7 @@
         <v>13</v>
       </c>
       <c r="Z20">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA20">
         <v>38</v>
@@ -5599,10 +5599,10 @@
         <v>26</v>
       </c>
       <c r="AF20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH20">
         <v>15.5</v>
@@ -5614,7 +5614,7 @@
         <v>44</v>
       </c>
       <c r="AK20">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL20">
         <v>36</v>
@@ -5626,10 +5626,10 @@
         <v>22</v>
       </c>
       <c r="AO20">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP20">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ20">
         <v>12</v>
@@ -5644,7 +5644,7 @@
         <v>13</v>
       </c>
       <c r="AU20">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV20">
         <v>11</v>
@@ -5662,7 +5662,7 @@
         <v>14.5</v>
       </c>
       <c r="BA20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB20">
         <v>40</v>
@@ -5677,13 +5677,13 @@
         <v>60</v>
       </c>
       <c r="BF20">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG20">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BH20">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI20">
         <v>3.5</v>
@@ -5698,7 +5698,7 @@
         <v>95</v>
       </c>
       <c r="BM20">
-        <v>75</v>
+        <v>14.5</v>
       </c>
       <c r="BN20">
         <v>6</v>
@@ -5710,13 +5710,13 @@
         <v>22</v>
       </c>
       <c r="BQ20">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="BR20">
         <v>32</v>
       </c>
       <c r="BS20">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="BT20">
         <v>5.6</v>
@@ -5728,19 +5728,19 @@
         <v>19</v>
       </c>
       <c r="BW20">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BX20">
         <v>29</v>
       </c>
       <c r="BY20">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BZ20">
         <v>22</v>
       </c>
       <c r="CA20">
-        <v>17.5</v>
+        <v>9.6</v>
       </c>
       <c r="CB20" t="s">
         <v>185</v>
@@ -5763,22 +5763,22 @@
         <v>167</v>
       </c>
       <c r="F21">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G21">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="H21">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I21">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K21">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L21">
         <v>1.21</v>
@@ -5793,31 +5793,31 @@
         <v>1.14</v>
       </c>
       <c r="P21">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R21">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S21">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T21">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U21">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V21">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W21">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="X21">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y21">
         <v>38</v>
@@ -5829,73 +5829,73 @@
         <v>140</v>
       </c>
       <c r="AB21">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC21">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD21">
         <v>23</v>
       </c>
       <c r="AE21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF21">
         <v>15</v>
       </c>
       <c r="AG21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH21">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI21">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ21">
         <v>18.5</v>
       </c>
       <c r="AK21">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL21">
         <v>23</v>
       </c>
       <c r="AM21">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AN21">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AO21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP21">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AQ21">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AR21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS21">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AT21">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU21">
         <v>10.5</v>
       </c>
       <c r="AV21">
-        <v>18</v>
+        <v>9.4</v>
       </c>
       <c r="AW21">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="AX21">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY21">
         <v>9.6</v>
@@ -5904,85 +5904,85 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB21">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BC21">
         <v>13</v>
       </c>
       <c r="BD21">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE21">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF21">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG21">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI21">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="BJ21">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BK21">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM21">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="BN21">
+        <v>5.2</v>
+      </c>
+      <c r="BO21">
+        <v>4.5</v>
+      </c>
+      <c r="BP21">
+        <v>11.5</v>
+      </c>
+      <c r="BQ21">
+        <v>4.6</v>
+      </c>
+      <c r="BR21">
+        <v>19.5</v>
+      </c>
+      <c r="BS21">
+        <v>13</v>
+      </c>
+      <c r="BT21">
+        <v>11.5</v>
+      </c>
+      <c r="BU21">
+        <v>4.6</v>
+      </c>
+      <c r="BV21">
+        <v>40</v>
+      </c>
+      <c r="BW21">
+        <v>5.6</v>
+      </c>
+      <c r="BX21">
+        <v>38</v>
+      </c>
+      <c r="BY21">
         <v>5.4</v>
       </c>
-      <c r="BO21">
-        <v>4</v>
-      </c>
-      <c r="BP21">
-        <v>13</v>
-      </c>
-      <c r="BQ21">
-        <v>7.2</v>
-      </c>
-      <c r="BR21">
-        <v>23</v>
-      </c>
-      <c r="BS21">
-        <v>3.4</v>
-      </c>
-      <c r="BT21">
-        <v>13</v>
-      </c>
-      <c r="BU21">
-        <v>7.2</v>
-      </c>
-      <c r="BV21">
-        <v>48</v>
-      </c>
-      <c r="BW21">
-        <v>3.7</v>
-      </c>
-      <c r="BX21">
-        <v>46</v>
-      </c>
-      <c r="BY21">
-        <v>3.7</v>
-      </c>
       <c r="BZ21">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="CA21">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="CB21" t="s">
         <v>185</v>
@@ -6038,7 +6038,7 @@
         <v>1.46</v>
       </c>
       <c r="Q22">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="R22">
         <v>1.16</v>
@@ -6059,7 +6059,7 @@
         <v>1.35</v>
       </c>
       <c r="X22">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y22">
         <v>7.4</v>
@@ -6083,7 +6083,7 @@
         <v>50</v>
       </c>
       <c r="AF22">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AG22">
         <v>21</v>
@@ -6122,7 +6122,7 @@
         <v>13</v>
       </c>
       <c r="AS22">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT22">
         <v>8.4</v>
@@ -6134,37 +6134,37 @@
         <v>11.5</v>
       </c>
       <c r="AW22">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX22">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AY22">
         <v>14.5</v>
       </c>
       <c r="AZ22">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BA22">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB22">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC22">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD22">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE22">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF22">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG22">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6250,13 +6250,13 @@
         <v>1.43</v>
       </c>
       <c r="G23">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H23">
         <v>10.5</v>
       </c>
       <c r="I23">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="J23">
         <v>4.2</v>
@@ -6277,28 +6277,28 @@
         <v>1.4</v>
       </c>
       <c r="P23">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q23">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R23">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T23">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U23">
         <v>1.48</v>
       </c>
       <c r="V23">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W23">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="X23">
         <v>13.5</v>
@@ -6313,22 +6313,22 @@
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC23">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD23">
         <v>55</v>
       </c>
       <c r="AE23">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AF23">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AG23">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH23">
         <v>44</v>
@@ -6337,7 +6337,7 @@
         <v>290</v>
       </c>
       <c r="AJ23">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AK23">
         <v>24</v>
@@ -6355,7 +6355,7 @@
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ23">
         <v>18.5</v>
@@ -6364,49 +6364,49 @@
         <v>5.2</v>
       </c>
       <c r="AS23">
+        <v>5.5</v>
+      </c>
+      <c r="AT23">
+        <v>5.3</v>
+      </c>
+      <c r="AU23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV23">
+        <v>5.2</v>
+      </c>
+      <c r="AW23">
         <v>5.4</v>
-      </c>
-      <c r="AT23">
-        <v>5.2</v>
-      </c>
-      <c r="AU23">
-        <v>8</v>
-      </c>
-      <c r="AV23">
-        <v>4.9</v>
-      </c>
-      <c r="AW23">
-        <v>5.3</v>
       </c>
       <c r="AX23">
         <v>6.2</v>
       </c>
       <c r="AY23">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA23">
+        <v>5.4</v>
+      </c>
+      <c r="BB23">
+        <v>10.5</v>
+      </c>
+      <c r="BC23">
+        <v>17</v>
+      </c>
+      <c r="BD23">
         <v>5.3</v>
       </c>
-      <c r="BB23">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC23">
-        <v>14</v>
-      </c>
-      <c r="BD23">
-        <v>5</v>
-      </c>
       <c r="BE23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF23">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG23">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6430,7 +6430,7 @@
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BP23">
         <v>1000</v>
@@ -6489,166 +6489,166 @@
         <v>170</v>
       </c>
       <c r="F24">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>2.82</v>
+        <v>2.32</v>
       </c>
       <c r="H24">
-        <v>2.68</v>
+        <v>3.55</v>
       </c>
       <c r="I24">
         <v>4.5</v>
       </c>
       <c r="J24">
-        <v>2.84</v>
+        <v>3.45</v>
       </c>
       <c r="K24">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="L24">
         <v>1.01</v>
       </c>
       <c r="M24">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N24">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="O24">
+        <v>1.3</v>
+      </c>
+      <c r="P24">
+        <v>1.92</v>
+      </c>
+      <c r="Q24">
+        <v>1.89</v>
+      </c>
+      <c r="R24">
+        <v>1.35</v>
+      </c>
+      <c r="S24">
+        <v>3.25</v>
+      </c>
+      <c r="T24">
+        <v>1.63</v>
+      </c>
+      <c r="U24">
+        <v>2.14</v>
+      </c>
+      <c r="V24">
         <v>1.29</v>
       </c>
-      <c r="P24">
-        <v>1.73</v>
-      </c>
-      <c r="Q24">
-        <v>1.71</v>
-      </c>
-      <c r="R24">
-        <v>1.24</v>
-      </c>
-      <c r="S24">
-        <v>2.68</v>
-      </c>
-      <c r="T24">
-        <v>1.01</v>
-      </c>
-      <c r="U24">
-        <v>1.01</v>
-      </c>
-      <c r="V24">
-        <v>1.28</v>
-      </c>
       <c r="W24">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP24">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ24">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR24">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS24">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT24">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU24">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AV24">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AW24">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX24">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AY24">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AZ24">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BA24">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB24">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC24">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BD24">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE24">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH24">
         <v>4.5</v>
@@ -6660,55 +6660,55 @@
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN24">
         <v>1000</v>
       </c>
       <c r="BO24">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BP24">
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT24">
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="CB24" t="s">
         <v>185</v>
@@ -6734,10 +6734,10 @@
         <v>1.47</v>
       </c>
       <c r="G25">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H25">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I25">
         <v>7.4</v>
@@ -6746,7 +6746,7 @@
         <v>4.8</v>
       </c>
       <c r="K25">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L25">
         <v>1.23</v>
@@ -6755,7 +6755,7 @@
         <v>1.03</v>
       </c>
       <c r="N25">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O25">
         <v>1.17</v>
@@ -6770,10 +6770,10 @@
         <v>1.7</v>
       </c>
       <c r="S25">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T25">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U25">
         <v>2.22</v>
@@ -6782,7 +6782,7 @@
         <v>1.15</v>
       </c>
       <c r="W25">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X25">
         <v>36</v>
@@ -6824,7 +6824,7 @@
         <v>17.5</v>
       </c>
       <c r="AK25">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AL25">
         <v>34</v>
@@ -6833,22 +6833,22 @@
         <v>100</v>
       </c>
       <c r="AN25">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO25">
         <v>85</v>
       </c>
       <c r="AP25">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ25">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="AR25">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="AS25">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT25">
         <v>10.5</v>
@@ -6860,7 +6860,7 @@
         <v>21</v>
       </c>
       <c r="AW25">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AX25">
         <v>9.800000000000001</v>
@@ -6872,7 +6872,7 @@
         <v>17</v>
       </c>
       <c r="BA25">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BB25">
         <v>12.5</v>
@@ -6881,52 +6881,52 @@
         <v>12.5</v>
       </c>
       <c r="BD25">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE25">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BF25">
         <v>4.8</v>
       </c>
       <c r="BG25">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH25">
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="BN25">
         <v>5.2</v>
       </c>
       <c r="BO25">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="BT25">
         <v>1000</v>
@@ -6938,19 +6938,19 @@
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="CB25" t="s">
         <v>185</v>
@@ -6976,7 +6976,7 @@
         <v>2.02</v>
       </c>
       <c r="G26">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H26">
         <v>3.35</v>
@@ -7215,22 +7215,22 @@
         <v>173</v>
       </c>
       <c r="F27">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G27">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H27">
         <v>3.6</v>
       </c>
       <c r="I27">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J27">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K27">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L27">
         <v>1.37</v>
@@ -7251,7 +7251,7 @@
         <v>1.86</v>
       </c>
       <c r="R27">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S27">
         <v>3.15</v>
@@ -7266,7 +7266,7 @@
         <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="X27">
         <v>17</v>
@@ -7275,7 +7275,7 @@
         <v>16</v>
       </c>
       <c r="Z27">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA27">
         <v>1000</v>
@@ -7287,7 +7287,7 @@
         <v>8.4</v>
       </c>
       <c r="AD27">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE27">
         <v>48</v>
@@ -7302,16 +7302,16 @@
         <v>17.5</v>
       </c>
       <c r="AI27">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="AJ27">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK27">
         <v>22</v>
       </c>
       <c r="AL27">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM27">
         <v>1000</v>
@@ -7320,7 +7320,7 @@
         <v>14.5</v>
       </c>
       <c r="AO27">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP27">
         <v>15</v>
@@ -7329,10 +7329,10 @@
         <v>13</v>
       </c>
       <c r="AR27">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS27">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT27">
         <v>9.6</v>
@@ -7344,10 +7344,10 @@
         <v>13.5</v>
       </c>
       <c r="AW27">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AX27">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY27">
         <v>9.800000000000001</v>
@@ -7356,16 +7356,16 @@
         <v>15</v>
       </c>
       <c r="BA27">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB27">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BC27">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE27">
         <v>55</v>
@@ -7383,7 +7383,7 @@
         <v>3.3</v>
       </c>
       <c r="BJ27">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK27">
         <v>8.199999999999999</v>
@@ -7398,16 +7398,16 @@
         <v>5.1</v>
       </c>
       <c r="BO27">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP27">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ27">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS27">
         <v>6.4</v>
@@ -7434,7 +7434,7 @@
         <v>27</v>
       </c>
       <c r="CA27">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB27" t="s">
         <v>185</v>
@@ -7463,10 +7463,10 @@
         <v>2.28</v>
       </c>
       <c r="H28">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I28">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J28">
         <v>3.8</v>
@@ -7490,13 +7490,13 @@
         <v>2.42</v>
       </c>
       <c r="Q28">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R28">
         <v>1.57</v>
       </c>
       <c r="S28">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T28">
         <v>1.58</v>
@@ -7514,16 +7514,16 @@
         <v>21</v>
       </c>
       <c r="Y28">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA28">
         <v>60</v>
       </c>
       <c r="AB28">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC28">
         <v>9</v>
@@ -7544,7 +7544,7 @@
         <v>15</v>
       </c>
       <c r="AI28">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ28">
         <v>29</v>
@@ -7559,13 +7559,13 @@
         <v>65</v>
       </c>
       <c r="AN28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO28">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP28">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28">
         <v>16</v>
@@ -7607,7 +7607,7 @@
         <v>18.5</v>
       </c>
       <c r="BD28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE28">
         <v>50</v>
@@ -7628,7 +7628,7 @@
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BL28">
         <v>1000</v>
@@ -7640,7 +7640,7 @@
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="BP28">
         <v>1000</v>
@@ -7658,7 +7658,7 @@
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -7699,22 +7699,22 @@
         <v>175</v>
       </c>
       <c r="F29">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G29">
         <v>3.2</v>
       </c>
       <c r="H29">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I29">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J29">
         <v>3.55</v>
       </c>
       <c r="K29">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L29">
         <v>1.36</v>
@@ -7732,13 +7732,13 @@
         <v>2</v>
       </c>
       <c r="Q29">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R29">
         <v>1.39</v>
       </c>
       <c r="S29">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T29">
         <v>1.74</v>
@@ -7747,13 +7747,13 @@
         <v>2.28</v>
       </c>
       <c r="V29">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W29">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X29">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y29">
         <v>11</v>
@@ -7768,7 +7768,7 @@
         <v>13</v>
       </c>
       <c r="AC29">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD29">
         <v>11.5</v>
@@ -7777,13 +7777,13 @@
         <v>26</v>
       </c>
       <c r="AF29">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG29">
         <v>13.5</v>
       </c>
       <c r="AH29">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI29">
         <v>38</v>
@@ -7798,7 +7798,7 @@
         <v>46</v>
       </c>
       <c r="AM29">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
         <v>32</v>
@@ -7831,7 +7831,7 @@
         <v>22</v>
       </c>
       <c r="AX29">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY29">
         <v>12.5</v>
@@ -7840,7 +7840,7 @@
         <v>15.5</v>
       </c>
       <c r="BA29">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BB29">
         <v>46</v>
@@ -7852,10 +7852,10 @@
         <v>38</v>
       </c>
       <c r="BE29">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG29">
         <v>17</v>
@@ -7888,13 +7888,13 @@
         <v>28</v>
       </c>
       <c r="BQ29">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR29">
         <v>42</v>
       </c>
       <c r="BS29">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT29">
         <v>5.4</v>
@@ -7906,19 +7906,19 @@
         <v>21</v>
       </c>
       <c r="BW29">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX29">
         <v>36</v>
       </c>
       <c r="BY29">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ29">
         <v>30</v>
       </c>
       <c r="CA29">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB29" t="s">
         <v>185</v>
@@ -7941,19 +7941,19 @@
         <v>176</v>
       </c>
       <c r="F30">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G30">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H30">
+        <v>3.65</v>
+      </c>
+      <c r="I30">
         <v>3.7</v>
       </c>
-      <c r="I30">
-        <v>3.8</v>
-      </c>
       <c r="J30">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K30">
         <v>3.7</v>
@@ -7974,7 +7974,7 @@
         <v>2</v>
       </c>
       <c r="Q30">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R30">
         <v>1.37</v>
@@ -7983,16 +7983,16 @@
         <v>3.45</v>
       </c>
       <c r="T30">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U30">
         <v>2.16</v>
       </c>
       <c r="V30">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W30">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X30">
         <v>14.5</v>
@@ -8061,7 +8061,7 @@
         <v>60</v>
       </c>
       <c r="AT30">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU30">
         <v>7.4</v>
@@ -8070,13 +8070,13 @@
         <v>14</v>
       </c>
       <c r="AW30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX30">
         <v>12</v>
       </c>
       <c r="AY30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ30">
         <v>16.5</v>
@@ -8130,7 +8130,7 @@
         <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="BR30">
         <v>1000</v>
@@ -8186,7 +8186,7 @@
         <v>1.94</v>
       </c>
       <c r="G31">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H31">
         <v>4.2</v>
@@ -8216,16 +8216,16 @@
         <v>2.12</v>
       </c>
       <c r="Q31">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S31">
         <v>3</v>
       </c>
       <c r="T31">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U31">
         <v>2.26</v>
@@ -8237,7 +8237,7 @@
         <v>2.02</v>
       </c>
       <c r="X31">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y31">
         <v>17.5</v>
@@ -8276,7 +8276,7 @@
         <v>22</v>
       </c>
       <c r="AK31">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL31">
         <v>32</v>
@@ -8288,7 +8288,7 @@
         <v>11.5</v>
       </c>
       <c r="AO31">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP31">
         <v>15.5</v>
@@ -8300,7 +8300,7 @@
         <v>29</v>
       </c>
       <c r="AS31">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AT31">
         <v>9.6</v>
@@ -8312,7 +8312,7 @@
         <v>15.5</v>
       </c>
       <c r="AW31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX31">
         <v>11</v>
@@ -8366,19 +8366,19 @@
         <v>4.8</v>
       </c>
       <c r="BO31">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP31">
         <v>13.5</v>
       </c>
       <c r="BQ31">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BR31">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS31">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT31">
         <v>7.8</v>
@@ -8396,13 +8396,13 @@
         <v>42</v>
       </c>
       <c r="BY31">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ31">
         <v>21</v>
       </c>
       <c r="CA31">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB31" t="s">
         <v>185</v>
@@ -8428,13 +8428,13 @@
         <v>5.5</v>
       </c>
       <c r="G32">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H32">
         <v>1.67</v>
       </c>
       <c r="I32">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J32">
         <v>4.2</v>
@@ -8458,22 +8458,22 @@
         <v>2.5</v>
       </c>
       <c r="Q32">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R32">
         <v>1.6</v>
       </c>
       <c r="S32">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T32">
         <v>1.69</v>
       </c>
       <c r="U32">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V32">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W32">
         <v>1.21</v>
@@ -8488,7 +8488,7 @@
         <v>11.5</v>
       </c>
       <c r="AA32">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB32">
         <v>25</v>
@@ -8500,7 +8500,7 @@
         <v>10.5</v>
       </c>
       <c r="AE32">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF32">
         <v>48</v>
@@ -8515,16 +8515,16 @@
         <v>27</v>
       </c>
       <c r="AJ32">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK32">
-        <v>65</v>
+        <v>790</v>
       </c>
       <c r="AL32">
         <v>60</v>
       </c>
       <c r="AM32">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN32">
         <v>55</v>
@@ -8536,7 +8536,7 @@
         <v>20</v>
       </c>
       <c r="AQ32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR32">
         <v>10.5</v>
@@ -8578,13 +8578,13 @@
         <v>50</v>
       </c>
       <c r="BE32">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF32">
         <v>29</v>
       </c>
       <c r="BG32">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH32">
         <v>4.8</v>
@@ -8614,13 +8614,13 @@
         <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="BR32">
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="BT32">
         <v>5</v>
@@ -8632,19 +8632,19 @@
         <v>1000</v>
       </c>
       <c r="BW32">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="BX32">
         <v>1000</v>
       </c>
       <c r="BY32">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="BZ32">
         <v>1000</v>
       </c>
       <c r="CA32">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="CB32" t="s">
         <v>185</v>
@@ -8670,7 +8670,7 @@
         <v>1.82</v>
       </c>
       <c r="G33">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H33">
         <v>4.4</v>
@@ -8679,7 +8679,7 @@
         <v>4.5</v>
       </c>
       <c r="J33">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K33">
         <v>4.5</v>
@@ -8697,7 +8697,7 @@
         <v>1.17</v>
       </c>
       <c r="P33">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q33">
         <v>1.51</v>
@@ -8709,25 +8709,25 @@
         <v>2.26</v>
       </c>
       <c r="T33">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U33">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V33">
         <v>1.28</v>
       </c>
       <c r="W33">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X33">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z33">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA33">
         <v>90</v>
@@ -8736,13 +8736,13 @@
         <v>15</v>
       </c>
       <c r="AC33">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD33">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE33">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF33">
         <v>15</v>
@@ -8775,7 +8775,7 @@
         <v>30</v>
       </c>
       <c r="AP33">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ33">
         <v>23</v>
@@ -8784,13 +8784,13 @@
         <v>36</v>
       </c>
       <c r="AS33">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AT33">
         <v>13.5</v>
       </c>
       <c r="AU33">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV33">
         <v>16.5</v>
@@ -8799,19 +8799,19 @@
         <v>38</v>
       </c>
       <c r="AX33">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY33">
         <v>9.6</v>
       </c>
       <c r="AZ33">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA33">
         <v>36</v>
       </c>
       <c r="BB33">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC33">
         <v>14.5</v>
@@ -8823,10 +8823,10 @@
         <v>48</v>
       </c>
       <c r="BF33">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG33">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH33">
         <v>4.7</v>
@@ -8835,7 +8835,7 @@
         <v>4.3</v>
       </c>
       <c r="BJ33">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK33">
         <v>7.6</v>
@@ -8844,16 +8844,16 @@
         <v>85</v>
       </c>
       <c r="BM33">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="BN33">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO33">
         <v>4.6</v>
       </c>
       <c r="BP33">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ33">
         <v>10</v>
@@ -8865,22 +8865,22 @@
         <v>14</v>
       </c>
       <c r="BT33">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU33">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV33">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BW33">
-        <v>20</v>
+        <v>8.4</v>
       </c>
       <c r="BX33">
         <v>32</v>
       </c>
       <c r="BY33">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="BZ33">
         <v>13</v>
@@ -8909,16 +8909,16 @@
         <v>180</v>
       </c>
       <c r="F34">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H34">
+        <v>1.77</v>
+      </c>
+      <c r="I34">
         <v>1.78</v>
-      </c>
-      <c r="I34">
-        <v>1.79</v>
       </c>
       <c r="J34">
         <v>4.2</v>
@@ -8939,10 +8939,10 @@
         <v>1.24</v>
       </c>
       <c r="P34">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q34">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R34">
         <v>1.53</v>
@@ -8954,16 +8954,16 @@
         <v>1.72</v>
       </c>
       <c r="U34">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V34">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="W34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X34">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y34">
         <v>11</v>
@@ -8972,10 +8972,10 @@
         <v>12</v>
       </c>
       <c r="AA34">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AB34">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC34">
         <v>9.6</v>
@@ -8984,16 +8984,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE34">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF34">
         <v>42</v>
       </c>
       <c r="AG34">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH34">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI34">
         <v>28</v>
@@ -9002,7 +9002,7 @@
         <v>1000</v>
       </c>
       <c r="AK34">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL34">
         <v>55</v>
@@ -9035,7 +9035,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV34">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW34">
         <v>15</v>
@@ -9053,7 +9053,7 @@
         <v>26</v>
       </c>
       <c r="BB34">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BC34">
         <v>50</v>
@@ -9068,13 +9068,13 @@
         <v>44</v>
       </c>
       <c r="BG34">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH34">
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
@@ -9110,13 +9110,13 @@
         <v>1000</v>
       </c>
       <c r="BU34">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BV34">
         <v>1000</v>
       </c>
       <c r="BW34">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BX34">
         <v>1000</v>
@@ -9154,19 +9154,19 @@
         <v>2.3</v>
       </c>
       <c r="G35">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H35">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I35">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J35">
+        <v>3.55</v>
+      </c>
+      <c r="K35">
         <v>3.6</v>
-      </c>
-      <c r="K35">
-        <v>3.65</v>
       </c>
       <c r="L35">
         <v>1.39</v>
@@ -9178,19 +9178,19 @@
         <v>4.2</v>
       </c>
       <c r="O35">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P35">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q35">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R35">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S35">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T35">
         <v>1.73</v>
@@ -9199,13 +9199,13 @@
         <v>2.3</v>
       </c>
       <c r="V35">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W35">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X35">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y35">
         <v>14.5</v>
@@ -9235,7 +9235,7 @@
         <v>11.5</v>
       </c>
       <c r="AH35">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI35">
         <v>44</v>
@@ -9247,13 +9247,13 @@
         <v>24</v>
       </c>
       <c r="AL35">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM35">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN35">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO35">
         <v>34</v>
@@ -9271,13 +9271,13 @@
         <v>55</v>
       </c>
       <c r="AT35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU35">
         <v>7.6</v>
       </c>
       <c r="AV35">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW35">
         <v>34</v>
@@ -9325,10 +9325,10 @@
         <v>8</v>
       </c>
       <c r="BL35">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BM35">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="BN35">
         <v>5.2</v>
@@ -9340,13 +9340,13 @@
         <v>16</v>
       </c>
       <c r="BQ35">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BR35">
         <v>28</v>
       </c>
       <c r="BS35">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BT35">
         <v>6.6</v>
@@ -9358,19 +9358,19 @@
         <v>26</v>
       </c>
       <c r="BW35">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="BX35">
         <v>36</v>
       </c>
       <c r="BY35">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="BZ35">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA35">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB35" t="s">
         <v>185</v>
@@ -9393,22 +9393,22 @@
         <v>182</v>
       </c>
       <c r="F36">
+        <v>1.65</v>
+      </c>
+      <c r="G36">
         <v>1.66</v>
       </c>
-      <c r="G36">
-        <v>1.68</v>
-      </c>
       <c r="H36">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I36">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J36">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K36">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L36">
         <v>1.26</v>
@@ -9426,7 +9426,7 @@
         <v>3</v>
       </c>
       <c r="Q36">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R36">
         <v>1.82</v>
@@ -9438,16 +9438,16 @@
         <v>1.55</v>
       </c>
       <c r="U36">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="V36">
         <v>1.22</v>
       </c>
       <c r="W36">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X36">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y36">
         <v>30</v>
@@ -9480,10 +9480,10 @@
         <v>16</v>
       </c>
       <c r="AI36">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ36">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK36">
         <v>14</v>
@@ -9510,7 +9510,7 @@
         <v>46</v>
       </c>
       <c r="AS36">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT36">
         <v>13.5</v>
@@ -9543,16 +9543,16 @@
         <v>13</v>
       </c>
       <c r="BD36">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE36">
         <v>48</v>
       </c>
       <c r="BF36">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG36">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH36">
         <v>5</v>
@@ -9570,7 +9570,7 @@
         <v>70</v>
       </c>
       <c r="BM36">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="BN36">
         <v>4.9</v>
@@ -9582,13 +9582,13 @@
         <v>10.5</v>
       </c>
       <c r="BQ36">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR36">
+        <v>18.5</v>
+      </c>
+      <c r="BS36">
         <v>9</v>
-      </c>
-      <c r="BR36">
-        <v>18</v>
-      </c>
-      <c r="BS36">
-        <v>13.5</v>
       </c>
       <c r="BT36">
         <v>9</v>
@@ -9600,19 +9600,19 @@
         <v>34</v>
       </c>
       <c r="BW36">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BX36">
         <v>34</v>
       </c>
       <c r="BY36">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BZ36">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA36">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB36" t="s">
         <v>185</v>
@@ -9877,10 +9877,10 @@
         <v>184</v>
       </c>
       <c r="F38">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H38">
         <v>5.1</v>
@@ -9913,7 +9913,7 @@
         <v>2.74</v>
       </c>
       <c r="R38">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S38">
         <v>5.8</v>
@@ -9925,7 +9925,7 @@
         <v>1.68</v>
       </c>
       <c r="V38">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W38">
         <v>2</v>
@@ -9970,7 +9970,7 @@
         <v>24</v>
       </c>
       <c r="AK38">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL38">
         <v>80</v>
@@ -9991,10 +9991,10 @@
         <v>11</v>
       </c>
       <c r="AR38">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS38">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT38">
         <v>5.5</v>
@@ -10006,7 +10006,7 @@
         <v>20</v>
       </c>
       <c r="AW38">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX38">
         <v>9</v>
@@ -10015,28 +10015,28 @@
         <v>10</v>
       </c>
       <c r="AZ38">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA38">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB38">
         <v>20</v>
       </c>
       <c r="BC38">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD38">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE38">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF38">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BG38">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH38">
         <v>2.66</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="190">
   <si>
     <t>League</t>
   </si>
@@ -289,6 +289,9 @@
     <t>English Sky Bet Championship</t>
   </si>
   <si>
+    <t>Chilean Primera B</t>
+  </si>
+  <si>
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
@@ -343,6 +346,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
     <t>22:00:00</t>
   </si>
   <si>
@@ -427,18 +433,18 @@
     <t>Wrexham</t>
   </si>
   <si>
+    <t>Blackburn</t>
+  </si>
+  <si>
     <t>Cardiff</t>
   </si>
   <si>
-    <t>Blackburn</t>
+    <t>Southampton</t>
   </si>
   <si>
     <t>Watford</t>
   </si>
   <si>
-    <t>Southampton</t>
-  </si>
-  <si>
     <t>Bolton</t>
   </si>
   <si>
@@ -454,6 +460,9 @@
     <t>Real Madrid</t>
   </si>
   <si>
+    <t>Puerto Montt</t>
+  </si>
+  <si>
     <t>Fluminense</t>
   </si>
   <si>
@@ -538,18 +547,18 @@
     <t>Burnley</t>
   </si>
   <si>
+    <t>Sheff Utd</t>
+  </si>
+  <si>
     <t>Stoke</t>
   </si>
   <si>
-    <t>Sheff Utd</t>
+    <t>Swansea</t>
   </si>
   <si>
     <t>Preston</t>
   </si>
   <si>
-    <t>Swansea</t>
-  </si>
-  <si>
     <t>West Ham</t>
   </si>
   <si>
@@ -565,13 +574,16 @@
     <t>Inter</t>
   </si>
   <si>
+    <t>CSD Rangers</t>
+  </si>
+  <si>
     <t>CA Platense</t>
   </si>
   <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-09-07 14:58:24</t>
+    <t>2026-09-07 17:10:43</t>
   </si>
 </sst>
 </file>
@@ -903,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB38"/>
+  <dimension ref="A1:CB39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1153,67 +1165,67 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F2">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G2">
         <v>1.7</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>6.6</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
         <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R2">
         <v>1.3</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
         <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W2">
         <v>2.42</v>
@@ -1222,7 +1234,7 @@
         <v>13</v>
       </c>
       <c r="Y2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z2">
         <v>60</v>
@@ -1243,13 +1255,13 @@
         <v>120</v>
       </c>
       <c r="AF2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG2">
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI2">
         <v>130</v>
@@ -1279,19 +1291,19 @@
         <v>16</v>
       </c>
       <c r="AR2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS2">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
         <v>7.8</v>
       </c>
       <c r="AV2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AW2">
         <v>55</v>
@@ -1312,37 +1324,37 @@
         <v>14.5</v>
       </c>
       <c r="BC2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BE2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF2">
         <v>11</v>
       </c>
       <c r="BG2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BH2">
         <v>3.2</v>
       </c>
       <c r="BI2">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN2">
         <v>4.1</v>
@@ -1351,43 +1363,43 @@
         <v>3.65</v>
       </c>
       <c r="BP2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT2">
         <v>9.6</v>
       </c>
       <c r="BU2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1395,19 +1407,19 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G3">
         <v>2.26</v>
@@ -1419,13 +1431,13 @@
         <v>4.1</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K3">
         <v>3.4</v>
       </c>
       <c r="L3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M3">
         <v>1.1</v>
@@ -1434,10 +1446,10 @@
         <v>3.05</v>
       </c>
       <c r="O3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q3">
         <v>2.4</v>
@@ -1467,7 +1479,7 @@
         <v>12</v>
       </c>
       <c r="Z3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA3">
         <v>100</v>
@@ -1479,13 +1491,13 @@
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE3">
         <v>70</v>
       </c>
       <c r="AF3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG3">
         <v>11.5</v>
@@ -1497,7 +1509,7 @@
         <v>95</v>
       </c>
       <c r="AJ3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK3">
         <v>29</v>
@@ -1509,7 +1521,7 @@
         <v>170</v>
       </c>
       <c r="AN3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO3">
         <v>90</v>
@@ -1548,10 +1560,10 @@
         <v>18.5</v>
       </c>
       <c r="BA3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC3">
         <v>23</v>
@@ -1572,10 +1584,10 @@
         <v>3.25</v>
       </c>
       <c r="BI3">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
         <v>8.4</v>
@@ -1584,10 +1596,10 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BN3">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BO3">
         <v>4.4</v>
@@ -1596,13 +1608,13 @@
         <v>21</v>
       </c>
       <c r="BQ3">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BR3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BS3">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BT3">
         <v>7.4</v>
@@ -1611,25 +1623,25 @@
         <v>6</v>
       </c>
       <c r="BV3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BW3">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX3">
         <v>60</v>
       </c>
       <c r="BY3">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BZ3">
         <v>40</v>
       </c>
       <c r="CA3">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="CB3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1637,94 +1649,94 @@
         <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F4">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G4">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P4">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T4">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE4">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF4">
         <v>12.5</v>
@@ -1736,7 +1748,7 @@
         <v>20</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
         <v>26</v>
@@ -1748,22 +1760,22 @@
         <v>44</v>
       </c>
       <c r="AM4">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP4">
         <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS4">
         <v>60</v>
@@ -1772,55 +1784,55 @@
         <v>7.6</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX4">
         <v>11</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA4">
         <v>46</v>
       </c>
       <c r="BB4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF4">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG4">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BH4">
         <v>3.15</v>
       </c>
       <c r="BI4">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1829,49 +1841,49 @@
         <v>11.5</v>
       </c>
       <c r="BN4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX4">
         <v>50</v>
       </c>
       <c r="BY4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1879,28 +1891,28 @@
         <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F5">
+        <v>3.05</v>
+      </c>
+      <c r="G5">
         <v>3.15</v>
       </c>
-      <c r="G5">
-        <v>3.2</v>
-      </c>
       <c r="H5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I5">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J5">
         <v>3.1</v>
@@ -1915,16 +1927,16 @@
         <v>1.13</v>
       </c>
       <c r="N5">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O5">
         <v>1.55</v>
       </c>
       <c r="P5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q5">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R5">
         <v>1.2</v>
@@ -1933,25 +1945,25 @@
         <v>5.7</v>
       </c>
       <c r="T5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
         <v>1.83</v>
       </c>
       <c r="V5">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA5">
         <v>46</v>
@@ -1969,16 +1981,16 @@
         <v>40</v>
       </c>
       <c r="AF5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ5">
         <v>60</v>
@@ -1993,22 +2005,22 @@
         <v>180</v>
       </c>
       <c r="AN5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO5">
         <v>46</v>
       </c>
       <c r="AP5">
+        <v>8</v>
+      </c>
+      <c r="AQ5">
         <v>7.8</v>
-      </c>
-      <c r="AQ5">
-        <v>7.6</v>
       </c>
       <c r="AR5">
         <v>14.5</v>
       </c>
       <c r="AS5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT5">
         <v>8.199999999999999</v>
@@ -2020,19 +2032,19 @@
         <v>12</v>
       </c>
       <c r="AW5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY5">
         <v>13</v>
       </c>
       <c r="AZ5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB5">
         <v>50</v>
@@ -2041,7 +2053,7 @@
         <v>42</v>
       </c>
       <c r="BD5">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BE5">
         <v>46</v>
@@ -2050,7 +2062,7 @@
         <v>50</v>
       </c>
       <c r="BG5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH5">
         <v>2.66</v>
@@ -2062,13 +2074,13 @@
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BN5">
         <v>5.9</v>
@@ -2080,16 +2092,16 @@
         <v>30</v>
       </c>
       <c r="BQ5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BR5">
         <v>55</v>
       </c>
       <c r="BS5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BT5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU5">
         <v>5</v>
@@ -2098,22 +2110,22 @@
         <v>25</v>
       </c>
       <c r="BW5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX5">
         <v>48</v>
       </c>
       <c r="BY5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BZ5">
         <v>50</v>
       </c>
       <c r="CA5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CB5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2121,31 +2133,31 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G6">
         <v>3.8</v>
       </c>
       <c r="H6">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I6">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K6">
         <v>3.85</v>
@@ -2157,7 +2169,7 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>1.23</v>
@@ -2169,10 +2181,10 @@
         <v>1.71</v>
       </c>
       <c r="R6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S6">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T6">
         <v>1.62</v>
@@ -2181,10 +2193,10 @@
         <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X6">
         <v>21</v>
@@ -2211,7 +2223,7 @@
         <v>21</v>
       </c>
       <c r="AF6">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG6">
         <v>15.5</v>
@@ -2220,7 +2232,7 @@
         <v>16</v>
       </c>
       <c r="AI6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
@@ -2229,13 +2241,13 @@
         <v>42</v>
       </c>
       <c r="AL6">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AM6">
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO6">
         <v>12.5</v>
@@ -2286,10 +2298,10 @@
         <v>36</v>
       </c>
       <c r="BE6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG6">
         <v>10.5</v>
@@ -2355,7 +2367,7 @@
         <v>2.32</v>
       </c>
       <c r="CB6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2363,19 +2375,19 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F7">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G7">
         <v>1.89</v>
@@ -2387,10 +2399,10 @@
         <v>5.4</v>
       </c>
       <c r="J7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
         <v>1.44</v>
@@ -2399,7 +2411,7 @@
         <v>1.09</v>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
         <v>1.4</v>
@@ -2420,22 +2432,22 @@
         <v>2.06</v>
       </c>
       <c r="U7">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V7">
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X7">
         <v>12</v>
       </c>
       <c r="Y7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA7">
         <v>180</v>
@@ -2444,7 +2456,7 @@
         <v>7.6</v>
       </c>
       <c r="AC7">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
         <v>24</v>
@@ -2459,7 +2471,7 @@
         <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI7">
         <v>110</v>
@@ -2492,7 +2504,7 @@
         <v>21</v>
       </c>
       <c r="AS7">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT7">
         <v>6.8</v>
@@ -2516,7 +2528,7 @@
         <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB7">
         <v>17.5</v>
@@ -2525,16 +2537,16 @@
         <v>19</v>
       </c>
       <c r="BD7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE7">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7">
         <v>13.5</v>
       </c>
       <c r="BG7">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7">
         <v>3.4</v>
@@ -2597,7 +2609,7 @@
         <v>2.86</v>
       </c>
       <c r="CB7" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2605,22 +2617,22 @@
         <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F8">
         <v>5.2</v>
       </c>
       <c r="G8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H8">
         <v>1.64</v>
@@ -2632,7 +2644,7 @@
         <v>4.2</v>
       </c>
       <c r="K8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L8">
         <v>1.26</v>
@@ -2644,7 +2656,7 @@
         <v>4.7</v>
       </c>
       <c r="O8">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P8">
         <v>2.28</v>
@@ -2656,7 +2668,7 @@
         <v>1.51</v>
       </c>
       <c r="S8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T8">
         <v>1.73</v>
@@ -2668,7 +2680,7 @@
         <v>2.4</v>
       </c>
       <c r="W8">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X8">
         <v>26</v>
@@ -2743,10 +2755,10 @@
         <v>9</v>
       </c>
       <c r="AV8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW8">
-        <v>4.7</v>
+        <v>14</v>
       </c>
       <c r="AX8">
         <v>5.6</v>
@@ -2818,7 +2830,7 @@
         <v>5.2</v>
       </c>
       <c r="BU8">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BV8">
         <v>12.5</v>
@@ -2830,16 +2842,16 @@
         <v>27</v>
       </c>
       <c r="BY8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA8">
         <v>3.8</v>
       </c>
       <c r="CB8" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2847,19 +2859,19 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F9">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
         <v>1.62</v>
@@ -2871,7 +2883,7 @@
         <v>6.8</v>
       </c>
       <c r="J9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K9">
         <v>4.6</v>
@@ -2892,7 +2904,7 @@
         <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R9">
         <v>1.45</v>
@@ -2955,13 +2967,13 @@
         <v>17</v>
       </c>
       <c r="AL9">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AM9">
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO9">
         <v>1000</v>
@@ -2970,7 +2982,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR9">
         <v>32</v>
@@ -3000,7 +3012,7 @@
         <v>19.5</v>
       </c>
       <c r="BA9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB9">
         <v>13.5</v>
@@ -3009,7 +3021,7 @@
         <v>14</v>
       </c>
       <c r="BD9">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BE9">
         <v>40</v>
@@ -3030,13 +3042,13 @@
         <v>11</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN9">
         <v>4.1</v>
@@ -3045,7 +3057,7 @@
         <v>3.8</v>
       </c>
       <c r="BP9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ9">
         <v>5.9</v>
@@ -3054,34 +3066,34 @@
         <v>25</v>
       </c>
       <c r="BS9">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT9">
         <v>10.5</v>
       </c>
       <c r="BU9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ9">
         <v>18</v>
       </c>
       <c r="CA9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3089,16 +3101,16 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F10">
         <v>1.57</v>
@@ -3116,7 +3128,7 @@
         <v>4.5</v>
       </c>
       <c r="K10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L10">
         <v>1.27</v>
@@ -3131,7 +3143,7 @@
         <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
         <v>1.64</v>
@@ -3140,7 +3152,7 @@
         <v>1.56</v>
       </c>
       <c r="S10">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T10">
         <v>1.78</v>
@@ -3155,13 +3167,13 @@
         <v>2.62</v>
       </c>
       <c r="X10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Y10">
         <v>28</v>
       </c>
       <c r="Z10">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3194,7 +3206,7 @@
         <v>17.5</v>
       </c>
       <c r="AK10">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL10">
         <v>34</v>
@@ -3209,10 +3221,10 @@
         <v>95</v>
       </c>
       <c r="AP10">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AQ10">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR10">
         <v>30</v>
@@ -3221,7 +3233,7 @@
         <v>44</v>
       </c>
       <c r="AT10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU10">
         <v>9.6</v>
@@ -3242,16 +3254,16 @@
         <v>17.5</v>
       </c>
       <c r="BA10">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BB10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC10">
         <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BE10">
         <v>55</v>
@@ -3323,7 +3335,7 @@
         <v>2.12</v>
       </c>
       <c r="CB10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3331,16 +3343,16 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F11">
         <v>2.34</v>
@@ -3484,16 +3496,16 @@
         <v>14</v>
       </c>
       <c r="BA11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BB11">
         <v>8.4</v>
       </c>
       <c r="BC11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD11">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="BE11">
         <v>10</v>
@@ -3565,7 +3577,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3573,31 +3585,31 @@
         <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F12">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G12">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H12">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I12">
         <v>6.8</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K12">
         <v>5.4</v>
@@ -3624,19 +3636,19 @@
         <v>1.72</v>
       </c>
       <c r="S12">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T12">
         <v>1.62</v>
       </c>
       <c r="U12">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V12">
         <v>1.17</v>
       </c>
       <c r="W12">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X12">
         <v>36</v>
@@ -3720,7 +3732,7 @@
         <v>9.6</v>
       </c>
       <c r="AY12">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12">
         <v>15.5</v>
@@ -3768,7 +3780,7 @@
         <v>5.1</v>
       </c>
       <c r="BO12">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP12">
         <v>10.5</v>
@@ -3807,7 +3819,7 @@
         <v>3.85</v>
       </c>
       <c r="CB12" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3815,31 +3827,31 @@
         <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F13">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G13">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H13">
         <v>3.7</v>
       </c>
       <c r="I13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J13">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K13">
         <v>3.7</v>
@@ -3857,7 +3869,7 @@
         <v>1.32</v>
       </c>
       <c r="P13">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q13">
         <v>1.95</v>
@@ -3875,10 +3887,10 @@
         <v>2.14</v>
       </c>
       <c r="V13">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W13">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X13">
         <v>15</v>
@@ -3980,7 +3992,7 @@
         <v>30</v>
       </c>
       <c r="BE13">
-        <v>48</v>
+        <v>9.6</v>
       </c>
       <c r="BF13">
         <v>14</v>
@@ -3998,13 +4010,13 @@
         <v>9.6</v>
       </c>
       <c r="BK13">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL13">
         <v>130</v>
       </c>
       <c r="BM13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN13">
         <v>5</v>
@@ -4013,13 +4025,13 @@
         <v>4.4</v>
       </c>
       <c r="BP13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS13">
         <v>10</v>
@@ -4034,22 +4046,22 @@
         <v>32</v>
       </c>
       <c r="BW13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ13">
         <v>27</v>
       </c>
       <c r="CA13">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB13" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4057,16 +4069,16 @@
         <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -4081,7 +4093,7 @@
         <v>3.8</v>
       </c>
       <c r="J14">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K14">
         <v>4.2</v>
@@ -4105,16 +4117,16 @@
         <v>1.63</v>
       </c>
       <c r="R14">
+        <v>1.57</v>
+      </c>
+      <c r="S14">
+        <v>2.46</v>
+      </c>
+      <c r="T14">
         <v>1.58</v>
       </c>
-      <c r="S14">
-        <v>2.44</v>
-      </c>
-      <c r="T14">
-        <v>1.56</v>
-      </c>
       <c r="U14">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V14">
         <v>1.35</v>
@@ -4291,7 +4303,7 @@
         <v>5</v>
       </c>
       <c r="CB14" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4299,16 +4311,16 @@
         <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F15">
         <v>5.8</v>
@@ -4317,7 +4329,7 @@
         <v>6.8</v>
       </c>
       <c r="H15">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="I15">
         <v>1.76</v>
@@ -4350,7 +4362,7 @@
         <v>1.31</v>
       </c>
       <c r="S15">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T15">
         <v>2.02</v>
@@ -4362,7 +4374,7 @@
         <v>2.3</v>
       </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X15">
         <v>13.5</v>
@@ -4428,10 +4440,10 @@
         <v>4.3</v>
       </c>
       <c r="AS15">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT15">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU15">
         <v>4.2</v>
@@ -4440,7 +4452,7 @@
         <v>4.5</v>
       </c>
       <c r="AW15">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX15">
         <v>6.6</v>
@@ -4533,7 +4545,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4541,70 +4553,70 @@
         <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F16">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="G16">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="H16">
+        <v>4.3</v>
+      </c>
+      <c r="I16">
+        <v>6.2</v>
+      </c>
+      <c r="J16">
+        <v>3.35</v>
+      </c>
+      <c r="K16">
         <v>4.5</v>
-      </c>
-      <c r="I16">
-        <v>6.8</v>
-      </c>
-      <c r="J16">
-        <v>3.7</v>
-      </c>
-      <c r="K16">
-        <v>4.8</v>
       </c>
       <c r="L16">
         <v>1.37</v>
       </c>
       <c r="M16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O16">
         <v>1.33</v>
       </c>
       <c r="P16">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q16">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R16">
         <v>1.29</v>
       </c>
       <c r="S16">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T16">
         <v>1.84</v>
       </c>
       <c r="U16">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V16">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W16">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4775,7 +4787,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4783,37 +4795,37 @@
         <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F17">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G17">
         <v>3.65</v>
       </c>
       <c r="H17">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I17">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="J17">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K17">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L17">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M17">
         <v>1.06</v>
@@ -4822,13 +4834,13 @@
         <v>4</v>
       </c>
       <c r="O17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P17">
         <v>2.04</v>
       </c>
       <c r="Q17">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="R17">
         <v>1.41</v>
@@ -4843,10 +4855,10 @@
         <v>2.24</v>
       </c>
       <c r="V17">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="W17">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X17">
         <v>16.5</v>
@@ -4867,13 +4879,13 @@
         <v>8.4</v>
       </c>
       <c r="AD17">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE17">
         <v>24</v>
       </c>
       <c r="AF17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG17">
         <v>15</v>
@@ -4936,22 +4948,22 @@
         <v>14.5</v>
       </c>
       <c r="BA17">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC17">
         <v>32</v>
       </c>
       <c r="BD17">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE17">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF17">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG17">
         <v>14</v>
@@ -4960,7 +4972,7 @@
         <v>3.55</v>
       </c>
       <c r="BI17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ17">
         <v>9.4</v>
@@ -5017,7 +5029,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="CB17" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5025,25 +5037,25 @@
         <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E18" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G18">
         <v>4.3</v>
       </c>
       <c r="H18">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I18">
         <v>1.94</v>
@@ -5112,7 +5124,7 @@
         <v>10.5</v>
       </c>
       <c r="AE18">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AF18">
         <v>36</v>
@@ -5133,7 +5145,7 @@
         <v>46</v>
       </c>
       <c r="AL18">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM18">
         <v>70</v>
@@ -5184,7 +5196,7 @@
         <v>55</v>
       </c>
       <c r="BC18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BD18">
         <v>38</v>
@@ -5205,7 +5217,7 @@
         <v>3.75</v>
       </c>
       <c r="BJ18">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK18">
         <v>7.8</v>
@@ -5214,7 +5226,7 @@
         <v>90</v>
       </c>
       <c r="BM18">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN18">
         <v>7.6</v>
@@ -5226,13 +5238,13 @@
         <v>29</v>
       </c>
       <c r="BQ18">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR18">
         <v>36</v>
       </c>
       <c r="BS18">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT18">
         <v>5.1</v>
@@ -5250,7 +5262,7 @@
         <v>24</v>
       </c>
       <c r="BY18">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ18">
         <v>17.5</v>
@@ -5259,7 +5271,7 @@
         <v>7.6</v>
       </c>
       <c r="CB18" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5267,22 +5279,22 @@
         <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E19" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F19">
         <v>1.87</v>
       </c>
       <c r="G19">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H19">
         <v>4.5</v>
@@ -5291,10 +5303,10 @@
         <v>4.6</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L19">
         <v>1.33</v>
@@ -5309,7 +5321,7 @@
         <v>1.22</v>
       </c>
       <c r="P19">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q19">
         <v>1.69</v>
@@ -5321,16 +5333,16 @@
         <v>2.72</v>
       </c>
       <c r="T19">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U19">
         <v>2.42</v>
       </c>
       <c r="V19">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W19">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X19">
         <v>20</v>
@@ -5339,7 +5351,7 @@
         <v>21</v>
       </c>
       <c r="Z19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA19">
         <v>95</v>
@@ -5354,7 +5366,7 @@
         <v>17.5</v>
       </c>
       <c r="AE19">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>13</v>
@@ -5396,10 +5408,10 @@
         <v>32</v>
       </c>
       <c r="AS19">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AT19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU19">
         <v>8.800000000000001</v>
@@ -5417,7 +5429,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ19">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA19">
         <v>44</v>
@@ -5429,13 +5441,13 @@
         <v>16</v>
       </c>
       <c r="BD19">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE19">
         <v>55</v>
       </c>
       <c r="BF19">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG19">
         <v>34</v>
@@ -5501,7 +5513,7 @@
         <v>9</v>
       </c>
       <c r="CB19" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5509,28 +5521,28 @@
         <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E20" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F20">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="G20">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="H20">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="I20">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J20">
         <v>3.7</v>
@@ -5539,13 +5551,13 @@
         <v>3.75</v>
       </c>
       <c r="L20">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N20">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O20">
         <v>1.26</v>
@@ -5560,19 +5572,19 @@
         <v>1.48</v>
       </c>
       <c r="S20">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T20">
         <v>1.66</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V20">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W20">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X20">
         <v>18</v>
@@ -5581,7 +5593,7 @@
         <v>13</v>
       </c>
       <c r="Z20">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA20">
         <v>38</v>
@@ -5605,16 +5617,16 @@
         <v>12.5</v>
       </c>
       <c r="AH20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI20">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ20">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK20">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL20">
         <v>36</v>
@@ -5623,7 +5635,7 @@
         <v>70</v>
       </c>
       <c r="AN20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO20">
         <v>18.5</v>
@@ -5635,7 +5647,7 @@
         <v>12</v>
       </c>
       <c r="AR20">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS20">
         <v>34</v>
@@ -5653,7 +5665,7 @@
         <v>23</v>
       </c>
       <c r="AX20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY20">
         <v>12</v>
@@ -5665,7 +5677,7 @@
         <v>32</v>
       </c>
       <c r="BB20">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BC20">
         <v>25</v>
@@ -5677,10 +5689,10 @@
         <v>60</v>
       </c>
       <c r="BF20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG20">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BH20">
         <v>3.75</v>
@@ -5692,37 +5704,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK20">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL20">
         <v>95</v>
       </c>
       <c r="BM20">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN20">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO20">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ20">
         <v>10</v>
       </c>
       <c r="BR20">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS20">
         <v>11</v>
       </c>
       <c r="BT20">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU20">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV20">
         <v>19</v>
@@ -5734,16 +5746,16 @@
         <v>29</v>
       </c>
       <c r="BY20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ20">
         <v>22</v>
       </c>
       <c r="CA20">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB20" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5751,46 +5763,46 @@
         <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F21">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G21">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H21">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I21">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J21">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K21">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L21">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="M21">
         <v>1.02</v>
       </c>
       <c r="N21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O21">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P21">
         <v>3.2</v>
@@ -5799,37 +5811,37 @@
         <v>1.41</v>
       </c>
       <c r="R21">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S21">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T21">
         <v>1.52</v>
       </c>
       <c r="U21">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V21">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W21">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA21">
         <v>140</v>
       </c>
       <c r="AB21">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC21">
         <v>12</v>
@@ -5841,25 +5853,25 @@
         <v>55</v>
       </c>
       <c r="AF21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG21">
         <v>11</v>
       </c>
       <c r="AH21">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI21">
         <v>48</v>
       </c>
       <c r="AJ21">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK21">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM21">
         <v>50</v>
@@ -5871,40 +5883,40 @@
         <v>36</v>
       </c>
       <c r="AP21">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AQ21">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AR21">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="AS21">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="AT21">
         <v>14.5</v>
       </c>
       <c r="AU21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV21">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="AW21">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="AX21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY21">
         <v>9.6</v>
       </c>
       <c r="AZ21">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA21">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BB21">
         <v>16</v>
@@ -5916,13 +5928,13 @@
         <v>19.5</v>
       </c>
       <c r="BE21">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="BF21">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG21">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="BH21">
         <v>6.2</v>
@@ -5940,10 +5952,10 @@
         <v>65</v>
       </c>
       <c r="BM21">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BN21">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BO21">
         <v>4.5</v>
@@ -5952,7 +5964,7 @@
         <v>11.5</v>
       </c>
       <c r="BQ21">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BR21">
         <v>19.5</v>
@@ -5961,31 +5973,31 @@
         <v>13</v>
       </c>
       <c r="BT21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BV21">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW21">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BX21">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BY21">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BZ21">
         <v>10.5</v>
       </c>
       <c r="CA21">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="CB21" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5993,16 +6005,16 @@
         <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E22" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F22">
         <v>3.5</v>
@@ -6017,10 +6029,10 @@
         <v>2.7</v>
       </c>
       <c r="J22">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K22">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="L22">
         <v>1.58</v>
@@ -6095,7 +6107,7 @@
         <v>90</v>
       </c>
       <c r="AJ22">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK22">
         <v>80</v>
@@ -6146,7 +6158,7 @@
         <v>22</v>
       </c>
       <c r="BA22">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB22">
         <v>8</v>
@@ -6176,7 +6188,7 @@
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BL22">
         <v>1000</v>
@@ -6206,7 +6218,7 @@
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="BV22">
         <v>1000</v>
@@ -6227,7 +6239,7 @@
         <v>1.18</v>
       </c>
       <c r="CB22" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6235,16 +6247,16 @@
         <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F23">
         <v>1.43</v>
@@ -6262,7 +6274,7 @@
         <v>4.2</v>
       </c>
       <c r="K23">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6274,7 +6286,7 @@
         <v>3.1</v>
       </c>
       <c r="O23">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P23">
         <v>1.71</v>
@@ -6289,10 +6301,10 @@
         <v>4.2</v>
       </c>
       <c r="T23">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="U23">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V23">
         <v>1.09</v>
@@ -6313,7 +6325,7 @@
         <v>1000</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC23">
         <v>11</v>
@@ -6322,7 +6334,7 @@
         <v>55</v>
       </c>
       <c r="AE23">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AF23">
         <v>8.6</v>
@@ -6331,10 +6343,10 @@
         <v>11.5</v>
       </c>
       <c r="AH23">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AI23">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AJ23">
         <v>13</v>
@@ -6346,7 +6358,7 @@
         <v>75</v>
       </c>
       <c r="AM23">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AN23">
         <v>12</v>
@@ -6358,7 +6370,7 @@
         <v>8.6</v>
       </c>
       <c r="AQ23">
-        <v>18.5</v>
+        <v>4.8</v>
       </c>
       <c r="AR23">
         <v>5.2</v>
@@ -6367,7 +6379,7 @@
         <v>5.5</v>
       </c>
       <c r="AT23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU23">
         <v>9.199999999999999</v>
@@ -6385,7 +6397,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ23">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BA23">
         <v>5.4</v>
@@ -6403,7 +6415,7 @@
         <v>5.4</v>
       </c>
       <c r="BF23">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG23">
         <v>5.5</v>
@@ -6418,13 +6430,13 @@
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="BN23">
         <v>1000</v>
@@ -6436,40 +6448,40 @@
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="CB23" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6477,31 +6489,31 @@
         <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G24">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H24">
         <v>3.55</v>
       </c>
       <c r="I24">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J24">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K24">
         <v>3.9</v>
@@ -6513,34 +6525,34 @@
         <v>1.07</v>
       </c>
       <c r="N24">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P24">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="Q24">
         <v>1.89</v>
       </c>
       <c r="R24">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S24">
         <v>3.25</v>
       </c>
       <c r="T24">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="U24">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V24">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W24">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X24">
         <v>18</v>
@@ -6570,7 +6582,7 @@
         <v>17</v>
       </c>
       <c r="AG24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH24">
         <v>21</v>
@@ -6597,58 +6609,58 @@
         <v>55</v>
       </c>
       <c r="AP24">
+        <v>3.6</v>
+      </c>
+      <c r="AQ24">
         <v>3.55</v>
       </c>
-      <c r="AQ24">
-        <v>3.5</v>
-      </c>
       <c r="AR24">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AS24">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT24">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU24">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AV24">
         <v>3.6</v>
       </c>
       <c r="AW24">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX24">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AY24">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AZ24">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BA24">
         <v>4.1</v>
       </c>
       <c r="BB24">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BC24">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BD24">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE24">
         <v>4.2</v>
       </c>
       <c r="BF24">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BG24">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH24">
         <v>4.5</v>
@@ -6711,7 +6723,7 @@
         <v>1.29</v>
       </c>
       <c r="CB24" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6719,31 +6731,31 @@
         <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E25" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F25">
         <v>1.47</v>
       </c>
       <c r="G25">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H25">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I25">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J25">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>5.5</v>
@@ -6755,13 +6767,13 @@
         <v>1.03</v>
       </c>
       <c r="N25">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>1.17</v>
       </c>
       <c r="P25">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q25">
         <v>1.51</v>
@@ -6773,7 +6785,7 @@
         <v>2.24</v>
       </c>
       <c r="T25">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U25">
         <v>2.22</v>
@@ -6782,7 +6794,7 @@
         <v>1.15</v>
       </c>
       <c r="W25">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X25">
         <v>36</v>
@@ -6803,7 +6815,7 @@
         <v>12.5</v>
       </c>
       <c r="AD25">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE25">
         <v>95</v>
@@ -6821,7 +6833,7 @@
         <v>80</v>
       </c>
       <c r="AJ25">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK25">
         <v>15</v>
@@ -6839,16 +6851,16 @@
         <v>85</v>
       </c>
       <c r="AP25">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AQ25">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR25">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS25">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT25">
         <v>10.5</v>
@@ -6860,7 +6872,7 @@
         <v>21</v>
       </c>
       <c r="AW25">
-        <v>32</v>
+        <v>8.6</v>
       </c>
       <c r="AX25">
         <v>9.800000000000001</v>
@@ -6872,7 +6884,7 @@
         <v>17</v>
       </c>
       <c r="BA25">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="BB25">
         <v>12.5</v>
@@ -6881,79 +6893,79 @@
         <v>12.5</v>
       </c>
       <c r="BD25">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BE25">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BF25">
         <v>4.8</v>
       </c>
       <c r="BG25">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH25">
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>1.57</v>
+        <v>3.8</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="BN25">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO25">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="CB25" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6961,25 +6973,25 @@
         <v>85</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E26" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F26">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G26">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H26">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I26">
         <v>3.65</v>
@@ -7006,28 +7018,28 @@
         <v>2.58</v>
       </c>
       <c r="Q26">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R26">
         <v>1.64</v>
       </c>
       <c r="S26">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T26">
         <v>1.54</v>
       </c>
       <c r="U26">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
         <v>1.37</v>
       </c>
       <c r="W26">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X26">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y26">
         <v>21</v>
@@ -7075,7 +7087,7 @@
         <v>60</v>
       </c>
       <c r="AN26">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO26">
         <v>23</v>
@@ -7090,13 +7102,13 @@
         <v>21</v>
       </c>
       <c r="AS26">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU26">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV26">
         <v>13</v>
@@ -7120,7 +7132,7 @@
         <v>21</v>
       </c>
       <c r="BC26">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD26">
         <v>16.5</v>
@@ -7195,7 +7207,7 @@
         <v>6.6</v>
       </c>
       <c r="CB26" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7203,34 +7215,34 @@
         <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E27" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F27">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G27">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H27">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I27">
         <v>3.8</v>
       </c>
       <c r="J27">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K27">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L27">
         <v>1.37</v>
@@ -7239,40 +7251,40 @@
         <v>1.06</v>
       </c>
       <c r="N27">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O27">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P27">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q27">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="R27">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T27">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U27">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="V27">
         <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="X27">
         <v>17</v>
       </c>
       <c r="Y27">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z27">
         <v>28</v>
@@ -7290,7 +7302,7 @@
         <v>16</v>
       </c>
       <c r="AE27">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF27">
         <v>14.5</v>
@@ -7302,7 +7314,7 @@
         <v>17.5</v>
       </c>
       <c r="AI27">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ27">
         <v>27</v>
@@ -7320,22 +7332,22 @@
         <v>14.5</v>
       </c>
       <c r="AO27">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP27">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ27">
         <v>13</v>
       </c>
       <c r="AR27">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS27">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AT27">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU27">
         <v>7.4</v>
@@ -7344,7 +7356,7 @@
         <v>13.5</v>
       </c>
       <c r="AW27">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AX27">
         <v>12</v>
@@ -7356,7 +7368,7 @@
         <v>15</v>
       </c>
       <c r="BA27">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB27">
         <v>21</v>
@@ -7365,7 +7377,7 @@
         <v>18</v>
       </c>
       <c r="BD27">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BE27">
         <v>55</v>
@@ -7374,7 +7386,7 @@
         <v>12.5</v>
       </c>
       <c r="BG27">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH27">
         <v>3.65</v>
@@ -7392,13 +7404,13 @@
         <v>130</v>
       </c>
       <c r="BM27">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="BN27">
         <v>5.1</v>
       </c>
       <c r="BO27">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP27">
         <v>17.5</v>
@@ -7422,22 +7434,22 @@
         <v>36</v>
       </c>
       <c r="BW27">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX27">
         <v>46</v>
       </c>
       <c r="BY27">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ27">
         <v>27</v>
       </c>
       <c r="CA27">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB27" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7445,241 +7457,241 @@
         <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F28">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
       <c r="G28">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="H28">
-        <v>3.35</v>
+        <v>2.46</v>
       </c>
       <c r="I28">
+        <v>2.5</v>
+      </c>
+      <c r="J28">
+        <v>3.55</v>
+      </c>
+      <c r="K28">
+        <v>3.6</v>
+      </c>
+      <c r="L28">
+        <v>1.36</v>
+      </c>
+      <c r="M28">
+        <v>1.07</v>
+      </c>
+      <c r="N28">
+        <v>4</v>
+      </c>
+      <c r="O28">
+        <v>1.31</v>
+      </c>
+      <c r="P28">
+        <v>2</v>
+      </c>
+      <c r="Q28">
+        <v>1.94</v>
+      </c>
+      <c r="R28">
+        <v>1.39</v>
+      </c>
+      <c r="S28">
+        <v>3.4</v>
+      </c>
+      <c r="T28">
+        <v>1.75</v>
+      </c>
+      <c r="U28">
+        <v>2.26</v>
+      </c>
+      <c r="V28">
+        <v>1.66</v>
+      </c>
+      <c r="W28">
+        <v>1.46</v>
+      </c>
+      <c r="X28">
+        <v>15.5</v>
+      </c>
+      <c r="Y28">
+        <v>11</v>
+      </c>
+      <c r="Z28">
+        <v>16.5</v>
+      </c>
+      <c r="AA28">
+        <v>34</v>
+      </c>
+      <c r="AB28">
+        <v>13</v>
+      </c>
+      <c r="AC28">
+        <v>8</v>
+      </c>
+      <c r="AD28">
+        <v>11.5</v>
+      </c>
+      <c r="AE28">
+        <v>26</v>
+      </c>
+      <c r="AF28">
+        <v>22</v>
+      </c>
+      <c r="AG28">
+        <v>13.5</v>
+      </c>
+      <c r="AH28">
+        <v>16.5</v>
+      </c>
+      <c r="AI28">
+        <v>38</v>
+      </c>
+      <c r="AJ28">
+        <v>55</v>
+      </c>
+      <c r="AK28">
+        <v>36</v>
+      </c>
+      <c r="AL28">
+        <v>46</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>32</v>
+      </c>
+      <c r="AO28">
+        <v>20</v>
+      </c>
+      <c r="AP28">
+        <v>14.5</v>
+      </c>
+      <c r="AQ28">
+        <v>10</v>
+      </c>
+      <c r="AR28">
+        <v>14</v>
+      </c>
+      <c r="AS28">
+        <v>28</v>
+      </c>
+      <c r="AT28">
+        <v>12</v>
+      </c>
+      <c r="AU28">
+        <v>7.4</v>
+      </c>
+      <c r="AV28">
+        <v>10.5</v>
+      </c>
+      <c r="AW28">
+        <v>22</v>
+      </c>
+      <c r="AX28">
+        <v>19.5</v>
+      </c>
+      <c r="AY28">
+        <v>12.5</v>
+      </c>
+      <c r="AZ28">
+        <v>14.5</v>
+      </c>
+      <c r="BA28">
+        <v>34</v>
+      </c>
+      <c r="BB28">
+        <v>46</v>
+      </c>
+      <c r="BC28">
+        <v>30</v>
+      </c>
+      <c r="BD28">
+        <v>38</v>
+      </c>
+      <c r="BE28">
+        <v>55</v>
+      </c>
+      <c r="BF28">
+        <v>26</v>
+      </c>
+      <c r="BG28">
+        <v>17</v>
+      </c>
+      <c r="BH28">
         <v>3.45</v>
       </c>
-      <c r="J28">
-        <v>3.8</v>
-      </c>
-      <c r="K28">
-        <v>3.9</v>
-      </c>
-      <c r="L28">
-        <v>1.29</v>
-      </c>
-      <c r="M28">
-        <v>1.04</v>
-      </c>
-      <c r="N28">
-        <v>5.3</v>
-      </c>
-      <c r="O28">
-        <v>1.22</v>
-      </c>
-      <c r="P28">
-        <v>2.42</v>
-      </c>
-      <c r="Q28">
-        <v>1.66</v>
-      </c>
-      <c r="R28">
-        <v>1.57</v>
-      </c>
-      <c r="S28">
-        <v>2.62</v>
-      </c>
-      <c r="T28">
-        <v>1.58</v>
-      </c>
-      <c r="U28">
-        <v>2.62</v>
-      </c>
-      <c r="V28">
-        <v>1.41</v>
-      </c>
-      <c r="W28">
-        <v>1.78</v>
-      </c>
-      <c r="X28">
+      <c r="BI28">
+        <v>3.2</v>
+      </c>
+      <c r="BJ28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK28">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL28">
+        <v>130</v>
+      </c>
+      <c r="BM28">
+        <v>11</v>
+      </c>
+      <c r="BN28">
+        <v>6.4</v>
+      </c>
+      <c r="BO28">
+        <v>5.7</v>
+      </c>
+      <c r="BP28">
+        <v>28</v>
+      </c>
+      <c r="BQ28">
+        <v>8.4</v>
+      </c>
+      <c r="BR28">
+        <v>42</v>
+      </c>
+      <c r="BS28">
+        <v>9.4</v>
+      </c>
+      <c r="BT28">
+        <v>5.4</v>
+      </c>
+      <c r="BU28">
+        <v>4.8</v>
+      </c>
+      <c r="BV28">
         <v>21</v>
       </c>
-      <c r="Y28">
-        <v>17.5</v>
-      </c>
-      <c r="Z28">
-        <v>26</v>
-      </c>
-      <c r="AA28">
-        <v>60</v>
-      </c>
-      <c r="AB28">
-        <v>14</v>
-      </c>
-      <c r="AC28">
-        <v>9</v>
-      </c>
-      <c r="AD28">
-        <v>14.5</v>
-      </c>
-      <c r="AE28">
-        <v>34</v>
-      </c>
-      <c r="AF28">
-        <v>17.5</v>
-      </c>
-      <c r="AG28">
-        <v>11.5</v>
-      </c>
-      <c r="AH28">
-        <v>15</v>
-      </c>
-      <c r="AI28">
+      <c r="BW28">
+        <v>8</v>
+      </c>
+      <c r="BX28">
         <v>36</v>
       </c>
-      <c r="AJ28">
-        <v>29</v>
-      </c>
-      <c r="AK28">
-        <v>21</v>
-      </c>
-      <c r="AL28">
-        <v>29</v>
-      </c>
-      <c r="AM28">
-        <v>65</v>
-      </c>
-      <c r="AN28">
-        <v>12</v>
-      </c>
-      <c r="AO28">
-        <v>23</v>
-      </c>
-      <c r="AP28">
-        <v>20</v>
-      </c>
-      <c r="AQ28">
-        <v>16</v>
-      </c>
-      <c r="AR28">
-        <v>23</v>
-      </c>
-      <c r="AS28">
-        <v>48</v>
-      </c>
-      <c r="AT28">
-        <v>12.5</v>
-      </c>
-      <c r="AU28">
-        <v>8.4</v>
-      </c>
-      <c r="AV28">
-        <v>12.5</v>
-      </c>
-      <c r="AW28">
-        <v>28</v>
-      </c>
-      <c r="AX28">
-        <v>15</v>
-      </c>
-      <c r="AY28">
-        <v>10</v>
-      </c>
-      <c r="AZ28">
-        <v>14</v>
-      </c>
-      <c r="BA28">
-        <v>32</v>
-      </c>
-      <c r="BB28">
-        <v>27</v>
-      </c>
-      <c r="BC28">
-        <v>18.5</v>
-      </c>
-      <c r="BD28">
-        <v>25</v>
-      </c>
-      <c r="BE28">
-        <v>50</v>
-      </c>
-      <c r="BF28">
-        <v>11</v>
-      </c>
-      <c r="BG28">
-        <v>20</v>
-      </c>
-      <c r="BH28">
-        <v>1000</v>
-      </c>
-      <c r="BI28">
-        <v>3.4</v>
-      </c>
-      <c r="BJ28">
-        <v>1000</v>
-      </c>
-      <c r="BK28">
-        <v>1.91</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>19</v>
-      </c>
-      <c r="BN28">
-        <v>1000</v>
-      </c>
-      <c r="BO28">
-        <v>1.71</v>
-      </c>
-      <c r="BP28">
-        <v>1000</v>
-      </c>
-      <c r="BQ28">
-        <v>2.22</v>
-      </c>
-      <c r="BR28">
-        <v>1000</v>
-      </c>
-      <c r="BS28">
-        <v>10</v>
-      </c>
-      <c r="BT28">
-        <v>1000</v>
-      </c>
-      <c r="BU28">
-        <v>1.83</v>
-      </c>
-      <c r="BV28">
-        <v>1000</v>
-      </c>
-      <c r="BW28">
-        <v>10</v>
-      </c>
-      <c r="BX28">
-        <v>1000</v>
-      </c>
       <c r="BY28">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA28">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB28" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7687,241 +7699,241 @@
         <v>90</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F29">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="G29">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="H29">
-        <v>2.46</v>
+        <v>3.35</v>
       </c>
       <c r="I29">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J29">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K29">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L29">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="M29">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="O29">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="P29">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="Q29">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="R29">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="S29">
+        <v>2.62</v>
+      </c>
+      <c r="T29">
+        <v>1.58</v>
+      </c>
+      <c r="U29">
+        <v>2.62</v>
+      </c>
+      <c r="V29">
+        <v>1.42</v>
+      </c>
+      <c r="W29">
+        <v>1.79</v>
+      </c>
+      <c r="X29">
+        <v>21</v>
+      </c>
+      <c r="Y29">
+        <v>17.5</v>
+      </c>
+      <c r="Z29">
+        <v>28</v>
+      </c>
+      <c r="AA29">
+        <v>60</v>
+      </c>
+      <c r="AB29">
+        <v>13.5</v>
+      </c>
+      <c r="AC29">
+        <v>9</v>
+      </c>
+      <c r="AD29">
+        <v>14</v>
+      </c>
+      <c r="AE29">
+        <v>34</v>
+      </c>
+      <c r="AF29">
+        <v>16.5</v>
+      </c>
+      <c r="AG29">
+        <v>11</v>
+      </c>
+      <c r="AH29">
+        <v>15</v>
+      </c>
+      <c r="AI29">
+        <v>36</v>
+      </c>
+      <c r="AJ29">
+        <v>29</v>
+      </c>
+      <c r="AK29">
+        <v>21</v>
+      </c>
+      <c r="AL29">
+        <v>29</v>
+      </c>
+      <c r="AM29">
+        <v>65</v>
+      </c>
+      <c r="AN29">
+        <v>12</v>
+      </c>
+      <c r="AO29">
+        <v>23</v>
+      </c>
+      <c r="AP29">
+        <v>19.5</v>
+      </c>
+      <c r="AQ29">
+        <v>16</v>
+      </c>
+      <c r="AR29">
+        <v>24</v>
+      </c>
+      <c r="AS29">
+        <v>48</v>
+      </c>
+      <c r="AT29">
+        <v>12.5</v>
+      </c>
+      <c r="AU29">
+        <v>8.4</v>
+      </c>
+      <c r="AV29">
+        <v>12.5</v>
+      </c>
+      <c r="AW29">
+        <v>28</v>
+      </c>
+      <c r="AX29">
+        <v>15.5</v>
+      </c>
+      <c r="AY29">
+        <v>10</v>
+      </c>
+      <c r="AZ29">
+        <v>13.5</v>
+      </c>
+      <c r="BA29">
+        <v>32</v>
+      </c>
+      <c r="BB29">
+        <v>27</v>
+      </c>
+      <c r="BC29">
+        <v>18.5</v>
+      </c>
+      <c r="BD29">
+        <v>26</v>
+      </c>
+      <c r="BE29">
+        <v>50</v>
+      </c>
+      <c r="BF29">
+        <v>11</v>
+      </c>
+      <c r="BG29">
+        <v>21</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
         <v>3.4</v>
       </c>
-      <c r="T29">
-        <v>1.74</v>
-      </c>
-      <c r="U29">
-        <v>2.28</v>
-      </c>
-      <c r="V29">
-        <v>1.66</v>
-      </c>
-      <c r="W29">
-        <v>1.46</v>
-      </c>
-      <c r="X29">
-        <v>15.5</v>
-      </c>
-      <c r="Y29">
-        <v>11</v>
-      </c>
-      <c r="Z29">
-        <v>16.5</v>
-      </c>
-      <c r="AA29">
-        <v>34</v>
-      </c>
-      <c r="AB29">
-        <v>13</v>
-      </c>
-      <c r="AC29">
-        <v>8</v>
-      </c>
-      <c r="AD29">
-        <v>11.5</v>
-      </c>
-      <c r="AE29">
-        <v>26</v>
-      </c>
-      <c r="AF29">
-        <v>22</v>
-      </c>
-      <c r="AG29">
-        <v>13.5</v>
-      </c>
-      <c r="AH29">
-        <v>17</v>
-      </c>
-      <c r="AI29">
-        <v>38</v>
-      </c>
-      <c r="AJ29">
-        <v>55</v>
-      </c>
-      <c r="AK29">
-        <v>36</v>
-      </c>
-      <c r="AL29">
-        <v>46</v>
-      </c>
-      <c r="AM29">
-        <v>1000</v>
-      </c>
-      <c r="AN29">
-        <v>32</v>
-      </c>
-      <c r="AO29">
-        <v>20</v>
-      </c>
-      <c r="AP29">
-        <v>14.5</v>
-      </c>
-      <c r="AQ29">
-        <v>10</v>
-      </c>
-      <c r="AR29">
-        <v>14</v>
-      </c>
-      <c r="AS29">
-        <v>28</v>
-      </c>
-      <c r="AT29">
-        <v>12</v>
-      </c>
-      <c r="AU29">
-        <v>7.4</v>
-      </c>
-      <c r="AV29">
-        <v>10.5</v>
-      </c>
-      <c r="AW29">
-        <v>22</v>
-      </c>
-      <c r="AX29">
-        <v>19.5</v>
-      </c>
-      <c r="AY29">
-        <v>12.5</v>
-      </c>
-      <c r="AZ29">
-        <v>15.5</v>
-      </c>
-      <c r="BA29">
-        <v>34</v>
-      </c>
-      <c r="BB29">
-        <v>46</v>
-      </c>
-      <c r="BC29">
-        <v>30</v>
-      </c>
-      <c r="BD29">
-        <v>38</v>
-      </c>
-      <c r="BE29">
-        <v>55</v>
-      </c>
-      <c r="BF29">
-        <v>27</v>
-      </c>
-      <c r="BG29">
-        <v>17</v>
-      </c>
-      <c r="BH29">
-        <v>3.45</v>
-      </c>
-      <c r="BI29">
-        <v>3.2</v>
-      </c>
       <c r="BJ29">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK29">
-        <v>8.199999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="BL29">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM29">
-        <v>28</v>
+        <v>2.22</v>
       </c>
       <c r="BN29">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO29">
-        <v>5.7</v>
+        <v>1.71</v>
       </c>
       <c r="BP29">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>8.4</v>
+        <v>2.22</v>
       </c>
       <c r="BR29">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS29">
-        <v>9.4</v>
+        <v>2.22</v>
       </c>
       <c r="BT29">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU29">
-        <v>4.8</v>
+        <v>1.83</v>
       </c>
       <c r="BV29">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW29">
-        <v>8</v>
+        <v>2.22</v>
       </c>
       <c r="BX29">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY29">
-        <v>9.199999999999999</v>
+        <v>2.22</v>
       </c>
       <c r="BZ29">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>8.800000000000001</v>
+        <v>2.22</v>
       </c>
       <c r="CB29" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7929,100 +7941,100 @@
         <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E30" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F30">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="G30">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="H30">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="I30">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="J30">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K30">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L30">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N30">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O30">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P30">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q30">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="R30">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="S30">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="T30">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="U30">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="V30">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="W30">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="X30">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y30">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z30">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AA30">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD30">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE30">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF30">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH30">
         <v>17.5</v>
@@ -8031,139 +8043,139 @@
         <v>55</v>
       </c>
       <c r="AJ30">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AK30">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AL30">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN30">
+        <v>11.5</v>
+      </c>
+      <c r="AO30">
+        <v>48</v>
+      </c>
+      <c r="AP30">
+        <v>15.5</v>
+      </c>
+      <c r="AQ30">
+        <v>15.5</v>
+      </c>
+      <c r="AR30">
+        <v>29</v>
+      </c>
+      <c r="AS30">
+        <v>50</v>
+      </c>
+      <c r="AT30">
+        <v>9.6</v>
+      </c>
+      <c r="AU30">
+        <v>8</v>
+      </c>
+      <c r="AV30">
+        <v>15.5</v>
+      </c>
+      <c r="AW30">
+        <v>29</v>
+      </c>
+      <c r="AX30">
+        <v>11</v>
+      </c>
+      <c r="AY30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ30">
         <v>16</v>
-      </c>
-      <c r="AO30">
-        <v>44</v>
-      </c>
-      <c r="AP30">
-        <v>13</v>
-      </c>
-      <c r="AQ30">
-        <v>13</v>
-      </c>
-      <c r="AR30">
-        <v>24</v>
-      </c>
-      <c r="AS30">
-        <v>60</v>
-      </c>
-      <c r="AT30">
-        <v>9.4</v>
-      </c>
-      <c r="AU30">
-        <v>7.4</v>
-      </c>
-      <c r="AV30">
-        <v>14</v>
-      </c>
-      <c r="AW30">
-        <v>38</v>
-      </c>
-      <c r="AX30">
-        <v>12</v>
-      </c>
-      <c r="AY30">
-        <v>10</v>
-      </c>
-      <c r="AZ30">
-        <v>16.5</v>
       </c>
       <c r="BA30">
         <v>46</v>
       </c>
       <c r="BB30">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BC30">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BD30">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BE30">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="BF30">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BG30">
         <v>38</v>
       </c>
       <c r="BH30">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BI30">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="BJ30">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL30">
+        <v>110</v>
+      </c>
+      <c r="BM30">
+        <v>12.5</v>
+      </c>
+      <c r="BN30">
+        <v>4.8</v>
+      </c>
+      <c r="BO30">
+        <v>4.4</v>
+      </c>
+      <c r="BP30">
+        <v>13.5</v>
+      </c>
+      <c r="BQ30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR30">
+        <v>26</v>
+      </c>
+      <c r="BS30">
+        <v>9.4</v>
+      </c>
+      <c r="BT30">
+        <v>7.8</v>
+      </c>
+      <c r="BU30">
         <v>6.8</v>
       </c>
-      <c r="BL30">
-        <v>1000</v>
-      </c>
-      <c r="BM30">
-        <v>30</v>
-      </c>
-      <c r="BN30">
-        <v>5.5</v>
-      </c>
-      <c r="BO30">
-        <v>4</v>
-      </c>
-      <c r="BP30">
-        <v>1000</v>
-      </c>
-      <c r="BQ30">
-        <v>3.05</v>
-      </c>
-      <c r="BR30">
-        <v>1000</v>
-      </c>
-      <c r="BS30">
-        <v>12</v>
-      </c>
-      <c r="BT30">
-        <v>1000</v>
-      </c>
-      <c r="BU30">
-        <v>5.4</v>
-      </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW30">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY30">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA30">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="CB30" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8171,241 +8183,241 @@
         <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F31">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="G31">
-        <v>1.97</v>
+        <v>2.22</v>
       </c>
       <c r="H31">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="I31">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="J31">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K31">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L31">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M31">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N31">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="O31">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="P31">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Q31">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="R31">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S31">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="T31">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="U31">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="V31">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="X31">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y31">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z31">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB31">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD31">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE31">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AF31">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG31">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH31">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI31">
         <v>55</v>
       </c>
       <c r="AJ31">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AK31">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AL31">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN31">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AO31">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP31">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AQ31">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AR31">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AS31">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AT31">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU31">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AV31">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW31">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AX31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY31">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ31">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA31">
         <v>46</v>
       </c>
       <c r="BB31">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BC31">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD31">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE31">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="BF31">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG31">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BH31">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BI31">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="BJ31">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK31">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BL31">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM31">
-        <v>24</v>
+        <v>2.82</v>
       </c>
       <c r="BN31">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BO31">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BP31">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>8.4</v>
+        <v>3.05</v>
       </c>
       <c r="BR31">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS31">
-        <v>9.4</v>
+        <v>2.82</v>
       </c>
       <c r="BT31">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU31">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV31">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
-        <v>10</v>
+        <v>2.62</v>
       </c>
       <c r="BX31">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY31">
-        <v>11</v>
+        <v>2.82</v>
       </c>
       <c r="BZ31">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
-        <v>8.6</v>
+        <v>2.82</v>
       </c>
       <c r="CB31" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8413,34 +8425,34 @@
         <v>90</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E32" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F32">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G32">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H32">
         <v>1.67</v>
       </c>
       <c r="I32">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="J32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K32">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L32">
         <v>1.28</v>
@@ -8449,16 +8461,16 @@
         <v>1.04</v>
       </c>
       <c r="N32">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O32">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P32">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q32">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R32">
         <v>1.6</v>
@@ -8470,10 +8482,10 @@
         <v>1.69</v>
       </c>
       <c r="U32">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V32">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="W32">
         <v>1.21</v>
@@ -8497,7 +8509,7 @@
         <v>10</v>
       </c>
       <c r="AD32">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AE32">
         <v>14.5</v>
@@ -8509,16 +8521,16 @@
         <v>21</v>
       </c>
       <c r="AH32">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI32">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ32">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AK32">
-        <v>790</v>
+        <v>640</v>
       </c>
       <c r="AL32">
         <v>60</v>
@@ -8530,7 +8542,7 @@
         <v>55</v>
       </c>
       <c r="AO32">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP32">
         <v>20</v>
@@ -8539,28 +8551,28 @@
         <v>11</v>
       </c>
       <c r="AR32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS32">
         <v>15.5</v>
       </c>
       <c r="AT32">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU32">
+        <v>9.6</v>
+      </c>
+      <c r="AV32">
         <v>9.4</v>
-      </c>
-      <c r="AV32">
-        <v>9.6</v>
       </c>
       <c r="AW32">
         <v>14</v>
       </c>
       <c r="AX32">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AY32">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AZ32">
         <v>16.5</v>
@@ -8569,7 +8581,7 @@
         <v>25</v>
       </c>
       <c r="BB32">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BC32">
         <v>50</v>
@@ -8581,7 +8593,7 @@
         <v>55</v>
       </c>
       <c r="BF32">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BG32">
         <v>6.6</v>
@@ -8602,7 +8614,7 @@
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>24</v>
+        <v>2.8</v>
       </c>
       <c r="BN32">
         <v>1000</v>
@@ -8647,7 +8659,7 @@
         <v>2.8</v>
       </c>
       <c r="CB32" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8655,22 +8667,22 @@
         <v>87</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E33" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F33">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G33">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H33">
         <v>4.4</v>
@@ -8682,7 +8694,7 @@
         <v>4.3</v>
       </c>
       <c r="K33">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L33">
         <v>1.28</v>
@@ -8697,7 +8709,7 @@
         <v>1.17</v>
       </c>
       <c r="P33">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q33">
         <v>1.51</v>
@@ -8712,19 +8724,19 @@
         <v>1.54</v>
       </c>
       <c r="U33">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="V33">
         <v>1.28</v>
       </c>
       <c r="W33">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X33">
         <v>28</v>
       </c>
       <c r="Y33">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z33">
         <v>40</v>
@@ -8739,7 +8751,7 @@
         <v>10.5</v>
       </c>
       <c r="AD33">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE33">
         <v>42</v>
@@ -8748,10 +8760,10 @@
         <v>15</v>
       </c>
       <c r="AG33">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH33">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI33">
         <v>42</v>
@@ -8763,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="AL33">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AM33">
         <v>55</v>
@@ -8772,13 +8784,13 @@
         <v>7</v>
       </c>
       <c r="AO33">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ33">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR33">
         <v>36</v>
@@ -8790,19 +8802,19 @@
         <v>13.5</v>
       </c>
       <c r="AU33">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV33">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW33">
         <v>38</v>
       </c>
       <c r="AX33">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY33">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ33">
         <v>14</v>
@@ -8811,13 +8823,13 @@
         <v>36</v>
       </c>
       <c r="BB33">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC33">
         <v>14.5</v>
       </c>
       <c r="BD33">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE33">
         <v>48</v>
@@ -8826,7 +8838,7 @@
         <v>6.6</v>
       </c>
       <c r="BG33">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH33">
         <v>4.7</v>
@@ -8838,7 +8850,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK33">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL33">
         <v>85</v>
@@ -8874,7 +8886,7 @@
         <v>29</v>
       </c>
       <c r="BW33">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX33">
         <v>32</v>
@@ -8889,7 +8901,7 @@
         <v>9.6</v>
       </c>
       <c r="CB33" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8897,16 +8909,16 @@
         <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E34" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -8939,22 +8951,22 @@
         <v>1.24</v>
       </c>
       <c r="P34">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q34">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R34">
         <v>1.53</v>
       </c>
       <c r="S34">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T34">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U34">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V34">
         <v>2.28</v>
@@ -8963,16 +8975,16 @@
         <v>1.24</v>
       </c>
       <c r="X34">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y34">
         <v>11</v>
       </c>
       <c r="Z34">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA34">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AB34">
         <v>21</v>
@@ -8984,13 +8996,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE34">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AF34">
         <v>42</v>
       </c>
       <c r="AG34">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH34">
         <v>17</v>
@@ -9002,25 +9014,25 @@
         <v>1000</v>
       </c>
       <c r="AK34">
+        <v>60</v>
+      </c>
+      <c r="AL34">
+        <v>60</v>
+      </c>
+      <c r="AM34">
+        <v>80</v>
+      </c>
+      <c r="AN34">
         <v>55</v>
       </c>
-      <c r="AL34">
-        <v>55</v>
-      </c>
-      <c r="AM34">
-        <v>75</v>
-      </c>
-      <c r="AN34">
-        <v>50</v>
-      </c>
       <c r="AO34">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP34">
         <v>18</v>
       </c>
       <c r="AQ34">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR34">
         <v>11</v>
@@ -9029,16 +9041,16 @@
         <v>17</v>
       </c>
       <c r="AT34">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU34">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV34">
         <v>9.4</v>
       </c>
       <c r="AW34">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX34">
         <v>36</v>
@@ -9053,7 +9065,7 @@
         <v>26</v>
       </c>
       <c r="BB34">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC34">
         <v>50</v>
@@ -9080,13 +9092,13 @@
         <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>22</v>
+        <v>2.2</v>
       </c>
       <c r="BN34">
         <v>1000</v>
@@ -9098,13 +9110,13 @@
         <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>13</v>
+        <v>2.2</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>15.5</v>
+        <v>2.2</v>
       </c>
       <c r="BT34">
         <v>1000</v>
@@ -9122,16 +9134,16 @@
         <v>1000</v>
       </c>
       <c r="BY34">
-        <v>10.5</v>
+        <v>2.2</v>
       </c>
       <c r="BZ34">
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="CB34" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9139,16 +9151,16 @@
         <v>87</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E35" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F35">
         <v>2.3</v>
@@ -9160,7 +9172,7 @@
         <v>3.45</v>
       </c>
       <c r="I35">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J35">
         <v>3.55</v>
@@ -9181,10 +9193,10 @@
         <v>1.29</v>
       </c>
       <c r="P35">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q35">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R35">
         <v>1.42</v>
@@ -9193,13 +9205,13 @@
         <v>3.25</v>
       </c>
       <c r="T35">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U35">
         <v>2.3</v>
       </c>
       <c r="V35">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W35">
         <v>1.76</v>
@@ -9208,7 +9220,7 @@
         <v>15.5</v>
       </c>
       <c r="Y35">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z35">
         <v>24</v>
@@ -9259,7 +9271,7 @@
         <v>34</v>
       </c>
       <c r="AP35">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ35">
         <v>13</v>
@@ -9271,7 +9283,7 @@
         <v>55</v>
       </c>
       <c r="AT35">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU35">
         <v>7.6</v>
@@ -9286,10 +9298,10 @@
         <v>13</v>
       </c>
       <c r="AY35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ35">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA35">
         <v>38</v>
@@ -9301,13 +9313,13 @@
         <v>21</v>
       </c>
       <c r="BD35">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE35">
         <v>65</v>
       </c>
       <c r="BF35">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG35">
         <v>29</v>
@@ -9373,7 +9385,7 @@
         <v>10.5</v>
       </c>
       <c r="CB35" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9381,28 +9393,28 @@
         <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F36">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G36">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H36">
+        <v>5.2</v>
+      </c>
+      <c r="I36">
         <v>5.3</v>
-      </c>
-      <c r="I36">
-        <v>5.5</v>
       </c>
       <c r="J36">
         <v>4.7</v>
@@ -9417,7 +9429,7 @@
         <v>1.03</v>
       </c>
       <c r="N36">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O36">
         <v>1.15</v>
@@ -9426,13 +9438,13 @@
         <v>3</v>
       </c>
       <c r="Q36">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R36">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S36">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T36">
         <v>1.55</v>
@@ -9441,13 +9453,13 @@
         <v>2.72</v>
       </c>
       <c r="V36">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W36">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="X36">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y36">
         <v>30</v>
@@ -9474,7 +9486,7 @@
         <v>13.5</v>
       </c>
       <c r="AG36">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH36">
         <v>16</v>
@@ -9489,28 +9501,28 @@
         <v>14</v>
       </c>
       <c r="AL36">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM36">
         <v>60</v>
       </c>
       <c r="AN36">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO36">
         <v>40</v>
       </c>
       <c r="AP36">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ36">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR36">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS36">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT36">
         <v>13.5</v>
@@ -9528,7 +9540,7 @@
         <v>12.5</v>
       </c>
       <c r="AY36">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ36">
         <v>15</v>
@@ -9549,37 +9561,37 @@
         <v>48</v>
       </c>
       <c r="BF36">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG36">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH36">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI36">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BJ36">
         <v>9</v>
       </c>
       <c r="BK36">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL36">
         <v>70</v>
       </c>
       <c r="BM36">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BN36">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO36">
         <v>4.4</v>
       </c>
       <c r="BP36">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ36">
         <v>8.800000000000001</v>
@@ -9588,34 +9600,34 @@
         <v>18.5</v>
       </c>
       <c r="BS36">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT36">
         <v>9</v>
       </c>
       <c r="BU36">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV36">
         <v>34</v>
       </c>
       <c r="BW36">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX36">
         <v>34</v>
       </c>
       <c r="BY36">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ36">
         <v>11.5</v>
       </c>
       <c r="CA36">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB36" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9623,241 +9635,241 @@
         <v>91</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E37" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P37">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="Q37">
+        <v>2.06</v>
+      </c>
+      <c r="R37">
+        <v>1.18</v>
+      </c>
+      <c r="S37">
+        <v>2.96</v>
+      </c>
+      <c r="T37">
         <v>1.01</v>
       </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
       <c r="U37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -9865,241 +9877,483 @@
         <v>92</v>
       </c>
       <c r="B38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" t="s">
+        <v>149</v>
+      </c>
+      <c r="E38" t="s">
+        <v>187</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>1.07</v>
+      </c>
+      <c r="Q38">
+        <v>1.01</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
+        <v>0</v>
+      </c>
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>0</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>0</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
+        <v>0</v>
+      </c>
+      <c r="AV38">
+        <v>0</v>
+      </c>
+      <c r="AW38">
+        <v>0</v>
+      </c>
+      <c r="AX38">
+        <v>0</v>
+      </c>
+      <c r="AY38">
+        <v>0</v>
+      </c>
+      <c r="AZ38">
+        <v>0</v>
+      </c>
+      <c r="BA38">
+        <v>0</v>
+      </c>
+      <c r="BB38">
+        <v>0</v>
+      </c>
+      <c r="BC38">
+        <v>0</v>
+      </c>
+      <c r="BD38">
+        <v>0</v>
+      </c>
+      <c r="BE38">
+        <v>0</v>
+      </c>
+      <c r="BF38">
+        <v>0</v>
+      </c>
+      <c r="BG38">
+        <v>0</v>
+      </c>
+      <c r="BH38">
+        <v>0</v>
+      </c>
+      <c r="BI38">
+        <v>0</v>
+      </c>
+      <c r="BJ38">
+        <v>0</v>
+      </c>
+      <c r="BK38">
+        <v>0</v>
+      </c>
+      <c r="BL38">
+        <v>0</v>
+      </c>
+      <c r="BM38">
+        <v>0</v>
+      </c>
+      <c r="BN38">
+        <v>0</v>
+      </c>
+      <c r="BO38">
+        <v>0</v>
+      </c>
+      <c r="BP38">
+        <v>0</v>
+      </c>
+      <c r="BQ38">
+        <v>0</v>
+      </c>
+      <c r="BR38">
+        <v>0</v>
+      </c>
+      <c r="BS38">
+        <v>0</v>
+      </c>
+      <c r="BT38">
+        <v>0</v>
+      </c>
+      <c r="BU38">
+        <v>0</v>
+      </c>
+      <c r="BV38">
+        <v>0</v>
+      </c>
+      <c r="BW38">
+        <v>0</v>
+      </c>
+      <c r="BX38">
+        <v>0</v>
+      </c>
+      <c r="BY38">
+        <v>0</v>
+      </c>
+      <c r="BZ38">
+        <v>0</v>
+      </c>
+      <c r="CA38">
+        <v>0</v>
+      </c>
+      <c r="CB38" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:80">
+      <c r="A39" t="s">
         <v>93</v>
       </c>
-      <c r="C38" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" t="s">
-        <v>147</v>
-      </c>
-      <c r="E38" t="s">
-        <v>184</v>
-      </c>
-      <c r="F38">
+      <c r="B39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" t="s">
+        <v>150</v>
+      </c>
+      <c r="E39" t="s">
+        <v>188</v>
+      </c>
+      <c r="F39">
         <v>1.93</v>
       </c>
-      <c r="G38">
+      <c r="G39">
         <v>1.99</v>
       </c>
-      <c r="H38">
+      <c r="H39">
         <v>5.1</v>
       </c>
-      <c r="I38">
+      <c r="I39">
         <v>5.5</v>
       </c>
-      <c r="J38">
+      <c r="J39">
         <v>3.2</v>
       </c>
-      <c r="K38">
-        <v>3.35</v>
-      </c>
-      <c r="L38">
+      <c r="K39">
+        <v>3.4</v>
+      </c>
+      <c r="L39">
         <v>1.6</v>
       </c>
-      <c r="M38">
+      <c r="M39">
         <v>1.13</v>
       </c>
-      <c r="N38">
+      <c r="N39">
         <v>2.58</v>
       </c>
-      <c r="O38">
+      <c r="O39">
         <v>1.58</v>
       </c>
-      <c r="P38">
+      <c r="P39">
         <v>1.53</v>
       </c>
-      <c r="Q38">
-        <v>2.74</v>
-      </c>
-      <c r="R38">
+      <c r="Q39">
+        <v>2.72</v>
+      </c>
+      <c r="R39">
         <v>1.19</v>
       </c>
-      <c r="S38">
+      <c r="S39">
         <v>5.8</v>
       </c>
-      <c r="T38">
+      <c r="T39">
         <v>2.34</v>
       </c>
-      <c r="U38">
+      <c r="U39">
         <v>1.68</v>
       </c>
-      <c r="V38">
+      <c r="V39">
         <v>1.22</v>
       </c>
-      <c r="W38">
+      <c r="W39">
         <v>2</v>
       </c>
-      <c r="X38">
+      <c r="X39">
         <v>8.6</v>
       </c>
-      <c r="Y38">
+      <c r="Y39">
         <v>13</v>
       </c>
-      <c r="Z38">
+      <c r="Z39">
         <v>48</v>
       </c>
-      <c r="AA38">
+      <c r="AA39">
         <v>210</v>
       </c>
-      <c r="AB38">
+      <c r="AB39">
         <v>6.2</v>
       </c>
-      <c r="AC38">
+      <c r="AC39">
         <v>7.8</v>
       </c>
-      <c r="AD38">
+      <c r="AD39">
         <v>23</v>
       </c>
-      <c r="AE38">
+      <c r="AE39">
         <v>130</v>
       </c>
-      <c r="AF38">
+      <c r="AF39">
         <v>10.5</v>
       </c>
-      <c r="AG38">
+      <c r="AG39">
         <v>11.5</v>
       </c>
-      <c r="AH38">
+      <c r="AH39">
         <v>29</v>
       </c>
-      <c r="AI38">
+      <c r="AI39">
         <v>160</v>
       </c>
-      <c r="AJ38">
+      <c r="AJ39">
         <v>24</v>
       </c>
-      <c r="AK38">
+      <c r="AK39">
         <v>34</v>
       </c>
-      <c r="AL38">
+      <c r="AL39">
         <v>80</v>
       </c>
-      <c r="AM38">
+      <c r="AM39">
         <v>300</v>
       </c>
-      <c r="AN38">
-        <v>25</v>
-      </c>
-      <c r="AO38">
+      <c r="AN39">
+        <v>24</v>
+      </c>
+      <c r="AO39">
         <v>240</v>
       </c>
-      <c r="AP38">
+      <c r="AP39">
         <v>7.6</v>
       </c>
-      <c r="AQ38">
+      <c r="AQ39">
         <v>11</v>
       </c>
-      <c r="AR38">
+      <c r="AR39">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS39">
+        <v>11</v>
+      </c>
+      <c r="AT39">
+        <v>5.5</v>
+      </c>
+      <c r="AU39">
+        <v>7</v>
+      </c>
+      <c r="AV39">
+        <v>20</v>
+      </c>
+      <c r="AW39">
+        <v>10.5</v>
+      </c>
+      <c r="AX39">
+        <v>9</v>
+      </c>
+      <c r="AY39">
         <v>10</v>
       </c>
-      <c r="AS38">
+      <c r="AZ39">
+        <v>8.6</v>
+      </c>
+      <c r="BA39">
         <v>10.5</v>
       </c>
-      <c r="AT38">
-        <v>5.5</v>
-      </c>
-      <c r="AU38">
-        <v>7</v>
-      </c>
-      <c r="AV38">
+      <c r="BB39">
         <v>20</v>
       </c>
-      <c r="AW38">
+      <c r="BC39">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD39">
         <v>10.5</v>
       </c>
-      <c r="AX38">
-        <v>9</v>
-      </c>
-      <c r="AY38">
-        <v>10</v>
-      </c>
-      <c r="AZ38">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA38">
-        <v>10.5</v>
-      </c>
-      <c r="BB38">
-        <v>20</v>
-      </c>
-      <c r="BC38">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD38">
+      <c r="BE39">
+        <v>11.5</v>
+      </c>
+      <c r="BF39">
+        <v>18</v>
+      </c>
+      <c r="BG39">
         <v>11</v>
       </c>
-      <c r="BE38">
-        <v>11</v>
-      </c>
-      <c r="BF38">
-        <v>18</v>
-      </c>
-      <c r="BG38">
-        <v>11</v>
-      </c>
-      <c r="BH38">
+      <c r="BH39">
         <v>2.66</v>
       </c>
-      <c r="BI38">
+      <c r="BI39">
         <v>2.48</v>
       </c>
-      <c r="BJ38">
+      <c r="BJ39">
         <v>12.5</v>
       </c>
-      <c r="BK38">
+      <c r="BK39">
         <v>7.4</v>
       </c>
-      <c r="BL38">
-        <v>1000</v>
-      </c>
-      <c r="BM38">
+      <c r="BL39">
+        <v>1000</v>
+      </c>
+      <c r="BM39">
         <v>17.5</v>
       </c>
-      <c r="BN38">
+      <c r="BN39">
         <v>4.3</v>
       </c>
-      <c r="BO38">
+      <c r="BO39">
         <v>3.85</v>
       </c>
-      <c r="BP38">
+      <c r="BP39">
         <v>15.5</v>
       </c>
-      <c r="BQ38">
+      <c r="BQ39">
         <v>8.4</v>
       </c>
-      <c r="BR38">
-        <v>1000</v>
-      </c>
-      <c r="BS38">
+      <c r="BR39">
+        <v>1000</v>
+      </c>
+      <c r="BS39">
         <v>13</v>
       </c>
-      <c r="BT38">
+      <c r="BT39">
         <v>8.6</v>
       </c>
-      <c r="BU38">
-        <v>5.9</v>
-      </c>
-      <c r="BV38">
+      <c r="BU39">
+        <v>6.4</v>
+      </c>
+      <c r="BV39">
         <v>65</v>
       </c>
-      <c r="BW38">
+      <c r="BW39">
         <v>14.5</v>
       </c>
-      <c r="BX38">
-        <v>1000</v>
-      </c>
-      <c r="BY38">
+      <c r="BX39">
+        <v>1000</v>
+      </c>
+      <c r="BY39">
         <v>15</v>
       </c>
-      <c r="BZ38">
-        <v>1000</v>
-      </c>
-      <c r="CA38">
+      <c r="BZ39">
+        <v>1000</v>
+      </c>
+      <c r="CA39">
         <v>13</v>
       </c>
-      <c r="CB38" t="s">
-        <v>185</v>
+      <c r="CB39" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -583,7 +583,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-09-07 17:10:43</t>
+    <t>2026-09-07 19:22:10</t>
   </si>
 </sst>
 </file>
@@ -1177,40 +1177,40 @@
         <v>151</v>
       </c>
       <c r="F2">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="G2">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R2">
         <v>1.3</v>
@@ -1222,22 +1222,22 @@
         <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W2">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AA2">
         <v>240</v>
@@ -1246,58 +1246,58 @@
         <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AE2">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI2">
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="AJ2">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK2">
         <v>21</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO2">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="AP2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AS2">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="AT2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
         <v>7.8</v>
@@ -1309,40 +1309,40 @@
         <v>55</v>
       </c>
       <c r="AX2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA2">
         <v>55</v>
       </c>
       <c r="BB2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE2">
-        <v>12.5</v>
+        <v>110</v>
       </c>
       <c r="BF2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG2">
         <v>85</v>
       </c>
       <c r="BH2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
@@ -1354,31 +1354,31 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BN2">
         <v>4.1</v>
       </c>
       <c r="BO2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ2">
         <v>7</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS2">
         <v>11</v>
       </c>
       <c r="BT2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BU2">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BV2">
         <v>1000</v>
@@ -1390,13 +1390,13 @@
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="s">
         <v>189</v>
@@ -1419,13 +1419,13 @@
         <v>152</v>
       </c>
       <c r="F3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G3">
         <v>2.26</v>
       </c>
       <c r="H3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I3">
         <v>4.1</v>
@@ -1434,40 +1434,40 @@
         <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
         <v>1.52</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
         <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
         <v>1.25</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
         <v>1.91</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
         <v>1.79</v>
@@ -1476,13 +1476,13 @@
         <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB3">
         <v>8</v>
@@ -1491,10 +1491,10 @@
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF3">
         <v>13</v>
@@ -1506,16 +1506,16 @@
         <v>22</v>
       </c>
       <c r="AI3">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
         <v>32</v>
       </c>
       <c r="AK3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3">
         <v>170</v>
@@ -1527,37 +1527,37 @@
         <v>90</v>
       </c>
       <c r="AP3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
         <v>10.5</v>
       </c>
       <c r="AR3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY3">
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
         <v>50</v>
@@ -1566,22 +1566,22 @@
         <v>23</v>
       </c>
       <c r="BC3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE3">
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG3">
         <v>46</v>
       </c>
       <c r="BH3">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="BI3">
         <v>2.72</v>
@@ -1596,10 +1596,10 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BN3">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BO3">
         <v>4.4</v>
@@ -1608,37 +1608,37 @@
         <v>21</v>
       </c>
       <c r="BQ3">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="BR3">
         <v>42</v>
       </c>
       <c r="BS3">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BW3">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="BX3">
         <v>60</v>
       </c>
       <c r="BY3">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>40</v>
       </c>
       <c r="CA3">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="s">
         <v>189</v>
@@ -1661,25 +1661,25 @@
         <v>153</v>
       </c>
       <c r="F4">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G4">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="H4">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
         <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1688,16 +1688,16 @@
         <v>3.25</v>
       </c>
       <c r="O4">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q4">
         <v>2.26</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
         <v>4.3</v>
@@ -1706,79 +1706,79 @@
         <v>1.94</v>
       </c>
       <c r="U4">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V4">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="X4">
         <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
         <v>20</v>
       </c>
       <c r="AI4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AK4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL4">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM4">
         <v>160</v>
       </c>
       <c r="AN4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
         <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT4">
         <v>7.6</v>
@@ -1787,100 +1787,100 @@
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW4">
         <v>42</v>
       </c>
       <c r="AX4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY4">
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB4">
+        <v>24</v>
+      </c>
+      <c r="BC4">
         <v>23</v>
       </c>
-      <c r="BC4">
-        <v>22</v>
-      </c>
       <c r="BD4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE4">
         <v>90</v>
       </c>
       <c r="BF4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG4">
         <v>48</v>
       </c>
       <c r="BH4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI4">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
+        <v>6.6</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>12.5</v>
+      </c>
+      <c r="BN4">
+        <v>5</v>
+      </c>
+      <c r="BO4">
+        <v>4.5</v>
+      </c>
+      <c r="BP4">
+        <v>17.5</v>
+      </c>
+      <c r="BQ4">
         <v>7.6</v>
       </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>11.5</v>
-      </c>
-      <c r="BN4">
-        <v>4.9</v>
-      </c>
-      <c r="BO4">
-        <v>4.2</v>
-      </c>
-      <c r="BP4">
-        <v>17</v>
-      </c>
-      <c r="BQ4">
-        <v>7.2</v>
-      </c>
       <c r="BR4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS4">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BV4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4">
         <v>34</v>
       </c>
       <c r="CA4">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB4" t="s">
         <v>189</v>
@@ -1903,22 +1903,22 @@
         <v>154</v>
       </c>
       <c r="F5">
+        <v>3.15</v>
+      </c>
+      <c r="G5">
+        <v>3.25</v>
+      </c>
+      <c r="H5">
+        <v>2.72</v>
+      </c>
+      <c r="I5">
+        <v>2.78</v>
+      </c>
+      <c r="J5">
         <v>3.05</v>
       </c>
-      <c r="G5">
-        <v>3.15</v>
-      </c>
-      <c r="H5">
-        <v>2.74</v>
-      </c>
-      <c r="I5">
-        <v>2.8</v>
-      </c>
-      <c r="J5">
+      <c r="K5">
         <v>3.1</v>
-      </c>
-      <c r="K5">
-        <v>3.15</v>
       </c>
       <c r="L5">
         <v>1.6</v>
@@ -1930,10 +1930,10 @@
         <v>2.72</v>
       </c>
       <c r="O5">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q5">
         <v>2.72</v>
@@ -1945,25 +1945,25 @@
         <v>5.7</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
         <v>1.83</v>
       </c>
       <c r="V5">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X5">
         <v>8.6</v>
       </c>
       <c r="Y5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA5">
         <v>46</v>
@@ -1981,16 +1981,16 @@
         <v>40</v>
       </c>
       <c r="AF5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH5">
         <v>23</v>
       </c>
       <c r="AI5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>60</v>
@@ -2005,13 +2005,13 @@
         <v>180</v>
       </c>
       <c r="AN5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO5">
         <v>46</v>
       </c>
       <c r="AP5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ5">
         <v>7.8</v>
@@ -2023,7 +2023,7 @@
         <v>40</v>
       </c>
       <c r="AT5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
         <v>6.4</v>
@@ -2035,7 +2035,7 @@
         <v>36</v>
       </c>
       <c r="AX5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY5">
         <v>13</v>
@@ -2056,7 +2056,7 @@
         <v>65</v>
       </c>
       <c r="BE5">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="BF5">
         <v>50</v>
@@ -2065,10 +2065,10 @@
         <v>42</v>
       </c>
       <c r="BH5">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI5">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ5">
         <v>11</v>
@@ -2077,28 +2077,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM5">
         <v>20</v>
       </c>
       <c r="BN5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP5">
         <v>30</v>
       </c>
       <c r="BQ5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BR5">
         <v>55</v>
       </c>
       <c r="BS5">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BT5">
         <v>5.5</v>
@@ -2110,10 +2110,10 @@
         <v>25</v>
       </c>
       <c r="BW5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY5">
         <v>15</v>
@@ -2148,13 +2148,13 @@
         <v>3.55</v>
       </c>
       <c r="G6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H6">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I6">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J6">
         <v>3.65</v>
@@ -2163,37 +2163,37 @@
         <v>3.85</v>
       </c>
       <c r="L6">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q6">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R6">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S6">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T6">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U6">
         <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W6">
         <v>1.36</v>
@@ -2205,7 +2205,7 @@
         <v>13</v>
       </c>
       <c r="Z6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA6">
         <v>28</v>
@@ -2229,7 +2229,7 @@
         <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI6">
         <v>34</v>
@@ -2238,37 +2238,37 @@
         <v>1000</v>
       </c>
       <c r="AK6">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN6">
         <v>32</v>
       </c>
       <c r="AO6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ6">
         <v>11.5</v>
       </c>
       <c r="AR6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS6">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT6">
         <v>16</v>
       </c>
       <c r="AU6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV6">
         <v>9.800000000000001</v>
@@ -2277,7 +2277,7 @@
         <v>18</v>
       </c>
       <c r="AX6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY6">
         <v>13.5</v>
@@ -2289,82 +2289,82 @@
         <v>24</v>
       </c>
       <c r="BB6">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BC6">
         <v>32</v>
       </c>
       <c r="BD6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BE6">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BF6">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BG6">
         <v>10.5</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI6">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK6">
-        <v>1.97</v>
+        <v>7.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.32</v>
+        <v>13.5</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO6">
-        <v>1.87</v>
+        <v>6.2</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>2.32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>2.32</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU6">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW6">
-        <v>2.32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY6">
-        <v>2.32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA6">
-        <v>2.32</v>
+        <v>8.6</v>
       </c>
       <c r="CB6" t="s">
         <v>189</v>
@@ -2387,25 +2387,25 @@
         <v>156</v>
       </c>
       <c r="F7">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G7">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
         <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M7">
         <v>1.09</v>
@@ -2414,7 +2414,7 @@
         <v>3.25</v>
       </c>
       <c r="O7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P7">
         <v>1.77</v>
@@ -2423,130 +2423,130 @@
         <v>2.2</v>
       </c>
       <c r="R7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U7">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V7">
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X7">
         <v>12</v>
       </c>
       <c r="Y7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z7">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA7">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
         <v>7.6</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE7">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
         <v>23</v>
       </c>
       <c r="AI7">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK7">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL7">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM7">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO7">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
         <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR7">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AS7">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AT7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU7">
         <v>7.4</v>
       </c>
       <c r="AV7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW7">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX7">
         <v>9.199999999999999</v>
       </c>
       <c r="AY7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7">
         <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC7">
         <v>19</v>
       </c>
       <c r="BD7">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BE7">
-        <v>8.199999999999999</v>
+        <v>80</v>
       </c>
       <c r="BF7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG7">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BH7">
         <v>3.4</v>
@@ -2555,58 +2555,58 @@
         <v>2.64</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK7">
-        <v>2.52</v>
+        <v>8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.86</v>
+        <v>5.2</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO7">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ7">
-        <v>2.64</v>
+        <v>9.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS7">
-        <v>2.86</v>
+        <v>4.7</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU7">
-        <v>2.34</v>
+        <v>6.4</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>2.86</v>
+        <v>4.8</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>2.86</v>
+        <v>4.9</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA7">
-        <v>2.86</v>
+        <v>4.6</v>
       </c>
       <c r="CB7" t="s">
         <v>189</v>
@@ -2638,16 +2638,16 @@
         <v>1.64</v>
       </c>
       <c r="I8">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="J8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L8">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M8">
         <v>1.04</v>
@@ -2656,28 +2656,28 @@
         <v>4.7</v>
       </c>
       <c r="O8">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P8">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q8">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="R8">
         <v>1.51</v>
       </c>
       <c r="S8">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T8">
         <v>1.73</v>
       </c>
       <c r="U8">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V8">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="W8">
         <v>1.18</v>
@@ -2689,7 +2689,7 @@
         <v>11</v>
       </c>
       <c r="Z8">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AA8">
         <v>21</v>
@@ -2710,13 +2710,13 @@
         <v>60</v>
       </c>
       <c r="AG8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AH8">
         <v>23</v>
       </c>
       <c r="AI8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ8">
         <v>160</v>
@@ -2737,7 +2737,7 @@
         <v>9.4</v>
       </c>
       <c r="AP8">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ8">
         <v>9.4</v>
@@ -2749,43 +2749,43 @@
         <v>12</v>
       </c>
       <c r="AT8">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AU8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV8">
         <v>9</v>
-      </c>
-      <c r="AV8">
-        <v>8.800000000000001</v>
       </c>
       <c r="AW8">
         <v>14</v>
       </c>
       <c r="AX8">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AY8">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AZ8">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="BA8">
         <v>21</v>
       </c>
       <c r="BB8">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BC8">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BD8">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BE8">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF8">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BG8">
         <v>6.8</v>
@@ -2794,61 +2794,61 @@
         <v>4.8</v>
       </c>
       <c r="BI8">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK8">
+        <v>7.2</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>5.6</v>
+      </c>
+      <c r="BN8">
         <v>11.5</v>
       </c>
-      <c r="BK8">
-        <v>3.4</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>4.6</v>
-      </c>
-      <c r="BN8">
-        <v>11</v>
-      </c>
       <c r="BO8">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="BP8">
         <v>55</v>
       </c>
       <c r="BQ8">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BT8">
         <v>5.2</v>
       </c>
       <c r="BU8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV8">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BW8">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="BX8">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BZ8">
         <v>18.5</v>
       </c>
       <c r="CA8">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="CB8" t="s">
         <v>189</v>
@@ -2871,28 +2871,28 @@
         <v>158</v>
       </c>
       <c r="F9">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G9">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H9">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
         <v>4.2</v>
       </c>
       <c r="K9">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L9">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
         <v>4.3</v>
@@ -2901,28 +2901,28 @@
         <v>1.27</v>
       </c>
       <c r="P9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S9">
         <v>3.05</v>
       </c>
       <c r="T9">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U9">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V9">
         <v>1.17</v>
       </c>
       <c r="W9">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X9">
         <v>18</v>
@@ -2931,28 +2931,28 @@
         <v>23</v>
       </c>
       <c r="Z9">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AA9">
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC9">
+        <v>9.6</v>
+      </c>
+      <c r="AD9">
+        <v>25</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG9">
         <v>10</v>
-      </c>
-      <c r="AD9">
-        <v>26</v>
-      </c>
-      <c r="AE9">
-        <v>1000</v>
-      </c>
-      <c r="AF9">
-        <v>9.6</v>
-      </c>
-      <c r="AG9">
-        <v>10.5</v>
       </c>
       <c r="AH9">
         <v>22</v>
@@ -2961,10 +2961,10 @@
         <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL9">
         <v>42</v>
@@ -2973,7 +2973,7 @@
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO9">
         <v>1000</v>
@@ -2982,19 +2982,19 @@
         <v>15.5</v>
       </c>
       <c r="AQ9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS9">
         <v>46</v>
       </c>
       <c r="AT9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9">
         <v>21</v>
@@ -3003,25 +3003,25 @@
         <v>55</v>
       </c>
       <c r="AX9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BA9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB9">
         <v>13.5</v>
       </c>
       <c r="BC9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD9">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BE9">
         <v>40</v>
@@ -3042,55 +3042,55 @@
         <v>11</v>
       </c>
       <c r="BK9">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO9">
         <v>3.8</v>
       </c>
       <c r="BP9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BQ9">
         <v>5.9</v>
       </c>
       <c r="BR9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS9">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BT9">
         <v>10.5</v>
       </c>
       <c r="BU9">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW9">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BZ9">
         <v>18</v>
       </c>
       <c r="CA9">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="CB9" t="s">
         <v>189</v>
@@ -3131,28 +3131,28 @@
         <v>4.8</v>
       </c>
       <c r="L10">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
         <v>2.38</v>
       </c>
       <c r="Q10">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R10">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T10">
         <v>1.78</v>
@@ -3167,28 +3167,28 @@
         <v>2.62</v>
       </c>
       <c r="X10">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Y10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC10">
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE10">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
         <v>11</v>
@@ -3197,37 +3197,37 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AJ10">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL10">
         <v>34</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN10">
         <v>6.8</v>
       </c>
       <c r="AO10">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
+        <v>19.5</v>
+      </c>
+      <c r="AQ10">
         <v>18.5</v>
       </c>
-      <c r="AQ10">
-        <v>19.5</v>
-      </c>
       <c r="AR10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS10">
         <v>44</v>
@@ -3236,10 +3236,10 @@
         <v>9.6</v>
       </c>
       <c r="AU10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW10">
         <v>46</v>
@@ -3248,13 +3248,13 @@
         <v>9.6</v>
       </c>
       <c r="AY10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA10">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BB10">
         <v>13</v>
@@ -3278,61 +3278,61 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.47</v>
+        <v>2.24</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK10">
-        <v>2.12</v>
+        <v>7.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO10">
-        <v>1.47</v>
+        <v>3.65</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ10">
-        <v>1.9</v>
+        <v>7.2</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS10">
-        <v>2.12</v>
+        <v>3.7</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU10">
-        <v>1.91</v>
+        <v>7.4</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>2.12</v>
+        <v>3.85</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>2.12</v>
+        <v>3.85</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA10">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
       <c r="CB10" t="s">
         <v>189</v>
@@ -3355,25 +3355,25 @@
         <v>160</v>
       </c>
       <c r="F11">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G11">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I11">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J11">
         <v>3.6</v>
       </c>
       <c r="K11">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L11">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M11">
         <v>1.05</v>
@@ -3382,22 +3382,22 @@
         <v>4.4</v>
       </c>
       <c r="O11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P11">
         <v>2.16</v>
       </c>
       <c r="Q11">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="R11">
         <v>1.46</v>
       </c>
       <c r="S11">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T11">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U11">
         <v>2.34</v>
@@ -3406,175 +3406,175 @@
         <v>1.45</v>
       </c>
       <c r="W11">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X11">
+        <v>22</v>
+      </c>
+      <c r="Y11">
         <v>18.5</v>
       </c>
-      <c r="Y11">
+      <c r="Z11">
+        <v>26</v>
+      </c>
+      <c r="AA11">
+        <v>120</v>
+      </c>
+      <c r="AB11">
+        <v>16.5</v>
+      </c>
+      <c r="AC11">
+        <v>8.4</v>
+      </c>
+      <c r="AD11">
+        <v>16.5</v>
+      </c>
+      <c r="AE11">
+        <v>70</v>
+      </c>
+      <c r="AF11">
+        <v>18</v>
+      </c>
+      <c r="AG11">
         <v>14.5</v>
       </c>
-      <c r="Z11">
-        <v>24</v>
-      </c>
-      <c r="AA11">
-        <v>60</v>
-      </c>
-      <c r="AB11">
-        <v>12.5</v>
-      </c>
-      <c r="AC11">
-        <v>8.6</v>
-      </c>
-      <c r="AD11">
-        <v>13.5</v>
-      </c>
-      <c r="AE11">
-        <v>38</v>
-      </c>
-      <c r="AF11">
-        <v>17.5</v>
-      </c>
-      <c r="AG11">
-        <v>12</v>
-      </c>
       <c r="AH11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI11">
         <v>48</v>
       </c>
       <c r="AJ11">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK11">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AL11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM11">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AQ11">
         <v>12.5</v>
       </c>
       <c r="AR11">
-        <v>19</v>
+        <v>3.35</v>
       </c>
       <c r="AS11">
-        <v>26</v>
+        <v>3.75</v>
       </c>
       <c r="AT11">
         <v>11</v>
       </c>
       <c r="AU11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW11">
-        <v>16</v>
+        <v>3.7</v>
       </c>
       <c r="AX11">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AY11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11">
         <v>10</v>
       </c>
-      <c r="AZ11">
+      <c r="BA11">
+        <v>3.55</v>
+      </c>
+      <c r="BB11">
+        <v>13</v>
+      </c>
+      <c r="BC11">
+        <v>3.6</v>
+      </c>
+      <c r="BD11">
         <v>14</v>
       </c>
-      <c r="BA11">
-        <v>19</v>
-      </c>
-      <c r="BB11">
-        <v>8.4</v>
-      </c>
-      <c r="BC11">
-        <v>12.5</v>
-      </c>
-      <c r="BD11">
-        <v>16.5</v>
-      </c>
       <c r="BE11">
+        <v>27</v>
+      </c>
+      <c r="BF11">
         <v>10</v>
-      </c>
-      <c r="BF11">
-        <v>14.5</v>
       </c>
       <c r="BG11">
         <v>17.5</v>
       </c>
       <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>2.2</v>
+      </c>
+      <c r="BJ11">
+        <v>10.5</v>
+      </c>
+      <c r="BK11">
+        <v>6.6</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>2.14</v>
+      </c>
+      <c r="BN11">
+        <v>6.4</v>
+      </c>
+      <c r="BO11">
+        <v>4.5</v>
+      </c>
+      <c r="BP11">
+        <v>25</v>
+      </c>
+      <c r="BQ11">
         <v>3.8</v>
       </c>
-      <c r="BI11">
-        <v>3.45</v>
-      </c>
-      <c r="BJ11">
-        <v>9</v>
-      </c>
-      <c r="BK11">
-        <v>7.8</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>14</v>
-      </c>
-      <c r="BN11">
-        <v>5.5</v>
-      </c>
-      <c r="BO11">
-        <v>4.9</v>
-      </c>
-      <c r="BP11">
-        <v>17</v>
-      </c>
-      <c r="BQ11">
-        <v>8.4</v>
-      </c>
       <c r="BR11">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BS11">
-        <v>10</v>
+        <v>2.02</v>
       </c>
       <c r="BT11">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU11">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV11">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BW11">
-        <v>9.6</v>
+        <v>2.02</v>
       </c>
       <c r="BX11">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BY11">
-        <v>11</v>
+        <v>2.04</v>
       </c>
       <c r="BZ11">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="CA11">
-        <v>9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="CB11" t="s">
         <v>189</v>
@@ -3597,10 +3597,10 @@
         <v>161</v>
       </c>
       <c r="F12">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G12">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H12">
         <v>5.7</v>
@@ -3609,7 +3609,7 @@
         <v>6.8</v>
       </c>
       <c r="J12">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K12">
         <v>5.4</v>
@@ -3618,40 +3618,40 @@
         <v>1.22</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
         <v>6.2</v>
       </c>
       <c r="O12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P12">
         <v>2.74</v>
       </c>
       <c r="Q12">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S12">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T12">
         <v>1.62</v>
       </c>
       <c r="U12">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V12">
         <v>1.17</v>
       </c>
       <c r="W12">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X12">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y12">
         <v>32</v>
@@ -3681,7 +3681,7 @@
         <v>12</v>
       </c>
       <c r="AH12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI12">
         <v>65</v>
@@ -3705,31 +3705,31 @@
         <v>65</v>
       </c>
       <c r="AP12">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="AQ12">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="AR12">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AS12">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT12">
+        <v>12</v>
+      </c>
+      <c r="AU12">
         <v>10.5</v>
-      </c>
-      <c r="AU12">
-        <v>10</v>
       </c>
       <c r="AV12">
         <v>20</v>
       </c>
       <c r="AW12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX12">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY12">
         <v>9.6</v>
@@ -3738,10 +3738,10 @@
         <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BB12">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC12">
         <v>11</v>
@@ -3750,13 +3750,13 @@
         <v>20</v>
       </c>
       <c r="BE12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF12">
         <v>4.6</v>
       </c>
       <c r="BG12">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BH12">
         <v>5.5</v>
@@ -3780,7 +3780,7 @@
         <v>5.1</v>
       </c>
       <c r="BO12">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BP12">
         <v>10.5</v>
@@ -3863,7 +3863,7 @@
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O13">
         <v>1.32</v>
@@ -3872,10 +3872,10 @@
         <v>1.96</v>
       </c>
       <c r="Q13">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R13">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S13">
         <v>3.4</v>
@@ -3893,10 +3893,10 @@
         <v>1.83</v>
       </c>
       <c r="X13">
+        <v>15.5</v>
+      </c>
+      <c r="Y13">
         <v>15</v>
-      </c>
-      <c r="Y13">
-        <v>14.5</v>
       </c>
       <c r="Z13">
         <v>28</v>
@@ -3908,7 +3908,7 @@
         <v>10.5</v>
       </c>
       <c r="AC13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD13">
         <v>16.5</v>
@@ -3938,10 +3938,10 @@
         <v>38</v>
       </c>
       <c r="AM13">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO13">
         <v>48</v>
@@ -3956,13 +3956,13 @@
         <v>14.5</v>
       </c>
       <c r="AS13">
-        <v>38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV13">
         <v>13.5</v>
@@ -3974,7 +3974,7 @@
         <v>11.5</v>
       </c>
       <c r="AY13">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13">
         <v>15.5</v>
@@ -3983,22 +3983,22 @@
         <v>27</v>
       </c>
       <c r="BB13">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BC13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD13">
         <v>30</v>
       </c>
       <c r="BE13">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH13">
         <v>3.4</v>
@@ -4010,13 +4010,13 @@
         <v>9.6</v>
       </c>
       <c r="BK13">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL13">
         <v>130</v>
       </c>
       <c r="BM13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN13">
         <v>5</v>
@@ -4025,7 +4025,7 @@
         <v>4.4</v>
       </c>
       <c r="BP13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ13">
         <v>7.8</v>
@@ -4046,7 +4046,7 @@
         <v>32</v>
       </c>
       <c r="BW13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX13">
         <v>42</v>
@@ -4058,7 +4058,7 @@
         <v>27</v>
       </c>
       <c r="CA13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB13" t="s">
         <v>189</v>
@@ -4081,64 +4081,64 @@
         <v>163</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G14">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I14">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J14">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L14">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M14">
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O14">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P14">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q14">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="R14">
+        <v>1.58</v>
+      </c>
+      <c r="S14">
+        <v>2.52</v>
+      </c>
+      <c r="T14">
         <v>1.57</v>
       </c>
-      <c r="S14">
-        <v>2.46</v>
-      </c>
-      <c r="T14">
-        <v>1.58</v>
-      </c>
       <c r="U14">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V14">
         <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="X14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y14">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z14">
         <v>32</v>
@@ -4150,19 +4150,19 @@
         <v>14</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14">
         <v>16</v>
       </c>
       <c r="AE14">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF14">
         <v>16</v>
       </c>
       <c r="AG14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH14">
         <v>16</v>
@@ -4171,13 +4171,13 @@
         <v>42</v>
       </c>
       <c r="AJ14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK14">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM14">
         <v>70</v>
@@ -4186,31 +4186,31 @@
         <v>10.5</v>
       </c>
       <c r="AO14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP14">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS14">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="AT14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU14">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV14">
         <v>13.5</v>
       </c>
       <c r="AW14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AX14">
         <v>13</v>
@@ -4219,10 +4219,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BB14">
         <v>21</v>
@@ -4231,10 +4231,10 @@
         <v>16.5</v>
       </c>
       <c r="BD14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE14">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="BF14">
         <v>8.800000000000001</v>
@@ -4243,64 +4243,64 @@
         <v>21</v>
       </c>
       <c r="BH14">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>3.75</v>
+        <v>1.52</v>
       </c>
       <c r="BJ14">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>7.6</v>
+        <v>1.94</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>6.4</v>
+        <v>2.22</v>
       </c>
       <c r="BN14">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>4.5</v>
+        <v>1.61</v>
       </c>
       <c r="BP14">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>9</v>
+        <v>2.22</v>
       </c>
       <c r="BR14">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>5.5</v>
+        <v>2.22</v>
       </c>
       <c r="BT14">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV14">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>5.6</v>
+        <v>2.22</v>
       </c>
       <c r="BX14">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>5.8</v>
+        <v>2.22</v>
       </c>
       <c r="BZ14">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>5</v>
+        <v>2.22</v>
       </c>
       <c r="CB14" t="s">
         <v>189</v>
@@ -4323,22 +4323,22 @@
         <v>164</v>
       </c>
       <c r="F15">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="G15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H15">
         <v>1.66</v>
       </c>
       <c r="I15">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="J15">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K15">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4347,142 +4347,142 @@
         <v>1.08</v>
       </c>
       <c r="N15">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O15">
         <v>1.36</v>
       </c>
       <c r="P15">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q15">
         <v>2</v>
       </c>
       <c r="R15">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S15">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T15">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U15">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="V15">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="W15">
         <v>1.18</v>
       </c>
       <c r="X15">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="Z15">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AA15">
-        <v>21</v>
+        <v>900</v>
       </c>
       <c r="AB15">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AP15">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="AQ15">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AR15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS15">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT15">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="AU15">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV15">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="AW15">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="AX15">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="AY15">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="AZ15">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="BA15">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="BB15">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="BC15">
-        <v>7</v>
+        <v>1.3</v>
       </c>
       <c r="BD15">
-        <v>7</v>
+        <v>1.3</v>
       </c>
       <c r="BE15">
-        <v>7</v>
+        <v>1.3</v>
       </c>
       <c r="BF15">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="BG15">
-        <v>4.7</v>
+        <v>2.64</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4565,40 +4565,40 @@
         <v>165</v>
       </c>
       <c r="F16">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G16">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="H16">
         <v>4.3</v>
       </c>
       <c r="I16">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J16">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K16">
         <v>4.5</v>
       </c>
       <c r="L16">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
         <v>1.07</v>
       </c>
       <c r="N16">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O16">
         <v>1.33</v>
       </c>
       <c r="P16">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q16">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="R16">
         <v>1.29</v>
@@ -4613,10 +4613,10 @@
         <v>1.87</v>
       </c>
       <c r="V16">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W16">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4634,7 +4634,7 @@
         <v>970</v>
       </c>
       <c r="AC16">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD16">
         <v>1000</v>
@@ -4643,10 +4643,10 @@
         <v>1000</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH16">
         <v>1000</v>
@@ -4655,79 +4655,79 @@
         <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM16">
         <v>1000</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AP16">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AQ16">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AR16">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AS16">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AT16">
-        <v>1.08</v>
+        <v>5.1</v>
       </c>
       <c r="AU16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AV16">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AW16">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AX16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AY16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AZ16">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BA16">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BB16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BC16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BD16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BE16">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BF16">
-        <v>1.18</v>
+        <v>3.4</v>
       </c>
       <c r="BG16">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI16">
         <v>1.01</v>
@@ -4736,55 +4736,55 @@
         <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN16">
         <v>1000</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP16">
         <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT16">
         <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ16">
         <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="CB16" t="s">
         <v>189</v>
@@ -4810,22 +4810,22 @@
         <v>3.4</v>
       </c>
       <c r="G17">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H17">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I17">
         <v>2.3</v>
       </c>
       <c r="J17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K17">
         <v>3.75</v>
       </c>
       <c r="L17">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="M17">
         <v>1.06</v>
@@ -4837,31 +4837,31 @@
         <v>1.3</v>
       </c>
       <c r="P17">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q17">
         <v>1.9</v>
       </c>
       <c r="R17">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S17">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T17">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U17">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V17">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W17">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X17">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y17">
         <v>11</v>
@@ -4870,40 +4870,40 @@
         <v>15</v>
       </c>
       <c r="AA17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB17">
         <v>15</v>
       </c>
       <c r="AC17">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE17">
         <v>24</v>
       </c>
       <c r="AF17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG17">
         <v>15</v>
       </c>
       <c r="AH17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI17">
         <v>36</v>
       </c>
       <c r="AJ17">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AK17">
         <v>42</v>
       </c>
       <c r="AL17">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AM17">
         <v>90</v>
@@ -4912,19 +4912,19 @@
         <v>38</v>
       </c>
       <c r="AO17">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP17">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR17">
         <v>13</v>
       </c>
       <c r="AS17">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT17">
         <v>13</v>
@@ -4933,100 +4933,100 @@
         <v>7.4</v>
       </c>
       <c r="AV17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX17">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AY17">
         <v>13</v>
       </c>
       <c r="AZ17">
+        <v>15</v>
+      </c>
+      <c r="BA17">
+        <v>30</v>
+      </c>
+      <c r="BB17">
+        <v>13</v>
+      </c>
+      <c r="BC17">
+        <v>34</v>
+      </c>
+      <c r="BD17">
+        <v>40</v>
+      </c>
+      <c r="BE17">
+        <v>13.5</v>
+      </c>
+      <c r="BF17">
+        <v>25</v>
+      </c>
+      <c r="BG17">
         <v>14.5</v>
       </c>
-      <c r="BA17">
-        <v>9.6</v>
-      </c>
-      <c r="BB17">
-        <v>11</v>
-      </c>
-      <c r="BC17">
-        <v>32</v>
-      </c>
-      <c r="BD17">
-        <v>10.5</v>
-      </c>
-      <c r="BE17">
-        <v>11</v>
-      </c>
-      <c r="BF17">
-        <v>9.6</v>
-      </c>
-      <c r="BG17">
-        <v>14</v>
-      </c>
       <c r="BH17">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>3.25</v>
+        <v>1.51</v>
       </c>
       <c r="BJ17">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>8.199999999999999</v>
+        <v>2.12</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>14.5</v>
+        <v>2.42</v>
       </c>
       <c r="BN17">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>10</v>
+        <v>2.42</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>11.5</v>
+        <v>2.42</v>
       </c>
       <c r="BT17">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BV17">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>8.4</v>
+        <v>2.42</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>10.5</v>
+        <v>2.42</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>9.800000000000001</v>
+        <v>2.42</v>
       </c>
       <c r="CB17" t="s">
         <v>189</v>
@@ -5055,10 +5055,10 @@
         <v>4.3</v>
       </c>
       <c r="H18">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="I18">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -5067,58 +5067,58 @@
         <v>4.2</v>
       </c>
       <c r="L18">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M18">
         <v>1.04</v>
       </c>
       <c r="N18">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P18">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q18">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R18">
         <v>1.56</v>
       </c>
       <c r="S18">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T18">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U18">
         <v>2.48</v>
       </c>
       <c r="V18">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W18">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X18">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z18">
         <v>14</v>
       </c>
       <c r="AA18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC18">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18">
         <v>10.5</v>
@@ -5139,25 +5139,25 @@
         <v>28</v>
       </c>
       <c r="AJ18">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
         <v>46</v>
       </c>
       <c r="AL18">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM18">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AN18">
         <v>38</v>
       </c>
       <c r="AO18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AP18">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ18">
         <v>11</v>
@@ -5172,10 +5172,10 @@
         <v>18</v>
       </c>
       <c r="AU18">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW18">
         <v>16</v>
@@ -5193,7 +5193,7 @@
         <v>24</v>
       </c>
       <c r="BB18">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BC18">
         <v>38</v>
@@ -5205,70 +5205,70 @@
         <v>55</v>
       </c>
       <c r="BF18">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BG18">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>3.4</v>
+      </c>
+      <c r="BJ18">
+        <v>10.5</v>
+      </c>
+      <c r="BK18">
+        <v>6.6</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>4.6</v>
+      </c>
+      <c r="BN18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO18">
+        <v>5.9</v>
+      </c>
+      <c r="BP18">
+        <v>40</v>
+      </c>
+      <c r="BQ18">
+        <v>4.1</v>
+      </c>
+      <c r="BR18">
+        <v>48</v>
+      </c>
+      <c r="BS18">
         <v>4.2</v>
       </c>
-      <c r="BI18">
-        <v>3.75</v>
-      </c>
-      <c r="BJ18">
-        <v>9</v>
-      </c>
-      <c r="BK18">
-        <v>7.8</v>
-      </c>
-      <c r="BL18">
-        <v>90</v>
-      </c>
-      <c r="BM18">
-        <v>11.5</v>
-      </c>
-      <c r="BN18">
-        <v>7.6</v>
-      </c>
-      <c r="BO18">
-        <v>6.6</v>
-      </c>
-      <c r="BP18">
-        <v>29</v>
-      </c>
-      <c r="BQ18">
+      <c r="BT18">
+        <v>5.9</v>
+      </c>
+      <c r="BU18">
+        <v>4.1</v>
+      </c>
+      <c r="BV18">
+        <v>15.5</v>
+      </c>
+      <c r="BW18">
         <v>9.199999999999999</v>
       </c>
-      <c r="BR18">
-        <v>36</v>
-      </c>
-      <c r="BS18">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT18">
-        <v>5.1</v>
-      </c>
-      <c r="BU18">
-        <v>4.5</v>
-      </c>
-      <c r="BV18">
-        <v>13</v>
-      </c>
-      <c r="BW18">
-        <v>6.8</v>
-      </c>
       <c r="BX18">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BY18">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="BZ18">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="CA18">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="CB18" t="s">
         <v>189</v>
@@ -5291,22 +5291,22 @@
         <v>168</v>
       </c>
       <c r="F19">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G19">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H19">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I19">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J19">
+        <v>4</v>
+      </c>
+      <c r="K19">
         <v>4.1</v>
-      </c>
-      <c r="K19">
-        <v>4.2</v>
       </c>
       <c r="L19">
         <v>1.33</v>
@@ -5327,22 +5327,22 @@
         <v>1.69</v>
       </c>
       <c r="R19">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S19">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T19">
         <v>1.67</v>
       </c>
       <c r="U19">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W19">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X19">
         <v>20</v>
@@ -5351,40 +5351,40 @@
         <v>21</v>
       </c>
       <c r="Z19">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA19">
         <v>95</v>
       </c>
       <c r="AB19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC19">
         <v>9.199999999999999</v>
       </c>
       <c r="AD19">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE19">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG19">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI19">
         <v>50</v>
       </c>
       <c r="AJ19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK19">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL19">
         <v>28</v>
@@ -5393,7 +5393,7 @@
         <v>70</v>
       </c>
       <c r="AN19">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO19">
         <v>40</v>
@@ -5414,19 +5414,19 @@
         <v>11</v>
       </c>
       <c r="AU19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV19">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW19">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX19">
         <v>12</v>
       </c>
       <c r="AY19">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19">
         <v>15</v>
@@ -5435,10 +5435,10 @@
         <v>44</v>
       </c>
       <c r="BB19">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC19">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD19">
         <v>26</v>
@@ -5447,70 +5447,70 @@
         <v>55</v>
       </c>
       <c r="BF19">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG19">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH19">
+        <v>4.6</v>
+      </c>
+      <c r="BI19">
+        <v>3.35</v>
+      </c>
+      <c r="BJ19">
+        <v>10.5</v>
+      </c>
+      <c r="BK19">
+        <v>7</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>5.3</v>
+      </c>
+      <c r="BN19">
+        <v>5.5</v>
+      </c>
+      <c r="BO19">
         <v>4</v>
       </c>
-      <c r="BI19">
-        <v>3.75</v>
-      </c>
-      <c r="BJ19">
-        <v>9</v>
-      </c>
-      <c r="BK19">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL19">
-        <v>95</v>
-      </c>
-      <c r="BM19">
-        <v>14</v>
-      </c>
-      <c r="BN19">
-        <v>4.8</v>
-      </c>
-      <c r="BO19">
+      <c r="BP19">
+        <v>14.5</v>
+      </c>
+      <c r="BQ19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR19">
+        <v>28</v>
+      </c>
+      <c r="BS19">
         <v>4.4</v>
       </c>
-      <c r="BP19">
-        <v>12</v>
-      </c>
-      <c r="BQ19">
-        <v>10.5</v>
-      </c>
-      <c r="BR19">
-        <v>23</v>
-      </c>
-      <c r="BS19">
-        <v>11.5</v>
-      </c>
       <c r="BT19">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BU19">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV19">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BW19">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="BX19">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BY19">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="BZ19">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CA19">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="CB19" t="s">
         <v>189</v>
@@ -5536,10 +5536,10 @@
         <v>2.78</v>
       </c>
       <c r="G20">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H20">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I20">
         <v>2.7</v>
@@ -5554,7 +5554,7 @@
         <v>1.37</v>
       </c>
       <c r="M20">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
         <v>4.6</v>
@@ -5566,10 +5566,10 @@
         <v>2.22</v>
       </c>
       <c r="Q20">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R20">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S20">
         <v>2.98</v>
@@ -5578,13 +5578,13 @@
         <v>1.66</v>
       </c>
       <c r="U20">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
         <v>1.58</v>
       </c>
       <c r="W20">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X20">
         <v>18</v>
@@ -5599,7 +5599,7 @@
         <v>38</v>
       </c>
       <c r="AB20">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC20">
         <v>8.199999999999999</v>
@@ -5611,7 +5611,7 @@
         <v>26</v>
       </c>
       <c r="AF20">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG20">
         <v>12.5</v>
@@ -5623,10 +5623,10 @@
         <v>36</v>
       </c>
       <c r="AJ20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK20">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL20">
         <v>36</v>
@@ -5635,19 +5635,19 @@
         <v>70</v>
       </c>
       <c r="AN20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO20">
         <v>18.5</v>
       </c>
       <c r="AP20">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ20">
         <v>12</v>
       </c>
       <c r="AR20">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS20">
         <v>34</v>
@@ -5656,31 +5656,31 @@
         <v>13</v>
       </c>
       <c r="AU20">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV20">
         <v>11</v>
       </c>
       <c r="AW20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX20">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA20">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB20">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD20">
         <v>32</v>
@@ -5689,70 +5689,70 @@
         <v>60</v>
       </c>
       <c r="BF20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BG20">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BH20">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BI20">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="BJ20">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK20">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL20">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="BN20">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BO20">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP20">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BQ20">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BR20">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BS20">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="BT20">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BU20">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BV20">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BW20">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BX20">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BY20">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="BZ20">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="CA20">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="CB20" t="s">
         <v>189</v>
@@ -5775,25 +5775,25 @@
         <v>170</v>
       </c>
       <c r="F21">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G21">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H21">
         <v>5.4</v>
       </c>
       <c r="I21">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J21">
         <v>4.7</v>
       </c>
       <c r="K21">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L21">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="M21">
         <v>1.02</v>
@@ -5811,22 +5811,22 @@
         <v>1.41</v>
       </c>
       <c r="R21">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S21">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T21">
         <v>1.52</v>
       </c>
       <c r="U21">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V21">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W21">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X21">
         <v>36</v>
@@ -5844,7 +5844,7 @@
         <v>16</v>
       </c>
       <c r="AC21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD21">
         <v>23</v>
@@ -5862,7 +5862,7 @@
         <v>16</v>
       </c>
       <c r="AI21">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ21">
         <v>18</v>
@@ -5883,7 +5883,7 @@
         <v>36</v>
       </c>
       <c r="AP21">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AQ21">
         <v>32</v>
@@ -5892,7 +5892,7 @@
         <v>48</v>
       </c>
       <c r="AS21">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT21">
         <v>14.5</v>
@@ -5901,100 +5901,100 @@
         <v>11</v>
       </c>
       <c r="AV21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW21">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AX21">
         <v>13</v>
       </c>
       <c r="AY21">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ21">
         <v>14.5</v>
       </c>
       <c r="BA21">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="BB21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD21">
         <v>19.5</v>
       </c>
       <c r="BE21">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF21">
+        <v>4.9</v>
+      </c>
+      <c r="BG21">
+        <v>23</v>
+      </c>
+      <c r="BH21">
+        <v>5.7</v>
+      </c>
+      <c r="BI21">
+        <v>4.4</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>6.6</v>
+      </c>
+      <c r="BL21">
+        <v>85</v>
+      </c>
+      <c r="BM21">
         <v>4.7</v>
       </c>
-      <c r="BG21">
-        <v>27</v>
-      </c>
-      <c r="BH21">
-        <v>6.2</v>
-      </c>
-      <c r="BI21">
-        <v>4.8</v>
-      </c>
-      <c r="BJ21">
-        <v>10</v>
-      </c>
-      <c r="BK21">
-        <v>7.6</v>
-      </c>
-      <c r="BL21">
-        <v>65</v>
-      </c>
-      <c r="BM21">
+      <c r="BN21">
         <v>5.5</v>
       </c>
-      <c r="BN21">
-        <v>5.6</v>
-      </c>
       <c r="BO21">
+        <v>4</v>
+      </c>
+      <c r="BP21">
+        <v>13</v>
+      </c>
+      <c r="BQ21">
+        <v>7.2</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>4.2</v>
+      </c>
+      <c r="BT21">
+        <v>12.5</v>
+      </c>
+      <c r="BU21">
+        <v>7.4</v>
+      </c>
+      <c r="BV21">
+        <v>46</v>
+      </c>
+      <c r="BW21">
         <v>4.5</v>
       </c>
-      <c r="BP21">
-        <v>11.5</v>
-      </c>
-      <c r="BQ21">
-        <v>4.3</v>
-      </c>
-      <c r="BR21">
-        <v>19.5</v>
-      </c>
-      <c r="BS21">
-        <v>13</v>
-      </c>
-      <c r="BT21">
-        <v>11</v>
-      </c>
-      <c r="BU21">
-        <v>4.2</v>
-      </c>
-      <c r="BV21">
-        <v>38</v>
-      </c>
-      <c r="BW21">
-        <v>5.3</v>
-      </c>
       <c r="BX21">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BY21">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BZ21">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="CB21" t="s">
         <v>189</v>
@@ -6017,7 +6017,7 @@
         <v>171</v>
       </c>
       <c r="F22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G22">
         <v>3.8</v>
@@ -6029,214 +6029,214 @@
         <v>2.7</v>
       </c>
       <c r="J22">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K22">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="L22">
         <v>1.58</v>
       </c>
       <c r="M22">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="N22">
         <v>2.38</v>
       </c>
       <c r="O22">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="P22">
         <v>1.46</v>
       </c>
       <c r="Q22">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R22">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S22">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="U22">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="V22">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W22">
         <v>1.35</v>
       </c>
       <c r="X22">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="Y22">
         <v>7.4</v>
       </c>
       <c r="Z22">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AA22">
-        <v>55</v>
+        <v>900</v>
       </c>
       <c r="AB22">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AC22">
+        <v>15</v>
+      </c>
+      <c r="AD22">
+        <v>970</v>
+      </c>
+      <c r="AE22">
+        <v>500</v>
+      </c>
+      <c r="AF22">
+        <v>500</v>
+      </c>
+      <c r="AG22">
+        <v>970</v>
+      </c>
+      <c r="AH22">
+        <v>500</v>
+      </c>
+      <c r="AI22">
+        <v>500</v>
+      </c>
+      <c r="AJ22">
+        <v>900</v>
+      </c>
+      <c r="AK22">
+        <v>500</v>
+      </c>
+      <c r="AL22">
+        <v>500</v>
+      </c>
+      <c r="AM22">
+        <v>500</v>
+      </c>
+      <c r="AN22">
+        <v>500</v>
+      </c>
+      <c r="AO22">
+        <v>500</v>
+      </c>
+      <c r="AP22">
+        <v>5.5</v>
+      </c>
+      <c r="AQ22">
+        <v>5.6</v>
+      </c>
+      <c r="AR22">
         <v>7</v>
       </c>
-      <c r="AD22">
-        <v>13.5</v>
-      </c>
-      <c r="AE22">
-        <v>50</v>
-      </c>
-      <c r="AF22">
-        <v>25</v>
-      </c>
-      <c r="AG22">
-        <v>21</v>
-      </c>
-      <c r="AH22">
-        <v>32</v>
-      </c>
-      <c r="AI22">
-        <v>90</v>
-      </c>
-      <c r="AJ22">
-        <v>100</v>
-      </c>
-      <c r="AK22">
-        <v>80</v>
-      </c>
-      <c r="AL22">
-        <v>120</v>
-      </c>
-      <c r="AM22">
-        <v>270</v>
-      </c>
-      <c r="AN22">
-        <v>120</v>
-      </c>
-      <c r="AO22">
-        <v>60</v>
-      </c>
-      <c r="AP22">
-        <v>6.6</v>
-      </c>
-      <c r="AQ22">
-        <v>6.6</v>
-      </c>
-      <c r="AR22">
-        <v>13</v>
-      </c>
       <c r="AS22">
-        <v>7.4</v>
+        <v>2.08</v>
       </c>
       <c r="AT22">
         <v>8.4</v>
       </c>
       <c r="AU22">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AV22">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW22">
-        <v>7.4</v>
+        <v>2.08</v>
       </c>
       <c r="AX22">
-        <v>20</v>
+        <v>2.24</v>
       </c>
       <c r="AY22">
-        <v>14.5</v>
+        <v>2.22</v>
       </c>
       <c r="AZ22">
-        <v>22</v>
+        <v>2.28</v>
       </c>
       <c r="BA22">
-        <v>8</v>
+        <v>2.08</v>
       </c>
       <c r="BB22">
-        <v>8</v>
+        <v>2.08</v>
       </c>
       <c r="BC22">
+        <v>2.08</v>
+      </c>
+      <c r="BD22">
+        <v>2.08</v>
+      </c>
+      <c r="BE22">
+        <v>2.28</v>
+      </c>
+      <c r="BF22">
+        <v>2.08</v>
+      </c>
+      <c r="BG22">
+        <v>2.08</v>
+      </c>
+      <c r="BH22">
+        <v>2.68</v>
+      </c>
+      <c r="BI22">
+        <v>2.24</v>
+      </c>
+      <c r="BJ22">
+        <v>17.5</v>
+      </c>
+      <c r="BK22">
+        <v>4</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>5.2</v>
+      </c>
+      <c r="BN22">
         <v>7.8</v>
       </c>
-      <c r="BD22">
-        <v>8</v>
-      </c>
-      <c r="BE22">
-        <v>8.4</v>
-      </c>
-      <c r="BF22">
-        <v>8</v>
-      </c>
-      <c r="BG22">
-        <v>7.6</v>
-      </c>
-      <c r="BH22">
-        <v>1000</v>
-      </c>
-      <c r="BI22">
-        <v>2.22</v>
-      </c>
-      <c r="BJ22">
-        <v>1000</v>
-      </c>
-      <c r="BK22">
-        <v>2.14</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>1.18</v>
-      </c>
-      <c r="BN22">
-        <v>1000</v>
-      </c>
       <c r="BO22">
-        <v>1.18</v>
+        <v>5.3</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.18</v>
+        <v>4.8</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.18</v>
+        <v>4.9</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU22">
-        <v>1.62</v>
+        <v>4.3</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW22">
-        <v>1.18</v>
+        <v>4.5</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.18</v>
+        <v>4.9</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.18</v>
+        <v>4.9</v>
       </c>
       <c r="CB22" t="s">
         <v>189</v>
@@ -6259,76 +6259,76 @@
         <v>172</v>
       </c>
       <c r="F23">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G23">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="H23">
         <v>10.5</v>
       </c>
       <c r="I23">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="J23">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="K23">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N23">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O23">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P23">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="Q23">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="R23">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S23">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T23">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="U23">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="V23">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W23">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="X23">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y23">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Z23">
         <v>120</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>740</v>
       </c>
       <c r="AB23">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC23">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD23">
         <v>55</v>
@@ -6337,148 +6337,148 @@
         <v>320</v>
       </c>
       <c r="AF23">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG23">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH23">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AI23">
         <v>280</v>
       </c>
       <c r="AJ23">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AK23">
+        <v>23</v>
+      </c>
+      <c r="AL23">
+        <v>70</v>
+      </c>
+      <c r="AM23">
+        <v>350</v>
+      </c>
+      <c r="AN23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO23">
+        <v>750</v>
+      </c>
+      <c r="AP23">
+        <v>11</v>
+      </c>
+      <c r="AQ23">
         <v>24</v>
       </c>
-      <c r="AL23">
-        <v>75</v>
-      </c>
-      <c r="AM23">
-        <v>360</v>
-      </c>
-      <c r="AN23">
-        <v>12</v>
-      </c>
-      <c r="AO23">
-        <v>1000</v>
-      </c>
-      <c r="AP23">
-        <v>8.6</v>
-      </c>
-      <c r="AQ23">
-        <v>4.8</v>
-      </c>
       <c r="AR23">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS23">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT23">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU23">
+        <v>10</v>
+      </c>
+      <c r="AV23">
+        <v>36</v>
+      </c>
+      <c r="AW23">
+        <v>6.6</v>
+      </c>
+      <c r="AX23">
+        <v>6.4</v>
+      </c>
+      <c r="AY23">
         <v>9.199999999999999</v>
       </c>
-      <c r="AV23">
-        <v>5.2</v>
-      </c>
-      <c r="AW23">
-        <v>5.4</v>
-      </c>
-      <c r="AX23">
-        <v>6.2</v>
-      </c>
-      <c r="AY23">
-        <v>9.6</v>
-      </c>
       <c r="AZ23">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="BA23">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC23">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BD23">
-        <v>5.3</v>
+        <v>42</v>
       </c>
       <c r="BE23">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF23">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG23">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="CB23" t="s">
         <v>189</v>
@@ -6501,22 +6501,22 @@
         <v>173</v>
       </c>
       <c r="F24">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G24">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H24">
         <v>3.55</v>
       </c>
       <c r="I24">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J24">
         <v>3.5</v>
       </c>
       <c r="K24">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6525,22 +6525,22 @@
         <v>1.07</v>
       </c>
       <c r="N24">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O24">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P24">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Q24">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T24">
         <v>1.76</v>
@@ -6549,178 +6549,178 @@
         <v>2.16</v>
       </c>
       <c r="V24">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W24">
         <v>1.79</v>
       </c>
       <c r="X24">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z24">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AA24">
+        <v>900</v>
+      </c>
+      <c r="AB24">
+        <v>13</v>
+      </c>
+      <c r="AC24">
+        <v>11</v>
+      </c>
+      <c r="AD24">
+        <v>22</v>
+      </c>
+      <c r="AE24">
+        <v>190</v>
+      </c>
+      <c r="AF24">
+        <v>19.5</v>
+      </c>
+      <c r="AG24">
+        <v>15</v>
+      </c>
+      <c r="AH24">
+        <v>25</v>
+      </c>
+      <c r="AI24">
+        <v>320</v>
+      </c>
+      <c r="AJ24">
         <v>85</v>
       </c>
-      <c r="AB24">
-        <v>12</v>
-      </c>
-      <c r="AC24">
-        <v>10</v>
-      </c>
-      <c r="AD24">
-        <v>19</v>
-      </c>
-      <c r="AE24">
+      <c r="AK24">
         <v>55</v>
       </c>
-      <c r="AF24">
-        <v>17</v>
-      </c>
-      <c r="AG24">
-        <v>13.5</v>
-      </c>
-      <c r="AH24">
-        <v>21</v>
-      </c>
-      <c r="AI24">
-        <v>65</v>
-      </c>
-      <c r="AJ24">
-        <v>32</v>
-      </c>
-      <c r="AK24">
-        <v>28</v>
-      </c>
       <c r="AL24">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="AM24">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN24">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AO24">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP24">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AQ24">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="AR24">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="AS24">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="AT24">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="AU24">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="AV24">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="AW24">
+        <v>2.68</v>
+      </c>
+      <c r="AX24">
+        <v>6.4</v>
+      </c>
+      <c r="AY24">
+        <v>7</v>
+      </c>
+      <c r="AZ24">
+        <v>13</v>
+      </c>
+      <c r="BA24">
+        <v>2.7</v>
+      </c>
+      <c r="BB24">
+        <v>2.6</v>
+      </c>
+      <c r="BC24">
+        <v>2.58</v>
+      </c>
+      <c r="BD24">
+        <v>2.64</v>
+      </c>
+      <c r="BE24">
+        <v>2.76</v>
+      </c>
+      <c r="BF24">
         <v>4</v>
       </c>
-      <c r="AX24">
-        <v>3.55</v>
-      </c>
-      <c r="AY24">
-        <v>3.35</v>
-      </c>
-      <c r="AZ24">
-        <v>3.7</v>
-      </c>
-      <c r="BA24">
-        <v>4.1</v>
-      </c>
-      <c r="BB24">
-        <v>3.85</v>
-      </c>
-      <c r="BC24">
-        <v>3.75</v>
-      </c>
-      <c r="BD24">
-        <v>3.95</v>
-      </c>
-      <c r="BE24">
-        <v>4.2</v>
-      </c>
-      <c r="BF24">
-        <v>3.65</v>
-      </c>
       <c r="BG24">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="BH24">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
         <v>1000</v>
       </c>
       <c r="BO24">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
         <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
         <v>189</v>
@@ -6755,40 +6755,40 @@
         <v>7.8</v>
       </c>
       <c r="J25">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="K25">
         <v>5.5</v>
       </c>
       <c r="L25">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M25">
         <v>1.03</v>
       </c>
       <c r="N25">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="O25">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P25">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Q25">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="R25">
         <v>1.7</v>
       </c>
       <c r="S25">
+        <v>2.18</v>
+      </c>
+      <c r="T25">
+        <v>1.64</v>
+      </c>
+      <c r="U25">
         <v>2.24</v>
-      </c>
-      <c r="T25">
-        <v>1.7</v>
-      </c>
-      <c r="U25">
-        <v>2.22</v>
       </c>
       <c r="V25">
         <v>1.15</v>
@@ -6797,172 +6797,172 @@
         <v>2.92</v>
       </c>
       <c r="X25">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="Y25">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="Z25">
+        <v>120</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>14</v>
+      </c>
+      <c r="AC25">
+        <v>13</v>
+      </c>
+      <c r="AD25">
+        <v>28</v>
+      </c>
+      <c r="AE25">
+        <v>140</v>
+      </c>
+      <c r="AF25">
+        <v>11</v>
+      </c>
+      <c r="AG25">
+        <v>12</v>
+      </c>
+      <c r="AH25">
+        <v>22</v>
+      </c>
+      <c r="AI25">
+        <v>260</v>
+      </c>
+      <c r="AJ25">
+        <v>15</v>
+      </c>
+      <c r="AK25">
+        <v>18.5</v>
+      </c>
+      <c r="AL25">
         <v>75</v>
       </c>
-      <c r="AA25">
-        <v>200</v>
-      </c>
-      <c r="AB25">
-        <v>12.5</v>
-      </c>
-      <c r="AC25">
-        <v>12.5</v>
-      </c>
-      <c r="AD25">
-        <v>27</v>
-      </c>
-      <c r="AE25">
-        <v>95</v>
-      </c>
-      <c r="AF25">
-        <v>11.5</v>
-      </c>
-      <c r="AG25">
-        <v>11</v>
-      </c>
-      <c r="AH25">
-        <v>21</v>
-      </c>
-      <c r="AI25">
-        <v>80</v>
-      </c>
-      <c r="AJ25">
-        <v>14.5</v>
-      </c>
-      <c r="AK25">
-        <v>15</v>
-      </c>
-      <c r="AL25">
-        <v>34</v>
-      </c>
       <c r="AM25">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="AN25">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AO25">
         <v>85</v>
       </c>
       <c r="AP25">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AQ25">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR25">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AS25">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="AT25">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU25">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV25">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AW25">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="AX25">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ25">
+        <v>15.5</v>
+      </c>
+      <c r="BA25">
+        <v>26</v>
+      </c>
+      <c r="BB25">
+        <v>12</v>
+      </c>
+      <c r="BC25">
+        <v>11</v>
+      </c>
+      <c r="BD25">
+        <v>12</v>
+      </c>
+      <c r="BE25">
+        <v>34</v>
+      </c>
+      <c r="BF25">
+        <v>4.2</v>
+      </c>
+      <c r="BG25">
+        <v>4.6</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>2.28</v>
+      </c>
+      <c r="BJ25">
+        <v>13.5</v>
+      </c>
+      <c r="BK25">
+        <v>7.2</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>2.22</v>
+      </c>
+      <c r="BN25">
+        <v>4.9</v>
+      </c>
+      <c r="BO25">
+        <v>3.6</v>
+      </c>
+      <c r="BP25">
+        <v>12</v>
+      </c>
+      <c r="BQ25">
+        <v>6.4</v>
+      </c>
+      <c r="BR25">
+        <v>29</v>
+      </c>
+      <c r="BS25">
+        <v>3.35</v>
+      </c>
+      <c r="BT25">
+        <v>15</v>
+      </c>
+      <c r="BU25">
+        <v>7.8</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>3.6</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>3.6</v>
+      </c>
+      <c r="BZ25">
         <v>17</v>
       </c>
-      <c r="BA25">
-        <v>8.4</v>
-      </c>
-      <c r="BB25">
-        <v>12.5</v>
-      </c>
-      <c r="BC25">
-        <v>12.5</v>
-      </c>
-      <c r="BD25">
-        <v>13.5</v>
-      </c>
-      <c r="BE25">
-        <v>40</v>
-      </c>
-      <c r="BF25">
-        <v>4.8</v>
-      </c>
-      <c r="BG25">
-        <v>8.4</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>3.8</v>
-      </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
-        <v>1.84</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>2.04</v>
-      </c>
-      <c r="BN25">
-        <v>5.1</v>
-      </c>
-      <c r="BO25">
-        <v>1.45</v>
-      </c>
-      <c r="BP25">
-        <v>1000</v>
-      </c>
-      <c r="BQ25">
-        <v>1.76</v>
-      </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
-      <c r="BS25">
-        <v>2.04</v>
-      </c>
-      <c r="BT25">
-        <v>1000</v>
-      </c>
-      <c r="BU25">
-        <v>2.04</v>
-      </c>
-      <c r="BV25">
-        <v>1000</v>
-      </c>
-      <c r="BW25">
-        <v>2.04</v>
-      </c>
-      <c r="BX25">
-        <v>1000</v>
-      </c>
-      <c r="BY25">
-        <v>2.04</v>
-      </c>
-      <c r="BZ25">
-        <v>1000</v>
-      </c>
       <c r="CA25">
-        <v>2.04</v>
+        <v>3.1</v>
       </c>
       <c r="CB25" t="s">
         <v>189</v>
@@ -6985,226 +6985,226 @@
         <v>175</v>
       </c>
       <c r="F26">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G26">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H26">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I26">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K26">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L26">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="M26">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N26">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O26">
         <v>1.19</v>
       </c>
       <c r="P26">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="Q26">
         <v>1.57</v>
       </c>
       <c r="R26">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="S26">
         <v>2.36</v>
       </c>
       <c r="T26">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="U26">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="V26">
         <v>1.37</v>
       </c>
       <c r="W26">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X26">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Y26">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Z26">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA26">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AB26">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AC26">
         <v>11</v>
       </c>
       <c r="AD26">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE26">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AF26">
+        <v>19.5</v>
+      </c>
+      <c r="AG26">
+        <v>12.5</v>
+      </c>
+      <c r="AH26">
         <v>17</v>
       </c>
-      <c r="AG26">
+      <c r="AI26">
+        <v>95</v>
+      </c>
+      <c r="AJ26">
+        <v>30</v>
+      </c>
+      <c r="AK26">
+        <v>23</v>
+      </c>
+      <c r="AL26">
+        <v>30</v>
+      </c>
+      <c r="AM26">
+        <v>250</v>
+      </c>
+      <c r="AN26">
+        <v>10.5</v>
+      </c>
+      <c r="AO26">
+        <v>28</v>
+      </c>
+      <c r="AP26">
+        <v>18</v>
+      </c>
+      <c r="AQ26">
+        <v>15.5</v>
+      </c>
+      <c r="AR26">
+        <v>22</v>
+      </c>
+      <c r="AS26">
+        <v>5.5</v>
+      </c>
+      <c r="AT26">
         <v>12</v>
       </c>
-      <c r="AH26">
-        <v>16</v>
-      </c>
-      <c r="AI26">
-        <v>38</v>
-      </c>
-      <c r="AJ26">
+      <c r="AU26">
+        <v>7.8</v>
+      </c>
+      <c r="AV26">
+        <v>12.5</v>
+      </c>
+      <c r="AW26">
+        <v>25</v>
+      </c>
+      <c r="AX26">
+        <v>13</v>
+      </c>
+      <c r="AY26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ26">
+        <v>11.5</v>
+      </c>
+      <c r="BA26">
         <v>26</v>
       </c>
-      <c r="AK26">
-        <v>20</v>
-      </c>
-      <c r="AL26">
-        <v>28</v>
-      </c>
-      <c r="AM26">
-        <v>60</v>
-      </c>
-      <c r="AN26">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO26">
-        <v>23</v>
-      </c>
-      <c r="AP26">
-        <v>20</v>
-      </c>
-      <c r="AQ26">
-        <v>17</v>
-      </c>
-      <c r="AR26">
-        <v>21</v>
-      </c>
-      <c r="AS26">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT26">
-        <v>12.5</v>
-      </c>
-      <c r="AU26">
-        <v>9</v>
-      </c>
-      <c r="AV26">
-        <v>13</v>
-      </c>
-      <c r="AW26">
-        <v>7.6</v>
-      </c>
-      <c r="AX26">
-        <v>14.5</v>
-      </c>
-      <c r="AY26">
-        <v>9.6</v>
-      </c>
-      <c r="AZ26">
-        <v>13</v>
-      </c>
-      <c r="BA26">
-        <v>24</v>
-      </c>
       <c r="BB26">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BC26">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BD26">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BE26">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BF26">
         <v>7.8</v>
       </c>
       <c r="BG26">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BH26">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BI26">
-        <v>4</v>
+        <v>1.54</v>
       </c>
       <c r="BJ26">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>7.4</v>
+        <v>1.92</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>10</v>
+        <v>2.26</v>
       </c>
       <c r="BN26">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP26">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>6.4</v>
+        <v>2.26</v>
       </c>
       <c r="BR26">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>7.8</v>
+        <v>2.26</v>
       </c>
       <c r="BT26">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV26">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>8</v>
+        <v>2.26</v>
       </c>
       <c r="BX26">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>8.4</v>
+        <v>2.26</v>
       </c>
       <c r="BZ26">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>6.6</v>
+        <v>2.26</v>
       </c>
       <c r="CB26" t="s">
         <v>189</v>
@@ -7227,16 +7227,16 @@
         <v>176</v>
       </c>
       <c r="F27">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G27">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H27">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I27">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J27">
         <v>3.7</v>
@@ -7245,25 +7245,25 @@
         <v>3.85</v>
       </c>
       <c r="L27">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N27">
         <v>4.1</v>
       </c>
       <c r="O27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P27">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q27">
         <v>1.92</v>
       </c>
       <c r="R27">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S27">
         <v>3.2</v>
@@ -7275,10 +7275,10 @@
         <v>2.22</v>
       </c>
       <c r="V27">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W27">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X27">
         <v>17</v>
@@ -7287,13 +7287,13 @@
         <v>15.5</v>
       </c>
       <c r="Z27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC27">
         <v>8.4</v>
@@ -7305,16 +7305,16 @@
         <v>46</v>
       </c>
       <c r="AF27">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG27">
         <v>11</v>
       </c>
       <c r="AH27">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI27">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ27">
         <v>27</v>
@@ -7323,31 +7323,31 @@
         <v>22</v>
       </c>
       <c r="AL27">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN27">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO27">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP27">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ27">
         <v>13</v>
       </c>
       <c r="AR27">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS27">
         <v>46</v>
       </c>
       <c r="AT27">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU27">
         <v>7.4</v>
@@ -7356,10 +7356,10 @@
         <v>13.5</v>
       </c>
       <c r="AW27">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AX27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY27">
         <v>9.800000000000001</v>
@@ -7371,82 +7371,82 @@
         <v>30</v>
       </c>
       <c r="BB27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC27">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD27">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BE27">
         <v>55</v>
       </c>
       <c r="BF27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG27">
         <v>23</v>
       </c>
       <c r="BH27">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BI27">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="BJ27">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK27">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BL27">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM27">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="BN27">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BO27">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BP27">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BR27">
+        <v>40</v>
+      </c>
+      <c r="BS27">
+        <v>4.2</v>
+      </c>
+      <c r="BT27">
+        <v>8.6</v>
+      </c>
+      <c r="BU27">
+        <v>5.3</v>
+      </c>
+      <c r="BV27">
+        <v>44</v>
+      </c>
+      <c r="BW27">
+        <v>4.3</v>
+      </c>
+      <c r="BX27">
+        <v>55</v>
+      </c>
+      <c r="BY27">
+        <v>4.4</v>
+      </c>
+      <c r="BZ27">
         <v>32</v>
       </c>
-      <c r="BS27">
-        <v>6.4</v>
-      </c>
-      <c r="BT27">
-        <v>7.2</v>
-      </c>
-      <c r="BU27">
-        <v>6.2</v>
-      </c>
-      <c r="BV27">
-        <v>36</v>
-      </c>
-      <c r="BW27">
-        <v>6.6</v>
-      </c>
-      <c r="BX27">
-        <v>46</v>
-      </c>
-      <c r="BY27">
-        <v>7</v>
-      </c>
-      <c r="BZ27">
-        <v>27</v>
-      </c>
       <c r="CA27">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="CB27" t="s">
         <v>189</v>
@@ -7469,16 +7469,16 @@
         <v>177</v>
       </c>
       <c r="F28">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G28">
         <v>3.2</v>
       </c>
       <c r="H28">
+        <v>2.44</v>
+      </c>
+      <c r="I28">
         <v>2.46</v>
-      </c>
-      <c r="I28">
-        <v>2.5</v>
       </c>
       <c r="J28">
         <v>3.55</v>
@@ -7487,7 +7487,7 @@
         <v>3.6</v>
       </c>
       <c r="L28">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M28">
         <v>1.07</v>
@@ -7502,28 +7502,28 @@
         <v>2</v>
       </c>
       <c r="Q28">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R28">
         <v>1.39</v>
       </c>
       <c r="S28">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T28">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U28">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V28">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W28">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X28">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y28">
         <v>11</v>
@@ -7568,7 +7568,7 @@
         <v>46</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN28">
         <v>32</v>
@@ -7583,10 +7583,10 @@
         <v>10</v>
       </c>
       <c r="AR28">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS28">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT28">
         <v>12</v>
@@ -7598,16 +7598,16 @@
         <v>10.5</v>
       </c>
       <c r="AW28">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX28">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY28">
         <v>12.5</v>
       </c>
       <c r="AZ28">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA28">
         <v>34</v>
@@ -7616,79 +7616,79 @@
         <v>46</v>
       </c>
       <c r="BC28">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD28">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE28">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BF28">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BG28">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH28">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BI28">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="BJ28">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BK28">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BL28">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="BN28">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO28">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP28">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR28">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BS28">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="BT28">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU28">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BV28">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BX28">
+        <v>40</v>
+      </c>
+      <c r="BY28">
+        <v>4.7</v>
+      </c>
+      <c r="BZ28">
         <v>36</v>
       </c>
-      <c r="BY28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ28">
-        <v>30</v>
-      </c>
       <c r="CA28">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="CB28" t="s">
         <v>189</v>
@@ -7711,19 +7711,19 @@
         <v>178</v>
       </c>
       <c r="F29">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G29">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H29">
+        <v>3.3</v>
+      </c>
+      <c r="I29">
         <v>3.35</v>
       </c>
-      <c r="I29">
-        <v>3.4</v>
-      </c>
       <c r="J29">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K29">
         <v>3.9</v>
@@ -7738,19 +7738,19 @@
         <v>5.3</v>
       </c>
       <c r="O29">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P29">
         <v>2.44</v>
       </c>
       <c r="Q29">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R29">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S29">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T29">
         <v>1.58</v>
@@ -7762,10 +7762,10 @@
         <v>1.42</v>
       </c>
       <c r="W29">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="X29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y29">
         <v>17.5</v>
@@ -7777,7 +7777,7 @@
         <v>60</v>
       </c>
       <c r="AB29">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC29">
         <v>9</v>
@@ -7786,10 +7786,10 @@
         <v>14</v>
       </c>
       <c r="AE29">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF29">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG29">
         <v>11</v>
@@ -7798,7 +7798,7 @@
         <v>15</v>
       </c>
       <c r="AI29">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ29">
         <v>29</v>
@@ -7810,7 +7810,7 @@
         <v>29</v>
       </c>
       <c r="AM29">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN29">
         <v>12</v>
@@ -7825,7 +7825,7 @@
         <v>16</v>
       </c>
       <c r="AR29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS29">
         <v>48</v>
@@ -7837,10 +7837,10 @@
         <v>8.4</v>
       </c>
       <c r="AV29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX29">
         <v>15.5</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="BC29">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD29">
         <v>26</v>
@@ -7953,64 +7953,64 @@
         <v>179</v>
       </c>
       <c r="F30">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G30">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H30">
+        <v>4.2</v>
+      </c>
+      <c r="I30">
         <v>4.3</v>
       </c>
-      <c r="I30">
-        <v>4.4</v>
-      </c>
       <c r="J30">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K30">
         <v>3.9</v>
       </c>
       <c r="L30">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M30">
         <v>1.06</v>
       </c>
       <c r="N30">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O30">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P30">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q30">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R30">
         <v>1.45</v>
       </c>
       <c r="S30">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="T30">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U30">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V30">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X30">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y30">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Z30">
         <v>34</v>
@@ -8019,31 +8019,31 @@
         <v>1000</v>
       </c>
       <c r="AB30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD30">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE30">
         <v>50</v>
       </c>
       <c r="AF30">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG30">
         <v>10.5</v>
       </c>
       <c r="AH30">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI30">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ30">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK30">
         <v>18.5</v>
@@ -8052,13 +8052,13 @@
         <v>32</v>
       </c>
       <c r="AM30">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AN30">
         <v>11.5</v>
       </c>
       <c r="AO30">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP30">
         <v>15.5</v>
@@ -8067,37 +8067,37 @@
         <v>15.5</v>
       </c>
       <c r="AR30">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AS30">
         <v>50</v>
       </c>
       <c r="AT30">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU30">
         <v>8</v>
       </c>
       <c r="AV30">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW30">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AX30">
         <v>11</v>
       </c>
       <c r="AY30">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ30">
+        <v>13.5</v>
+      </c>
+      <c r="BA30">
+        <v>38</v>
+      </c>
+      <c r="BB30">
         <v>16</v>
-      </c>
-      <c r="BA30">
-        <v>46</v>
-      </c>
-      <c r="BB30">
-        <v>19.5</v>
       </c>
       <c r="BC30">
         <v>17</v>
@@ -8109,70 +8109,70 @@
         <v>50</v>
       </c>
       <c r="BF30">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG30">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BH30">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BI30">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BJ30">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BK30">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BL30">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="BN30">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BO30">
+        <v>4</v>
+      </c>
+      <c r="BP30">
+        <v>16</v>
+      </c>
+      <c r="BQ30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR30">
+        <v>30</v>
+      </c>
+      <c r="BS30">
+        <v>4.5</v>
+      </c>
+      <c r="BT30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU30">
+        <v>5.8</v>
+      </c>
+      <c r="BV30">
+        <v>40</v>
+      </c>
+      <c r="BW30">
+        <v>4.6</v>
+      </c>
+      <c r="BX30">
+        <v>50</v>
+      </c>
+      <c r="BY30">
+        <v>4.7</v>
+      </c>
+      <c r="BZ30">
+        <v>25</v>
+      </c>
+      <c r="CA30">
         <v>4.4</v>
-      </c>
-      <c r="BP30">
-        <v>13.5</v>
-      </c>
-      <c r="BQ30">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR30">
-        <v>26</v>
-      </c>
-      <c r="BS30">
-        <v>9.4</v>
-      </c>
-      <c r="BT30">
-        <v>7.8</v>
-      </c>
-      <c r="BU30">
-        <v>6.8</v>
-      </c>
-      <c r="BV30">
-        <v>34</v>
-      </c>
-      <c r="BW30">
-        <v>10</v>
-      </c>
-      <c r="BX30">
-        <v>42</v>
-      </c>
-      <c r="BY30">
-        <v>11</v>
-      </c>
-      <c r="BZ30">
-        <v>21</v>
-      </c>
-      <c r="CA30">
-        <v>9</v>
       </c>
       <c r="CB30" t="s">
         <v>189</v>
@@ -8198,19 +8198,19 @@
         <v>2.18</v>
       </c>
       <c r="G31">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H31">
+        <v>3.7</v>
+      </c>
+      <c r="I31">
+        <v>3.8</v>
+      </c>
+      <c r="J31">
+        <v>3.55</v>
+      </c>
+      <c r="K31">
         <v>3.65</v>
-      </c>
-      <c r="I31">
-        <v>3.75</v>
-      </c>
-      <c r="J31">
-        <v>3.65</v>
-      </c>
-      <c r="K31">
-        <v>3.7</v>
       </c>
       <c r="L31">
         <v>1.36</v>
@@ -8228,7 +8228,7 @@
         <v>2</v>
       </c>
       <c r="Q31">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R31">
         <v>1.38</v>
@@ -8240,19 +8240,19 @@
         <v>1.79</v>
       </c>
       <c r="U31">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W31">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X31">
         <v>14.5</v>
       </c>
       <c r="Y31">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z31">
         <v>27</v>
@@ -8273,13 +8273,13 @@
         <v>44</v>
       </c>
       <c r="AF31">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG31">
         <v>11</v>
       </c>
       <c r="AH31">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI31">
         <v>55</v>
@@ -8297,10 +8297,10 @@
         <v>95</v>
       </c>
       <c r="AN31">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO31">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP31">
         <v>13</v>
@@ -8309,7 +8309,7 @@
         <v>13</v>
       </c>
       <c r="AR31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS31">
         <v>60</v>
@@ -8327,13 +8327,13 @@
         <v>38</v>
       </c>
       <c r="AX31">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY31">
         <v>10</v>
       </c>
       <c r="AZ31">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA31">
         <v>46</v>
@@ -8348,73 +8348,73 @@
         <v>32</v>
       </c>
       <c r="BE31">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="BF31">
         <v>14.5</v>
       </c>
       <c r="BG31">
+        <v>32</v>
+      </c>
+      <c r="BH31">
+        <v>3.55</v>
+      </c>
+      <c r="BI31">
+        <v>3.1</v>
+      </c>
+      <c r="BJ31">
+        <v>11.5</v>
+      </c>
+      <c r="BK31">
+        <v>7.2</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>6.4</v>
+      </c>
+      <c r="BN31">
+        <v>5.3</v>
+      </c>
+      <c r="BO31">
+        <v>4.2</v>
+      </c>
+      <c r="BP31">
+        <v>21</v>
+      </c>
+      <c r="BQ31">
+        <v>11.5</v>
+      </c>
+      <c r="BR31">
         <v>38</v>
       </c>
-      <c r="BH31">
-        <v>3.8</v>
-      </c>
-      <c r="BI31">
-        <v>2.9</v>
-      </c>
-      <c r="BJ31">
-        <v>1000</v>
-      </c>
-      <c r="BK31">
-        <v>6.8</v>
-      </c>
-      <c r="BL31">
-        <v>1000</v>
-      </c>
-      <c r="BM31">
-        <v>2.82</v>
-      </c>
-      <c r="BN31">
+      <c r="BS31">
+        <v>5.6</v>
+      </c>
+      <c r="BT31">
+        <v>7.6</v>
+      </c>
+      <c r="BU31">
+        <v>5.6</v>
+      </c>
+      <c r="BV31">
+        <v>40</v>
+      </c>
+      <c r="BW31">
+        <v>5.6</v>
+      </c>
+      <c r="BX31">
+        <v>55</v>
+      </c>
+      <c r="BY31">
+        <v>5.8</v>
+      </c>
+      <c r="BZ31">
+        <v>34</v>
+      </c>
+      <c r="CA31">
         <v>5.5</v>
-      </c>
-      <c r="BO31">
-        <v>4</v>
-      </c>
-      <c r="BP31">
-        <v>1000</v>
-      </c>
-      <c r="BQ31">
-        <v>3.05</v>
-      </c>
-      <c r="BR31">
-        <v>1000</v>
-      </c>
-      <c r="BS31">
-        <v>2.82</v>
-      </c>
-      <c r="BT31">
-        <v>1000</v>
-      </c>
-      <c r="BU31">
-        <v>5.4</v>
-      </c>
-      <c r="BV31">
-        <v>1000</v>
-      </c>
-      <c r="BW31">
-        <v>2.62</v>
-      </c>
-      <c r="BX31">
-        <v>1000</v>
-      </c>
-      <c r="BY31">
-        <v>2.82</v>
-      </c>
-      <c r="BZ31">
-        <v>1000</v>
-      </c>
-      <c r="CA31">
-        <v>2.82</v>
       </c>
       <c r="CB31" t="s">
         <v>189</v>
@@ -8440,19 +8440,19 @@
         <v>5.6</v>
       </c>
       <c r="G32">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H32">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I32">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="J32">
         <v>4.3</v>
       </c>
       <c r="K32">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L32">
         <v>1.28</v>
@@ -8461,31 +8461,31 @@
         <v>1.04</v>
       </c>
       <c r="N32">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O32">
         <v>1.2</v>
       </c>
       <c r="P32">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q32">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R32">
         <v>1.6</v>
       </c>
       <c r="S32">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T32">
         <v>1.69</v>
       </c>
       <c r="U32">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V32">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="W32">
         <v>1.21</v>
@@ -8506,13 +8506,13 @@
         <v>25</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD32">
         <v>9.6</v>
       </c>
       <c r="AE32">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AF32">
         <v>48</v>
@@ -8524,19 +8524,19 @@
         <v>17</v>
       </c>
       <c r="AI32">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ32">
         <v>150</v>
       </c>
       <c r="AK32">
-        <v>640</v>
+        <v>65</v>
       </c>
       <c r="AL32">
         <v>60</v>
       </c>
       <c r="AM32">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN32">
         <v>55</v>
@@ -8557,19 +8557,19 @@
         <v>15.5</v>
       </c>
       <c r="AT32">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU32">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV32">
         <v>9.4</v>
       </c>
       <c r="AW32">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX32">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AY32">
         <v>19.5</v>
@@ -8578,19 +8578,19 @@
         <v>16.5</v>
       </c>
       <c r="BA32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB32">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BC32">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BD32">
         <v>50</v>
       </c>
       <c r="BE32">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF32">
         <v>46</v>
@@ -8602,61 +8602,61 @@
         <v>4.8</v>
       </c>
       <c r="BI32">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK32">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="BN32">
         <v>1000</v>
       </c>
       <c r="BO32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ32">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS32">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="BT32">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BU32">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW32">
-        <v>2.66</v>
+        <v>7.8</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY32">
-        <v>2.86</v>
+        <v>4.9</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA32">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="CB32" t="s">
         <v>189</v>
@@ -8682,10 +8682,10 @@
         <v>1.84</v>
       </c>
       <c r="G33">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H33">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I33">
         <v>4.5</v>
@@ -8703,37 +8703,37 @@
         <v>1.03</v>
       </c>
       <c r="N33">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O33">
         <v>1.17</v>
       </c>
       <c r="P33">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q33">
         <v>1.51</v>
       </c>
       <c r="R33">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S33">
         <v>2.26</v>
       </c>
       <c r="T33">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U33">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="V33">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W33">
         <v>2.16</v>
       </c>
       <c r="X33">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y33">
         <v>26</v>
@@ -8742,7 +8742,7 @@
         <v>40</v>
       </c>
       <c r="AA33">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB33">
         <v>15</v>
@@ -8751,13 +8751,13 @@
         <v>10.5</v>
       </c>
       <c r="AD33">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE33">
         <v>42</v>
       </c>
       <c r="AF33">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG33">
         <v>10.5</v>
@@ -8766,37 +8766,37 @@
         <v>15</v>
       </c>
       <c r="AI33">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ33">
         <v>21</v>
       </c>
       <c r="AK33">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL33">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM33">
         <v>55</v>
       </c>
       <c r="AN33">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AO33">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP33">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ33">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AR33">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS33">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT33">
         <v>13.5</v>
@@ -8811,7 +8811,7 @@
         <v>38</v>
       </c>
       <c r="AX33">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY33">
         <v>9.800000000000001</v>
@@ -8823,10 +8823,10 @@
         <v>36</v>
       </c>
       <c r="BB33">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC33">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD33">
         <v>22</v>
@@ -8838,67 +8838,67 @@
         <v>6.6</v>
       </c>
       <c r="BG33">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH33">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="BI33">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="BJ33">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK33">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="BL33">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM33">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="BN33">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BO33">
+        <v>4.1</v>
+      </c>
+      <c r="BP33">
+        <v>14.5</v>
+      </c>
+      <c r="BQ33">
+        <v>8.4</v>
+      </c>
+      <c r="BR33">
+        <v>23</v>
+      </c>
+      <c r="BS33">
+        <v>14.5</v>
+      </c>
+      <c r="BT33">
+        <v>9.6</v>
+      </c>
+      <c r="BU33">
+        <v>6.2</v>
+      </c>
+      <c r="BV33">
+        <v>34</v>
+      </c>
+      <c r="BW33">
+        <v>4.5</v>
+      </c>
+      <c r="BX33">
+        <v>44</v>
+      </c>
+      <c r="BY33">
         <v>4.6</v>
       </c>
-      <c r="BP33">
-        <v>14</v>
-      </c>
-      <c r="BQ33">
-        <v>10</v>
-      </c>
-      <c r="BR33">
-        <v>19.5</v>
-      </c>
-      <c r="BS33">
-        <v>14</v>
-      </c>
-      <c r="BT33">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU33">
-        <v>7.2</v>
-      </c>
-      <c r="BV33">
-        <v>29</v>
-      </c>
-      <c r="BW33">
-        <v>8.6</v>
-      </c>
-      <c r="BX33">
-        <v>32</v>
-      </c>
-      <c r="BY33">
-        <v>8.4</v>
-      </c>
       <c r="BZ33">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="CA33">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB33" t="s">
         <v>189</v>
@@ -8927,10 +8927,10 @@
         <v>5.1</v>
       </c>
       <c r="H34">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="I34">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="J34">
         <v>4.2</v>
@@ -8945,31 +8945,31 @@
         <v>1.05</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O34">
         <v>1.24</v>
       </c>
       <c r="P34">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q34">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R34">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S34">
         <v>2.8</v>
       </c>
       <c r="T34">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U34">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V34">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="W34">
         <v>1.24</v>
@@ -8978,13 +8978,13 @@
         <v>19.5</v>
       </c>
       <c r="Y34">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z34">
         <v>11.5</v>
       </c>
       <c r="AA34">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AB34">
         <v>21</v>
@@ -8999,7 +8999,7 @@
         <v>16.5</v>
       </c>
       <c r="AF34">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG34">
         <v>19</v>
@@ -9008,10 +9008,10 @@
         <v>17</v>
       </c>
       <c r="AI34">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK34">
         <v>60</v>
@@ -9041,10 +9041,10 @@
         <v>17</v>
       </c>
       <c r="AT34">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AU34">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV34">
         <v>9.4</v>
@@ -9056,19 +9056,19 @@
         <v>36</v>
       </c>
       <c r="AY34">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ34">
         <v>16.5</v>
       </c>
       <c r="BA34">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB34">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="BC34">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BD34">
         <v>50</v>
@@ -9077,7 +9077,7 @@
         <v>70</v>
       </c>
       <c r="BF34">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BG34">
         <v>8.199999999999999</v>
@@ -9086,61 +9086,61 @@
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>1.49</v>
+        <v>2.14</v>
       </c>
       <c r="BJ34">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK34">
-        <v>1.99</v>
+        <v>7.2</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO34">
-        <v>1.88</v>
+        <v>6.4</v>
       </c>
       <c r="BP34">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ34">
-        <v>2.2</v>
+        <v>3.65</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="BT34">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU34">
-        <v>1.59</v>
+        <v>3.8</v>
       </c>
       <c r="BV34">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW34">
-        <v>2.22</v>
+        <v>8.4</v>
       </c>
       <c r="BX34">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY34">
-        <v>2.2</v>
+        <v>3.45</v>
       </c>
       <c r="BZ34">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA34">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="CB34" t="s">
         <v>189</v>
@@ -9163,10 +9163,10 @@
         <v>184</v>
       </c>
       <c r="F35">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G35">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H35">
         <v>3.45</v>
@@ -9184,7 +9184,7 @@
         <v>1.39</v>
       </c>
       <c r="M35">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N35">
         <v>4.2</v>
@@ -9193,7 +9193,7 @@
         <v>1.29</v>
       </c>
       <c r="P35">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q35">
         <v>1.93</v>
@@ -9205,7 +9205,7 @@
         <v>3.25</v>
       </c>
       <c r="T35">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U35">
         <v>2.3</v>
@@ -9214,10 +9214,10 @@
         <v>1.4</v>
       </c>
       <c r="W35">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X35">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y35">
         <v>14</v>
@@ -9226,7 +9226,7 @@
         <v>24</v>
       </c>
       <c r="AA35">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB35">
         <v>11.5</v>
@@ -9265,7 +9265,7 @@
         <v>80</v>
       </c>
       <c r="AN35">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO35">
         <v>34</v>
@@ -9295,13 +9295,13 @@
         <v>34</v>
       </c>
       <c r="AX35">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY35">
         <v>10.5</v>
       </c>
       <c r="AZ35">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA35">
         <v>38</v>
@@ -9310,7 +9310,7 @@
         <v>27</v>
       </c>
       <c r="BC35">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD35">
         <v>32</v>
@@ -9322,67 +9322,67 @@
         <v>15.5</v>
       </c>
       <c r="BG35">
+        <v>30</v>
+      </c>
+      <c r="BH35">
+        <v>4.1</v>
+      </c>
+      <c r="BI35">
+        <v>3.05</v>
+      </c>
+      <c r="BJ35">
+        <v>10.5</v>
+      </c>
+      <c r="BK35">
+        <v>7</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>5.4</v>
+      </c>
+      <c r="BN35">
+        <v>6</v>
+      </c>
+      <c r="BO35">
+        <v>4.1</v>
+      </c>
+      <c r="BP35">
+        <v>20</v>
+      </c>
+      <c r="BQ35">
+        <v>12</v>
+      </c>
+      <c r="BR35">
+        <v>34</v>
+      </c>
+      <c r="BS35">
+        <v>4.7</v>
+      </c>
+      <c r="BT35">
+        <v>7.8</v>
+      </c>
+      <c r="BU35">
+        <v>5.1</v>
+      </c>
+      <c r="BV35">
+        <v>30</v>
+      </c>
+      <c r="BW35">
+        <v>4.7</v>
+      </c>
+      <c r="BX35">
+        <v>44</v>
+      </c>
+      <c r="BY35">
+        <v>4.8</v>
+      </c>
+      <c r="BZ35">
         <v>29</v>
       </c>
-      <c r="BH35">
-        <v>3.6</v>
-      </c>
-      <c r="BI35">
-        <v>3.35</v>
-      </c>
-      <c r="BJ35">
-        <v>9</v>
-      </c>
-      <c r="BK35">
-        <v>8</v>
-      </c>
-      <c r="BL35">
-        <v>110</v>
-      </c>
-      <c r="BM35">
-        <v>16</v>
-      </c>
-      <c r="BN35">
-        <v>5.2</v>
-      </c>
-      <c r="BO35">
-        <v>4.8</v>
-      </c>
-      <c r="BP35">
-        <v>16</v>
-      </c>
-      <c r="BQ35">
-        <v>9</v>
-      </c>
-      <c r="BR35">
-        <v>28</v>
-      </c>
-      <c r="BS35">
-        <v>11.5</v>
-      </c>
-      <c r="BT35">
-        <v>6.6</v>
-      </c>
-      <c r="BU35">
-        <v>6</v>
-      </c>
-      <c r="BV35">
-        <v>26</v>
-      </c>
-      <c r="BW35">
-        <v>11</v>
-      </c>
-      <c r="BX35">
-        <v>36</v>
-      </c>
-      <c r="BY35">
-        <v>12.5</v>
-      </c>
-      <c r="BZ35">
-        <v>24</v>
-      </c>
       <c r="CA35">
-        <v>10.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB35" t="s">
         <v>189</v>
@@ -9405,10 +9405,10 @@
         <v>185</v>
       </c>
       <c r="F36">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G36">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H36">
         <v>5.2</v>
@@ -9417,10 +9417,10 @@
         <v>5.3</v>
       </c>
       <c r="J36">
+        <v>4.6</v>
+      </c>
+      <c r="K36">
         <v>4.7</v>
-      </c>
-      <c r="K36">
-        <v>4.8</v>
       </c>
       <c r="L36">
         <v>1.26</v>
@@ -9441,7 +9441,7 @@
         <v>1.48</v>
       </c>
       <c r="R36">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S36">
         <v>2.2</v>
@@ -9456,7 +9456,7 @@
         <v>1.23</v>
       </c>
       <c r="W36">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X36">
         <v>32</v>
@@ -9468,7 +9468,7 @@
         <v>50</v>
       </c>
       <c r="AA36">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB36">
         <v>14.5</v>
@@ -9483,19 +9483,19 @@
         <v>55</v>
       </c>
       <c r="AF36">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG36">
         <v>10</v>
       </c>
       <c r="AH36">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI36">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ36">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK36">
         <v>14</v>
@@ -9513,19 +9513,19 @@
         <v>40</v>
       </c>
       <c r="AP36">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ36">
         <v>27</v>
       </c>
       <c r="AR36">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS36">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AT36">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU36">
         <v>10.5</v>
@@ -9534,13 +9534,13 @@
         <v>19</v>
       </c>
       <c r="AW36">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX36">
         <v>12.5</v>
       </c>
       <c r="AY36">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ36">
         <v>15</v>
@@ -9552,7 +9552,7 @@
         <v>17</v>
       </c>
       <c r="BC36">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD36">
         <v>21</v>
@@ -9564,67 +9564,67 @@
         <v>5.6</v>
       </c>
       <c r="BG36">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH36">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI36">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BJ36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BK36">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="BL36">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BM36">
-        <v>15</v>
+        <v>6.2</v>
       </c>
       <c r="BN36">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BO36">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BP36">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BQ36">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BR36">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BS36">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="BT36">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BU36">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BV36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW36">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="BX36">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BY36">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="BZ36">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="CA36">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="CB36" t="s">
         <v>189</v>
@@ -9647,13 +9647,13 @@
         <v>186</v>
       </c>
       <c r="F37">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G37">
         <v>2.88</v>
       </c>
       <c r="H37">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="I37">
         <v>4.5</v>
@@ -9662,7 +9662,7 @@
         <v>2.76</v>
       </c>
       <c r="K37">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -9671,7 +9671,7 @@
         <v>1.01</v>
       </c>
       <c r="N37">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O37">
         <v>1.4</v>
@@ -9680,13 +9680,13 @@
         <v>1.53</v>
       </c>
       <c r="Q37">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S37">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="T37">
         <v>1.01</v>
@@ -9701,112 +9701,112 @@
         <v>1.53</v>
       </c>
       <c r="X37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y37">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z37">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB37">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC37">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD37">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF37">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG37">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH37">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ37">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK37">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO37">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP37">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AQ37">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AR37">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AS37">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AT37">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AU37">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AV37">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AW37">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AX37">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="AY37">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="AZ37">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BA37">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BB37">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BC37">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BD37">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BE37">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BF37">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BG37">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9889,226 +9889,226 @@
         <v>187</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P38">
-        <v>1.07</v>
+        <v>1.58</v>
       </c>
       <c r="Q38">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AI38">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL38">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP38">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AU38">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV38">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW38">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AX38">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AY38">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ38">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BA38">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BB38">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC38">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD38">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BE38">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BF38">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG38">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BH38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BJ38">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BK38">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BL38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM38">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN38">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BO38">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BP38">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BQ38">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BR38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS38">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT38">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BU38">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BV38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW38">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY38">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ38">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="CA38">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CB38" t="s">
         <v>189</v>
@@ -10131,7 +10131,7 @@
         <v>188</v>
       </c>
       <c r="F39">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G39">
         <v>1.99</v>
@@ -10149,34 +10149,34 @@
         <v>3.4</v>
       </c>
       <c r="L39">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M39">
         <v>1.13</v>
       </c>
       <c r="N39">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O39">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P39">
         <v>1.53</v>
       </c>
       <c r="Q39">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R39">
         <v>1.19</v>
       </c>
       <c r="S39">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="T39">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U39">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V39">
         <v>1.22</v>
@@ -10191,13 +10191,13 @@
         <v>13</v>
       </c>
       <c r="Z39">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AA39">
         <v>210</v>
       </c>
       <c r="AB39">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC39">
         <v>7.8</v>
@@ -10215,19 +10215,19 @@
         <v>11.5</v>
       </c>
       <c r="AH39">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI39">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ39">
         <v>24</v>
       </c>
       <c r="AK39">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL39">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM39">
         <v>300</v>
@@ -10245,22 +10245,22 @@
         <v>11</v>
       </c>
       <c r="AR39">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS39">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT39">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU39">
         <v>7</v>
       </c>
       <c r="AV39">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW39">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AX39">
         <v>9</v>
@@ -10269,88 +10269,88 @@
         <v>10</v>
       </c>
       <c r="AZ39">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BA39">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BB39">
         <v>20</v>
       </c>
       <c r="BC39">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BD39">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE39">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF39">
+        <v>17.5</v>
+      </c>
+      <c r="BG39">
+        <v>12.5</v>
+      </c>
+      <c r="BH39">
+        <v>1000</v>
+      </c>
+      <c r="BI39">
+        <v>1.74</v>
+      </c>
+      <c r="BJ39">
         <v>18</v>
       </c>
-      <c r="BG39">
-        <v>11</v>
-      </c>
-      <c r="BH39">
-        <v>2.66</v>
-      </c>
-      <c r="BI39">
-        <v>2.48</v>
-      </c>
-      <c r="BJ39">
+      <c r="BK39">
+        <v>3.7</v>
+      </c>
+      <c r="BL39">
+        <v>1000</v>
+      </c>
+      <c r="BM39">
+        <v>1.73</v>
+      </c>
+      <c r="BN39">
+        <v>5</v>
+      </c>
+      <c r="BO39">
+        <v>3.65</v>
+      </c>
+      <c r="BP39">
+        <v>23</v>
+      </c>
+      <c r="BQ39">
+        <v>1.61</v>
+      </c>
+      <c r="BR39">
+        <v>1000</v>
+      </c>
+      <c r="BS39">
+        <v>1.69</v>
+      </c>
+      <c r="BT39">
         <v>12.5</v>
-      </c>
-      <c r="BK39">
-        <v>7.4</v>
-      </c>
-      <c r="BL39">
-        <v>1000</v>
-      </c>
-      <c r="BM39">
-        <v>17.5</v>
-      </c>
-      <c r="BN39">
-        <v>4.3</v>
-      </c>
-      <c r="BO39">
-        <v>3.85</v>
-      </c>
-      <c r="BP39">
-        <v>15.5</v>
-      </c>
-      <c r="BQ39">
-        <v>8.4</v>
-      </c>
-      <c r="BR39">
-        <v>1000</v>
-      </c>
-      <c r="BS39">
-        <v>13</v>
-      </c>
-      <c r="BT39">
-        <v>8.6</v>
       </c>
       <c r="BU39">
         <v>6.4</v>
       </c>
       <c r="BV39">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW39">
-        <v>14.5</v>
+        <v>1.7</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>15</v>
+        <v>1.73</v>
       </c>
       <c r="BZ39">
         <v>1000</v>
       </c>
       <c r="CA39">
-        <v>13</v>
+        <v>1.69</v>
       </c>
       <c r="CB39" t="s">
         <v>189</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -583,7 +583,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-09-07 19:22:10</t>
+    <t>2026-09-07 21:33:57</t>
   </si>
 </sst>
 </file>
@@ -1177,226 +1177,226 @@
         <v>151</v>
       </c>
       <c r="F2">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="G2">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>2.72</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>2.06</v>
       </c>
       <c r="O2">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="Q2">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="T2">
+        <v>3.25</v>
+      </c>
+      <c r="U2">
+        <v>1.39</v>
+      </c>
+      <c r="V2">
+        <v>1.17</v>
+      </c>
+      <c r="W2">
         <v>2.08</v>
       </c>
-      <c r="U2">
-        <v>1.83</v>
-      </c>
-      <c r="V2">
-        <v>1.19</v>
-      </c>
-      <c r="W2">
-        <v>2.32</v>
-      </c>
       <c r="X2">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="Y2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Z2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA2">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="AB2">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AE2">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AG2">
+        <v>15</v>
+      </c>
+      <c r="AH2">
+        <v>55</v>
+      </c>
+      <c r="AI2">
+        <v>390</v>
+      </c>
+      <c r="AJ2">
+        <v>24</v>
+      </c>
+      <c r="AK2">
+        <v>48</v>
+      </c>
+      <c r="AL2">
+        <v>170</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>44</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>5.3</v>
+      </c>
+      <c r="AQ2">
         <v>10.5</v>
       </c>
-      <c r="AH2">
-        <v>25</v>
-      </c>
-      <c r="AI2">
-        <v>280</v>
-      </c>
-      <c r="AJ2">
-        <v>17.5</v>
-      </c>
-      <c r="AK2">
-        <v>21</v>
-      </c>
-      <c r="AL2">
+      <c r="AR2">
         <v>46</v>
       </c>
-      <c r="AM2">
-        <v>180</v>
-      </c>
-      <c r="AN2">
-        <v>13.5</v>
-      </c>
-      <c r="AO2">
-        <v>140</v>
-      </c>
-      <c r="AP2">
-        <v>10.5</v>
-      </c>
-      <c r="AQ2">
-        <v>15.5</v>
-      </c>
-      <c r="AR2">
-        <v>40</v>
-      </c>
       <c r="AS2">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="AU2">
         <v>7.8</v>
       </c>
       <c r="AV2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AW2">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AX2">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="BA2">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="BB2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BC2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="BD2">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="BE2">
-        <v>110</v>
+        <v>490</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="BG2">
-        <v>85</v>
+        <v>330</v>
       </c>
       <c r="BH2">
-        <v>3.15</v>
+        <v>1.57</v>
       </c>
       <c r="BI2">
-        <v>2.88</v>
+        <v>1.52</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="BK2">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BN2">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP2">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BQ2">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>910</v>
       </c>
       <c r="BS2">
+        <v>19.5</v>
+      </c>
+      <c r="BT2">
+        <v>12.5</v>
+      </c>
+      <c r="BU2">
         <v>11</v>
       </c>
-      <c r="BT2">
-        <v>9.4</v>
-      </c>
-      <c r="BU2">
-        <v>8</v>
-      </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="CB2" t="s">
         <v>189</v>
@@ -1419,226 +1419,226 @@
         <v>152</v>
       </c>
       <c r="F3">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G3">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H3">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="I3">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1.68</v>
+        <v>5.1</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>1.23</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.96</v>
       </c>
       <c r="S3">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
         <v>1.79</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>5.5</v>
+      </c>
+      <c r="AD3">
+        <v>9.6</v>
+      </c>
+      <c r="AE3">
+        <v>36</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>5.5</v>
+      </c>
+      <c r="AH3">
+        <v>7.4</v>
+      </c>
+      <c r="AI3">
+        <v>29</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>11</v>
+      </c>
+      <c r="AL3">
+        <v>16</v>
+      </c>
+      <c r="AM3">
+        <v>50</v>
+      </c>
+      <c r="AN3">
+        <v>14</v>
+      </c>
+      <c r="AO3">
+        <v>60</v>
+      </c>
+      <c r="AP3">
+        <v>9.6</v>
+      </c>
+      <c r="AQ3">
+        <v>9.6</v>
+      </c>
+      <c r="AR3">
+        <v>9.6</v>
+      </c>
+      <c r="AS3">
+        <v>9.6</v>
+      </c>
+      <c r="AT3">
+        <v>9.6</v>
+      </c>
+      <c r="AU3">
+        <v>5.1</v>
+      </c>
+      <c r="AV3">
+        <v>8.4</v>
+      </c>
+      <c r="AW3">
+        <v>27</v>
+      </c>
+      <c r="AX3">
+        <v>9.6</v>
+      </c>
+      <c r="AY3">
+        <v>4.7</v>
+      </c>
+      <c r="AZ3">
+        <v>6.8</v>
+      </c>
+      <c r="BA3">
+        <v>23</v>
+      </c>
+      <c r="BB3">
+        <v>9.6</v>
+      </c>
+      <c r="BC3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD3">
+        <v>13.5</v>
+      </c>
+      <c r="BE3">
+        <v>42</v>
+      </c>
+      <c r="BF3">
         <v>12.5</v>
       </c>
-      <c r="Z3">
-        <v>29</v>
-      </c>
-      <c r="AA3">
-        <v>110</v>
-      </c>
-      <c r="AB3">
-        <v>8</v>
-      </c>
-      <c r="AC3">
-        <v>7.4</v>
-      </c>
-      <c r="AD3">
-        <v>17.5</v>
-      </c>
-      <c r="AE3">
-        <v>65</v>
-      </c>
-      <c r="AF3">
-        <v>13</v>
-      </c>
-      <c r="AG3">
-        <v>11.5</v>
-      </c>
-      <c r="AH3">
-        <v>22</v>
-      </c>
-      <c r="AI3">
-        <v>85</v>
-      </c>
-      <c r="AJ3">
+      <c r="BG3">
+        <v>44</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>25</v>
+      </c>
+      <c r="BJ3">
+        <v>1.59</v>
+      </c>
+      <c r="BK3">
+        <v>1.54</v>
+      </c>
+      <c r="BL3">
+        <v>38</v>
+      </c>
+      <c r="BM3">
         <v>32</v>
       </c>
-      <c r="AK3">
-        <v>30</v>
-      </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
-      <c r="AM3">
-        <v>170</v>
-      </c>
-      <c r="AN3">
-        <v>29</v>
-      </c>
-      <c r="AO3">
-        <v>90</v>
-      </c>
-      <c r="AP3">
-        <v>9</v>
-      </c>
-      <c r="AQ3">
-        <v>10.5</v>
-      </c>
-      <c r="AR3">
-        <v>23</v>
-      </c>
-      <c r="AS3">
-        <v>60</v>
-      </c>
-      <c r="AT3">
-        <v>7.4</v>
-      </c>
-      <c r="AU3">
-        <v>6.6</v>
-      </c>
-      <c r="AV3">
-        <v>14.5</v>
-      </c>
-      <c r="AW3">
-        <v>40</v>
-      </c>
-      <c r="AX3">
-        <v>11.5</v>
-      </c>
-      <c r="AY3">
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>25</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>25</v>
+      </c>
+      <c r="BR3">
+        <v>5.5</v>
+      </c>
+      <c r="BS3">
+        <v>5.1</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>25</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>25</v>
+      </c>
+      <c r="BX3">
         <v>10</v>
       </c>
-      <c r="AZ3">
-        <v>17.5</v>
-      </c>
-      <c r="BA3">
-        <v>50</v>
-      </c>
-      <c r="BB3">
-        <v>23</v>
-      </c>
-      <c r="BC3">
-        <v>21</v>
-      </c>
-      <c r="BD3">
-        <v>34</v>
-      </c>
-      <c r="BE3">
-        <v>100</v>
-      </c>
-      <c r="BF3">
-        <v>21</v>
-      </c>
-      <c r="BG3">
-        <v>46</v>
-      </c>
-      <c r="BH3">
-        <v>2.92</v>
-      </c>
-      <c r="BI3">
-        <v>2.72</v>
-      </c>
-      <c r="BJ3">
-        <v>12.5</v>
-      </c>
-      <c r="BK3">
-        <v>8.4</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>11</v>
-      </c>
-      <c r="BN3">
-        <v>4.8</v>
-      </c>
-      <c r="BO3">
-        <v>4.4</v>
-      </c>
-      <c r="BP3">
-        <v>21</v>
-      </c>
-      <c r="BQ3">
-        <v>14</v>
-      </c>
-      <c r="BR3">
-        <v>42</v>
-      </c>
-      <c r="BS3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT3">
-        <v>7.2</v>
-      </c>
-      <c r="BU3">
-        <v>6.2</v>
-      </c>
-      <c r="BV3">
-        <v>38</v>
-      </c>
-      <c r="BW3">
-        <v>9</v>
-      </c>
-      <c r="BX3">
-        <v>60</v>
-      </c>
       <c r="BY3">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="CA3">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="CB3" t="s">
         <v>189</v>
@@ -1661,226 +1661,226 @@
         <v>153</v>
       </c>
       <c r="F4">
-        <v>2.18</v>
+        <v>1.42</v>
       </c>
       <c r="G4">
-        <v>2.26</v>
+        <v>1.45</v>
       </c>
       <c r="H4">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>6.4</v>
+      </c>
+      <c r="O4">
+        <v>1.17</v>
+      </c>
+      <c r="P4">
+        <v>2.14</v>
+      </c>
+      <c r="Q4">
+        <v>1.83</v>
+      </c>
+      <c r="R4">
+        <v>1.35</v>
+      </c>
+      <c r="S4">
+        <v>3.55</v>
+      </c>
+      <c r="T4">
+        <v>1.06</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
         <v>1.09</v>
       </c>
-      <c r="N4">
-        <v>3.25</v>
-      </c>
-      <c r="O4">
-        <v>1.42</v>
-      </c>
-      <c r="P4">
-        <v>1.75</v>
-      </c>
-      <c r="Q4">
-        <v>2.26</v>
-      </c>
-      <c r="R4">
-        <v>1.28</v>
-      </c>
-      <c r="S4">
-        <v>4.3</v>
-      </c>
-      <c r="T4">
-        <v>1.94</v>
-      </c>
-      <c r="U4">
-        <v>1.98</v>
-      </c>
-      <c r="V4">
-        <v>1.33</v>
-      </c>
       <c r="W4">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AE4">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AF4">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AH4">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AI4">
         <v>85</v>
       </c>
       <c r="AJ4">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="AK4">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="AL4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM4">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AO4">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR4">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AS4">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="AT4">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU4">
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW4">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AX4">
+        <v>6.2</v>
+      </c>
+      <c r="AY4">
+        <v>6.8</v>
+      </c>
+      <c r="AZ4">
+        <v>15</v>
+      </c>
+      <c r="BA4">
+        <v>55</v>
+      </c>
+      <c r="BB4">
+        <v>12</v>
+      </c>
+      <c r="BC4">
+        <v>13.5</v>
+      </c>
+      <c r="BD4">
+        <v>30</v>
+      </c>
+      <c r="BE4">
+        <v>85</v>
+      </c>
+      <c r="BF4">
         <v>11.5</v>
       </c>
-      <c r="AY4">
-        <v>10</v>
-      </c>
-      <c r="AZ4">
-        <v>17.5</v>
-      </c>
-      <c r="BA4">
-        <v>48</v>
-      </c>
-      <c r="BB4">
-        <v>24</v>
-      </c>
-      <c r="BC4">
-        <v>23</v>
-      </c>
-      <c r="BD4">
-        <v>40</v>
-      </c>
-      <c r="BE4">
-        <v>90</v>
-      </c>
-      <c r="BF4">
-        <v>18.5</v>
-      </c>
       <c r="BG4">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="BH4">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BM4">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN4">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="BO4">
-        <v>4.5</v>
+        <v>1.84</v>
       </c>
       <c r="BP4">
-        <v>17.5</v>
+        <v>8</v>
       </c>
       <c r="BQ4">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="BS4">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BT4">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>860</v>
       </c>
       <c r="CA4">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB4" t="s">
         <v>189</v>
@@ -1903,226 +1903,226 @@
         <v>154</v>
       </c>
       <c r="F5">
+        <v>3.4</v>
+      </c>
+      <c r="G5">
+        <v>3.45</v>
+      </c>
+      <c r="H5">
+        <v>2.76</v>
+      </c>
+      <c r="I5">
+        <v>2.8</v>
+      </c>
+      <c r="J5">
+        <v>2.82</v>
+      </c>
+      <c r="K5">
+        <v>2.88</v>
+      </c>
+      <c r="L5">
+        <v>1.94</v>
+      </c>
+      <c r="M5">
+        <v>1.18</v>
+      </c>
+      <c r="N5">
+        <v>4.2</v>
+      </c>
+      <c r="O5">
+        <v>1.01</v>
+      </c>
+      <c r="P5">
+        <v>2.3</v>
+      </c>
+      <c r="Q5">
+        <v>1.63</v>
+      </c>
+      <c r="R5">
+        <v>1.33</v>
+      </c>
+      <c r="S5">
+        <v>3.05</v>
+      </c>
+      <c r="T5">
+        <v>1.05</v>
+      </c>
+      <c r="U5">
+        <v>1.96</v>
+      </c>
+      <c r="V5">
+        <v>2.6</v>
+      </c>
+      <c r="W5">
+        <v>1.13</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>580</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>980</v>
+      </c>
+      <c r="AD5">
+        <v>990</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>790</v>
+      </c>
+      <c r="AH5">
+        <v>990</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
         <v>3.15</v>
       </c>
-      <c r="G5">
+      <c r="AQ5">
+        <v>1.22</v>
+      </c>
+      <c r="AR5">
+        <v>2.2</v>
+      </c>
+      <c r="AS5">
+        <v>2.46</v>
+      </c>
+      <c r="AT5">
+        <v>5.1</v>
+      </c>
+      <c r="AU5">
         <v>3.25</v>
       </c>
-      <c r="H5">
-        <v>2.72</v>
-      </c>
-      <c r="I5">
-        <v>2.78</v>
-      </c>
-      <c r="J5">
-        <v>3.05</v>
-      </c>
-      <c r="K5">
-        <v>3.1</v>
-      </c>
-      <c r="L5">
+      <c r="AV5">
+        <v>2.46</v>
+      </c>
+      <c r="AW5">
+        <v>1.9</v>
+      </c>
+      <c r="AX5">
+        <v>5.1</v>
+      </c>
+      <c r="AY5">
+        <v>5.1</v>
+      </c>
+      <c r="AZ5">
+        <v>3.25</v>
+      </c>
+      <c r="BA5">
+        <v>1.42</v>
+      </c>
+      <c r="BB5">
+        <v>5.1</v>
+      </c>
+      <c r="BC5">
+        <v>5.1</v>
+      </c>
+      <c r="BD5">
+        <v>5.1</v>
+      </c>
+      <c r="BE5">
+        <v>3.15</v>
+      </c>
+      <c r="BF5">
+        <v>5.8</v>
+      </c>
+      <c r="BG5">
         <v>1.6</v>
       </c>
-      <c r="M5">
-        <v>1.13</v>
-      </c>
-      <c r="N5">
-        <v>2.72</v>
-      </c>
-      <c r="O5">
-        <v>1.56</v>
-      </c>
-      <c r="P5">
-        <v>1.56</v>
-      </c>
-      <c r="Q5">
-        <v>2.72</v>
-      </c>
-      <c r="R5">
-        <v>1.2</v>
-      </c>
-      <c r="S5">
+      <c r="BH5">
+        <v>2.08</v>
+      </c>
+      <c r="BI5">
+        <v>1.96</v>
+      </c>
+      <c r="BJ5">
+        <v>16</v>
+      </c>
+      <c r="BK5">
+        <v>15.5</v>
+      </c>
+      <c r="BL5">
+        <v>730</v>
+      </c>
+      <c r="BM5">
+        <v>11</v>
+      </c>
+      <c r="BN5">
+        <v>6.6</v>
+      </c>
+      <c r="BO5">
         <v>5.7</v>
       </c>
-      <c r="T5">
-        <v>2.18</v>
-      </c>
-      <c r="U5">
-        <v>1.83</v>
-      </c>
-      <c r="V5">
-        <v>1.56</v>
-      </c>
-      <c r="W5">
-        <v>1.45</v>
-      </c>
-      <c r="X5">
-        <v>8.6</v>
-      </c>
-      <c r="Y5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z5">
-        <v>16</v>
-      </c>
-      <c r="AA5">
-        <v>46</v>
-      </c>
-      <c r="AB5">
-        <v>9</v>
-      </c>
-      <c r="AC5">
-        <v>7</v>
-      </c>
-      <c r="AD5">
-        <v>13</v>
-      </c>
-      <c r="AE5">
-        <v>40</v>
-      </c>
-      <c r="AF5">
-        <v>19.5</v>
-      </c>
-      <c r="AG5">
-        <v>14.5</v>
-      </c>
-      <c r="AH5">
-        <v>23</v>
-      </c>
-      <c r="AI5">
-        <v>65</v>
-      </c>
-      <c r="AJ5">
-        <v>60</v>
-      </c>
-      <c r="AK5">
-        <v>48</v>
-      </c>
-      <c r="AL5">
-        <v>75</v>
-      </c>
-      <c r="AM5">
-        <v>180</v>
-      </c>
-      <c r="AN5">
-        <v>60</v>
-      </c>
-      <c r="AO5">
-        <v>46</v>
-      </c>
-      <c r="AP5">
-        <v>7.8</v>
-      </c>
-      <c r="AQ5">
-        <v>7.8</v>
-      </c>
-      <c r="AR5">
-        <v>14.5</v>
-      </c>
-      <c r="AS5">
-        <v>40</v>
-      </c>
-      <c r="AT5">
-        <v>8.4</v>
-      </c>
-      <c r="AU5">
-        <v>6.4</v>
-      </c>
-      <c r="AV5">
-        <v>12</v>
-      </c>
-      <c r="AW5">
-        <v>36</v>
-      </c>
-      <c r="AX5">
-        <v>17.5</v>
-      </c>
-      <c r="AY5">
-        <v>13</v>
-      </c>
-      <c r="AZ5">
-        <v>20</v>
-      </c>
-      <c r="BA5">
+      <c r="BP5">
         <v>55</v>
       </c>
-      <c r="BB5">
-        <v>50</v>
-      </c>
-      <c r="BC5">
-        <v>42</v>
-      </c>
-      <c r="BD5">
-        <v>65</v>
-      </c>
-      <c r="BE5">
-        <v>90</v>
-      </c>
-      <c r="BF5">
-        <v>50</v>
-      </c>
-      <c r="BG5">
-        <v>42</v>
-      </c>
-      <c r="BH5">
-        <v>2.64</v>
-      </c>
-      <c r="BI5">
-        <v>2.52</v>
-      </c>
-      <c r="BJ5">
-        <v>11</v>
-      </c>
-      <c r="BK5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BL5">
-        <v>210</v>
-      </c>
-      <c r="BM5">
-        <v>20</v>
-      </c>
-      <c r="BN5">
-        <v>6</v>
-      </c>
-      <c r="BO5">
-        <v>5.5</v>
-      </c>
-      <c r="BP5">
-        <v>30</v>
-      </c>
       <c r="BQ5">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BR5">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="BS5">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="BT5">
         <v>5.5</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV5">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="BX5">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="BY5">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="BZ5">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="CA5">
-        <v>15.5</v>
+        <v>85</v>
       </c>
       <c r="CB5" t="s">
         <v>189</v>
@@ -2157,10 +2157,10 @@
         <v>2.18</v>
       </c>
       <c r="J6">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K6">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L6">
         <v>1.34</v>
@@ -2172,13 +2172,13 @@
         <v>5.1</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P6">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q6">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R6">
         <v>1.54</v>
@@ -2187,13 +2187,13 @@
         <v>2.72</v>
       </c>
       <c r="T6">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V6">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W6">
         <v>1.36</v>
@@ -2211,7 +2211,7 @@
         <v>28</v>
       </c>
       <c r="AB6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC6">
         <v>8.6</v>
@@ -2232,7 +2232,7 @@
         <v>15.5</v>
       </c>
       <c r="AI6">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
@@ -2241,19 +2241,19 @@
         <v>38</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN6">
         <v>32</v>
       </c>
       <c r="AO6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ6">
         <v>11.5</v>
@@ -2262,7 +2262,7 @@
         <v>13.5</v>
       </c>
       <c r="AS6">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AT6">
         <v>16</v>
@@ -2298,22 +2298,22 @@
         <v>32</v>
       </c>
       <c r="BE6">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BF6">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BG6">
         <v>10.5</v>
       </c>
       <c r="BH6">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI6">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6">
         <v>7.8</v>
@@ -2322,7 +2322,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN6">
         <v>7</v>
@@ -2331,19 +2331,19 @@
         <v>6.2</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ6">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS6">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BT6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU6">
         <v>4.7</v>
@@ -2355,16 +2355,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BX6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
         <v>18.5</v>
       </c>
       <c r="CA6">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="s">
         <v>189</v>
@@ -2393,19 +2393,19 @@
         <v>1.9</v>
       </c>
       <c r="H7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K7">
         <v>3.7</v>
       </c>
       <c r="L7">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M7">
         <v>1.09</v>
@@ -2423,7 +2423,7 @@
         <v>2.2</v>
       </c>
       <c r="R7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S7">
         <v>4.2</v>
@@ -2459,7 +2459,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE7">
         <v>1000</v>
@@ -2471,7 +2471,7 @@
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI7">
         <v>1000</v>
@@ -2483,7 +2483,7 @@
         <v>22</v>
       </c>
       <c r="AL7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM7">
         <v>1000</v>
@@ -2504,7 +2504,7 @@
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AT7">
         <v>7</v>
@@ -2513,7 +2513,7 @@
         <v>7.4</v>
       </c>
       <c r="AV7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW7">
         <v>50</v>
@@ -2522,7 +2522,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7">
         <v>19.5</v>
@@ -2540,73 +2540,73 @@
         <v>36</v>
       </c>
       <c r="BE7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BF7">
         <v>14</v>
       </c>
       <c r="BG7">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BH7">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="BI7">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="BJ7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BK7">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="BN7">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BO7">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BP7">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BQ7">
         <v>9.6</v>
       </c>
       <c r="BR7">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BS7">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="BT7">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BU7">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW7">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY7">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="BZ7">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="CA7">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="CB7" t="s">
         <v>189</v>
@@ -2647,7 +2647,7 @@
         <v>4.6</v>
       </c>
       <c r="L8">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M8">
         <v>1.04</v>
@@ -2737,7 +2737,7 @@
         <v>9.4</v>
       </c>
       <c r="AP8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AQ8">
         <v>9.4</v>
@@ -2794,10 +2794,10 @@
         <v>4.8</v>
       </c>
       <c r="BI8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ8">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
         <v>7.2</v>
@@ -2806,25 +2806,25 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BN8">
         <v>11.5</v>
       </c>
       <c r="BO8">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="BP8">
         <v>55</v>
       </c>
       <c r="BQ8">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS8">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT8">
         <v>5.2</v>
@@ -2833,22 +2833,22 @@
         <v>3.95</v>
       </c>
       <c r="BV8">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BW8">
-        <v>7.6</v>
+        <v>3.45</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY8">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BZ8">
         <v>18.5</v>
       </c>
       <c r="CA8">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="CB8" t="s">
         <v>189</v>
@@ -2901,10 +2901,10 @@
         <v>1.27</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R9">
         <v>1.44</v>
@@ -2916,7 +2916,7 @@
         <v>1.9</v>
       </c>
       <c r="U9">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V9">
         <v>1.17</v>
@@ -2925,13 +2925,13 @@
         <v>2.56</v>
       </c>
       <c r="X9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y9">
         <v>23</v>
       </c>
       <c r="Z9">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2964,7 +2964,7 @@
         <v>15.5</v>
       </c>
       <c r="AK9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL9">
         <v>42</v>
@@ -2982,7 +2982,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR9">
         <v>30</v>
@@ -3000,7 +3000,7 @@
         <v>21</v>
       </c>
       <c r="AW9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX9">
         <v>9</v>
@@ -3012,7 +3012,7 @@
         <v>17</v>
       </c>
       <c r="BA9">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB9">
         <v>13.5</v>
@@ -3113,7 +3113,7 @@
         <v>159</v>
       </c>
       <c r="F10">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G10">
         <v>1.61</v>
@@ -3122,7 +3122,7 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J10">
         <v>4.5</v>
@@ -3131,25 +3131,25 @@
         <v>4.8</v>
       </c>
       <c r="L10">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q10">
         <v>1.66</v>
       </c>
       <c r="R10">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S10">
         <v>2.64</v>
@@ -3164,16 +3164,16 @@
         <v>1.18</v>
       </c>
       <c r="W10">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X10">
         <v>23</v>
       </c>
       <c r="Y10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z10">
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3197,10 +3197,10 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI10">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
         <v>15.5</v>
@@ -3212,7 +3212,7 @@
         <v>34</v>
       </c>
       <c r="AM10">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
         <v>6.8</v>
@@ -3224,10 +3224,10 @@
         <v>19.5</v>
       </c>
       <c r="AQ10">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AS10">
         <v>44</v>
@@ -3239,7 +3239,7 @@
         <v>9.4</v>
       </c>
       <c r="AV10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW10">
         <v>46</v>
@@ -3254,7 +3254,7 @@
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BB10">
         <v>13</v>
@@ -3296,7 +3296,7 @@
         <v>4.7</v>
       </c>
       <c r="BO10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP10">
         <v>13</v>
@@ -3370,7 +3370,7 @@
         <v>3.6</v>
       </c>
       <c r="K11">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L11">
         <v>1.33</v>
@@ -3382,13 +3382,13 @@
         <v>4.4</v>
       </c>
       <c r="O11">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P11">
         <v>2.16</v>
       </c>
       <c r="Q11">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="R11">
         <v>1.46</v>
@@ -3403,13 +3403,13 @@
         <v>2.34</v>
       </c>
       <c r="V11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
         <v>1.65</v>
       </c>
       <c r="X11">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y11">
         <v>18.5</v>
@@ -3448,7 +3448,7 @@
         <v>40</v>
       </c>
       <c r="AK11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL11">
         <v>42</v>
@@ -3463,16 +3463,16 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ11">
         <v>12.5</v>
       </c>
       <c r="AR11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AS11">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AT11">
         <v>11</v>
@@ -3484,7 +3484,7 @@
         <v>10</v>
       </c>
       <c r="AW11">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AX11">
         <v>12.5</v>
@@ -3496,13 +3496,13 @@
         <v>10</v>
       </c>
       <c r="BA11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BB11">
         <v>13</v>
       </c>
       <c r="BC11">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BD11">
         <v>14</v>
@@ -3538,7 +3538,7 @@
         <v>6.4</v>
       </c>
       <c r="BO11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP11">
         <v>25</v>
@@ -3556,7 +3556,7 @@
         <v>7.6</v>
       </c>
       <c r="BU11">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV11">
         <v>34</v>
@@ -3600,16 +3600,16 @@
         <v>1.51</v>
       </c>
       <c r="G12">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H12">
         <v>5.7</v>
       </c>
       <c r="I12">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K12">
         <v>5.4</v>
@@ -3618,7 +3618,7 @@
         <v>1.22</v>
       </c>
       <c r="M12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N12">
         <v>6.2</v>
@@ -3627,10 +3627,10 @@
         <v>1.14</v>
       </c>
       <c r="P12">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q12">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R12">
         <v>1.73</v>
@@ -3642,10 +3642,10 @@
         <v>1.62</v>
       </c>
       <c r="U12">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W12">
         <v>2.74</v>
@@ -3699,13 +3699,13 @@
         <v>80</v>
       </c>
       <c r="AN12">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AO12">
         <v>65</v>
       </c>
       <c r="AP12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ12">
         <v>25</v>
@@ -3714,7 +3714,7 @@
         <v>42</v>
       </c>
       <c r="AS12">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT12">
         <v>12</v>
@@ -3780,7 +3780,7 @@
         <v>5.1</v>
       </c>
       <c r="BO12">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP12">
         <v>10.5</v>
@@ -3845,7 +3845,7 @@
         <v>2.2</v>
       </c>
       <c r="H13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I13">
         <v>3.9</v>
@@ -3863,19 +3863,19 @@
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O13">
         <v>1.32</v>
       </c>
       <c r="P13">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q13">
         <v>1.94</v>
       </c>
       <c r="R13">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S13">
         <v>3.4</v>
@@ -3884,7 +3884,7 @@
         <v>1.78</v>
       </c>
       <c r="U13">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V13">
         <v>1.34</v>
@@ -3893,7 +3893,7 @@
         <v>1.83</v>
       </c>
       <c r="X13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y13">
         <v>15</v>
@@ -3956,7 +3956,7 @@
         <v>14.5</v>
       </c>
       <c r="AS13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT13">
         <v>9</v>
@@ -3992,7 +3992,7 @@
         <v>30</v>
       </c>
       <c r="BE13">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF13">
         <v>13.5</v>
@@ -4093,10 +4093,10 @@
         <v>3.85</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L14">
         <v>1.27</v>
@@ -4105,25 +4105,25 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O14">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P14">
         <v>2.46</v>
       </c>
       <c r="Q14">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R14">
         <v>1.58</v>
       </c>
       <c r="S14">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T14">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U14">
         <v>2.54</v>
@@ -4135,10 +4135,10 @@
         <v>1.96</v>
       </c>
       <c r="X14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z14">
         <v>32</v>
@@ -4180,7 +4180,7 @@
         <v>28</v>
       </c>
       <c r="AM14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN14">
         <v>10.5</v>
@@ -4189,7 +4189,7 @@
         <v>29</v>
       </c>
       <c r="AP14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ14">
         <v>16.5</v>
@@ -4201,7 +4201,7 @@
         <v>55</v>
       </c>
       <c r="AT14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU14">
         <v>8.800000000000001</v>
@@ -4240,7 +4240,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4326,16 +4326,16 @@
         <v>5.1</v>
       </c>
       <c r="G15">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="H15">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="I15">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="J15">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -4374,7 +4374,7 @@
         <v>2.28</v>
       </c>
       <c r="W15">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4428,10 +4428,10 @@
         <v>1000</v>
       </c>
       <c r="AO15">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AP15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AQ15">
         <v>4.2</v>
@@ -4443,40 +4443,40 @@
         <v>6.2</v>
       </c>
       <c r="AT15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AU15">
         <v>6.2</v>
       </c>
       <c r="AV15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AW15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AX15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AY15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AZ15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BA15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BB15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BC15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BD15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BE15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BF15">
         <v>1.55</v>
@@ -4571,7 +4571,7 @@
         <v>1.97</v>
       </c>
       <c r="H16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I16">
         <v>5.5</v>
@@ -4580,7 +4580,7 @@
         <v>3.55</v>
       </c>
       <c r="K16">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4622,13 +4622,13 @@
         <v>1000</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB16">
         <v>970</v>
@@ -4637,7 +4637,7 @@
         <v>42</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AE16">
         <v>1000</v>
@@ -4649,7 +4649,7 @@
         <v>500</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AI16">
         <v>1000</v>
@@ -4664,61 +4664,61 @@
         <v>500</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN16">
         <v>60</v>
       </c>
       <c r="AO16">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AP16">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AQ16">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AR16">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AS16">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AT16">
         <v>5.1</v>
       </c>
       <c r="AU16">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AV16">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AW16">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AX16">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AY16">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AZ16">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="BA16">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="BB16">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="BC16">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="BD16">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="BE16">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="BF16">
         <v>3.4</v>
@@ -4807,7 +4807,7 @@
         <v>166</v>
       </c>
       <c r="F17">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G17">
         <v>3.6</v>
@@ -4825,19 +4825,19 @@
         <v>3.75</v>
       </c>
       <c r="L17">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M17">
         <v>1.06</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O17">
         <v>1.3</v>
       </c>
       <c r="P17">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q17">
         <v>1.9</v>
@@ -4855,7 +4855,7 @@
         <v>2.22</v>
       </c>
       <c r="V17">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W17">
         <v>1.38</v>
@@ -4864,7 +4864,7 @@
         <v>15.5</v>
       </c>
       <c r="Y17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z17">
         <v>15</v>
@@ -4888,7 +4888,7 @@
         <v>26</v>
       </c>
       <c r="AG17">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH17">
         <v>17</v>
@@ -4912,7 +4912,7 @@
         <v>38</v>
       </c>
       <c r="AO17">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP17">
         <v>13.5</v>
@@ -4951,16 +4951,16 @@
         <v>30</v>
       </c>
       <c r="BB17">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="BC17">
         <v>34</v>
       </c>
       <c r="BD17">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE17">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF17">
         <v>25</v>
@@ -5055,10 +5055,10 @@
         <v>4.3</v>
       </c>
       <c r="H18">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="I18">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -5067,7 +5067,7 @@
         <v>4.2</v>
       </c>
       <c r="L18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M18">
         <v>1.04</v>
@@ -5076,7 +5076,7 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P18">
         <v>2.38</v>
@@ -5139,7 +5139,7 @@
         <v>28</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AK18">
         <v>46</v>
@@ -5148,7 +5148,7 @@
         <v>55</v>
       </c>
       <c r="AM18">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="AN18">
         <v>38</v>
@@ -5205,7 +5205,7 @@
         <v>55</v>
       </c>
       <c r="BF18">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BG18">
         <v>9</v>
@@ -5217,22 +5217,22 @@
         <v>3.4</v>
       </c>
       <c r="BJ18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK18">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BN18">
         <v>9.199999999999999</v>
       </c>
       <c r="BO18">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BP18">
         <v>40</v>
@@ -5244,25 +5244,25 @@
         <v>48</v>
       </c>
       <c r="BS18">
+        <v>4.1</v>
+      </c>
+      <c r="BT18">
+        <v>5.6</v>
+      </c>
+      <c r="BU18">
         <v>4.2</v>
       </c>
-      <c r="BT18">
-        <v>5.9</v>
-      </c>
-      <c r="BU18">
-        <v>4.1</v>
-      </c>
       <c r="BV18">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BW18">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="BX18">
         <v>30</v>
       </c>
       <c r="BY18">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BZ18">
         <v>23</v>
@@ -5291,16 +5291,16 @@
         <v>168</v>
       </c>
       <c r="F19">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G19">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H19">
+        <v>4.5</v>
+      </c>
+      <c r="I19">
         <v>4.6</v>
-      </c>
-      <c r="I19">
-        <v>4.7</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -5330,7 +5330,7 @@
         <v>1.56</v>
       </c>
       <c r="S19">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T19">
         <v>1.67</v>
@@ -5342,16 +5342,16 @@
         <v>1.27</v>
       </c>
       <c r="W19">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X19">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y19">
         <v>21</v>
       </c>
       <c r="Z19">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA19">
         <v>95</v>
@@ -5363,7 +5363,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD19">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE19">
         <v>48</v>
@@ -5399,16 +5399,16 @@
         <v>40</v>
       </c>
       <c r="AP19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ19">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AR19">
         <v>32</v>
       </c>
       <c r="AS19">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AT19">
         <v>11</v>
@@ -5420,16 +5420,16 @@
         <v>17.5</v>
       </c>
       <c r="AW19">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX19">
         <v>12</v>
       </c>
       <c r="AY19">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA19">
         <v>44</v>
@@ -5438,7 +5438,7 @@
         <v>18.5</v>
       </c>
       <c r="BC19">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD19">
         <v>26</v>
@@ -5492,7 +5492,7 @@
         <v>9.6</v>
       </c>
       <c r="BU19">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV19">
         <v>40</v>
@@ -5542,7 +5542,7 @@
         <v>2.66</v>
       </c>
       <c r="I20">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J20">
         <v>3.7</v>
@@ -5581,7 +5581,7 @@
         <v>2.44</v>
       </c>
       <c r="V20">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W20">
         <v>1.54</v>
@@ -5605,7 +5605,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE20">
         <v>26</v>
@@ -5620,25 +5620,25 @@
         <v>15</v>
       </c>
       <c r="AI20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ20">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK20">
         <v>27</v>
       </c>
       <c r="AL20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM20">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO20">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP20">
         <v>17</v>
@@ -5665,19 +5665,19 @@
         <v>24</v>
       </c>
       <c r="AX20">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY20">
         <v>11.5</v>
       </c>
       <c r="AZ20">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB20">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC20">
         <v>26</v>
@@ -5689,7 +5689,7 @@
         <v>60</v>
       </c>
       <c r="BF20">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG20">
         <v>17</v>
@@ -5701,7 +5701,7 @@
         <v>3.15</v>
       </c>
       <c r="BJ20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK20">
         <v>6.8</v>
@@ -5710,49 +5710,49 @@
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BN20">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO20">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP20">
         <v>25</v>
       </c>
       <c r="BQ20">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BR20">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS20">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BT20">
         <v>6.4</v>
       </c>
       <c r="BU20">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BV20">
         <v>23</v>
       </c>
       <c r="BW20">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BX20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY20">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BZ20">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="CA20">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="CB20" t="s">
         <v>189</v>
@@ -5775,7 +5775,7 @@
         <v>170</v>
       </c>
       <c r="F21">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G21">
         <v>1.66</v>
@@ -5784,7 +5784,7 @@
         <v>5.4</v>
       </c>
       <c r="I21">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J21">
         <v>4.7</v>
@@ -5811,19 +5811,19 @@
         <v>1.41</v>
       </c>
       <c r="R21">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S21">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T21">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U21">
         <v>2.82</v>
       </c>
       <c r="V21">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W21">
         <v>2.5</v>
@@ -5847,13 +5847,13 @@
         <v>12.5</v>
       </c>
       <c r="AD21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE21">
         <v>55</v>
       </c>
       <c r="AF21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG21">
         <v>11</v>
@@ -5880,16 +5880,16 @@
         <v>5.1</v>
       </c>
       <c r="AO21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP21">
         <v>30</v>
       </c>
       <c r="AQ21">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AR21">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AS21">
         <v>17.5</v>
@@ -5901,10 +5901,10 @@
         <v>11</v>
       </c>
       <c r="AV21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW21">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AX21">
         <v>13</v>
@@ -5928,7 +5928,7 @@
         <v>19.5</v>
       </c>
       <c r="BE21">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF21">
         <v>4.9</v>
@@ -5940,7 +5940,7 @@
         <v>5.7</v>
       </c>
       <c r="BI21">
-        <v>4.4</v>
+        <v>2.82</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
@@ -6029,40 +6029,40 @@
         <v>2.7</v>
       </c>
       <c r="J22">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K22">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="L22">
         <v>1.58</v>
       </c>
       <c r="M22">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N22">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="P22">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
       </c>
       <c r="R22">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S22">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="T22">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="U22">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="V22">
         <v>1.59</v>
@@ -6071,37 +6071,37 @@
         <v>1.35</v>
       </c>
       <c r="X22">
-        <v>16.5</v>
+        <v>7.4</v>
       </c>
       <c r="Y22">
         <v>7.4</v>
       </c>
       <c r="Z22">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AA22">
         <v>900</v>
       </c>
       <c r="AB22">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AC22">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AD22">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AE22">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AF22">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AG22">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH22">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AI22">
         <v>500</v>
@@ -6119,124 +6119,124 @@
         <v>500</v>
       </c>
       <c r="AN22">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AO22">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP22">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ22">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AR22">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AS22">
-        <v>2.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT22">
         <v>8.4</v>
       </c>
       <c r="AU22">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV22">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW22">
-        <v>2.08</v>
+        <v>9.6</v>
       </c>
       <c r="AX22">
-        <v>2.24</v>
+        <v>20</v>
       </c>
       <c r="AY22">
-        <v>2.22</v>
+        <v>14.5</v>
       </c>
       <c r="AZ22">
-        <v>2.28</v>
+        <v>22</v>
       </c>
       <c r="BA22">
-        <v>2.08</v>
+        <v>10.5</v>
       </c>
       <c r="BB22">
-        <v>2.08</v>
+        <v>11</v>
       </c>
       <c r="BC22">
-        <v>2.08</v>
+        <v>10.5</v>
       </c>
       <c r="BD22">
-        <v>2.08</v>
+        <v>11</v>
       </c>
       <c r="BE22">
-        <v>2.28</v>
+        <v>12</v>
       </c>
       <c r="BF22">
-        <v>2.08</v>
+        <v>10</v>
       </c>
       <c r="BG22">
-        <v>2.08</v>
+        <v>10</v>
       </c>
       <c r="BH22">
         <v>2.68</v>
       </c>
       <c r="BI22">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ22">
         <v>17.5</v>
       </c>
       <c r="BK22">
+        <v>3.45</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>2.66</v>
+      </c>
+      <c r="BN22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO22">
+        <v>2.96</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
         <v>4</v>
       </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>5.2</v>
-      </c>
-      <c r="BN22">
-        <v>7.8</v>
-      </c>
-      <c r="BO22">
-        <v>5.3</v>
-      </c>
-      <c r="BP22">
-        <v>1000</v>
-      </c>
-      <c r="BQ22">
-        <v>4.8</v>
-      </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BT22">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="BV22">
         <v>34</v>
       </c>
       <c r="BW22">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="CB22" t="s">
         <v>189</v>
@@ -6259,226 +6259,226 @@
         <v>172</v>
       </c>
       <c r="F23">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="G23">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="H23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J23">
+        <v>4.5</v>
+      </c>
+      <c r="K23">
         <v>4.7</v>
       </c>
-      <c r="K23">
-        <v>5.1</v>
-      </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M23">
         <v>1.08</v>
       </c>
       <c r="N23">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O23">
         <v>1.38</v>
       </c>
       <c r="P23">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q23">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R23">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S23">
         <v>4</v>
       </c>
       <c r="T23">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="U23">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V23">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W23">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="X23">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="Y23">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z23">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA23">
-        <v>740</v>
+        <v>530</v>
       </c>
       <c r="AB23">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC23">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD23">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AE23">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="AF23">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AG23">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH23">
         <v>42</v>
       </c>
       <c r="AI23">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AJ23">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AK23">
         <v>23</v>
       </c>
       <c r="AL23">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM23">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AN23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO23">
-        <v>750</v>
+        <v>510</v>
       </c>
       <c r="AP23">
         <v>11</v>
       </c>
       <c r="AQ23">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR23">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AS23">
+        <v>9.4</v>
+      </c>
+      <c r="AT23">
+        <v>6</v>
+      </c>
+      <c r="AU23">
+        <v>9.6</v>
+      </c>
+      <c r="AV23">
+        <v>32</v>
+      </c>
+      <c r="AW23">
+        <v>11</v>
+      </c>
+      <c r="AX23">
         <v>6.8</v>
       </c>
-      <c r="AT23">
-        <v>5.6</v>
-      </c>
-      <c r="AU23">
-        <v>10</v>
-      </c>
-      <c r="AV23">
-        <v>36</v>
-      </c>
-      <c r="AW23">
-        <v>6.6</v>
-      </c>
-      <c r="AX23">
-        <v>6.4</v>
-      </c>
       <c r="AY23">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA23">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BB23">
         <v>10</v>
       </c>
       <c r="BC23">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD23">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE23">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF23">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG23">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
+        <v>1.44</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
         <v>1.01</v>
       </c>
-      <c r="BP23">
-        <v>1000</v>
-      </c>
-      <c r="BQ23">
-        <v>1.29</v>
-      </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="CB23" t="s">
         <v>189</v>
@@ -6516,7 +6516,7 @@
         <v>3.5</v>
       </c>
       <c r="K24">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6525,13 +6525,13 @@
         <v>1.07</v>
       </c>
       <c r="N24">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P24">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q24">
         <v>1.9</v>
@@ -6543,7 +6543,7 @@
         <v>3.2</v>
       </c>
       <c r="T24">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U24">
         <v>2.16</v>
@@ -6555,7 +6555,7 @@
         <v>1.79</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y24">
         <v>20</v>
@@ -6606,7 +6606,7 @@
         <v>22</v>
       </c>
       <c r="AO24">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP24">
         <v>2.8</v>
@@ -6615,7 +6615,7 @@
         <v>7.6</v>
       </c>
       <c r="AR24">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AS24">
         <v>2.72</v>
@@ -6633,7 +6633,7 @@
         <v>2.68</v>
       </c>
       <c r="AX24">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY24">
         <v>7</v>
@@ -6645,22 +6645,22 @@
         <v>2.7</v>
       </c>
       <c r="BB24">
-        <v>2.6</v>
+        <v>17</v>
       </c>
       <c r="BC24">
         <v>2.58</v>
       </c>
       <c r="BD24">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BE24">
         <v>2.76</v>
       </c>
       <c r="BF24">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="BG24">
-        <v>2.72</v>
+        <v>7.2</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6749,16 +6749,16 @@
         <v>1.52</v>
       </c>
       <c r="H25">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I25">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J25">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K25">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L25">
         <v>1.25</v>
@@ -6767,16 +6767,16 @@
         <v>1.03</v>
       </c>
       <c r="N25">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P25">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q25">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="R25">
         <v>1.7</v>
@@ -6785,7 +6785,7 @@
         <v>2.18</v>
       </c>
       <c r="T25">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="U25">
         <v>2.24</v>
@@ -6797,112 +6797,112 @@
         <v>2.92</v>
       </c>
       <c r="X25">
+        <v>36</v>
+      </c>
+      <c r="Y25">
         <v>80</v>
       </c>
-      <c r="Y25">
-        <v>55</v>
-      </c>
       <c r="Z25">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB25">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD25">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE25">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="AF25">
         <v>11</v>
       </c>
       <c r="AG25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI25">
         <v>260</v>
       </c>
       <c r="AJ25">
+        <v>14.5</v>
+      </c>
+      <c r="AK25">
         <v>15</v>
       </c>
-      <c r="AK25">
-        <v>18.5</v>
-      </c>
       <c r="AL25">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AM25">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AN25">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AO25">
         <v>85</v>
       </c>
       <c r="AP25">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="AQ25">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR25">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AS25">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AT25">
+        <v>10.5</v>
+      </c>
+      <c r="AU25">
+        <v>10.5</v>
+      </c>
+      <c r="AV25">
+        <v>7.8</v>
+      </c>
+      <c r="AW25">
+        <v>36</v>
+      </c>
+      <c r="AX25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY25">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU25">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV25">
-        <v>11.5</v>
-      </c>
-      <c r="AW25">
-        <v>29</v>
-      </c>
-      <c r="AX25">
-        <v>8.4</v>
-      </c>
-      <c r="AY25">
-        <v>8</v>
-      </c>
       <c r="AZ25">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA25">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BB25">
         <v>12</v>
       </c>
       <c r="BC25">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD25">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="BE25">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BF25">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG25">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6997,7 +6997,7 @@
         <v>3.7</v>
       </c>
       <c r="J26">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K26">
         <v>4.1</v>
@@ -7009,28 +7009,28 @@
         <v>1.04</v>
       </c>
       <c r="N26">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O26">
         <v>1.19</v>
       </c>
       <c r="P26">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="Q26">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R26">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="S26">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T26">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="U26">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="V26">
         <v>1.37</v>
@@ -7039,91 +7039,91 @@
         <v>1.87</v>
       </c>
       <c r="X26">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y26">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z26">
+        <v>34</v>
+      </c>
+      <c r="AA26">
+        <v>70</v>
+      </c>
+      <c r="AB26">
+        <v>15.5</v>
+      </c>
+      <c r="AC26">
+        <v>10</v>
+      </c>
+      <c r="AD26">
+        <v>15.5</v>
+      </c>
+      <c r="AE26">
         <v>36</v>
       </c>
-      <c r="AA26">
-        <v>500</v>
-      </c>
-      <c r="AB26">
-        <v>17</v>
-      </c>
-      <c r="AC26">
-        <v>11</v>
-      </c>
-      <c r="AD26">
-        <v>18.5</v>
-      </c>
-      <c r="AE26">
-        <v>85</v>
-      </c>
       <c r="AF26">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG26">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH26">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI26">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AJ26">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK26">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL26">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM26">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="AN26">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO26">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AP26">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ26">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR26">
         <v>22</v>
       </c>
       <c r="AS26">
-        <v>5.5</v>
+        <v>38</v>
       </c>
       <c r="AT26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU26">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV26">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW26">
         <v>25</v>
       </c>
       <c r="AX26">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY26">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA26">
         <v>26</v>
@@ -7132,19 +7132,19 @@
         <v>19</v>
       </c>
       <c r="BC26">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD26">
         <v>19</v>
       </c>
       <c r="BE26">
-        <v>5.4</v>
+        <v>38</v>
       </c>
       <c r="BF26">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG26">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BH26">
         <v>4.9</v>
@@ -7227,22 +7227,22 @@
         <v>176</v>
       </c>
       <c r="F27">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G27">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H27">
         <v>3.75</v>
       </c>
       <c r="I27">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J27">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K27">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L27">
         <v>1.36</v>
@@ -7257,31 +7257,31 @@
         <v>1.3</v>
       </c>
       <c r="P27">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q27">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S27">
         <v>3.2</v>
       </c>
       <c r="T27">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U27">
         <v>2.22</v>
       </c>
       <c r="V27">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X27">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y27">
         <v>15.5</v>
@@ -7290,7 +7290,7 @@
         <v>29</v>
       </c>
       <c r="AA27">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AB27">
         <v>10.5</v>
@@ -7299,10 +7299,10 @@
         <v>8.4</v>
       </c>
       <c r="AD27">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE27">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF27">
         <v>13.5</v>
@@ -7311,82 +7311,82 @@
         <v>11</v>
       </c>
       <c r="AH27">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI27">
         <v>55</v>
       </c>
       <c r="AJ27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK27">
         <v>22</v>
       </c>
       <c r="AL27">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM27">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN27">
         <v>15</v>
       </c>
       <c r="AO27">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP27">
         <v>14</v>
       </c>
       <c r="AQ27">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR27">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AS27">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AT27">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU27">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV27">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW27">
+        <v>38</v>
+      </c>
+      <c r="AX27">
+        <v>12</v>
+      </c>
+      <c r="AY27">
+        <v>9.6</v>
+      </c>
+      <c r="AZ27">
+        <v>15.5</v>
+      </c>
+      <c r="BA27">
+        <v>42</v>
+      </c>
+      <c r="BB27">
+        <v>23</v>
+      </c>
+      <c r="BC27">
+        <v>19</v>
+      </c>
+      <c r="BD27">
+        <v>30</v>
+      </c>
+      <c r="BE27">
         <v>36</v>
-      </c>
-      <c r="AX27">
-        <v>11.5</v>
-      </c>
-      <c r="AY27">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ27">
-        <v>15</v>
-      </c>
-      <c r="BA27">
-        <v>30</v>
-      </c>
-      <c r="BB27">
-        <v>20</v>
-      </c>
-      <c r="BC27">
-        <v>18.5</v>
-      </c>
-      <c r="BD27">
-        <v>26</v>
-      </c>
-      <c r="BE27">
-        <v>55</v>
       </c>
       <c r="BF27">
         <v>13</v>
       </c>
       <c r="BG27">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BH27">
         <v>4</v>
@@ -7395,58 +7395,58 @@
         <v>3</v>
       </c>
       <c r="BJ27">
+        <v>13.5</v>
+      </c>
+      <c r="BK27">
+        <v>7.2</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>4.6</v>
+      </c>
+      <c r="BN27">
+        <v>5.8</v>
+      </c>
+      <c r="BO27">
+        <v>4.2</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
         <v>11</v>
-      </c>
-      <c r="BK27">
-        <v>7</v>
-      </c>
-      <c r="BL27">
-        <v>1000</v>
-      </c>
-      <c r="BM27">
-        <v>4.8</v>
-      </c>
-      <c r="BN27">
-        <v>6</v>
-      </c>
-      <c r="BO27">
-        <v>4.1</v>
-      </c>
-      <c r="BP27">
-        <v>1000</v>
-      </c>
-      <c r="BQ27">
-        <v>10.5</v>
       </c>
       <c r="BR27">
         <v>40</v>
       </c>
       <c r="BS27">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BT27">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU27">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV27">
         <v>44</v>
       </c>
       <c r="BW27">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BX27">
         <v>55</v>
       </c>
       <c r="BY27">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BZ27">
         <v>32</v>
       </c>
       <c r="CA27">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="CB27" t="s">
         <v>189</v>
@@ -7499,7 +7499,7 @@
         <v>1.31</v>
       </c>
       <c r="P28">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q28">
         <v>1.93</v>
@@ -7523,7 +7523,7 @@
         <v>1.45</v>
       </c>
       <c r="X28">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y28">
         <v>11</v>
@@ -7565,16 +7565,16 @@
         <v>36</v>
       </c>
       <c r="AL28">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM28">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN28">
         <v>32</v>
       </c>
       <c r="AO28">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP28">
         <v>14.5</v>
@@ -7604,13 +7604,13 @@
         <v>20</v>
       </c>
       <c r="AY28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ28">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB28">
         <v>46</v>
@@ -7628,7 +7628,7 @@
         <v>20</v>
       </c>
       <c r="BG28">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH28">
         <v>3.85</v>
@@ -7711,7 +7711,7 @@
         <v>178</v>
       </c>
       <c r="F29">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G29">
         <v>2.3</v>
@@ -7738,7 +7738,7 @@
         <v>5.3</v>
       </c>
       <c r="O29">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P29">
         <v>2.44</v>
@@ -7750,13 +7750,13 @@
         <v>1.58</v>
       </c>
       <c r="S29">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="T29">
         <v>1.58</v>
       </c>
       <c r="U29">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V29">
         <v>1.42</v>
@@ -7768,10 +7768,10 @@
         <v>22</v>
       </c>
       <c r="Y29">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA29">
         <v>60</v>
@@ -7783,7 +7783,7 @@
         <v>9</v>
       </c>
       <c r="AD29">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE29">
         <v>32</v>
@@ -7798,7 +7798,7 @@
         <v>15</v>
       </c>
       <c r="AI29">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ29">
         <v>29</v>
@@ -7822,7 +7822,7 @@
         <v>19.5</v>
       </c>
       <c r="AQ29">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR29">
         <v>23</v>
@@ -7831,7 +7831,7 @@
         <v>48</v>
       </c>
       <c r="AT29">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU29">
         <v>8.4</v>
@@ -7843,7 +7843,7 @@
         <v>29</v>
       </c>
       <c r="AX29">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY29">
         <v>10</v>
@@ -7858,7 +7858,7 @@
         <v>27</v>
       </c>
       <c r="BC29">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD29">
         <v>26</v>
@@ -7953,46 +7953,46 @@
         <v>179</v>
       </c>
       <c r="F30">
+        <v>1.94</v>
+      </c>
+      <c r="G30">
         <v>1.95</v>
-      </c>
-      <c r="G30">
-        <v>1.97</v>
       </c>
       <c r="H30">
         <v>4.2</v>
       </c>
       <c r="I30">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J30">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K30">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L30">
         <v>1.35</v>
       </c>
       <c r="M30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N30">
         <v>4.6</v>
       </c>
       <c r="O30">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P30">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q30">
         <v>1.79</v>
       </c>
       <c r="R30">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S30">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="T30">
         <v>1.73</v>
@@ -8001,49 +8001,49 @@
         <v>2.3</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W30">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X30">
         <v>18.5</v>
       </c>
       <c r="Y30">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z30">
         <v>34</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC30">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD30">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE30">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF30">
         <v>13</v>
       </c>
       <c r="AG30">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH30">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI30">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ30">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK30">
         <v>18.5</v>
@@ -8052,25 +8052,25 @@
         <v>32</v>
       </c>
       <c r="AM30">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AN30">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO30">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP30">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ30">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR30">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AS30">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AT30">
         <v>10</v>
@@ -8079,34 +8079,34 @@
         <v>8</v>
       </c>
       <c r="AV30">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW30">
         <v>42</v>
       </c>
       <c r="AX30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY30">
         <v>9.4</v>
       </c>
       <c r="AZ30">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA30">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BB30">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BC30">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD30">
         <v>28</v>
       </c>
       <c r="BE30">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF30">
         <v>10.5</v>
@@ -8207,7 +8207,7 @@
         <v>3.8</v>
       </c>
       <c r="J31">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K31">
         <v>3.65</v>
@@ -8228,7 +8228,7 @@
         <v>2</v>
       </c>
       <c r="Q31">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R31">
         <v>1.38</v>
@@ -8240,7 +8240,7 @@
         <v>1.79</v>
       </c>
       <c r="U31">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V31">
         <v>1.35</v>
@@ -8252,7 +8252,7 @@
         <v>14.5</v>
       </c>
       <c r="Y31">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z31">
         <v>27</v>
@@ -8267,13 +8267,13 @@
         <v>8</v>
       </c>
       <c r="AD31">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE31">
         <v>44</v>
       </c>
       <c r="AF31">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG31">
         <v>11</v>
@@ -8288,7 +8288,7 @@
         <v>27</v>
       </c>
       <c r="AK31">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL31">
         <v>38</v>
@@ -8333,13 +8333,13 @@
         <v>10</v>
       </c>
       <c r="AZ31">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA31">
         <v>46</v>
       </c>
       <c r="BB31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC31">
         <v>20</v>
@@ -8351,7 +8351,7 @@
         <v>50</v>
       </c>
       <c r="BF31">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG31">
         <v>32</v>
@@ -8443,7 +8443,7 @@
         <v>5.7</v>
       </c>
       <c r="H32">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I32">
         <v>1.69</v>
@@ -8509,7 +8509,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD32">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE32">
         <v>15</v>
@@ -8527,7 +8527,7 @@
         <v>27</v>
       </c>
       <c r="AJ32">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AK32">
         <v>65</v>
@@ -8536,7 +8536,7 @@
         <v>60</v>
       </c>
       <c r="AM32">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN32">
         <v>55</v>
@@ -8554,13 +8554,13 @@
         <v>11</v>
       </c>
       <c r="AS32">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT32">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU32">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV32">
         <v>9.4</v>
@@ -8569,7 +8569,7 @@
         <v>14.5</v>
       </c>
       <c r="AX32">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AY32">
         <v>19.5</v>
@@ -8578,13 +8578,13 @@
         <v>16.5</v>
       </c>
       <c r="BA32">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB32">
         <v>40</v>
       </c>
       <c r="BC32">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BD32">
         <v>50</v>
@@ -8706,19 +8706,19 @@
         <v>6.6</v>
       </c>
       <c r="O33">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P33">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q33">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R33">
         <v>1.77</v>
       </c>
       <c r="S33">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T33">
         <v>1.53</v>
@@ -8739,10 +8739,10 @@
         <v>26</v>
       </c>
       <c r="Z33">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA33">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB33">
         <v>15</v>
@@ -8754,7 +8754,7 @@
         <v>18</v>
       </c>
       <c r="AE33">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF33">
         <v>15.5</v>
@@ -8775,13 +8775,13 @@
         <v>16.5</v>
       </c>
       <c r="AL33">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM33">
         <v>55</v>
       </c>
       <c r="AN33">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO33">
         <v>28</v>
@@ -8790,10 +8790,10 @@
         <v>26</v>
       </c>
       <c r="AQ33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR33">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS33">
         <v>65</v>
@@ -8805,7 +8805,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV33">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW33">
         <v>38</v>
@@ -8826,19 +8826,19 @@
         <v>19.5</v>
       </c>
       <c r="BC33">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD33">
         <v>22</v>
       </c>
       <c r="BE33">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF33">
         <v>6.6</v>
       </c>
       <c r="BG33">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH33">
         <v>15.5</v>
@@ -8921,16 +8921,16 @@
         <v>183</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G34">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H34">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I34">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="J34">
         <v>4.2</v>
@@ -8951,22 +8951,22 @@
         <v>1.24</v>
       </c>
       <c r="P34">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q34">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R34">
         <v>1.52</v>
       </c>
       <c r="S34">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T34">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U34">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V34">
         <v>2.3</v>
@@ -8990,7 +8990,7 @@
         <v>21</v>
       </c>
       <c r="AC34">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD34">
         <v>9.800000000000001</v>
@@ -9002,19 +9002,19 @@
         <v>40</v>
       </c>
       <c r="AG34">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH34">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI34">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ34">
         <v>120</v>
       </c>
       <c r="AK34">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL34">
         <v>60</v>
@@ -9023,13 +9023,13 @@
         <v>80</v>
       </c>
       <c r="AN34">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO34">
         <v>8.800000000000001</v>
       </c>
       <c r="AP34">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ34">
         <v>10</v>
@@ -9041,19 +9041,19 @@
         <v>17</v>
       </c>
       <c r="AT34">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AU34">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV34">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW34">
         <v>15.5</v>
       </c>
       <c r="AX34">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY34">
         <v>18.5</v>
@@ -9065,10 +9065,10 @@
         <v>27</v>
       </c>
       <c r="BB34">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BC34">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BD34">
         <v>50</v>
@@ -9080,67 +9080,67 @@
         <v>48</v>
       </c>
       <c r="BG34">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH34">
         <v>1000</v>
       </c>
       <c r="BI34">
+        <v>1.62</v>
+      </c>
+      <c r="BJ34">
+        <v>1000</v>
+      </c>
+      <c r="BK34">
         <v>2.14</v>
       </c>
-      <c r="BJ34">
-        <v>13</v>
-      </c>
-      <c r="BK34">
-        <v>7.2</v>
-      </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="BN34">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BO34">
-        <v>6.4</v>
+        <v>2.08</v>
       </c>
       <c r="BP34">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="BT34">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU34">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV34">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BW34">
-        <v>8.4</v>
+        <v>2.56</v>
       </c>
       <c r="BX34">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY34">
-        <v>3.45</v>
+        <v>1.6</v>
       </c>
       <c r="BZ34">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA34">
-        <v>3.35</v>
+        <v>1.6</v>
       </c>
       <c r="CB34" t="s">
         <v>189</v>
@@ -9163,10 +9163,10 @@
         <v>184</v>
       </c>
       <c r="F35">
+        <v>2.3</v>
+      </c>
+      <c r="G35">
         <v>2.32</v>
-      </c>
-      <c r="G35">
-        <v>2.34</v>
       </c>
       <c r="H35">
         <v>3.45</v>
@@ -9178,7 +9178,7 @@
         <v>3.55</v>
       </c>
       <c r="K35">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L35">
         <v>1.39</v>
@@ -9193,19 +9193,19 @@
         <v>1.29</v>
       </c>
       <c r="P35">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q35">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R35">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S35">
         <v>3.25</v>
       </c>
       <c r="T35">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U35">
         <v>2.3</v>
@@ -9214,7 +9214,7 @@
         <v>1.4</v>
       </c>
       <c r="W35">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X35">
         <v>15</v>
@@ -9226,13 +9226,13 @@
         <v>24</v>
       </c>
       <c r="AA35">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB35">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC35">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD35">
         <v>15</v>
@@ -9310,7 +9310,7 @@
         <v>27</v>
       </c>
       <c r="BC35">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD35">
         <v>32</v>
@@ -9319,70 +9319,70 @@
         <v>65</v>
       </c>
       <c r="BF35">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG35">
         <v>30</v>
       </c>
       <c r="BH35">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BI35">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BJ35">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BK35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BL35">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM35">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="BN35">
+        <v>5.2</v>
+      </c>
+      <c r="BO35">
+        <v>4.8</v>
+      </c>
+      <c r="BP35">
+        <v>16.5</v>
+      </c>
+      <c r="BQ35">
+        <v>14</v>
+      </c>
+      <c r="BR35">
+        <v>28</v>
+      </c>
+      <c r="BS35">
+        <v>11.5</v>
+      </c>
+      <c r="BT35">
+        <v>6.6</v>
+      </c>
+      <c r="BU35">
         <v>6</v>
       </c>
-      <c r="BO35">
-        <v>4.1</v>
-      </c>
-      <c r="BP35">
-        <v>20</v>
-      </c>
-      <c r="BQ35">
-        <v>12</v>
-      </c>
-      <c r="BR35">
-        <v>34</v>
-      </c>
-      <c r="BS35">
-        <v>4.7</v>
-      </c>
-      <c r="BT35">
-        <v>7.8</v>
-      </c>
-      <c r="BU35">
-        <v>5.1</v>
-      </c>
       <c r="BV35">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BW35">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BX35">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BY35">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="BZ35">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="CA35">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="CB35" t="s">
         <v>189</v>
@@ -9405,16 +9405,16 @@
         <v>185</v>
       </c>
       <c r="F36">
+        <v>1.66</v>
+      </c>
+      <c r="G36">
         <v>1.68</v>
       </c>
-      <c r="G36">
-        <v>1.7</v>
-      </c>
       <c r="H36">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I36">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J36">
         <v>4.6</v>
@@ -9423,7 +9423,7 @@
         <v>4.7</v>
       </c>
       <c r="L36">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M36">
         <v>1.03</v>
@@ -9453,10 +9453,10 @@
         <v>2.72</v>
       </c>
       <c r="V36">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W36">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X36">
         <v>32</v>
@@ -9489,13 +9489,13 @@
         <v>10</v>
       </c>
       <c r="AH36">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI36">
         <v>46</v>
       </c>
       <c r="AJ36">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK36">
         <v>14</v>
@@ -9510,7 +9510,7 @@
         <v>5.9</v>
       </c>
       <c r="AO36">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP36">
         <v>30</v>
@@ -9522,7 +9522,7 @@
         <v>46</v>
       </c>
       <c r="AS36">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AT36">
         <v>14</v>
@@ -9531,10 +9531,10 @@
         <v>10.5</v>
       </c>
       <c r="AV36">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW36">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX36">
         <v>12.5</v>
@@ -9546,7 +9546,7 @@
         <v>15</v>
       </c>
       <c r="BA36">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB36">
         <v>17</v>
@@ -9567,64 +9567,64 @@
         <v>34</v>
       </c>
       <c r="BH36">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI36">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BJ36">
+        <v>9</v>
+      </c>
+      <c r="BK36">
+        <v>8</v>
+      </c>
+      <c r="BL36">
+        <v>70</v>
+      </c>
+      <c r="BM36">
+        <v>15.5</v>
+      </c>
+      <c r="BN36">
+        <v>4.8</v>
+      </c>
+      <c r="BO36">
+        <v>4.4</v>
+      </c>
+      <c r="BP36">
         <v>10</v>
       </c>
-      <c r="BK36">
-        <v>4.8</v>
-      </c>
-      <c r="BL36">
-        <v>1000</v>
-      </c>
-      <c r="BM36">
-        <v>6.2</v>
-      </c>
-      <c r="BN36">
-        <v>5.4</v>
-      </c>
-      <c r="BO36">
-        <v>3.9</v>
-      </c>
-      <c r="BP36">
-        <v>11.5</v>
-      </c>
       <c r="BQ36">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR36">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BS36">
         <v>13.5</v>
       </c>
       <c r="BT36">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BU36">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV36">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BW36">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BX36">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BY36">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BZ36">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="CA36">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="CB36" t="s">
         <v>189</v>
@@ -9647,166 +9647,166 @@
         <v>186</v>
       </c>
       <c r="F37">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="G37">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="H37">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="I37">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J37">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="K37">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="L37">
         <v>1.01</v>
       </c>
       <c r="M37">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N37">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O37">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P37">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="Q37">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="R37">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S37">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="T37">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U37">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V37">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="W37">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="X37">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="Y37">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Z37">
         <v>75</v>
       </c>
       <c r="AA37">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AB37">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC37">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AD37">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE37">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AF37">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AG37">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AH37">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AI37">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AJ37">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK37">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AL37">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM37">
         <v>500</v>
       </c>
       <c r="AN37">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AO37">
         <v>500</v>
       </c>
       <c r="AP37">
-        <v>2.44</v>
+        <v>9</v>
       </c>
       <c r="AQ37">
-        <v>2.12</v>
+        <v>9.4</v>
       </c>
       <c r="AR37">
-        <v>2.3</v>
+        <v>19.5</v>
       </c>
       <c r="AS37">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="AT37">
-        <v>2.04</v>
+        <v>7.4</v>
       </c>
       <c r="AU37">
-        <v>1.97</v>
+        <v>6.2</v>
       </c>
       <c r="AV37">
-        <v>2.2</v>
+        <v>12.5</v>
       </c>
       <c r="AW37">
-        <v>2.38</v>
+        <v>5.9</v>
       </c>
       <c r="AX37">
-        <v>2.18</v>
+        <v>12</v>
       </c>
       <c r="AY37">
-        <v>2.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ37">
-        <v>2.26</v>
+        <v>16.5</v>
       </c>
       <c r="BA37">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="BB37">
-        <v>2.34</v>
+        <v>5.5</v>
       </c>
       <c r="BC37">
-        <v>2.32</v>
+        <v>5.4</v>
       </c>
       <c r="BD37">
-        <v>2.38</v>
+        <v>40</v>
       </c>
       <c r="BE37">
-        <v>2.44</v>
+        <v>6.2</v>
       </c>
       <c r="BF37">
-        <v>2.32</v>
+        <v>5.4</v>
       </c>
       <c r="BG37">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -9889,7 +9889,7 @@
         <v>187</v>
       </c>
       <c r="F38">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G38">
         <v>1.59</v>
@@ -9898,7 +9898,7 @@
         <v>8</v>
       </c>
       <c r="I38">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J38">
         <v>3.95</v>
@@ -9913,28 +9913,28 @@
         <v>1.11</v>
       </c>
       <c r="N38">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O38">
         <v>1.51</v>
       </c>
       <c r="P38">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q38">
         <v>2.56</v>
       </c>
       <c r="R38">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S38">
         <v>5.1</v>
       </c>
       <c r="T38">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U38">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V38">
         <v>1.12</v>
@@ -9943,7 +9943,7 @@
         <v>2.68</v>
       </c>
       <c r="X38">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y38">
         <v>18.5</v>
@@ -9970,7 +9970,7 @@
         <v>7.4</v>
       </c>
       <c r="AG38">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH38">
         <v>44</v>
@@ -9982,7 +9982,7 @@
         <v>14.5</v>
       </c>
       <c r="AK38">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL38">
         <v>160</v>
@@ -10000,13 +10000,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ38">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR38">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS38">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT38">
         <v>5.1</v>
@@ -10015,10 +10015,10 @@
         <v>8.6</v>
       </c>
       <c r="AV38">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AW38">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AX38">
         <v>6.6</v>
@@ -10030,25 +10030,25 @@
         <v>30</v>
       </c>
       <c r="BA38">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BB38">
         <v>12</v>
       </c>
       <c r="BC38">
-        <v>18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD38">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BE38">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF38">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG38">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10069,16 +10069,16 @@
         <v>21</v>
       </c>
       <c r="BN38">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO38">
         <v>3.2</v>
       </c>
       <c r="BP38">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BR38">
         <v>1000</v>
@@ -10087,10 +10087,10 @@
         <v>21</v>
       </c>
       <c r="BT38">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BU38">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BV38">
         <v>1000</v>
@@ -10105,10 +10105,10 @@
         <v>21</v>
       </c>
       <c r="BZ38">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CA38">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="CB38" t="s">
         <v>189</v>
@@ -10131,7 +10131,7 @@
         <v>188</v>
       </c>
       <c r="F39">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G39">
         <v>1.99</v>
@@ -10155,13 +10155,13 @@
         <v>1.13</v>
       </c>
       <c r="N39">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O39">
         <v>1.56</v>
       </c>
       <c r="P39">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q39">
         <v>2.7</v>
@@ -10170,7 +10170,7 @@
         <v>1.19</v>
       </c>
       <c r="S39">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T39">
         <v>2.28</v>
@@ -10188,13 +10188,13 @@
         <v>8.6</v>
       </c>
       <c r="Y39">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z39">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA39">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB39">
         <v>6.4</v>
@@ -10203,7 +10203,7 @@
         <v>7.8</v>
       </c>
       <c r="AD39">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE39">
         <v>130</v>
@@ -10233,10 +10233,10 @@
         <v>300</v>
       </c>
       <c r="AN39">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO39">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP39">
         <v>7.6</v>
@@ -10245,10 +10245,10 @@
         <v>11</v>
       </c>
       <c r="AR39">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS39">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT39">
         <v>5.7</v>
@@ -10260,7 +10260,7 @@
         <v>19.5</v>
       </c>
       <c r="AW39">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX39">
         <v>9</v>
@@ -10269,88 +10269,88 @@
         <v>10</v>
       </c>
       <c r="AZ39">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="BA39">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB39">
         <v>20</v>
       </c>
       <c r="BC39">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="BD39">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE39">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF39">
         <v>17.5</v>
       </c>
       <c r="BG39">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH39">
         <v>1000</v>
       </c>
       <c r="BI39">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="BJ39">
         <v>18</v>
       </c>
       <c r="BK39">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="BN39">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BO39">
-        <v>3.65</v>
+        <v>2.38</v>
       </c>
       <c r="BP39">
         <v>23</v>
       </c>
       <c r="BQ39">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BR39">
         <v>1000</v>
       </c>
       <c r="BS39">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BT39">
         <v>12.5</v>
       </c>
       <c r="BU39">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV39">
         <v>1000</v>
       </c>
       <c r="BW39">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BX39">
         <v>1000</v>
       </c>
       <c r="BY39">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="BZ39">
         <v>1000</v>
       </c>
       <c r="CA39">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CB39" t="s">
         <v>189</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -547,7 +547,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-09-07 23:44:51</t>
+    <t>2026-09-08 01:56:41</t>
   </si>
 </sst>
 </file>
@@ -1141,16 +1141,16 @@
         <v>143</v>
       </c>
       <c r="F2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J2">
         <v>3.75</v>
@@ -1165,31 +1165,31 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O2">
         <v>1.23</v>
       </c>
       <c r="P2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q2">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S2">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U2">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V2">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W2">
         <v>1.36</v>
@@ -1198,52 +1198,52 @@
         <v>21</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
         <v>11</v>
       </c>
       <c r="AE2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI2">
         <v>30</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK2">
         <v>38</v>
       </c>
       <c r="AL2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO2">
         <v>11.5</v>
@@ -1255,13 +1255,13 @@
         <v>11.5</v>
       </c>
       <c r="AR2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU2">
         <v>8</v>
@@ -1270,7 +1270,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX2">
         <v>25</v>
@@ -1282,7 +1282,7 @@
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB2">
         <v>46</v>
@@ -1291,10 +1291,10 @@
         <v>32</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BF2">
         <v>25</v>
@@ -1303,10 +1303,10 @@
         <v>10.5</v>
       </c>
       <c r="BH2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ2">
         <v>8.800000000000001</v>
@@ -1315,7 +1315,7 @@
         <v>7.8</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM2">
         <v>15.5</v>
@@ -1324,13 +1324,13 @@
         <v>7</v>
       </c>
       <c r="BO2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BP2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR2">
         <v>32</v>
@@ -1339,13 +1339,13 @@
         <v>12</v>
       </c>
       <c r="BT2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU2">
         <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW2">
         <v>8.199999999999999</v>
@@ -1357,10 +1357,10 @@
         <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="s">
         <v>177</v>
@@ -1383,7 +1383,7 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G3">
         <v>1.91</v>
@@ -1392,40 +1392,40 @@
         <v>4.9</v>
       </c>
       <c r="I3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
         <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P3">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U3">
         <v>1.89</v>
@@ -1443,22 +1443,22 @@
         <v>15</v>
       </c>
       <c r="Z3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC3">
         <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF3">
         <v>10.5</v>
@@ -1476,19 +1476,19 @@
         <v>21</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP3">
         <v>10.5</v>
@@ -1503,7 +1503,7 @@
         <v>90</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
         <v>7.4</v>
@@ -1512,7 +1512,7 @@
         <v>18</v>
       </c>
       <c r="AW3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AX3">
         <v>9.4</v>
@@ -1521,10 +1521,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB3">
         <v>18</v>
@@ -1536,16 +1536,16 @@
         <v>36</v>
       </c>
       <c r="BE3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BF3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG3">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BH3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI3">
         <v>2.84</v>
@@ -1560,49 +1560,49 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BN3">
         <v>4.3</v>
       </c>
       <c r="BO3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ3">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BR3">
         <v>32</v>
       </c>
       <c r="BS3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BZ3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1625,22 +1625,22 @@
         <v>145</v>
       </c>
       <c r="F4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G4">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="H4">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="I4">
         <v>1.69</v>
       </c>
       <c r="J4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L4">
         <v>1.32</v>
@@ -1649,34 +1649,34 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q4">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R4">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S4">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T4">
         <v>1.73</v>
       </c>
       <c r="U4">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X4">
         <v>26</v>
@@ -1685,7 +1685,7 @@
         <v>11</v>
       </c>
       <c r="Z4">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AA4">
         <v>21</v>
@@ -1700,7 +1700,7 @@
         <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF4">
         <v>60</v>
@@ -1712,28 +1712,28 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ4">
         <v>160</v>
       </c>
       <c r="AK4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AL4">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AM4">
         <v>110</v>
       </c>
       <c r="AN4">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AO4">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AP4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
         <v>9.4</v>
@@ -1745,10 +1745,10 @@
         <v>14.5</v>
       </c>
       <c r="AT4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV4">
         <v>9</v>
@@ -1757,43 +1757,43 @@
         <v>14</v>
       </c>
       <c r="AX4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AY4">
+        <v>18</v>
+      </c>
+      <c r="AZ4">
         <v>16.5</v>
       </c>
-      <c r="AZ4">
-        <v>16</v>
-      </c>
       <c r="BA4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB4">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC4">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BD4">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BE4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH4">
         <v>4.8</v>
       </c>
       <c r="BI4">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
         <v>7.2</v>
@@ -1802,10 +1802,10 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BN4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BO4">
         <v>7</v>
@@ -1814,13 +1814,13 @@
         <v>55</v>
       </c>
       <c r="BQ4">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BT4">
         <v>4.5</v>
@@ -1832,19 +1832,19 @@
         <v>10.5</v>
       </c>
       <c r="BW4">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BX4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY4">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BZ4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA4">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1867,226 +1867,226 @@
         <v>146</v>
       </c>
       <c r="F5">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="G5">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M5">
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P5">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="Q5">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R5">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="S5">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="T5">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="U5">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V5">
         <v>1.15</v>
       </c>
       <c r="W5">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="X5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AA5">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AB5">
+        <v>14</v>
+      </c>
+      <c r="AC5">
+        <v>12</v>
+      </c>
+      <c r="AD5">
+        <v>30</v>
+      </c>
+      <c r="AE5">
+        <v>100</v>
+      </c>
+      <c r="AF5">
+        <v>12</v>
+      </c>
+      <c r="AG5">
+        <v>11.5</v>
+      </c>
+      <c r="AH5">
+        <v>18.5</v>
+      </c>
+      <c r="AI5">
+        <v>80</v>
+      </c>
+      <c r="AJ5">
         <v>14.5</v>
       </c>
-      <c r="AC5">
-        <v>12.5</v>
-      </c>
-      <c r="AD5">
-        <v>25</v>
-      </c>
-      <c r="AE5">
-        <v>80</v>
-      </c>
-      <c r="AF5">
-        <v>13</v>
-      </c>
-      <c r="AG5">
-        <v>12</v>
-      </c>
-      <c r="AH5">
-        <v>19.5</v>
-      </c>
-      <c r="AI5">
-        <v>65</v>
-      </c>
-      <c r="AJ5">
-        <v>15.5</v>
-      </c>
       <c r="AK5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM5">
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AO5">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP5">
         <v>25</v>
       </c>
       <c r="AQ5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AR5">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AS5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AT5">
+        <v>11.5</v>
+      </c>
+      <c r="AU5">
+        <v>10</v>
+      </c>
+      <c r="AV5">
+        <v>22</v>
+      </c>
+      <c r="AW5">
+        <v>55</v>
+      </c>
+      <c r="AX5">
+        <v>10</v>
+      </c>
+      <c r="AY5">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5">
+        <v>15</v>
+      </c>
+      <c r="BA5">
+        <v>38</v>
+      </c>
+      <c r="BB5">
         <v>12</v>
       </c>
-      <c r="AU5">
-        <v>10.5</v>
-      </c>
-      <c r="AV5">
-        <v>20</v>
-      </c>
-      <c r="AW5">
-        <v>48</v>
-      </c>
-      <c r="AX5">
-        <v>10.5</v>
-      </c>
-      <c r="AY5">
-        <v>9.6</v>
-      </c>
-      <c r="AZ5">
-        <v>15.5</v>
-      </c>
-      <c r="BA5">
-        <v>42</v>
-      </c>
-      <c r="BB5">
-        <v>12.5</v>
-      </c>
       <c r="BC5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE5">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="BF5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BH5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BI5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BJ5">
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="BL5">
         <v>95</v>
       </c>
       <c r="BM5">
+        <v>6.8</v>
+      </c>
+      <c r="BN5">
+        <v>4.7</v>
+      </c>
+      <c r="BO5">
+        <v>3.95</v>
+      </c>
+      <c r="BP5">
+        <v>9</v>
+      </c>
+      <c r="BQ5">
+        <v>4</v>
+      </c>
+      <c r="BR5">
+        <v>19.5</v>
+      </c>
+      <c r="BS5">
         <v>5.3</v>
       </c>
-      <c r="BN5">
-        <v>5.1</v>
-      </c>
-      <c r="BO5">
-        <v>4</v>
-      </c>
-      <c r="BP5">
-        <v>10.5</v>
-      </c>
-      <c r="BQ5">
-        <v>3.65</v>
-      </c>
-      <c r="BR5">
-        <v>22</v>
-      </c>
-      <c r="BS5">
-        <v>4.4</v>
-      </c>
       <c r="BT5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BU5">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV5">
         <v>55</v>
       </c>
       <c r="BW5">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BX5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY5">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BZ5">
         <v>12.5</v>
       </c>
       <c r="CA5">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="CB5" t="s">
         <v>177</v>
@@ -2115,49 +2115,49 @@
         <v>2.56</v>
       </c>
       <c r="H6">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
         <v>3.8</v>
       </c>
       <c r="L6">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O6">
         <v>1.27</v>
       </c>
       <c r="P6">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q6">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R6">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S6">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T6">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="U6">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
         <v>1.64</v>
@@ -2166,82 +2166,82 @@
         <v>17</v>
       </c>
       <c r="Y6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA6">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AB6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC6">
         <v>8.4</v>
       </c>
       <c r="AD6">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF6">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG6">
         <v>12</v>
       </c>
       <c r="AH6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI6">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM6">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN6">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AO6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AP6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ6">
         <v>12.5</v>
       </c>
       <c r="AR6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY6">
         <v>10.5</v>
@@ -2253,82 +2253,82 @@
         <v>34</v>
       </c>
       <c r="BB6">
+        <v>32</v>
+      </c>
+      <c r="BC6">
+        <v>22</v>
+      </c>
+      <c r="BD6">
+        <v>30</v>
+      </c>
+      <c r="BE6">
+        <v>60</v>
+      </c>
+      <c r="BF6">
+        <v>16</v>
+      </c>
+      <c r="BG6">
+        <v>18.5</v>
+      </c>
+      <c r="BH6">
+        <v>3.85</v>
+      </c>
+      <c r="BI6">
+        <v>3.5</v>
+      </c>
+      <c r="BJ6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK6">
+        <v>7.8</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>14.5</v>
+      </c>
+      <c r="BN6">
+        <v>5.6</v>
+      </c>
+      <c r="BO6">
+        <v>5.1</v>
+      </c>
+      <c r="BP6">
+        <v>18</v>
+      </c>
+      <c r="BQ6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR6">
         <v>28</v>
       </c>
-      <c r="BC6">
+      <c r="BS6">
+        <v>10.5</v>
+      </c>
+      <c r="BT6">
+        <v>6.2</v>
+      </c>
+      <c r="BU6">
+        <v>5.6</v>
+      </c>
+      <c r="BV6">
         <v>21</v>
       </c>
-      <c r="BD6">
-        <v>27</v>
-      </c>
-      <c r="BE6">
-        <v>9.4</v>
-      </c>
-      <c r="BF6">
+      <c r="BW6">
+        <v>9.6</v>
+      </c>
+      <c r="BX6">
+        <v>30</v>
+      </c>
+      <c r="BY6">
         <v>11</v>
       </c>
-      <c r="BG6">
-        <v>17.5</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>2.18</v>
-      </c>
-      <c r="BJ6">
-        <v>10.5</v>
-      </c>
-      <c r="BK6">
-        <v>7</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>2.14</v>
-      </c>
-      <c r="BN6">
-        <v>6.6</v>
-      </c>
-      <c r="BO6">
-        <v>4.4</v>
-      </c>
-      <c r="BP6">
-        <v>26</v>
-      </c>
-      <c r="BQ6">
-        <v>3.8</v>
-      </c>
-      <c r="BR6">
-        <v>40</v>
-      </c>
-      <c r="BS6">
-        <v>2.04</v>
-      </c>
-      <c r="BT6">
-        <v>7.4</v>
-      </c>
-      <c r="BU6">
-        <v>5</v>
-      </c>
-      <c r="BV6">
-        <v>30</v>
-      </c>
-      <c r="BW6">
-        <v>3.85</v>
-      </c>
-      <c r="BX6">
-        <v>46</v>
-      </c>
-      <c r="BY6">
-        <v>2.04</v>
-      </c>
       <c r="BZ6">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="CA6">
-        <v>3.85</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="s">
         <v>177</v>
@@ -2357,46 +2357,46 @@
         <v>2.2</v>
       </c>
       <c r="H7">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J7">
         <v>3.5</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O7">
         <v>1.35</v>
       </c>
       <c r="P7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
         <v>1.34</v>
@@ -2417,25 +2417,25 @@
         <v>85</v>
       </c>
       <c r="AB7">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI7">
         <v>65</v>
@@ -2444,43 +2444,43 @@
         <v>29</v>
       </c>
       <c r="AK7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL7">
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO7">
         <v>55</v>
       </c>
       <c r="AP7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR7">
         <v>21</v>
       </c>
       <c r="AS7">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="AT7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AX7">
         <v>11.5</v>
@@ -2489,13 +2489,13 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA7">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BB7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC7">
         <v>20</v>
@@ -2504,16 +2504,16 @@
         <v>30</v>
       </c>
       <c r="BE7">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="BF7">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI7">
         <v>3.1</v>
@@ -2522,31 +2522,31 @@
         <v>9.6</v>
       </c>
       <c r="BK7">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ7">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BR7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT7">
         <v>7</v>
@@ -2558,19 +2558,19 @@
         <v>32</v>
       </c>
       <c r="BW7">
+        <v>11</v>
+      </c>
+      <c r="BX7">
+        <v>44</v>
+      </c>
+      <c r="BY7">
+        <v>12</v>
+      </c>
+      <c r="BZ7">
+        <v>27</v>
+      </c>
+      <c r="CA7">
         <v>10.5</v>
-      </c>
-      <c r="BX7">
-        <v>42</v>
-      </c>
-      <c r="BY7">
-        <v>11.5</v>
-      </c>
-      <c r="BZ7">
-        <v>26</v>
-      </c>
-      <c r="CA7">
-        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="s">
         <v>177</v>
@@ -2593,25 +2593,25 @@
         <v>149</v>
       </c>
       <c r="F8">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G8">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H8">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I8">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K8">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L8">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M8">
         <v>1.04</v>
@@ -2623,28 +2623,28 @@
         <v>1.22</v>
       </c>
       <c r="P8">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q8">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R8">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S8">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="T8">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U8">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="X8">
         <v>22</v>
@@ -2653,46 +2653,46 @@
         <v>26</v>
       </c>
       <c r="Z8">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC8">
         <v>10.5</v>
       </c>
       <c r="AD8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF8">
         <v>11</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI8">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
+        <v>16</v>
+      </c>
+      <c r="AK8">
         <v>15.5</v>
       </c>
-      <c r="AK8">
-        <v>16</v>
-      </c>
       <c r="AL8">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN8">
         <v>7</v>
@@ -2704,16 +2704,16 @@
         <v>19.5</v>
       </c>
       <c r="AQ8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR8">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AS8">
         <v>44</v>
       </c>
       <c r="AT8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8">
         <v>9.4</v>
@@ -2722,10 +2722,10 @@
         <v>20</v>
       </c>
       <c r="AW8">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AX8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY8">
         <v>9.199999999999999</v>
@@ -2734,85 +2734,85 @@
         <v>17</v>
       </c>
       <c r="BA8">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BB8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD8">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BE8">
+        <v>60</v>
+      </c>
+      <c r="BF8">
+        <v>6.6</v>
+      </c>
+      <c r="BG8">
+        <v>50</v>
+      </c>
+      <c r="BH8">
+        <v>4.1</v>
+      </c>
+      <c r="BI8">
+        <v>3.75</v>
+      </c>
+      <c r="BJ8">
+        <v>12</v>
+      </c>
+      <c r="BK8">
+        <v>4.6</v>
+      </c>
+      <c r="BL8">
+        <v>130</v>
+      </c>
+      <c r="BM8">
+        <v>6.4</v>
+      </c>
+      <c r="BN8">
+        <v>4.4</v>
+      </c>
+      <c r="BO8">
+        <v>4</v>
+      </c>
+      <c r="BP8">
+        <v>12.5</v>
+      </c>
+      <c r="BQ8">
+        <v>4.7</v>
+      </c>
+      <c r="BR8">
+        <v>27</v>
+      </c>
+      <c r="BS8">
+        <v>5.4</v>
+      </c>
+      <c r="BT8">
+        <v>11.5</v>
+      </c>
+      <c r="BU8">
+        <v>4.5</v>
+      </c>
+      <c r="BV8">
         <v>55</v>
       </c>
-      <c r="BF8">
-        <v>6.2</v>
-      </c>
-      <c r="BG8">
-        <v>34</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>2.14</v>
-      </c>
-      <c r="BJ8">
-        <v>13.5</v>
-      </c>
-      <c r="BK8">
-        <v>7.4</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>2.14</v>
-      </c>
-      <c r="BN8">
+      <c r="BW8">
+        <v>6</v>
+      </c>
+      <c r="BX8">
+        <v>60</v>
+      </c>
+      <c r="BY8">
+        <v>6</v>
+      </c>
+      <c r="BZ8">
+        <v>18.5</v>
+      </c>
+      <c r="CA8">
         <v>5</v>
-      </c>
-      <c r="BO8">
-        <v>3.7</v>
-      </c>
-      <c r="BP8">
-        <v>13.5</v>
-      </c>
-      <c r="BQ8">
-        <v>3</v>
-      </c>
-      <c r="BR8">
-        <v>32</v>
-      </c>
-      <c r="BS8">
-        <v>3.4</v>
-      </c>
-      <c r="BT8">
-        <v>13.5</v>
-      </c>
-      <c r="BU8">
-        <v>7.4</v>
-      </c>
-      <c r="BV8">
-        <v>1000</v>
-      </c>
-      <c r="BW8">
-        <v>3.65</v>
-      </c>
-      <c r="BX8">
-        <v>1000</v>
-      </c>
-      <c r="BY8">
-        <v>3.65</v>
-      </c>
-      <c r="BZ8">
-        <v>20</v>
-      </c>
-      <c r="CA8">
-        <v>3.2</v>
       </c>
       <c r="CB8" t="s">
         <v>177</v>
@@ -2835,76 +2835,76 @@
         <v>150</v>
       </c>
       <c r="F9">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G9">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L9">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P9">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="Q9">
+        <v>1.76</v>
+      </c>
+      <c r="R9">
+        <v>1.49</v>
+      </c>
+      <c r="S9">
+        <v>2.92</v>
+      </c>
+      <c r="T9">
         <v>1.84</v>
       </c>
-      <c r="R9">
-        <v>1.44</v>
-      </c>
-      <c r="S9">
-        <v>3.05</v>
-      </c>
-      <c r="T9">
-        <v>1.9</v>
-      </c>
       <c r="U9">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V9">
         <v>1.18</v>
       </c>
       <c r="W9">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X9">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Y9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z9">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="AA9">
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD9">
         <v>25</v>
@@ -2913,13 +2913,13 @@
         <v>1000</v>
       </c>
       <c r="AF9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG9">
         <v>10</v>
       </c>
       <c r="AH9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI9">
         <v>1000</v>
@@ -2928,37 +2928,37 @@
         <v>15.5</v>
       </c>
       <c r="AK9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL9">
+        <v>34</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>7.8</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>16.5</v>
+      </c>
+      <c r="AQ9">
+        <v>20</v>
+      </c>
+      <c r="AR9">
         <v>42</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO9">
-        <v>1000</v>
-      </c>
-      <c r="AP9">
-        <v>15.5</v>
-      </c>
-      <c r="AQ9">
-        <v>19.5</v>
-      </c>
-      <c r="AR9">
-        <v>38</v>
       </c>
       <c r="AS9">
         <v>46</v>
       </c>
       <c r="AT9">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV9">
         <v>20</v>
@@ -2967,94 +2967,94 @@
         <v>48</v>
       </c>
       <c r="AX9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA9">
         <v>48</v>
       </c>
       <c r="BB9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC9">
         <v>14.5</v>
       </c>
       <c r="BD9">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BE9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF9">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG9">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BH9">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BI9">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BJ9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN9">
         <v>4.2</v>
       </c>
       <c r="BO9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP9">
         <v>10.5</v>
       </c>
       <c r="BQ9">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BR9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BS9">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BU9">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="CA9">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>177</v>
@@ -3077,16 +3077,16 @@
         <v>151</v>
       </c>
       <c r="F10">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G10">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I10">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J10">
         <v>4.1</v>
@@ -3095,7 +3095,7 @@
         <v>4.3</v>
       </c>
       <c r="L10">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M10">
         <v>1.04</v>
@@ -3104,25 +3104,25 @@
         <v>5.3</v>
       </c>
       <c r="O10">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R10">
         <v>1.57</v>
       </c>
       <c r="S10">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="T10">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U10">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="V10">
         <v>1.34</v>
@@ -3131,7 +3131,7 @@
         <v>1.98</v>
       </c>
       <c r="X10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y10">
         <v>21</v>
@@ -3143,16 +3143,16 @@
         <v>80</v>
       </c>
       <c r="AB10">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC10">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD10">
         <v>16</v>
       </c>
       <c r="AE10">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF10">
         <v>15</v>
@@ -3167,7 +3167,7 @@
         <v>42</v>
       </c>
       <c r="AJ10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK10">
         <v>19.5</v>
@@ -3179,10 +3179,10 @@
         <v>65</v>
       </c>
       <c r="AN10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO10">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP10">
         <v>19</v>
@@ -3194,19 +3194,19 @@
         <v>26</v>
       </c>
       <c r="AS10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV10">
         <v>13.5</v>
       </c>
       <c r="AW10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX10">
         <v>13</v>
@@ -3218,7 +3218,7 @@
         <v>14</v>
       </c>
       <c r="BA10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB10">
         <v>21</v>
@@ -3236,67 +3236,67 @@
         <v>9</v>
       </c>
       <c r="BG10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI10">
-        <v>1.52</v>
+        <v>3.8</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK10">
-        <v>1.94</v>
+        <v>7.6</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM10">
-        <v>2.22</v>
+        <v>8.6</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO10">
-        <v>1.61</v>
+        <v>4.5</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ10">
-        <v>2.22</v>
+        <v>10</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS10">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU10">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW10">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY10">
-        <v>2.22</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA10">
-        <v>2.22</v>
+        <v>6.6</v>
       </c>
       <c r="CB10" t="s">
         <v>177</v>
@@ -3319,226 +3319,226 @@
         <v>152</v>
       </c>
       <c r="F11">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G11">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="H11">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="I11">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="J11">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K11">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M11">
         <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O11">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P11">
         <v>1.79</v>
       </c>
       <c r="Q11">
+        <v>2.14</v>
+      </c>
+      <c r="R11">
+        <v>1.3</v>
+      </c>
+      <c r="S11">
+        <v>3.9</v>
+      </c>
+      <c r="T11">
         <v>2</v>
       </c>
-      <c r="R11">
-        <v>1.28</v>
-      </c>
-      <c r="S11">
-        <v>3.3</v>
-      </c>
-      <c r="T11">
-        <v>1.98</v>
-      </c>
       <c r="U11">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="V11">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="W11">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y11">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="Z11">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AA11">
+        <v>19</v>
+      </c>
+      <c r="AB11">
+        <v>17</v>
+      </c>
+      <c r="AC11">
+        <v>8.6</v>
+      </c>
+      <c r="AD11">
+        <v>10.5</v>
+      </c>
+      <c r="AE11">
+        <v>21</v>
+      </c>
+      <c r="AF11">
+        <v>50</v>
+      </c>
+      <c r="AG11">
+        <v>22</v>
+      </c>
+      <c r="AH11">
+        <v>23</v>
+      </c>
+      <c r="AI11">
+        <v>100</v>
+      </c>
+      <c r="AJ11">
         <v>900</v>
       </c>
-      <c r="AB11">
-        <v>1000</v>
-      </c>
-      <c r="AC11">
-        <v>970</v>
-      </c>
-      <c r="AD11">
-        <v>1000</v>
-      </c>
-      <c r="AE11">
-        <v>1000</v>
-      </c>
-      <c r="AF11">
-        <v>1000</v>
-      </c>
-      <c r="AG11">
-        <v>1000</v>
-      </c>
-      <c r="AH11">
-        <v>1000</v>
-      </c>
-      <c r="AI11">
-        <v>1000</v>
-      </c>
-      <c r="AJ11">
-        <v>1000</v>
-      </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO11">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="AP11">
-        <v>1.34</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR11">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS11">
+        <v>14</v>
+      </c>
+      <c r="AT11">
+        <v>12</v>
+      </c>
+      <c r="AU11">
+        <v>6</v>
+      </c>
+      <c r="AV11">
+        <v>7.8</v>
+      </c>
+      <c r="AW11">
+        <v>15</v>
+      </c>
+      <c r="AX11">
+        <v>20</v>
+      </c>
+      <c r="AY11">
+        <v>16.5</v>
+      </c>
+      <c r="AZ11">
+        <v>17</v>
+      </c>
+      <c r="BA11">
+        <v>20</v>
+      </c>
+      <c r="BB11">
+        <v>60</v>
+      </c>
+      <c r="BC11">
+        <v>32</v>
+      </c>
+      <c r="BD11">
+        <v>36</v>
+      </c>
+      <c r="BE11">
+        <v>60</v>
+      </c>
+      <c r="BF11">
+        <v>48</v>
+      </c>
+      <c r="BG11">
+        <v>9.6</v>
+      </c>
+      <c r="BH11">
+        <v>3.25</v>
+      </c>
+      <c r="BI11">
+        <v>2.94</v>
+      </c>
+      <c r="BJ11">
+        <v>11</v>
+      </c>
+      <c r="BK11">
         <v>6.2</v>
       </c>
-      <c r="AT11">
-        <v>1.34</v>
-      </c>
-      <c r="AU11">
-        <v>6.2</v>
-      </c>
-      <c r="AV11">
-        <v>1.34</v>
-      </c>
-      <c r="AW11">
-        <v>1.34</v>
-      </c>
-      <c r="AX11">
-        <v>1.34</v>
-      </c>
-      <c r="AY11">
-        <v>1.34</v>
-      </c>
-      <c r="AZ11">
-        <v>1.34</v>
-      </c>
-      <c r="BA11">
-        <v>1.34</v>
-      </c>
-      <c r="BB11">
-        <v>1.34</v>
-      </c>
-      <c r="BC11">
-        <v>1.34</v>
-      </c>
-      <c r="BD11">
-        <v>1.34</v>
-      </c>
-      <c r="BE11">
-        <v>1.34</v>
-      </c>
-      <c r="BF11">
-        <v>1.55</v>
-      </c>
-      <c r="BG11">
-        <v>2.64</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.01</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>1.01</v>
-      </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="CB11" t="s">
         <v>177</v>
@@ -3561,226 +3561,226 @@
         <v>153</v>
       </c>
       <c r="F12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G12">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="H12">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J12">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K12">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
         <v>3.5</v>
       </c>
       <c r="O12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P12">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q12">
+        <v>2.06</v>
+      </c>
+      <c r="R12">
+        <v>1.32</v>
+      </c>
+      <c r="S12">
+        <v>3.75</v>
+      </c>
+      <c r="T12">
+        <v>1.89</v>
+      </c>
+      <c r="U12">
         <v>1.92</v>
-      </c>
-      <c r="R12">
-        <v>1.29</v>
-      </c>
-      <c r="S12">
-        <v>3.25</v>
-      </c>
-      <c r="T12">
-        <v>1.84</v>
-      </c>
-      <c r="U12">
-        <v>1.87</v>
       </c>
       <c r="V12">
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="X12">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="Y12">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="Z12">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AA12">
         <v>900</v>
       </c>
       <c r="AB12">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12">
+        <v>8.6</v>
+      </c>
+      <c r="AD12">
+        <v>22</v>
+      </c>
+      <c r="AE12">
+        <v>90</v>
+      </c>
+      <c r="AF12">
+        <v>11</v>
+      </c>
+      <c r="AG12">
+        <v>11</v>
+      </c>
+      <c r="AH12">
+        <v>22</v>
+      </c>
+      <c r="AI12">
+        <v>210</v>
+      </c>
+      <c r="AJ12">
+        <v>20</v>
+      </c>
+      <c r="AK12">
+        <v>21</v>
+      </c>
+      <c r="AL12">
         <v>42</v>
-      </c>
-      <c r="AD12">
-        <v>500</v>
-      </c>
-      <c r="AE12">
-        <v>500</v>
-      </c>
-      <c r="AF12">
-        <v>500</v>
-      </c>
-      <c r="AG12">
-        <v>500</v>
-      </c>
-      <c r="AH12">
-        <v>500</v>
-      </c>
-      <c r="AI12">
-        <v>500</v>
-      </c>
-      <c r="AJ12">
-        <v>900</v>
-      </c>
-      <c r="AK12">
-        <v>500</v>
-      </c>
-      <c r="AL12">
-        <v>500</v>
       </c>
       <c r="AM12">
         <v>580</v>
       </c>
       <c r="AN12">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="AO12">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP12">
-        <v>1.43</v>
+        <v>6</v>
       </c>
       <c r="AQ12">
-        <v>1.42</v>
+        <v>6.6</v>
       </c>
       <c r="AR12">
-        <v>1.42</v>
+        <v>8.4</v>
       </c>
       <c r="AS12">
-        <v>1.44</v>
+        <v>10</v>
       </c>
       <c r="AT12">
         <v>5.1</v>
       </c>
       <c r="AU12">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="AV12">
-        <v>1.42</v>
+        <v>7.2</v>
       </c>
       <c r="AW12">
-        <v>1.43</v>
+        <v>9.4</v>
       </c>
       <c r="AX12">
-        <v>1.39</v>
+        <v>5.4</v>
       </c>
       <c r="AY12">
-        <v>1.38</v>
+        <v>5.4</v>
       </c>
       <c r="AZ12">
-        <v>1.41</v>
+        <v>7.2</v>
       </c>
       <c r="BA12">
-        <v>1.43</v>
+        <v>9.4</v>
       </c>
       <c r="BB12">
-        <v>1.42</v>
+        <v>7</v>
       </c>
       <c r="BC12">
-        <v>1.41</v>
+        <v>7</v>
       </c>
       <c r="BD12">
-        <v>1.43</v>
+        <v>8.4</v>
       </c>
       <c r="BE12">
-        <v>1.43</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF12">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="BG12">
-        <v>1.55</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH12">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK12">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO12">
-        <v>1.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ12">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS12">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU12">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW12">
-        <v>1.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA12">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="CB12" t="s">
         <v>177</v>
@@ -3803,31 +3803,31 @@
         <v>154</v>
       </c>
       <c r="F13">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G13">
         <v>3.6</v>
       </c>
       <c r="H13">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I13">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J13">
         <v>3.6</v>
       </c>
       <c r="K13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L13">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N13">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O13">
         <v>1.3</v>
@@ -3836,22 +3836,22 @@
         <v>2.02</v>
       </c>
       <c r="Q13">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T13">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U13">
         <v>2.22</v>
       </c>
       <c r="V13">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W13">
         <v>1.38</v>
@@ -3863,7 +3863,7 @@
         <v>10.5</v>
       </c>
       <c r="Z13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA13">
         <v>32</v>
@@ -3875,22 +3875,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF13">
         <v>26</v>
       </c>
       <c r="AG13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH13">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI13">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AJ13">
         <v>150</v>
@@ -3899,13 +3899,13 @@
         <v>42</v>
       </c>
       <c r="AL13">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM13">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN13">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO13">
         <v>16.5</v>
@@ -3935,7 +3935,7 @@
         <v>20</v>
       </c>
       <c r="AX13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY13">
         <v>13</v>
@@ -3944,85 +3944,85 @@
         <v>15</v>
       </c>
       <c r="BA13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB13">
         <v>55</v>
       </c>
       <c r="BC13">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BD13">
         <v>42</v>
       </c>
       <c r="BE13">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="BF13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG13">
         <v>14.5</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI13">
-        <v>1.51</v>
+        <v>3.25</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK13">
-        <v>2.12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>2.42</v>
+        <v>16</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO13">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>2.42</v>
+        <v>11</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS13">
-        <v>2.42</v>
+        <v>12.5</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU13">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW13">
-        <v>2.42</v>
+        <v>12.5</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>2.42</v>
+        <v>11</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>2.42</v>
+        <v>10.5</v>
       </c>
       <c r="CB13" t="s">
         <v>177</v>
@@ -4051,52 +4051,52 @@
         <v>4.3</v>
       </c>
       <c r="H14">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="I14">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K14">
         <v>4.2</v>
       </c>
       <c r="L14">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M14">
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O14">
         <v>1.22</v>
       </c>
       <c r="P14">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q14">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R14">
         <v>1.56</v>
       </c>
       <c r="S14">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="T14">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U14">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V14">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W14">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X14">
         <v>21</v>
@@ -4120,7 +4120,7 @@
         <v>10.5</v>
       </c>
       <c r="AE14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF14">
         <v>36</v>
@@ -4150,7 +4150,7 @@
         <v>38</v>
       </c>
       <c r="AO14">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP14">
         <v>19</v>
@@ -4168,7 +4168,7 @@
         <v>18</v>
       </c>
       <c r="AU14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV14">
         <v>9.6</v>
@@ -4189,10 +4189,10 @@
         <v>24</v>
       </c>
       <c r="BB14">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BC14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BD14">
         <v>38</v>
@@ -4201,70 +4201,70 @@
         <v>55</v>
       </c>
       <c r="BF14">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BG14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI14">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BJ14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BK14">
+        <v>8</v>
+      </c>
+      <c r="BL14">
+        <v>90</v>
+      </c>
+      <c r="BM14">
+        <v>13</v>
+      </c>
+      <c r="BN14">
+        <v>7.6</v>
+      </c>
+      <c r="BO14">
+        <v>6.8</v>
+      </c>
+      <c r="BP14">
+        <v>32</v>
+      </c>
+      <c r="BQ14">
+        <v>10.5</v>
+      </c>
+      <c r="BR14">
+        <v>36</v>
+      </c>
+      <c r="BS14">
+        <v>10.5</v>
+      </c>
+      <c r="BT14">
+        <v>4.9</v>
+      </c>
+      <c r="BU14">
+        <v>4.5</v>
+      </c>
+      <c r="BV14">
+        <v>13</v>
+      </c>
+      <c r="BW14">
         <v>7</v>
       </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>4.5</v>
-      </c>
-      <c r="BN14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BO14">
-        <v>6</v>
-      </c>
-      <c r="BP14">
-        <v>40</v>
-      </c>
-      <c r="BQ14">
-        <v>4.1</v>
-      </c>
-      <c r="BR14">
-        <v>48</v>
-      </c>
-      <c r="BS14">
-        <v>4.1</v>
-      </c>
-      <c r="BT14">
-        <v>5.6</v>
-      </c>
-      <c r="BU14">
-        <v>4.2</v>
-      </c>
-      <c r="BV14">
-        <v>18</v>
-      </c>
-      <c r="BW14">
-        <v>3.6</v>
-      </c>
       <c r="BX14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BY14">
-        <v>3.95</v>
+        <v>9.4</v>
       </c>
       <c r="BZ14">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="CA14">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB14" t="s">
         <v>177</v>
@@ -4287,16 +4287,16 @@
         <v>156</v>
       </c>
       <c r="F15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G15">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H15">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I15">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J15">
         <v>4.7</v>
@@ -4305,58 +4305,58 @@
         <v>4.8</v>
       </c>
       <c r="L15">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M15">
         <v>1.02</v>
       </c>
       <c r="N15">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P15">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q15">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R15">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="S15">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="T15">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U15">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="V15">
         <v>1.22</v>
       </c>
       <c r="W15">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z15">
         <v>55</v>
       </c>
       <c r="AA15">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB15">
         <v>16</v>
       </c>
       <c r="AC15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD15">
         <v>22</v>
@@ -4365,7 +4365,7 @@
         <v>55</v>
       </c>
       <c r="AF15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG15">
         <v>11</v>
@@ -4377,7 +4377,7 @@
         <v>46</v>
       </c>
       <c r="AJ15">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK15">
         <v>15</v>
@@ -4386,16 +4386,16 @@
         <v>22</v>
       </c>
       <c r="AM15">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AN15">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AO15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AQ15">
         <v>30</v>
@@ -4404,22 +4404,22 @@
         <v>46</v>
       </c>
       <c r="AS15">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AT15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV15">
         <v>20</v>
       </c>
       <c r="AW15">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY15">
         <v>9.800000000000001</v>
@@ -4431,7 +4431,7 @@
         <v>40</v>
       </c>
       <c r="BB15">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC15">
         <v>14</v>
@@ -4440,70 +4440,70 @@
         <v>19.5</v>
       </c>
       <c r="BE15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF15">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG15">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BH15">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI15">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BJ15">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK15">
         <v>7.8</v>
       </c>
       <c r="BL15">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BM15">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP15">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ15">
         <v>8.6</v>
       </c>
       <c r="BR15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS15">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="BT15">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU15">
         <v>8.4</v>
       </c>
       <c r="BV15">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BW15">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX15">
         <v>32</v>
       </c>
       <c r="BY15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ15">
         <v>10.5</v>
-      </c>
-      <c r="BZ15">
-        <v>10</v>
       </c>
       <c r="CA15">
         <v>6.2</v>
@@ -4529,16 +4529,16 @@
         <v>157</v>
       </c>
       <c r="F16">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="G16">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="H16">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="I16">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="J16">
         <v>3.7</v>
@@ -4547,10 +4547,10 @@
         <v>3.75</v>
       </c>
       <c r="L16">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N16">
         <v>4.6</v>
@@ -4565,10 +4565,10 @@
         <v>1.79</v>
       </c>
       <c r="R16">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S16">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="T16">
         <v>1.66</v>
@@ -4577,25 +4577,25 @@
         <v>2.46</v>
       </c>
       <c r="V16">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="W16">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="X16">
         <v>18</v>
       </c>
       <c r="Y16">
+        <v>14</v>
+      </c>
+      <c r="Z16">
+        <v>19.5</v>
+      </c>
+      <c r="AA16">
+        <v>42</v>
+      </c>
+      <c r="AB16">
         <v>13</v>
-      </c>
-      <c r="Z16">
-        <v>18.5</v>
-      </c>
-      <c r="AA16">
-        <v>38</v>
-      </c>
-      <c r="AB16">
-        <v>13.5</v>
       </c>
       <c r="AC16">
         <v>8.199999999999999</v>
@@ -4604,151 +4604,151 @@
         <v>12</v>
       </c>
       <c r="AE16">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF16">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AG16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI16">
         <v>34</v>
       </c>
       <c r="AJ16">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM16">
         <v>65</v>
       </c>
       <c r="AN16">
+        <v>18.5</v>
+      </c>
+      <c r="AO16">
         <v>21</v>
-      </c>
-      <c r="AO16">
-        <v>18</v>
       </c>
       <c r="AP16">
         <v>17</v>
       </c>
       <c r="AQ16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR16">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS16">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV16">
         <v>11</v>
       </c>
       <c r="AW16">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX16">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AY16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ16">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA16">
         <v>32</v>
       </c>
       <c r="BB16">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BC16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE16">
         <v>60</v>
       </c>
       <c r="BF16">
+        <v>17.5</v>
+      </c>
+      <c r="BG16">
+        <v>20</v>
+      </c>
+      <c r="BH16">
+        <v>3.75</v>
+      </c>
+      <c r="BI16">
+        <v>3.5</v>
+      </c>
+      <c r="BJ16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK16">
+        <v>7.8</v>
+      </c>
+      <c r="BL16">
+        <v>95</v>
+      </c>
+      <c r="BM16">
+        <v>17.5</v>
+      </c>
+      <c r="BN16">
+        <v>5.9</v>
+      </c>
+      <c r="BO16">
+        <v>5.3</v>
+      </c>
+      <c r="BP16">
+        <v>19</v>
+      </c>
+      <c r="BQ16">
+        <v>16.5</v>
+      </c>
+      <c r="BR16">
+        <v>29</v>
+      </c>
+      <c r="BS16">
+        <v>11</v>
+      </c>
+      <c r="BT16">
+        <v>5.9</v>
+      </c>
+      <c r="BU16">
+        <v>5.4</v>
+      </c>
+      <c r="BV16">
+        <v>21</v>
+      </c>
+      <c r="BW16">
+        <v>16.5</v>
+      </c>
+      <c r="BX16">
+        <v>29</v>
+      </c>
+      <c r="BY16">
+        <v>11</v>
+      </c>
+      <c r="BZ16">
+        <v>22</v>
+      </c>
+      <c r="CA16">
         <v>18.5</v>
-      </c>
-      <c r="BG16">
-        <v>17</v>
-      </c>
-      <c r="BH16">
-        <v>4.2</v>
-      </c>
-      <c r="BI16">
-        <v>3.15</v>
-      </c>
-      <c r="BJ16">
-        <v>11</v>
-      </c>
-      <c r="BK16">
-        <v>6.8</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>5.5</v>
-      </c>
-      <c r="BN16">
-        <v>6.8</v>
-      </c>
-      <c r="BO16">
-        <v>4.9</v>
-      </c>
-      <c r="BP16">
-        <v>25</v>
-      </c>
-      <c r="BQ16">
-        <v>14</v>
-      </c>
-      <c r="BR16">
-        <v>32</v>
-      </c>
-      <c r="BS16">
-        <v>4.8</v>
-      </c>
-      <c r="BT16">
-        <v>6.4</v>
-      </c>
-      <c r="BU16">
-        <v>4.8</v>
-      </c>
-      <c r="BV16">
-        <v>23</v>
-      </c>
-      <c r="BW16">
-        <v>13</v>
-      </c>
-      <c r="BX16">
-        <v>32</v>
-      </c>
-      <c r="BY16">
-        <v>4.8</v>
-      </c>
-      <c r="BZ16">
-        <v>29</v>
-      </c>
-      <c r="CA16">
-        <v>4.8</v>
       </c>
       <c r="CB16" t="s">
         <v>177</v>
@@ -4771,22 +4771,22 @@
         <v>158</v>
       </c>
       <c r="F17">
+        <v>1.84</v>
+      </c>
+      <c r="G17">
         <v>1.86</v>
       </c>
-      <c r="G17">
-        <v>1.87</v>
-      </c>
       <c r="H17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I17">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
         <v>1.33</v>
@@ -4810,7 +4810,7 @@
         <v>1.56</v>
       </c>
       <c r="S17">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T17">
         <v>1.67</v>
@@ -4822,28 +4822,28 @@
         <v>1.27</v>
       </c>
       <c r="W17">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X17">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA17">
         <v>95</v>
       </c>
       <c r="AB17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC17">
         <v>9.199999999999999</v>
       </c>
       <c r="AD17">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE17">
         <v>48</v>
@@ -4852,28 +4852,28 @@
         <v>12.5</v>
       </c>
       <c r="AG17">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH17">
         <v>16</v>
       </c>
       <c r="AI17">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ17">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK17">
         <v>17</v>
       </c>
       <c r="AL17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM17">
         <v>70</v>
       </c>
       <c r="AN17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO17">
         <v>40</v>
@@ -4912,19 +4912,19 @@
         <v>15.5</v>
       </c>
       <c r="BA17">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB17">
         <v>18.5</v>
       </c>
       <c r="BC17">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF17">
         <v>8.199999999999999</v>
@@ -4933,64 +4933,64 @@
         <v>36</v>
       </c>
       <c r="BH17">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BI17">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BJ17">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BK17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL17">
+        <v>95</v>
+      </c>
+      <c r="BM17">
+        <v>13.5</v>
+      </c>
+      <c r="BN17">
+        <v>4.7</v>
+      </c>
+      <c r="BO17">
+        <v>4.4</v>
+      </c>
+      <c r="BP17">
+        <v>12</v>
+      </c>
+      <c r="BQ17">
+        <v>10</v>
+      </c>
+      <c r="BR17">
+        <v>23</v>
+      </c>
+      <c r="BS17">
+        <v>15.5</v>
+      </c>
+      <c r="BT17">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU17">
         <v>7</v>
       </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>5.3</v>
-      </c>
-      <c r="BN17">
-        <v>5.5</v>
-      </c>
-      <c r="BO17">
-        <v>4</v>
-      </c>
-      <c r="BP17">
-        <v>14.5</v>
-      </c>
-      <c r="BQ17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR17">
-        <v>28</v>
-      </c>
-      <c r="BS17">
-        <v>4.4</v>
-      </c>
-      <c r="BT17">
-        <v>9.6</v>
-      </c>
-      <c r="BU17">
-        <v>6.8</v>
-      </c>
       <c r="BV17">
+        <v>36</v>
+      </c>
+      <c r="BW17">
+        <v>12.5</v>
+      </c>
+      <c r="BX17">
         <v>40</v>
       </c>
-      <c r="BW17">
-        <v>4.7</v>
-      </c>
-      <c r="BX17">
-        <v>46</v>
-      </c>
       <c r="BY17">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="BZ17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CA17">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="CB17" t="s">
         <v>177</v>
@@ -5013,127 +5013,127 @@
         <v>159</v>
       </c>
       <c r="F18">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G18">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I18">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J18">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K18">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L18">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M18">
         <v>1.08</v>
       </c>
       <c r="N18">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O18">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P18">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="Q18">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R18">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S18">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T18">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U18">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W18">
         <v>3.05</v>
       </c>
       <c r="X18">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y18">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z18">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AA18">
-        <v>560</v>
+        <v>440</v>
       </c>
       <c r="AB18">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC18">
         <v>11</v>
       </c>
       <c r="AD18">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AE18">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AF18">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AG18">
         <v>11</v>
       </c>
       <c r="AH18">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI18">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AJ18">
+        <v>12</v>
+      </c>
+      <c r="AK18">
+        <v>19</v>
+      </c>
+      <c r="AL18">
+        <v>50</v>
+      </c>
+      <c r="AM18">
+        <v>280</v>
+      </c>
+      <c r="AN18">
+        <v>9</v>
+      </c>
+      <c r="AO18">
+        <v>350</v>
+      </c>
+      <c r="AP18">
         <v>11.5</v>
       </c>
-      <c r="AK18">
-        <v>23</v>
-      </c>
-      <c r="AL18">
-        <v>55</v>
-      </c>
-      <c r="AM18">
-        <v>340</v>
-      </c>
-      <c r="AN18">
-        <v>9.4</v>
-      </c>
-      <c r="AO18">
-        <v>510</v>
-      </c>
-      <c r="AP18">
-        <v>11</v>
-      </c>
       <c r="AQ18">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR18">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AS18">
         <v>11</v>
       </c>
       <c r="AT18">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU18">
         <v>9.6</v>
@@ -5142,7 +5142,7 @@
         <v>32</v>
       </c>
       <c r="AW18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX18">
         <v>6.8</v>
@@ -5154,25 +5154,25 @@
         <v>28</v>
       </c>
       <c r="BA18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BB18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC18">
         <v>16</v>
       </c>
       <c r="BD18">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BE18">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF18">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG18">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5196,7 +5196,7 @@
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BP18">
         <v>1000</v>
@@ -5255,55 +5255,55 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G19">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H19">
         <v>2.52</v>
       </c>
       <c r="I19">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="J19">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K19">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="L19">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="M19">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N19">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O19">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="P19">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q19">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R19">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S19">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="T19">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U19">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="V19">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W19">
         <v>1.35</v>
@@ -5312,7 +5312,7 @@
         <v>7.4</v>
       </c>
       <c r="Y19">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="Z19">
         <v>15.5</v>
@@ -5321,25 +5321,25 @@
         <v>900</v>
       </c>
       <c r="AB19">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC19">
         <v>7</v>
       </c>
       <c r="AD19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE19">
         <v>180</v>
       </c>
       <c r="AF19">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="AG19">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH19">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI19">
         <v>500</v>
@@ -5348,7 +5348,7 @@
         <v>900</v>
       </c>
       <c r="AK19">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AL19">
         <v>500</v>
@@ -5363,118 +5363,118 @@
         <v>55</v>
       </c>
       <c r="AP19">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ19">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR19">
         <v>13</v>
       </c>
       <c r="AS19">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT19">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU19">
         <v>6.4</v>
       </c>
       <c r="AV19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW19">
-        <v>9.6</v>
+        <v>34</v>
       </c>
       <c r="AX19">
         <v>20</v>
       </c>
       <c r="AY19">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA19">
         <v>10.5</v>
       </c>
       <c r="BB19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC19">
         <v>10.5</v>
       </c>
       <c r="BD19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG19">
         <v>10</v>
       </c>
       <c r="BH19">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="BJ19">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BK19">
-        <v>3.45</v>
+        <v>1.52</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>2.66</v>
+        <v>3.8</v>
       </c>
       <c r="BN19">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BO19">
-        <v>2.96</v>
+        <v>5.1</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>4.1</v>
+        <v>1.64</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="BV19">
         <v>34</v>
       </c>
       <c r="BW19">
-        <v>3.85</v>
+        <v>2.22</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>4.1</v>
+        <v>1.63</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>4.1</v>
+        <v>1.64</v>
       </c>
       <c r="CB19" t="s">
         <v>177</v>
@@ -5497,166 +5497,166 @@
         <v>161</v>
       </c>
       <c r="F20">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="G20">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="H20">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I20">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J20">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K20">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M20">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O20">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="P20">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q20">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R20">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S20">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="T20">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="U20">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="X20">
+        <v>22</v>
+      </c>
+      <c r="Y20">
+        <v>19.5</v>
+      </c>
+      <c r="Z20">
+        <v>36</v>
+      </c>
+      <c r="AA20">
+        <v>170</v>
+      </c>
+      <c r="AB20">
+        <v>13.5</v>
+      </c>
+      <c r="AC20">
+        <v>9</v>
+      </c>
+      <c r="AD20">
         <v>18.5</v>
       </c>
-      <c r="Y20">
-        <v>15</v>
-      </c>
-      <c r="Z20">
-        <v>38</v>
-      </c>
-      <c r="AA20">
-        <v>440</v>
-      </c>
-      <c r="AB20">
-        <v>10.5</v>
-      </c>
-      <c r="AC20">
-        <v>8.6</v>
-      </c>
-      <c r="AD20">
-        <v>16</v>
-      </c>
       <c r="AE20">
+        <v>50</v>
+      </c>
+      <c r="AF20">
+        <v>17</v>
+      </c>
+      <c r="AG20">
+        <v>13</v>
+      </c>
+      <c r="AH20">
+        <v>20</v>
+      </c>
+      <c r="AI20">
         <v>55</v>
       </c>
-      <c r="AF20">
-        <v>14.5</v>
-      </c>
-      <c r="AG20">
-        <v>11</v>
-      </c>
-      <c r="AH20">
-        <v>18</v>
-      </c>
-      <c r="AI20">
-        <v>65</v>
-      </c>
       <c r="AJ20">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK20">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL20">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AM20">
-        <v>380</v>
+        <v>95</v>
       </c>
       <c r="AN20">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO20">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP20">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="AQ20">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AR20">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="AS20">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT20">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU20">
+        <v>6.2</v>
+      </c>
+      <c r="AV20">
+        <v>9</v>
+      </c>
+      <c r="AW20">
+        <v>5.1</v>
+      </c>
+      <c r="AX20">
+        <v>6.4</v>
+      </c>
+      <c r="AY20">
+        <v>7</v>
+      </c>
+      <c r="AZ20">
+        <v>4.5</v>
+      </c>
+      <c r="BA20">
+        <v>5.2</v>
+      </c>
+      <c r="BB20">
+        <v>4.9</v>
+      </c>
+      <c r="BC20">
+        <v>4.6</v>
+      </c>
+      <c r="BD20">
+        <v>4.9</v>
+      </c>
+      <c r="BE20">
+        <v>5.4</v>
+      </c>
+      <c r="BF20">
+        <v>4.1</v>
+      </c>
+      <c r="BG20">
         <v>7.2</v>
-      </c>
-      <c r="AV20">
-        <v>13.5</v>
-      </c>
-      <c r="AW20">
-        <v>7.4</v>
-      </c>
-      <c r="AX20">
-        <v>12</v>
-      </c>
-      <c r="AY20">
-        <v>9.4</v>
-      </c>
-      <c r="AZ20">
-        <v>15</v>
-      </c>
-      <c r="BA20">
-        <v>7.6</v>
-      </c>
-      <c r="BB20">
-        <v>17</v>
-      </c>
-      <c r="BC20">
-        <v>11.5</v>
-      </c>
-      <c r="BD20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE20">
-        <v>8</v>
-      </c>
-      <c r="BF20">
-        <v>14</v>
-      </c>
-      <c r="BG20">
-        <v>7.4</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5739,46 +5739,46 @@
         <v>162</v>
       </c>
       <c r="F21">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G21">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H21">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I21">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K21">
         <v>5.4</v>
       </c>
       <c r="L21">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M21">
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O21">
         <v>1.17</v>
       </c>
       <c r="P21">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="Q21">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R21">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S21">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="T21">
         <v>1.7</v>
@@ -5787,22 +5787,22 @@
         <v>2.22</v>
       </c>
       <c r="V21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W21">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="X21">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Y21">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Z21">
         <v>170</v>
       </c>
       <c r="AA21">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AB21">
         <v>12.5</v>
@@ -5811,7 +5811,7 @@
         <v>12.5</v>
       </c>
       <c r="AD21">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE21">
         <v>230</v>
@@ -5832,10 +5832,10 @@
         <v>14.5</v>
       </c>
       <c r="AK21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM21">
         <v>100</v>
@@ -5844,16 +5844,16 @@
         <v>5.4</v>
       </c>
       <c r="AO21">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AP21">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AQ21">
         <v>17</v>
       </c>
       <c r="AR21">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AS21">
         <v>10</v>
@@ -5865,19 +5865,19 @@
         <v>10.5</v>
       </c>
       <c r="AV21">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AW21">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AX21">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY21">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ21">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA21">
         <v>36</v>
@@ -5889,76 +5889,76 @@
         <v>12.5</v>
       </c>
       <c r="BD21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE21">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BF21">
         <v>4.7</v>
       </c>
       <c r="BG21">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BH21">
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="BJ21">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="BN21">
         <v>4.9</v>
       </c>
       <c r="BO21">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="BP21">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
         <v>6.4</v>
       </c>
       <c r="BR21">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>3.35</v>
+        <v>2.52</v>
       </c>
       <c r="BT21">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>7.8</v>
+        <v>2.2</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
       <c r="BZ21">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="CB21" t="s">
         <v>177</v>
@@ -5981,7 +5981,7 @@
         <v>163</v>
       </c>
       <c r="F22">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G22">
         <v>2.16</v>
@@ -5990,7 +5990,7 @@
         <v>3.45</v>
       </c>
       <c r="I22">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J22">
         <v>3.85</v>
@@ -5999,40 +5999,40 @@
         <v>4.1</v>
       </c>
       <c r="L22">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="M22">
         <v>1.04</v>
       </c>
       <c r="N22">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P22">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="Q22">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R22">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="S22">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="T22">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U22">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="V22">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X22">
         <v>26</v>
@@ -6059,22 +6059,22 @@
         <v>36</v>
       </c>
       <c r="AF22">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG22">
         <v>11.5</v>
       </c>
       <c r="AH22">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ22">
         <v>28</v>
       </c>
       <c r="AK22">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL22">
         <v>27</v>
@@ -6083,19 +6083,19 @@
         <v>55</v>
       </c>
       <c r="AN22">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO22">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP22">
         <v>21</v>
       </c>
       <c r="AQ22">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR22">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS22">
         <v>38</v>
@@ -6104,16 +6104,16 @@
         <v>13</v>
       </c>
       <c r="AU22">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV22">
         <v>13</v>
       </c>
       <c r="AW22">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX22">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY22">
         <v>9.800000000000001</v>
@@ -6125,40 +6125,40 @@
         <v>26</v>
       </c>
       <c r="BB22">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC22">
         <v>16.5</v>
       </c>
       <c r="BD22">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE22">
         <v>38</v>
       </c>
       <c r="BF22">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG22">
         <v>19.5</v>
       </c>
       <c r="BH22">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BN22">
         <v>1000</v>
@@ -6170,13 +6170,13 @@
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BT22">
         <v>1000</v>
@@ -6188,19 +6188,19 @@
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="CB22" t="s">
         <v>177</v>
@@ -6223,97 +6223,97 @@
         <v>164</v>
       </c>
       <c r="F23">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="H23">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I23">
+        <v>4.1</v>
+      </c>
+      <c r="J23">
+        <v>3.8</v>
+      </c>
+      <c r="K23">
+        <v>3.9</v>
+      </c>
+      <c r="L23">
+        <v>1.38</v>
+      </c>
+      <c r="M23">
+        <v>1.06</v>
+      </c>
+      <c r="N23">
         <v>4.4</v>
       </c>
-      <c r="J23">
-        <v>3.95</v>
-      </c>
-      <c r="K23">
-        <v>4</v>
-      </c>
-      <c r="L23">
-        <v>1.35</v>
-      </c>
-      <c r="M23">
-        <v>1.05</v>
-      </c>
-      <c r="N23">
-        <v>4.6</v>
-      </c>
       <c r="O23">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P23">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="Q23">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="R23">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S23">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="T23">
         <v>1.73</v>
       </c>
       <c r="U23">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W23">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="X23">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y23">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z23">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA23">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB23">
         <v>11</v>
       </c>
       <c r="AC23">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD23">
         <v>16.5</v>
       </c>
       <c r="AE23">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF23">
         <v>13</v>
       </c>
       <c r="AG23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH23">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI23">
         <v>55</v>
       </c>
       <c r="AJ23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK23">
         <v>18.5</v>
@@ -6322,25 +6322,25 @@
         <v>32</v>
       </c>
       <c r="AM23">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN23">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AO23">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP23">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ23">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR23">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AS23">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AT23">
         <v>10</v>
@@ -6352,13 +6352,13 @@
         <v>15</v>
       </c>
       <c r="AW23">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY23">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ23">
         <v>15.5</v>
@@ -6367,28 +6367,28 @@
         <v>46</v>
       </c>
       <c r="BB23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC23">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD23">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE23">
         <v>55</v>
       </c>
       <c r="BF23">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG23">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BH23">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI23">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ23">
         <v>11</v>
@@ -6400,16 +6400,16 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BN23">
         <v>5.5</v>
       </c>
       <c r="BO23">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="BP23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BQ23">
         <v>9.199999999999999</v>
@@ -6418,13 +6418,13 @@
         <v>30</v>
       </c>
       <c r="BS23">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT23">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU23">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV23">
         <v>40</v>
@@ -6442,7 +6442,7 @@
         <v>25</v>
       </c>
       <c r="CA23">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CB23" t="s">
         <v>177</v>
@@ -6465,10 +6465,10 @@
         <v>165</v>
       </c>
       <c r="F24">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G24">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H24">
         <v>3.7</v>
@@ -6483,13 +6483,13 @@
         <v>3.65</v>
       </c>
       <c r="L24">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M24">
         <v>1.07</v>
       </c>
       <c r="N24">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O24">
         <v>1.32</v>
@@ -6498,7 +6498,7 @@
         <v>2</v>
       </c>
       <c r="Q24">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R24">
         <v>1.38</v>
@@ -6516,7 +6516,7 @@
         <v>1.35</v>
       </c>
       <c r="W24">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X24">
         <v>14.5</v>
@@ -6525,10 +6525,10 @@
         <v>14.5</v>
       </c>
       <c r="Z24">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA24">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB24">
         <v>10</v>
@@ -6537,7 +6537,7 @@
         <v>8</v>
       </c>
       <c r="AD24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE24">
         <v>44</v>
@@ -6546,7 +6546,7 @@
         <v>13.5</v>
       </c>
       <c r="AG24">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH24">
         <v>17</v>
@@ -6558,7 +6558,7 @@
         <v>27</v>
       </c>
       <c r="AK24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL24">
         <v>38</v>
@@ -6567,10 +6567,10 @@
         <v>95</v>
       </c>
       <c r="AN24">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO24">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP24">
         <v>13</v>
@@ -6597,19 +6597,19 @@
         <v>38</v>
       </c>
       <c r="AX24">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY24">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ24">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA24">
         <v>46</v>
       </c>
       <c r="BB24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC24">
         <v>20</v>
@@ -6642,13 +6642,13 @@
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BN24">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BO24">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BP24">
         <v>21</v>
@@ -6660,31 +6660,31 @@
         <v>38</v>
       </c>
       <c r="BS24">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BT24">
         <v>7.6</v>
       </c>
       <c r="BU24">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV24">
         <v>40</v>
       </c>
       <c r="BW24">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BX24">
         <v>55</v>
       </c>
       <c r="BY24">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BZ24">
         <v>34</v>
       </c>
       <c r="CA24">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="CB24" t="s">
         <v>177</v>
@@ -6725,13 +6725,13 @@
         <v>3.6</v>
       </c>
       <c r="L25">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M25">
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O25">
         <v>1.31</v>
@@ -6740,10 +6740,10 @@
         <v>2.02</v>
       </c>
       <c r="Q25">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R25">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S25">
         <v>3.35</v>
@@ -6866,43 +6866,43 @@
         <v>20</v>
       </c>
       <c r="BG25">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BH25">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BI25">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ25">
         <v>11</v>
       </c>
       <c r="BK25">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BN25">
         <v>7.6</v>
       </c>
       <c r="BO25">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ25">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BR25">
         <v>48</v>
       </c>
       <c r="BS25">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BT25">
         <v>6.2</v>
@@ -6911,7 +6911,7 @@
         <v>4.5</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW25">
         <v>13</v>
@@ -6920,13 +6920,13 @@
         <v>40</v>
       </c>
       <c r="BY25">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BZ25">
         <v>36</v>
       </c>
       <c r="CA25">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="CB25" t="s">
         <v>177</v>
@@ -6967,10 +6967,10 @@
         <v>3.85</v>
       </c>
       <c r="L26">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N26">
         <v>5.2</v>
@@ -6979,16 +6979,16 @@
         <v>1.22</v>
       </c>
       <c r="P26">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q26">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R26">
         <v>1.56</v>
       </c>
       <c r="S26">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T26">
         <v>1.6</v>
@@ -7003,10 +7003,10 @@
         <v>1.8</v>
       </c>
       <c r="X26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y26">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z26">
         <v>28</v>
@@ -7024,7 +7024,7 @@
         <v>14.5</v>
       </c>
       <c r="AE26">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF26">
         <v>16.5</v>
@@ -7054,13 +7054,13 @@
         <v>12</v>
       </c>
       <c r="AO26">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP26">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ26">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR26">
         <v>24</v>
@@ -7081,7 +7081,7 @@
         <v>29</v>
       </c>
       <c r="AX26">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY26">
         <v>10</v>
@@ -7102,73 +7102,73 @@
         <v>26</v>
       </c>
       <c r="BE26">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF26">
         <v>11</v>
       </c>
       <c r="BG26">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH26">
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ26">
         <v>1000</v>
       </c>
       <c r="BK26">
-        <v>1.91</v>
+        <v>5.3</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BN26">
         <v>1000</v>
       </c>
       <c r="BO26">
-        <v>1.71</v>
+        <v>3.6</v>
       </c>
       <c r="BP26">
         <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>2.22</v>
+        <v>8</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BT26">
         <v>1000</v>
       </c>
       <c r="BU26">
-        <v>1.83</v>
+        <v>4.5</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="CB26" t="s">
         <v>177</v>
@@ -7191,7 +7191,7 @@
         <v>168</v>
       </c>
       <c r="F27">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G27">
         <v>2.14</v>
@@ -7203,40 +7203,40 @@
         <v>3.85</v>
       </c>
       <c r="J27">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K27">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L27">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M27">
         <v>1.07</v>
       </c>
       <c r="N27">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O27">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P27">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="Q27">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="R27">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S27">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T27">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U27">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="V27">
         <v>1.35</v>
@@ -7245,7 +7245,7 @@
         <v>1.87</v>
       </c>
       <c r="X27">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y27">
         <v>14.5</v>
@@ -7254,19 +7254,19 @@
         <v>27</v>
       </c>
       <c r="AA27">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC27">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD27">
         <v>15.5</v>
       </c>
       <c r="AE27">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF27">
         <v>13.5</v>
@@ -7275,7 +7275,7 @@
         <v>10.5</v>
       </c>
       <c r="AH27">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI27">
         <v>55</v>
@@ -7284,25 +7284,25 @@
         <v>26</v>
       </c>
       <c r="AK27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL27">
         <v>36</v>
       </c>
       <c r="AM27">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN27">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO27">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AP27">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ27">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR27">
         <v>24</v>
@@ -7311,19 +7311,19 @@
         <v>60</v>
       </c>
       <c r="AT27">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU27">
         <v>7.6</v>
       </c>
       <c r="AV27">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW27">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX27">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY27">
         <v>9.800000000000001</v>
@@ -7347,10 +7347,10 @@
         <v>75</v>
       </c>
       <c r="BF27">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG27">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH27">
         <v>4</v>
@@ -7368,16 +7368,16 @@
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BN27">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO27">
-        <v>2.66</v>
+        <v>3.95</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ27">
         <v>11</v>
@@ -7386,10 +7386,10 @@
         <v>40</v>
       </c>
       <c r="BS27">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BT27">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU27">
         <v>5.4</v>
@@ -7398,19 +7398,19 @@
         <v>44</v>
       </c>
       <c r="BW27">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BX27">
         <v>55</v>
       </c>
       <c r="BY27">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BZ27">
         <v>32</v>
       </c>
       <c r="CA27">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="CB27" t="s">
         <v>177</v>
@@ -7433,76 +7433,76 @@
         <v>169</v>
       </c>
       <c r="F28">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="G28">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="H28">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="I28">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="J28">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K28">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L28">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M28">
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O28">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P28">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="Q28">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R28">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S28">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T28">
         <v>1.69</v>
       </c>
       <c r="U28">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V28">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="W28">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X28">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Y28">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z28">
         <v>11.5</v>
       </c>
       <c r="AA28">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AB28">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AC28">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD28">
         <v>9.800000000000001</v>
@@ -7511,19 +7511,19 @@
         <v>15</v>
       </c>
       <c r="AF28">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AG28">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH28">
         <v>17</v>
       </c>
       <c r="AI28">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ28">
-        <v>130</v>
+        <v>690</v>
       </c>
       <c r="AK28">
         <v>65</v>
@@ -7532,40 +7532,40 @@
         <v>60</v>
       </c>
       <c r="AM28">
-        <v>120</v>
+        <v>310</v>
       </c>
       <c r="AN28">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO28">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AP28">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AQ28">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR28">
         <v>11</v>
       </c>
       <c r="AS28">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AT28">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU28">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV28">
         <v>9.4</v>
       </c>
       <c r="AW28">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX28">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AY28">
         <v>19.5</v>
@@ -7580,79 +7580,79 @@
         <v>40</v>
       </c>
       <c r="BC28">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BD28">
         <v>50</v>
       </c>
       <c r="BE28">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BF28">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BG28">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BH28">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI28">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BJ28">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BK28">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BP28">
         <v>55</v>
       </c>
       <c r="BQ28">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BR28">
         <v>55</v>
       </c>
       <c r="BS28">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BT28">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU28">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV28">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BW28">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX28">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BY28">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BZ28">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="CA28">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="CB28" t="s">
         <v>177</v>
@@ -7675,10 +7675,10 @@
         <v>170</v>
       </c>
       <c r="F29">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G29">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H29">
         <v>4.4</v>
@@ -7705,22 +7705,22 @@
         <v>1.16</v>
       </c>
       <c r="P29">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q29">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R29">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="S29">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T29">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U29">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="V29">
         <v>1.28</v>
@@ -7729,13 +7729,13 @@
         <v>2.16</v>
       </c>
       <c r="X29">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y29">
         <v>26</v>
       </c>
       <c r="Z29">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA29">
         <v>85</v>
@@ -7747,7 +7747,7 @@
         <v>10.5</v>
       </c>
       <c r="AD29">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE29">
         <v>42</v>
@@ -7756,7 +7756,7 @@
         <v>15.5</v>
       </c>
       <c r="AG29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH29">
         <v>15</v>
@@ -7777,22 +7777,22 @@
         <v>55</v>
       </c>
       <c r="AN29">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AO29">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP29">
         <v>26</v>
       </c>
       <c r="AQ29">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR29">
         <v>36</v>
       </c>
       <c r="AS29">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT29">
         <v>13.5</v>
@@ -7801,7 +7801,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV29">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW29">
         <v>38</v>
@@ -7822,79 +7822,79 @@
         <v>19.5</v>
       </c>
       <c r="BC29">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE29">
         <v>48</v>
       </c>
       <c r="BF29">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG29">
         <v>26</v>
       </c>
       <c r="BH29">
-        <v>15.5</v>
+        <v>4.7</v>
       </c>
       <c r="BI29">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BJ29">
+        <v>8.6</v>
+      </c>
+      <c r="BK29">
+        <v>7.8</v>
+      </c>
+      <c r="BL29">
+        <v>70</v>
+      </c>
+      <c r="BM29">
+        <v>15</v>
+      </c>
+      <c r="BN29">
+        <v>5</v>
+      </c>
+      <c r="BO29">
+        <v>4.6</v>
+      </c>
+      <c r="BP29">
+        <v>11.5</v>
+      </c>
+      <c r="BQ29">
         <v>10</v>
       </c>
-      <c r="BK29">
-        <v>3.6</v>
-      </c>
-      <c r="BL29">
-        <v>1000</v>
-      </c>
-      <c r="BM29">
-        <v>4.9</v>
-      </c>
-      <c r="BN29">
-        <v>6</v>
-      </c>
-      <c r="BO29">
-        <v>4.1</v>
-      </c>
-      <c r="BP29">
-        <v>14.5</v>
-      </c>
-      <c r="BQ29">
-        <v>8.4</v>
-      </c>
       <c r="BR29">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BS29">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BT29">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BU29">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BV29">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BW29">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="BX29">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BY29">
-        <v>4.6</v>
+        <v>22</v>
       </c>
       <c r="BZ29">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="CA29">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="CB29" t="s">
         <v>177</v>
@@ -7923,10 +7923,10 @@
         <v>5.2</v>
       </c>
       <c r="H30">
+        <v>1.75</v>
+      </c>
+      <c r="I30">
         <v>1.76</v>
-      </c>
-      <c r="I30">
-        <v>1.77</v>
       </c>
       <c r="J30">
         <v>4.2</v>
@@ -7935,7 +7935,7 @@
         <v>4.3</v>
       </c>
       <c r="L30">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M30">
         <v>1.05</v>
@@ -7947,10 +7947,10 @@
         <v>1.24</v>
       </c>
       <c r="P30">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q30">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R30">
         <v>1.51</v>
@@ -7962,13 +7962,13 @@
         <v>1.74</v>
       </c>
       <c r="U30">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V30">
         <v>2.3</v>
       </c>
       <c r="W30">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X30">
         <v>19.5</v>
@@ -7980,7 +7980,7 @@
         <v>11.5</v>
       </c>
       <c r="AA30">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AB30">
         <v>21</v>
@@ -8016,10 +8016,10 @@
         <v>60</v>
       </c>
       <c r="AM30">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN30">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="AO30">
         <v>8.6</v>
@@ -8028,7 +8028,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ30">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR30">
         <v>11</v>
@@ -8037,10 +8037,10 @@
         <v>17</v>
       </c>
       <c r="AT30">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AU30">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV30">
         <v>9.6</v>
@@ -8049,7 +8049,7 @@
         <v>15</v>
       </c>
       <c r="AX30">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY30">
         <v>18.5</v>
@@ -8058,10 +8058,10 @@
         <v>16.5</v>
       </c>
       <c r="BA30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB30">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BC30">
         <v>50</v>
@@ -8073,70 +8073,70 @@
         <v>70</v>
       </c>
       <c r="BF30">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BG30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH30">
+        <v>3.9</v>
+      </c>
+      <c r="BI30">
+        <v>3.65</v>
+      </c>
+      <c r="BJ30">
+        <v>9.6</v>
+      </c>
+      <c r="BK30">
         <v>8.4</v>
       </c>
-      <c r="BH30">
-        <v>1000</v>
-      </c>
-      <c r="BI30">
-        <v>3.2</v>
-      </c>
-      <c r="BJ30">
-        <v>1000</v>
-      </c>
-      <c r="BK30">
-        <v>6.8</v>
-      </c>
       <c r="BL30">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM30">
-        <v>2.9</v>
+        <v>15</v>
       </c>
       <c r="BN30">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO30">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BP30">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ30">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="BR30">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS30">
-        <v>2.9</v>
+        <v>13</v>
       </c>
       <c r="BT30">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU30">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV30">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW30">
-        <v>2.62</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX30">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY30">
-        <v>2.9</v>
+        <v>10</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA30">
-        <v>2.9</v>
+        <v>12.5</v>
       </c>
       <c r="CB30" t="s">
         <v>177</v>
@@ -8168,10 +8168,10 @@
         <v>3.4</v>
       </c>
       <c r="I31">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J31">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K31">
         <v>3.65</v>
@@ -8183,16 +8183,16 @@
         <v>1.07</v>
       </c>
       <c r="N31">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O31">
         <v>1.29</v>
       </c>
       <c r="P31">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q31">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R31">
         <v>1.42</v>
@@ -8213,7 +8213,7 @@
         <v>1.75</v>
       </c>
       <c r="X31">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y31">
         <v>14</v>
@@ -8231,7 +8231,7 @@
         <v>7.8</v>
       </c>
       <c r="AD31">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE31">
         <v>38</v>
@@ -8243,7 +8243,7 @@
         <v>11.5</v>
       </c>
       <c r="AH31">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI31">
         <v>44</v>
@@ -8252,10 +8252,10 @@
         <v>30</v>
       </c>
       <c r="AK31">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM31">
         <v>80</v>
@@ -8276,7 +8276,7 @@
         <v>22</v>
       </c>
       <c r="AS31">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT31">
         <v>10</v>
@@ -8300,7 +8300,7 @@
         <v>15</v>
       </c>
       <c r="BA31">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB31">
         <v>27</v>
@@ -8309,16 +8309,16 @@
         <v>21</v>
       </c>
       <c r="BD31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE31">
         <v>65</v>
       </c>
       <c r="BF31">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG31">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH31">
         <v>3.55</v>
@@ -8336,7 +8336,7 @@
         <v>110</v>
       </c>
       <c r="BM31">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BN31">
         <v>5.2</v>
@@ -8354,7 +8354,7 @@
         <v>28</v>
       </c>
       <c r="BS31">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT31">
         <v>6.6</v>
@@ -8363,7 +8363,7 @@
         <v>6</v>
       </c>
       <c r="BV31">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW31">
         <v>11</v>
@@ -8372,7 +8372,7 @@
         <v>36</v>
       </c>
       <c r="BY31">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ31">
         <v>24</v>
@@ -8410,7 +8410,7 @@
         <v>5.5</v>
       </c>
       <c r="I32">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J32">
         <v>4.6</v>
@@ -8425,40 +8425,40 @@
         <v>1.03</v>
       </c>
       <c r="N32">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O32">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P32">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q32">
         <v>1.47</v>
       </c>
       <c r="R32">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S32">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="T32">
         <v>1.54</v>
       </c>
       <c r="U32">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V32">
         <v>1.21</v>
       </c>
       <c r="W32">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X32">
         <v>34</v>
       </c>
       <c r="Y32">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z32">
         <v>55</v>
@@ -8467,7 +8467,7 @@
         <v>130</v>
       </c>
       <c r="AB32">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC32">
         <v>11.5</v>
@@ -8482,16 +8482,16 @@
         <v>13</v>
       </c>
       <c r="AG32">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH32">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI32">
         <v>46</v>
       </c>
       <c r="AJ32">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK32">
         <v>13.5</v>
@@ -8500,28 +8500,28 @@
         <v>23</v>
       </c>
       <c r="AM32">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN32">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO32">
         <v>44</v>
       </c>
       <c r="AP32">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR32">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS32">
         <v>42</v>
       </c>
       <c r="AT32">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU32">
         <v>10.5</v>
@@ -8530,7 +8530,7 @@
         <v>19.5</v>
       </c>
       <c r="AW32">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX32">
         <v>12.5</v>
@@ -8557,19 +8557,19 @@
         <v>48</v>
       </c>
       <c r="BF32">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG32">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH32">
         <v>4.9</v>
       </c>
       <c r="BI32">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ32">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK32">
         <v>8</v>
@@ -8578,7 +8578,7 @@
         <v>70</v>
       </c>
       <c r="BM32">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BN32">
         <v>4.8</v>
@@ -8587,7 +8587,7 @@
         <v>4.4</v>
       </c>
       <c r="BP32">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ32">
         <v>8.800000000000001</v>
@@ -8596,31 +8596,31 @@
         <v>18.5</v>
       </c>
       <c r="BS32">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BT32">
         <v>9</v>
       </c>
       <c r="BU32">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV32">
         <v>34</v>
       </c>
       <c r="BW32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX32">
         <v>34</v>
       </c>
       <c r="BY32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ32">
         <v>11.5</v>
       </c>
       <c r="CA32">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB32" t="s">
         <v>177</v>
@@ -8643,58 +8643,58 @@
         <v>174</v>
       </c>
       <c r="F33">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G33">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="H33">
         <v>3.3</v>
       </c>
       <c r="I33">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K33">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L33">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M33">
         <v>1.1</v>
       </c>
       <c r="N33">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O33">
         <v>1.43</v>
       </c>
       <c r="P33">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="Q33">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R33">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S33">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T33">
         <v>1.89</v>
       </c>
       <c r="U33">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W33">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="X33">
         <v>12.5</v>
@@ -8742,7 +8742,7 @@
         <v>60</v>
       </c>
       <c r="AM33">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN33">
         <v>30</v>
@@ -8766,7 +8766,7 @@
         <v>7.4</v>
       </c>
       <c r="AU33">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV33">
         <v>12.5</v>
@@ -8885,172 +8885,172 @@
         <v>175</v>
       </c>
       <c r="F34">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="G34">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="H34">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="I34">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="J34">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K34">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="L34">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M34">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N34">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O34">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P34">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q34">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
         <v>1.19</v>
       </c>
       <c r="S34">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T34">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="U34">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V34">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="W34">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="X34">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y34">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z34">
         <v>160</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB34">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AC34">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD34">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AE34">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AF34">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AG34">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH34">
         <v>85</v>
       </c>
       <c r="AI34">
-        <v>290</v>
+        <v>700</v>
       </c>
       <c r="AJ34">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK34">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AL34">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM34">
         <v>580</v>
       </c>
       <c r="AN34">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP34">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ34">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AR34">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS34">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AT34">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU34">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AV34">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW34">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AX34">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AY34">
         <v>10.5</v>
       </c>
       <c r="AZ34">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BA34">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB34">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BC34">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BD34">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BE34">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BF34">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BG34">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BH34">
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BJ34">
         <v>20</v>
@@ -9065,16 +9065,16 @@
         <v>21</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO34">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="BP34">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BQ34">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR34">
         <v>1000</v>
@@ -9083,7 +9083,7 @@
         <v>21</v>
       </c>
       <c r="BT34">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU34">
         <v>6.8</v>
@@ -9101,10 +9101,10 @@
         <v>21</v>
       </c>
       <c r="BZ34">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA34">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="CB34" t="s">
         <v>177</v>
@@ -9127,16 +9127,16 @@
         <v>176</v>
       </c>
       <c r="F35">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G35">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H35">
         <v>5.1</v>
       </c>
       <c r="I35">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J35">
         <v>3.2</v>
@@ -9145,31 +9145,31 @@
         <v>3.35</v>
       </c>
       <c r="L35">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M35">
         <v>1.13</v>
       </c>
       <c r="N35">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O35">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P35">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q35">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
         <v>1.19</v>
       </c>
       <c r="S35">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T35">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U35">
         <v>1.7</v>
@@ -9181,7 +9181,7 @@
         <v>2</v>
       </c>
       <c r="X35">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y35">
         <v>12.5</v>
@@ -9241,13 +9241,13 @@
         <v>11</v>
       </c>
       <c r="AR35">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS35">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT35">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU35">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>19.5</v>
       </c>
       <c r="AW35">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX35">
         <v>9</v>
@@ -9268,7 +9268,7 @@
         <v>24</v>
       </c>
       <c r="BA35">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BB35">
         <v>20</v>
@@ -9277,16 +9277,16 @@
         <v>24</v>
       </c>
       <c r="BD35">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE35">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BF35">
         <v>17.5</v>
       </c>
       <c r="BG35">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -9310,7 +9310,7 @@
         <v>4.8</v>
       </c>
       <c r="BO35">
-        <v>2.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP35">
         <v>23</v>
@@ -9328,7 +9328,7 @@
         <v>12.5</v>
       </c>
       <c r="BU35">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BV35">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -547,7 +547,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-09-08 01:56:41</t>
+    <t>2026-09-08 04:08:25</t>
   </si>
 </sst>
 </file>
@@ -1141,166 +1141,166 @@
         <v>143</v>
       </c>
       <c r="F2">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="G2">
+        <v>4.1</v>
+      </c>
+      <c r="H2">
+        <v>2.02</v>
+      </c>
+      <c r="I2">
+        <v>2.06</v>
+      </c>
+      <c r="J2">
         <v>3.8</v>
-      </c>
-      <c r="H2">
-        <v>2.1</v>
-      </c>
-      <c r="I2">
-        <v>2.18</v>
-      </c>
-      <c r="J2">
-        <v>3.75</v>
       </c>
       <c r="K2">
         <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O2">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P2">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q2">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R2">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S2">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U2">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="V2">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="W2">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="X2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z2">
+        <v>14.5</v>
+      </c>
+      <c r="AA2">
+        <v>24</v>
+      </c>
+      <c r="AB2">
+        <v>20</v>
+      </c>
+      <c r="AC2">
+        <v>9</v>
+      </c>
+      <c r="AD2">
+        <v>10.5</v>
+      </c>
+      <c r="AE2">
+        <v>18.5</v>
+      </c>
+      <c r="AF2">
+        <v>32</v>
+      </c>
+      <c r="AG2">
         <v>16</v>
       </c>
-      <c r="AA2">
-        <v>26</v>
-      </c>
-      <c r="AB2">
-        <v>19</v>
-      </c>
-      <c r="AC2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD2">
-        <v>11</v>
-      </c>
-      <c r="AE2">
-        <v>20</v>
-      </c>
-      <c r="AF2">
-        <v>29</v>
-      </c>
-      <c r="AG2">
-        <v>15</v>
-      </c>
       <c r="AH2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ2">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM2">
         <v>65</v>
       </c>
       <c r="AN2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO2">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AP2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ2">
         <v>11.5</v>
       </c>
       <c r="AR2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT2">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AU2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW2">
         <v>17</v>
       </c>
       <c r="AX2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AY2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2">
         <v>25</v>
       </c>
       <c r="BB2">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BC2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BG2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH2">
         <v>4</v>
@@ -1309,58 +1309,58 @@
         <v>3.7</v>
       </c>
       <c r="BJ2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL2">
         <v>85</v>
       </c>
       <c r="BM2">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BN2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BO2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BP2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT2">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW2">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA2">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="s">
         <v>177</v>
@@ -1383,64 +1383,64 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="G3">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="H3">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I3">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
         <v>1.75</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U3">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="X3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z3">
         <v>38</v>
@@ -1452,13 +1452,13 @@
         <v>7.4</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE3">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF3">
         <v>10.5</v>
@@ -1473,82 +1473,82 @@
         <v>85</v>
       </c>
       <c r="AJ3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK3">
         <v>23</v>
       </c>
       <c r="AL3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN3">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AO3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP3">
         <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS3">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AX3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA3">
         <v>65</v>
       </c>
       <c r="BB3">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE3">
         <v>80</v>
       </c>
       <c r="BF3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BG3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BH3">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI3">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="BJ3">
         <v>11</v>
@@ -1563,31 +1563,31 @@
         <v>18</v>
       </c>
       <c r="BN3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ3">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BR3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BU3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW3">
         <v>14</v>
@@ -1599,10 +1599,10 @@
         <v>15</v>
       </c>
       <c r="BZ3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1625,7 +1625,7 @@
         <v>145</v>
       </c>
       <c r="F4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G4">
         <v>5.8</v>
@@ -1640,7 +1640,7 @@
         <v>4.3</v>
       </c>
       <c r="K4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L4">
         <v>1.32</v>
@@ -1658,19 +1658,19 @@
         <v>2.38</v>
       </c>
       <c r="Q4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R4">
         <v>1.55</v>
       </c>
       <c r="S4">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U4">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V4">
         <v>2.44</v>
@@ -1691,7 +1691,7 @@
         <v>21</v>
       </c>
       <c r="AB4">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AC4">
         <v>10.5</v>
@@ -1700,7 +1700,7 @@
         <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF4">
         <v>60</v>
@@ -1712,31 +1712,31 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ4">
         <v>160</v>
       </c>
       <c r="AK4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AL4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM4">
+        <v>150</v>
+      </c>
+      <c r="AN4">
         <v>110</v>
       </c>
-      <c r="AN4">
-        <v>75</v>
-      </c>
       <c r="AO4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4">
         <v>10</v>
@@ -1766,13 +1766,13 @@
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB4">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BD4">
         <v>40</v>
@@ -1796,16 +1796,16 @@
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BN4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BO4">
         <v>7</v>
@@ -1814,13 +1814,13 @@
         <v>55</v>
       </c>
       <c r="BQ4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BT4">
         <v>4.5</v>
@@ -1832,19 +1832,19 @@
         <v>10.5</v>
       </c>
       <c r="BW4">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BX4">
         <v>26</v>
       </c>
       <c r="BY4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BZ4">
         <v>18</v>
       </c>
       <c r="CA4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1867,10 +1867,10 @@
         <v>146</v>
       </c>
       <c r="F5">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G5">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H5">
         <v>7</v>
@@ -1879,7 +1879,7 @@
         <v>7.8</v>
       </c>
       <c r="J5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="K5">
         <v>5.3</v>
@@ -1891,70 +1891,70 @@
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O5">
         <v>1.15</v>
       </c>
       <c r="P5">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q5">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R5">
         <v>1.78</v>
       </c>
       <c r="S5">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T5">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U5">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V5">
         <v>1.15</v>
       </c>
       <c r="W5">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="X5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y5">
         <v>38</v>
       </c>
       <c r="Z5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA5">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC5">
         <v>12</v>
       </c>
       <c r="AD5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
         <v>18.5</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
         <v>14.5</v>
@@ -1963,37 +1963,37 @@
         <v>14.5</v>
       </c>
       <c r="AL5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AO5">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR5">
         <v>55</v>
       </c>
       <c r="AS5">
+        <v>110</v>
+      </c>
+      <c r="AT5">
+        <v>12</v>
+      </c>
+      <c r="AU5">
         <v>11</v>
       </c>
-      <c r="AT5">
-        <v>11.5</v>
-      </c>
-      <c r="AU5">
-        <v>10</v>
-      </c>
       <c r="AV5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW5">
         <v>55</v>
@@ -2005,88 +2005,88 @@
         <v>9.4</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC5">
         <v>12</v>
       </c>
       <c r="BD5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BE5">
         <v>50</v>
       </c>
       <c r="BF5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG5">
         <v>44</v>
       </c>
       <c r="BH5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ5">
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL5">
         <v>95</v>
       </c>
       <c r="BM5">
+        <v>5.6</v>
+      </c>
+      <c r="BN5">
+        <v>5.1</v>
+      </c>
+      <c r="BO5">
+        <v>4</v>
+      </c>
+      <c r="BP5">
+        <v>10</v>
+      </c>
+      <c r="BQ5">
         <v>6.8</v>
       </c>
-      <c r="BN5">
-        <v>4.7</v>
-      </c>
-      <c r="BO5">
-        <v>3.95</v>
-      </c>
-      <c r="BP5">
-        <v>9</v>
-      </c>
-      <c r="BQ5">
-        <v>4</v>
-      </c>
       <c r="BR5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BS5">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BT5">
         <v>11</v>
       </c>
       <c r="BU5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BV5">
         <v>55</v>
       </c>
       <c r="BW5">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BX5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY5">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="BZ5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA5">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="s">
         <v>177</v>
@@ -2109,22 +2109,22 @@
         <v>147</v>
       </c>
       <c r="F6">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="G6">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="H6">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K6">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L6">
         <v>1.36</v>
@@ -2133,76 +2133,76 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P6">
         <v>2.22</v>
       </c>
       <c r="Q6">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T6">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="W6">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="X6">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Y6">
+        <v>13.5</v>
+      </c>
+      <c r="Z6">
+        <v>19</v>
+      </c>
+      <c r="AA6">
+        <v>38</v>
+      </c>
+      <c r="AB6">
         <v>14</v>
       </c>
-      <c r="Z6">
+      <c r="AC6">
+        <v>8.6</v>
+      </c>
+      <c r="AD6">
+        <v>12</v>
+      </c>
+      <c r="AE6">
+        <v>27</v>
+      </c>
+      <c r="AF6">
         <v>21</v>
       </c>
-      <c r="AA6">
-        <v>46</v>
-      </c>
-      <c r="AB6">
-        <v>13</v>
-      </c>
-      <c r="AC6">
-        <v>8.4</v>
-      </c>
-      <c r="AD6">
+      <c r="AG6">
         <v>12.5</v>
       </c>
-      <c r="AE6">
-        <v>30</v>
-      </c>
-      <c r="AF6">
-        <v>17.5</v>
-      </c>
-      <c r="AG6">
-        <v>12</v>
-      </c>
       <c r="AH6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ6">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AK6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL6">
         <v>36</v>
@@ -2211,64 +2211,64 @@
         <v>70</v>
       </c>
       <c r="AN6">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AO6">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AP6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS6">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AT6">
+        <v>13</v>
+      </c>
+      <c r="AU6">
+        <v>7.8</v>
+      </c>
+      <c r="AV6">
+        <v>11</v>
+      </c>
+      <c r="AW6">
+        <v>22</v>
+      </c>
+      <c r="AX6">
+        <v>18.5</v>
+      </c>
+      <c r="AY6">
         <v>11.5</v>
-      </c>
-      <c r="AU6">
-        <v>7.6</v>
-      </c>
-      <c r="AV6">
-        <v>11.5</v>
-      </c>
-      <c r="AW6">
-        <v>27</v>
-      </c>
-      <c r="AX6">
-        <v>16</v>
-      </c>
-      <c r="AY6">
-        <v>10.5</v>
       </c>
       <c r="AZ6">
         <v>14.5</v>
       </c>
       <c r="BA6">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BB6">
+        <v>40</v>
+      </c>
+      <c r="BC6">
+        <v>25</v>
+      </c>
+      <c r="BD6">
         <v>32</v>
-      </c>
-      <c r="BC6">
-        <v>22</v>
-      </c>
-      <c r="BD6">
-        <v>30</v>
       </c>
       <c r="BE6">
         <v>60</v>
       </c>
       <c r="BF6">
+        <v>18.5</v>
+      </c>
+      <c r="BG6">
         <v>16</v>
-      </c>
-      <c r="BG6">
-        <v>18.5</v>
       </c>
       <c r="BH6">
         <v>3.85</v>
@@ -2289,46 +2289,46 @@
         <v>14.5</v>
       </c>
       <c r="BN6">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO6">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BP6">
+        <v>20</v>
+      </c>
+      <c r="BQ6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR6">
+        <v>30</v>
+      </c>
+      <c r="BS6">
+        <v>11</v>
+      </c>
+      <c r="BT6">
+        <v>5.7</v>
+      </c>
+      <c r="BU6">
+        <v>5.2</v>
+      </c>
+      <c r="BV6">
         <v>18</v>
-      </c>
-      <c r="BQ6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR6">
-        <v>28</v>
-      </c>
-      <c r="BS6">
-        <v>10.5</v>
-      </c>
-      <c r="BT6">
-        <v>6.2</v>
-      </c>
-      <c r="BU6">
-        <v>5.6</v>
-      </c>
-      <c r="BV6">
-        <v>21</v>
       </c>
       <c r="BW6">
         <v>9.6</v>
       </c>
       <c r="BX6">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BY6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
         <v>21</v>
       </c>
       <c r="CA6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="s">
         <v>177</v>
@@ -2351,7 +2351,7 @@
         <v>148</v>
       </c>
       <c r="F7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G7">
         <v>2.2</v>
@@ -2363,34 +2363,34 @@
         <v>3.95</v>
       </c>
       <c r="J7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
         <v>3.6</v>
       </c>
       <c r="L7">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T7">
         <v>1.86</v>
@@ -2408,7 +2408,7 @@
         <v>13.5</v>
       </c>
       <c r="Y7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z7">
         <v>27</v>
@@ -2423,13 +2423,13 @@
         <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG7">
         <v>11.5</v>
@@ -2438,7 +2438,7 @@
         <v>19.5</v>
       </c>
       <c r="AI7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ7">
         <v>29</v>
@@ -2450,10 +2450,10 @@
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AN7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO7">
         <v>55</v>
@@ -2465,7 +2465,7 @@
         <v>12</v>
       </c>
       <c r="AR7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS7">
         <v>55</v>
@@ -2477,10 +2477,10 @@
         <v>7</v>
       </c>
       <c r="AV7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX7">
         <v>11.5</v>
@@ -2489,10 +2489,10 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB7">
         <v>22</v>
@@ -2507,16 +2507,16 @@
         <v>65</v>
       </c>
       <c r="BF7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG7">
         <v>36</v>
       </c>
       <c r="BH7">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BI7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BJ7">
         <v>9.6</v>
@@ -2525,10 +2525,10 @@
         <v>7.2</v>
       </c>
       <c r="BL7">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BM7">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN7">
         <v>4.9</v>
@@ -2540,13 +2540,13 @@
         <v>16</v>
       </c>
       <c r="BQ7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR7">
         <v>32</v>
       </c>
       <c r="BS7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT7">
         <v>7</v>
@@ -2558,19 +2558,19 @@
         <v>32</v>
       </c>
       <c r="BW7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX7">
         <v>44</v>
       </c>
       <c r="BY7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ7">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="CA7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB7" t="s">
         <v>177</v>
@@ -2593,19 +2593,19 @@
         <v>149</v>
       </c>
       <c r="F8">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="G8">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="H8">
+        <v>5.3</v>
+      </c>
+      <c r="I8">
         <v>5.7</v>
       </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
       <c r="J8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K8">
         <v>4.6</v>
@@ -2617,115 +2617,115 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O8">
         <v>1.22</v>
       </c>
       <c r="P8">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q8">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R8">
         <v>1.55</v>
       </c>
       <c r="S8">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T8">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U8">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="X8">
         <v>22</v>
       </c>
       <c r="Y8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA8">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG8">
         <v>10</v>
       </c>
       <c r="AH8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ8">
+        <v>17</v>
+      </c>
+      <c r="AK8">
         <v>16</v>
-      </c>
-      <c r="AK8">
-        <v>15.5</v>
       </c>
       <c r="AL8">
         <v>29</v>
       </c>
       <c r="AM8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN8">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP8">
         <v>19.5</v>
       </c>
       <c r="AQ8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AS8">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AT8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AW8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY8">
         <v>9.199999999999999</v>
@@ -2734,22 +2734,22 @@
         <v>17</v>
       </c>
       <c r="BA8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB8">
+        <v>15.5</v>
+      </c>
+      <c r="BC8">
         <v>14.5</v>
-      </c>
-      <c r="BC8">
-        <v>14</v>
       </c>
       <c r="BD8">
         <v>26</v>
       </c>
       <c r="BE8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF8">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG8">
         <v>50</v>
@@ -2758,61 +2758,61 @@
         <v>4.1</v>
       </c>
       <c r="BI8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
         <v>4.6</v>
       </c>
       <c r="BL8">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BN8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ8">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BR8">
         <v>27</v>
       </c>
       <c r="BS8">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BT8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU8">
         <v>4.5</v>
       </c>
       <c r="BV8">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BW8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX8">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ8">
         <v>18.5</v>
       </c>
       <c r="CA8">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="CB8" t="s">
         <v>177</v>
@@ -2835,25 +2835,25 @@
         <v>150</v>
       </c>
       <c r="F9">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H9">
         <v>6</v>
       </c>
       <c r="I9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K9">
         <v>4.6</v>
       </c>
       <c r="L9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M9">
         <v>1.05</v>
@@ -2874,7 +2874,7 @@
         <v>1.49</v>
       </c>
       <c r="S9">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T9">
         <v>1.84</v>
@@ -2889,16 +2889,16 @@
         <v>2.58</v>
       </c>
       <c r="X9">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y9">
         <v>24</v>
       </c>
       <c r="Z9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="AB9">
         <v>10</v>
@@ -2907,10 +2907,10 @@
         <v>10</v>
       </c>
       <c r="AD9">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF9">
         <v>10.5</v>
@@ -2931,25 +2931,25 @@
         <v>16</v>
       </c>
       <c r="AL9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN9">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP9">
         <v>16.5</v>
       </c>
       <c r="AQ9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR9">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS9">
         <v>46</v>
@@ -2958,13 +2958,13 @@
         <v>9</v>
       </c>
       <c r="AU9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV9">
         <v>20</v>
       </c>
       <c r="AW9">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AX9">
         <v>9.4</v>
@@ -2973,28 +2973,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA9">
         <v>48</v>
       </c>
       <c r="BB9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC9">
         <v>14.5</v>
       </c>
       <c r="BD9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE9">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BF9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG9">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
@@ -3006,22 +3006,22 @@
         <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN9">
         <v>4.2</v>
       </c>
       <c r="BO9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ9">
         <v>6.4</v>
@@ -3030,31 +3030,31 @@
         <v>24</v>
       </c>
       <c r="BS9">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT9">
         <v>9.6</v>
       </c>
       <c r="BU9">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX9">
         <v>55</v>
       </c>
       <c r="BY9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ9">
         <v>16.5</v>
       </c>
       <c r="CA9">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="s">
         <v>177</v>
@@ -3077,64 +3077,64 @@
         <v>151</v>
       </c>
       <c r="F10">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G10">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H10">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I10">
         <v>3.95</v>
       </c>
       <c r="J10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L10">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="Q10">
+        <v>1.7</v>
+      </c>
+      <c r="R10">
+        <v>1.54</v>
+      </c>
+      <c r="S10">
+        <v>2.78</v>
+      </c>
+      <c r="T10">
         <v>1.64</v>
       </c>
-      <c r="R10">
-        <v>1.57</v>
-      </c>
-      <c r="S10">
-        <v>2.66</v>
-      </c>
-      <c r="T10">
-        <v>1.59</v>
-      </c>
       <c r="U10">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="V10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
         <v>1.98</v>
       </c>
       <c r="X10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y10">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z10">
         <v>32</v>
@@ -3143,7 +3143,7 @@
         <v>80</v>
       </c>
       <c r="AB10">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC10">
         <v>9.4</v>
@@ -3152,19 +3152,19 @@
         <v>16</v>
       </c>
       <c r="AE10">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ10">
         <v>25</v>
@@ -3173,19 +3173,19 @@
         <v>19.5</v>
       </c>
       <c r="AL10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AM10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AP10">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AQ10">
         <v>17.5</v>
@@ -3197,10 +3197,10 @@
         <v>50</v>
       </c>
       <c r="AT10">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU10">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV10">
         <v>13.5</v>
@@ -3209,13 +3209,13 @@
         <v>34</v>
       </c>
       <c r="AX10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY10">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA10">
         <v>36</v>
@@ -3230,34 +3230,34 @@
         <v>24</v>
       </c>
       <c r="BE10">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF10">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BH10">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BJ10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK10">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BM10">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BN10">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BO10">
         <v>4.5</v>
@@ -3269,10 +3269,10 @@
         <v>10</v>
       </c>
       <c r="BR10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS10">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BT10">
         <v>7.8</v>
@@ -3281,22 +3281,22 @@
         <v>6.4</v>
       </c>
       <c r="BV10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BW10">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY10">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA10">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="CB10" t="s">
         <v>177</v>
@@ -3319,103 +3319,103 @@
         <v>152</v>
       </c>
       <c r="F11">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="G11">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="H11">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="I11">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="J11">
+        <v>3.5</v>
+      </c>
+      <c r="K11">
         <v>3.65</v>
       </c>
-      <c r="K11">
-        <v>3.9</v>
-      </c>
       <c r="L11">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M11">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N11">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O11">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P11">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q11">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R11">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S11">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T11">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U11">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="V11">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="W11">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="X11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y11">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z11">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AA11">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AB11">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AC11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE11">
+        <v>24</v>
+      </c>
+      <c r="AF11">
+        <v>32</v>
+      </c>
+      <c r="AG11">
+        <v>17.5</v>
+      </c>
+      <c r="AH11">
         <v>21</v>
       </c>
-      <c r="AF11">
-        <v>50</v>
-      </c>
-      <c r="AG11">
-        <v>22</v>
-      </c>
-      <c r="AH11">
-        <v>23</v>
-      </c>
       <c r="AI11">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ11">
         <v>900</v>
       </c>
       <c r="AK11">
-        <v>700</v>
+        <v>65</v>
       </c>
       <c r="AL11">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AM11">
         <v>580</v>
@@ -3424,73 +3424,73 @@
         <v>600</v>
       </c>
       <c r="AO11">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AP11">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR11">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AT11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU11">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AV11">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AW11">
+        <v>21</v>
+      </c>
+      <c r="AX11">
+        <v>23</v>
+      </c>
+      <c r="AY11">
         <v>15</v>
       </c>
-      <c r="AX11">
-        <v>20</v>
-      </c>
-      <c r="AY11">
-        <v>16.5</v>
-      </c>
       <c r="AZ11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA11">
         <v>20</v>
       </c>
       <c r="BB11">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="BC11">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BD11">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BE11">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="BF11">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BG11">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="BH11">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI11">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BJ11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3499,46 +3499,46 @@
         <v>13.5</v>
       </c>
       <c r="BN11">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BO11">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BP11">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT11">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BU11">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BV11">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BW11">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY11">
         <v>10</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA11">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="s">
         <v>177</v>
@@ -3561,19 +3561,19 @@
         <v>153</v>
       </c>
       <c r="F12">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G12">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H12">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I12">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J12">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
         <v>3.9</v>
@@ -3588,7 +3588,7 @@
         <v>3.5</v>
       </c>
       <c r="O12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P12">
         <v>1.86</v>
@@ -3603,7 +3603,7 @@
         <v>3.75</v>
       </c>
       <c r="T12">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="U12">
         <v>1.92</v>
@@ -3612,7 +3612,7 @@
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X12">
         <v>13.5</v>
@@ -3642,13 +3642,13 @@
         <v>11</v>
       </c>
       <c r="AG12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH12">
         <v>22</v>
       </c>
       <c r="AI12">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="AJ12">
         <v>20</v>
@@ -3663,85 +3663,85 @@
         <v>580</v>
       </c>
       <c r="AN12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO12">
         <v>600</v>
       </c>
       <c r="AP12">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ12">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AR12">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="AS12">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="AT12">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AU12">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="AV12">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="AW12">
-        <v>9.4</v>
+        <v>46</v>
       </c>
       <c r="AX12">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AY12">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AZ12">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="BA12">
-        <v>9.4</v>
+        <v>50</v>
       </c>
       <c r="BB12">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="BC12">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BD12">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BE12">
-        <v>9.800000000000001</v>
+        <v>90</v>
       </c>
       <c r="BF12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BG12">
-        <v>9.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BH12">
         <v>3.3</v>
       </c>
       <c r="BI12">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BJ12">
         <v>11</v>
       </c>
       <c r="BK12">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN12">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO12">
         <v>3.85</v>
@@ -3750,37 +3750,37 @@
         <v>13.5</v>
       </c>
       <c r="BQ12">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR12">
         <v>32</v>
       </c>
       <c r="BS12">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT12">
         <v>9</v>
       </c>
       <c r="BU12">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV12">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW12">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ12">
         <v>27</v>
       </c>
       <c r="CA12">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB12" t="s">
         <v>177</v>
@@ -3803,16 +3803,16 @@
         <v>154</v>
       </c>
       <c r="F13">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="G13">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="H13">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="I13">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="J13">
         <v>3.6</v>
@@ -3824,7 +3824,7 @@
         <v>1.4</v>
       </c>
       <c r="M13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
         <v>4.1</v>
@@ -3839,22 +3839,22 @@
         <v>1.92</v>
       </c>
       <c r="R13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S13">
         <v>3.35</v>
       </c>
       <c r="T13">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U13">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="W13">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X13">
         <v>15.5</v>
@@ -3863,10 +3863,10 @@
         <v>10.5</v>
       </c>
       <c r="Z13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA13">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AB13">
         <v>15</v>
@@ -3878,49 +3878,49 @@
         <v>11</v>
       </c>
       <c r="AE13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH13">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI13">
+        <v>48</v>
+      </c>
+      <c r="AJ13">
+        <v>75</v>
+      </c>
+      <c r="AK13">
         <v>46</v>
       </c>
-      <c r="AJ13">
-        <v>150</v>
-      </c>
-      <c r="AK13">
-        <v>42</v>
-      </c>
       <c r="AL13">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM13">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AN13">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AO13">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP13">
         <v>13.5</v>
       </c>
       <c r="AQ13">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS13">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT13">
         <v>13</v>
@@ -3929,16 +3929,16 @@
         <v>7.4</v>
       </c>
       <c r="AV13">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX13">
         <v>23</v>
       </c>
       <c r="AY13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ13">
         <v>15</v>
@@ -3950,7 +3950,7 @@
         <v>55</v>
       </c>
       <c r="BC13">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BD13">
         <v>42</v>
@@ -3959,13 +3959,13 @@
         <v>65</v>
       </c>
       <c r="BF13">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BG13">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH13">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI13">
         <v>3.25</v>
@@ -3974,55 +3974,55 @@
         <v>9.4</v>
       </c>
       <c r="BK13">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BN13">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BO13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR13">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT13">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU13">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BW13">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB13" t="s">
         <v>177</v>
@@ -4045,43 +4045,43 @@
         <v>155</v>
       </c>
       <c r="F14">
+        <v>3.9</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>2.02</v>
+      </c>
+      <c r="J14">
+        <v>3.9</v>
+      </c>
+      <c r="K14">
         <v>4.1</v>
       </c>
-      <c r="G14">
-        <v>4.3</v>
-      </c>
-      <c r="H14">
-        <v>1.92</v>
-      </c>
-      <c r="I14">
-        <v>1.94</v>
-      </c>
-      <c r="J14">
-        <v>3.95</v>
-      </c>
-      <c r="K14">
-        <v>4.2</v>
-      </c>
       <c r="L14">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M14">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N14">
         <v>5.1</v>
       </c>
       <c r="O14">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P14">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q14">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R14">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S14">
         <v>2.72</v>
@@ -4093,106 +4093,106 @@
         <v>2.48</v>
       </c>
       <c r="V14">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="W14">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X14">
         <v>21</v>
       </c>
       <c r="Y14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC14">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
       </c>
       <c r="AE14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF14">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI14">
         <v>28</v>
       </c>
       <c r="AJ14">
-        <v>490</v>
+        <v>75</v>
       </c>
       <c r="AK14">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL14">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM14">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="AN14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO14">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AP14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ14">
         <v>11</v>
       </c>
       <c r="AR14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU14">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14">
         <v>9.6</v>
       </c>
       <c r="AW14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BC14">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BD14">
         <v>38</v>
@@ -4201,70 +4201,70 @@
         <v>55</v>
       </c>
       <c r="BF14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG14">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH14">
         <v>4.1</v>
       </c>
       <c r="BI14">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ14">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL14">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM14">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BN14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BP14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BQ14">
         <v>10.5</v>
       </c>
       <c r="BR14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS14">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BW14">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BX14">
         <v>24</v>
       </c>
       <c r="BY14">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ14">
         <v>17.5</v>
       </c>
       <c r="CA14">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB14" t="s">
         <v>177</v>
@@ -4299,67 +4299,67 @@
         <v>5.5</v>
       </c>
       <c r="J15">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K15">
         <v>4.8</v>
       </c>
       <c r="L15">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P15">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q15">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="R15">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="S15">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="T15">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="U15">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="V15">
         <v>1.22</v>
       </c>
       <c r="W15">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z15">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA15">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB15">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AC15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE15">
         <v>55</v>
@@ -4368,142 +4368,142 @@
         <v>14.5</v>
       </c>
       <c r="AG15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15">
         <v>16</v>
       </c>
       <c r="AI15">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ15">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK15">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AM15">
         <v>55</v>
       </c>
       <c r="AN15">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AO15">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP15">
+        <v>27</v>
+      </c>
+      <c r="AQ15">
         <v>28</v>
-      </c>
-      <c r="AQ15">
-        <v>30</v>
       </c>
       <c r="AR15">
         <v>46</v>
       </c>
       <c r="AS15">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="AT15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU15">
         <v>10.5</v>
       </c>
       <c r="AV15">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AW15">
         <v>48</v>
       </c>
       <c r="AX15">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY15">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
         <v>14.5</v>
       </c>
       <c r="BA15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC15">
         <v>14</v>
       </c>
       <c r="BD15">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF15">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BG15">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BH15">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BI15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ15">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BK15">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL15">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BM15">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN15">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BO15">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP15">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BS15">
         <v>8.4</v>
       </c>
       <c r="BT15">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BU15">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV15">
         <v>34</v>
       </c>
       <c r="BW15">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BX15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY15">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BZ15">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CA15">
         <v>6.2</v>
@@ -4532,70 +4532,70 @@
         <v>2.6</v>
       </c>
       <c r="G16">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H16">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="I16">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J16">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K16">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L16">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M16">
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O16">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P16">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="Q16">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="R16">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="S16">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="T16">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="U16">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="V16">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y16">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z16">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA16">
         <v>42</v>
       </c>
       <c r="AB16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC16">
         <v>8.199999999999999</v>
@@ -4604,25 +4604,25 @@
         <v>12</v>
       </c>
       <c r="AE16">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG16">
         <v>12</v>
       </c>
       <c r="AH16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI16">
         <v>34</v>
       </c>
       <c r="AJ16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL16">
         <v>32</v>
@@ -4631,43 +4631,43 @@
         <v>65</v>
       </c>
       <c r="AN16">
+        <v>16</v>
+      </c>
+      <c r="AO16">
+        <v>19</v>
+      </c>
+      <c r="AP16">
         <v>18.5</v>
       </c>
-      <c r="AO16">
-        <v>21</v>
-      </c>
-      <c r="AP16">
-        <v>17</v>
-      </c>
       <c r="AQ16">
+        <v>14</v>
+      </c>
+      <c r="AR16">
+        <v>19</v>
+      </c>
+      <c r="AS16">
+        <v>38</v>
+      </c>
+      <c r="AT16">
         <v>13</v>
-      </c>
-      <c r="AR16">
-        <v>18.5</v>
-      </c>
-      <c r="AS16">
-        <v>36</v>
-      </c>
-      <c r="AT16">
-        <v>12</v>
       </c>
       <c r="AU16">
         <v>8</v>
       </c>
       <c r="AV16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA16">
         <v>32</v>
@@ -4676,79 +4676,79 @@
         <v>34</v>
       </c>
       <c r="BC16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD16">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE16">
         <v>60</v>
       </c>
       <c r="BF16">
+        <v>15.5</v>
+      </c>
+      <c r="BG16">
+        <v>18</v>
+      </c>
+      <c r="BH16">
+        <v>3.85</v>
+      </c>
+      <c r="BI16">
+        <v>3.6</v>
+      </c>
+      <c r="BJ16">
+        <v>8.6</v>
+      </c>
+      <c r="BK16">
+        <v>8</v>
+      </c>
+      <c r="BL16">
+        <v>85</v>
+      </c>
+      <c r="BM16">
+        <v>70</v>
+      </c>
+      <c r="BN16">
+        <v>5.8</v>
+      </c>
+      <c r="BO16">
+        <v>5.4</v>
+      </c>
+      <c r="BP16">
+        <v>18</v>
+      </c>
+      <c r="BQ16">
+        <v>16</v>
+      </c>
+      <c r="BR16">
+        <v>26</v>
+      </c>
+      <c r="BS16">
+        <v>13</v>
+      </c>
+      <c r="BT16">
+        <v>6</v>
+      </c>
+      <c r="BU16">
+        <v>5.6</v>
+      </c>
+      <c r="BV16">
+        <v>19</v>
+      </c>
+      <c r="BW16">
         <v>17.5</v>
       </c>
-      <c r="BG16">
-        <v>20</v>
-      </c>
-      <c r="BH16">
-        <v>3.75</v>
-      </c>
-      <c r="BI16">
-        <v>3.5</v>
-      </c>
-      <c r="BJ16">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK16">
-        <v>7.8</v>
-      </c>
-      <c r="BL16">
-        <v>95</v>
-      </c>
-      <c r="BM16">
-        <v>17.5</v>
-      </c>
-      <c r="BN16">
-        <v>5.9</v>
-      </c>
-      <c r="BO16">
-        <v>5.3</v>
-      </c>
-      <c r="BP16">
-        <v>19</v>
-      </c>
-      <c r="BQ16">
-        <v>16.5</v>
-      </c>
-      <c r="BR16">
-        <v>29</v>
-      </c>
-      <c r="BS16">
-        <v>11</v>
-      </c>
-      <c r="BT16">
-        <v>5.9</v>
-      </c>
-      <c r="BU16">
-        <v>5.4</v>
-      </c>
-      <c r="BV16">
-        <v>21</v>
-      </c>
-      <c r="BW16">
-        <v>16.5</v>
-      </c>
       <c r="BX16">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BY16">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="BZ16">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="CA16">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="CB16" t="s">
         <v>177</v>
@@ -4771,10 +4771,10 @@
         <v>158</v>
       </c>
       <c r="F17">
+        <v>1.83</v>
+      </c>
+      <c r="G17">
         <v>1.84</v>
-      </c>
-      <c r="G17">
-        <v>1.86</v>
       </c>
       <c r="H17">
         <v>4.6</v>
@@ -4789,112 +4789,112 @@
         <v>4.2</v>
       </c>
       <c r="L17">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="P17">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="Q17">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="R17">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="S17">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="T17">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="U17">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V17">
         <v>1.27</v>
       </c>
       <c r="W17">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X17">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Y17">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z17">
         <v>38</v>
       </c>
       <c r="AA17">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB17">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AC17">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD17">
         <v>17.5</v>
       </c>
       <c r="AE17">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF17">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AG17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI17">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ17">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM17">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN17">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO17">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AQ17">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AR17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS17">
         <v>75</v>
       </c>
       <c r="AT17">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU17">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV17">
         <v>17</v>
@@ -4903,94 +4903,94 @@
         <v>42</v>
       </c>
       <c r="AX17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY17">
         <v>9.6</v>
       </c>
       <c r="AZ17">
+        <v>14.5</v>
+      </c>
+      <c r="BA17">
+        <v>40</v>
+      </c>
+      <c r="BB17">
+        <v>19</v>
+      </c>
+      <c r="BC17">
         <v>15.5</v>
       </c>
-      <c r="BA17">
-        <v>42</v>
-      </c>
-      <c r="BB17">
-        <v>18.5</v>
-      </c>
-      <c r="BC17">
+      <c r="BD17">
+        <v>24</v>
+      </c>
+      <c r="BE17">
+        <v>50</v>
+      </c>
+      <c r="BF17">
+        <v>7.4</v>
+      </c>
+      <c r="BG17">
+        <v>30</v>
+      </c>
+      <c r="BH17">
+        <v>4.3</v>
+      </c>
+      <c r="BI17">
+        <v>4</v>
+      </c>
+      <c r="BJ17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK17">
+        <v>8</v>
+      </c>
+      <c r="BL17">
+        <v>80</v>
+      </c>
+      <c r="BM17">
         <v>16</v>
       </c>
-      <c r="BD17">
-        <v>25</v>
-      </c>
-      <c r="BE17">
-        <v>55</v>
-      </c>
-      <c r="BF17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG17">
-        <v>36</v>
-      </c>
-      <c r="BH17">
-        <v>4</v>
-      </c>
-      <c r="BI17">
-        <v>3.8</v>
-      </c>
-      <c r="BJ17">
-        <v>9</v>
-      </c>
-      <c r="BK17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BL17">
-        <v>95</v>
-      </c>
-      <c r="BM17">
-        <v>13.5</v>
-      </c>
       <c r="BN17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ17">
         <v>10</v>
       </c>
       <c r="BR17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS17">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BT17">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU17">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BV17">
+        <v>32</v>
+      </c>
+      <c r="BW17">
+        <v>24</v>
+      </c>
+      <c r="BX17">
         <v>36</v>
-      </c>
-      <c r="BW17">
-        <v>12.5</v>
-      </c>
-      <c r="BX17">
-        <v>40</v>
       </c>
       <c r="BY17">
         <v>12.5</v>
       </c>
       <c r="BZ17">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CA17">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="CB17" t="s">
         <v>177</v>
@@ -5013,226 +5013,226 @@
         <v>159</v>
       </c>
       <c r="F18">
+        <v>1.44</v>
+      </c>
+      <c r="G18">
         <v>1.46</v>
       </c>
-      <c r="G18">
-        <v>1.48</v>
-      </c>
       <c r="H18">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I18">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K18">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M18">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N18">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O18">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="P18">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="Q18">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="R18">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S18">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="T18">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="U18">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="V18">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W18">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X18">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="Y18">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Z18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA18">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="AB18">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD18">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AE18">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AF18">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG18">
         <v>11</v>
       </c>
       <c r="AH18">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AI18">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AJ18">
         <v>12</v>
       </c>
       <c r="AK18">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL18">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM18">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="AN18">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AO18">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="AP18">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ18">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AR18">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="AS18">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AT18">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU18">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV18">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AW18">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="AX18">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BA18">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="BB18">
         <v>10.5</v>
       </c>
       <c r="BC18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD18">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BE18">
+        <v>100</v>
+      </c>
+      <c r="BF18">
+        <v>6.8</v>
+      </c>
+      <c r="BG18">
+        <v>120</v>
+      </c>
+      <c r="BH18">
+        <v>4.3</v>
+      </c>
+      <c r="BI18">
+        <v>3.3</v>
+      </c>
+      <c r="BJ18">
         <v>14.5</v>
       </c>
-      <c r="BF18">
-        <v>8</v>
-      </c>
-      <c r="BG18">
-        <v>15</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.33</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO18">
-        <v>1.41</v>
+        <v>3.4</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="CB18" t="s">
         <v>177</v>
@@ -5255,91 +5255,91 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G19">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="H19">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I19">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J19">
+        <v>2.74</v>
+      </c>
+      <c r="K19">
         <v>2.84</v>
       </c>
-      <c r="K19">
-        <v>2.98</v>
-      </c>
       <c r="L19">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M19">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="N19">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="O19">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="P19">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="Q19">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R19">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="S19">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="T19">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="U19">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="V19">
         <v>1.6</v>
       </c>
       <c r="W19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X19">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="Z19">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA19">
         <v>900</v>
       </c>
       <c r="AB19">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19">
         <v>7</v>
       </c>
       <c r="AD19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE19">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AF19">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG19">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AH19">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AI19">
         <v>500</v>
@@ -5348,7 +5348,7 @@
         <v>900</v>
       </c>
       <c r="AK19">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AL19">
         <v>500</v>
@@ -5357,124 +5357,124 @@
         <v>500</v>
       </c>
       <c r="AN19">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="AO19">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP19">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ19">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR19">
         <v>13</v>
       </c>
       <c r="AS19">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT19">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU19">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW19">
-        <v>34</v>
+        <v>16.5</v>
       </c>
       <c r="AX19">
         <v>20</v>
       </c>
       <c r="AY19">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AZ19">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BA19">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BB19">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BC19">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD19">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BE19">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF19">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BG19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="BI19">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="BJ19">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="BK19">
-        <v>1.52</v>
+        <v>7.4</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="BN19">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BO19">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.62</v>
+        <v>12.5</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.64</v>
+        <v>6.6</v>
       </c>
       <c r="BT19">
+        <v>5.2</v>
+      </c>
+      <c r="BU19">
+        <v>4.6</v>
+      </c>
+      <c r="BV19">
         <v>1000</v>
       </c>
-      <c r="BU19">
-        <v>3.85</v>
-      </c>
-      <c r="BV19">
-        <v>34</v>
-      </c>
       <c r="BW19">
-        <v>2.22</v>
+        <v>10.5</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.63</v>
+        <v>13.5</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.64</v>
+        <v>6.6</v>
       </c>
       <c r="CB19" t="s">
         <v>177</v>
@@ -5497,16 +5497,16 @@
         <v>161</v>
       </c>
       <c r="F20">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G20">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H20">
         <v>3.6</v>
       </c>
       <c r="I20">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J20">
         <v>3.7</v>
@@ -5524,52 +5524,52 @@
         <v>4.3</v>
       </c>
       <c r="O20">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P20">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q20">
         <v>1.8</v>
       </c>
       <c r="R20">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S20">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T20">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U20">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X20">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y20">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z20">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA20">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AB20">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AC20">
         <v>9</v>
       </c>
       <c r="AD20">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE20">
         <v>50</v>
@@ -5578,16 +5578,16 @@
         <v>17</v>
       </c>
       <c r="AG20">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH20">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI20">
         <v>55</v>
       </c>
       <c r="AJ20">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK20">
         <v>25</v>
@@ -5602,121 +5602,121 @@
         <v>13.5</v>
       </c>
       <c r="AO20">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP20">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="AQ20">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AR20">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AS20">
-        <v>5.3</v>
+        <v>48</v>
       </c>
       <c r="AT20">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU20">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV20">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AW20">
-        <v>5.1</v>
+        <v>27</v>
       </c>
       <c r="AX20">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AY20">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA20">
-        <v>5.2</v>
+        <v>30</v>
       </c>
       <c r="BB20">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="BC20">
-        <v>4.6</v>
+        <v>15.5</v>
       </c>
       <c r="BD20">
-        <v>4.9</v>
+        <v>23</v>
       </c>
       <c r="BE20">
-        <v>5.4</v>
+        <v>55</v>
       </c>
       <c r="BF20">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BG20">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA20">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB20" t="s">
         <v>177</v>
@@ -5739,22 +5739,22 @@
         <v>162</v>
       </c>
       <c r="F21">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="G21">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="H21">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I21">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="K21">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L21">
         <v>1.27</v>
@@ -5766,55 +5766,55 @@
         <v>6.2</v>
       </c>
       <c r="O21">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P21">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q21">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R21">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S21">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="T21">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U21">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V21">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W21">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="X21">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y21">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Z21">
         <v>170</v>
       </c>
       <c r="AA21">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="AB21">
         <v>12.5</v>
       </c>
       <c r="AC21">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD21">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AE21">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="AF21">
         <v>11</v>
@@ -5823,142 +5823,142 @@
         <v>10.5</v>
       </c>
       <c r="AH21">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI21">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="AJ21">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AK21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL21">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM21">
+        <v>95</v>
+      </c>
+      <c r="AN21">
+        <v>5.1</v>
+      </c>
+      <c r="AO21">
         <v>100</v>
       </c>
-      <c r="AN21">
-        <v>5.4</v>
-      </c>
-      <c r="AO21">
-        <v>95</v>
-      </c>
       <c r="AP21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ21">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AR21">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AS21">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT21">
+        <v>11</v>
+      </c>
+      <c r="AU21">
+        <v>11.5</v>
+      </c>
+      <c r="AV21">
+        <v>26</v>
+      </c>
+      <c r="AW21">
+        <v>60</v>
+      </c>
+      <c r="AX21">
+        <v>9.4</v>
+      </c>
+      <c r="AY21">
+        <v>9.4</v>
+      </c>
+      <c r="AZ21">
+        <v>19.5</v>
+      </c>
+      <c r="BA21">
+        <v>46</v>
+      </c>
+      <c r="BB21">
+        <v>11.5</v>
+      </c>
+      <c r="BC21">
+        <v>12</v>
+      </c>
+      <c r="BD21">
+        <v>22</v>
+      </c>
+      <c r="BE21">
+        <v>55</v>
+      </c>
+      <c r="BF21">
+        <v>4.3</v>
+      </c>
+      <c r="BG21">
+        <v>50</v>
+      </c>
+      <c r="BH21">
+        <v>4.9</v>
+      </c>
+      <c r="BI21">
+        <v>4.3</v>
+      </c>
+      <c r="BJ21">
         <v>10.5</v>
       </c>
-      <c r="AU21">
-        <v>10.5</v>
-      </c>
-      <c r="AV21">
-        <v>23</v>
-      </c>
-      <c r="AW21">
-        <v>48</v>
-      </c>
-      <c r="AX21">
-        <v>9.6</v>
-      </c>
-      <c r="AY21">
-        <v>9</v>
-      </c>
-      <c r="AZ21">
-        <v>17</v>
-      </c>
-      <c r="BA21">
-        <v>36</v>
-      </c>
-      <c r="BB21">
-        <v>12</v>
-      </c>
-      <c r="BC21">
-        <v>12.5</v>
-      </c>
-      <c r="BD21">
-        <v>15</v>
-      </c>
-      <c r="BE21">
-        <v>40</v>
-      </c>
-      <c r="BF21">
-        <v>4.7</v>
-      </c>
-      <c r="BG21">
-        <v>15</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>1.74</v>
-      </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
       <c r="BK21">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>2.52</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN21">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BO21">
-        <v>1.65</v>
+        <v>3.85</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BQ21">
+        <v>7</v>
+      </c>
+      <c r="BR21">
+        <v>19.5</v>
+      </c>
+      <c r="BS21">
         <v>6.4</v>
       </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>2.52</v>
-      </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU21">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>2.52</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY21">
-        <v>2.52</v>
+        <v>8</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA21">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="CB21" t="s">
         <v>177</v>
@@ -5981,61 +5981,61 @@
         <v>163</v>
       </c>
       <c r="F22">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G22">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H22">
         <v>3.45</v>
       </c>
       <c r="I22">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J22">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K22">
         <v>4.1</v>
       </c>
       <c r="L22">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M22">
         <v>1.04</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O22">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P22">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Q22">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R22">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S22">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="T22">
         <v>1.51</v>
       </c>
       <c r="U22">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W22">
         <v>1.87</v>
       </c>
       <c r="X22">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y22">
         <v>22</v>
@@ -6050,19 +6050,19 @@
         <v>15.5</v>
       </c>
       <c r="AC22">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD22">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE22">
         <v>36</v>
       </c>
       <c r="AF22">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH22">
         <v>14.5</v>
@@ -6086,7 +6086,7 @@
         <v>10.5</v>
       </c>
       <c r="AO22">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP22">
         <v>21</v>
@@ -6095,10 +6095,10 @@
         <v>18.5</v>
       </c>
       <c r="AR22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS22">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AT22">
         <v>13</v>
@@ -6131,76 +6131,76 @@
         <v>16.5</v>
       </c>
       <c r="BD22">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BE22">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BF22">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG22">
         <v>19.5</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI22">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK22">
-        <v>1.87</v>
+        <v>7.6</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM22">
-        <v>2.22</v>
+        <v>11.5</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO22">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ22">
-        <v>2.22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS22">
-        <v>2.22</v>
+        <v>8.6</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU22">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW22">
-        <v>2.22</v>
+        <v>8.6</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY22">
-        <v>2.22</v>
+        <v>9.4</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA22">
-        <v>2.22</v>
+        <v>7.4</v>
       </c>
       <c r="CB22" t="s">
         <v>177</v>
@@ -6223,19 +6223,19 @@
         <v>164</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="G23">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I23">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J23">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K23">
         <v>3.9</v>
@@ -6250,10 +6250,10 @@
         <v>4.4</v>
       </c>
       <c r="O23">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P23">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q23">
         <v>1.84</v>
@@ -6262,61 +6262,61 @@
         <v>1.45</v>
       </c>
       <c r="S23">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T23">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U23">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V23">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W23">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="X23">
         <v>17</v>
       </c>
       <c r="Y23">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z23">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA23">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AB23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC23">
         <v>8.4</v>
       </c>
       <c r="AD23">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE23">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF23">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH23">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI23">
         <v>55</v>
       </c>
       <c r="AJ23">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK23">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL23">
         <v>32</v>
@@ -6325,37 +6325,37 @@
         <v>85</v>
       </c>
       <c r="AN23">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO23">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AP23">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR23">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS23">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AT23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW23">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AX23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY23">
         <v>9.6</v>
@@ -6364,85 +6364,85 @@
         <v>15.5</v>
       </c>
       <c r="BA23">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB23">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BC23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD23">
         <v>29</v>
       </c>
       <c r="BE23">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF23">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG23">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BH23">
+        <v>3.65</v>
+      </c>
+      <c r="BI23">
+        <v>3.4</v>
+      </c>
+      <c r="BJ23">
+        <v>9.4</v>
+      </c>
+      <c r="BK23">
+        <v>8.4</v>
+      </c>
+      <c r="BL23">
+        <v>110</v>
+      </c>
+      <c r="BM23">
+        <v>24</v>
+      </c>
+      <c r="BN23">
+        <v>4.7</v>
+      </c>
+      <c r="BO23">
         <v>4.3</v>
       </c>
-      <c r="BI23">
-        <v>3.15</v>
-      </c>
-      <c r="BJ23">
+      <c r="BP23">
+        <v>13</v>
+      </c>
+      <c r="BQ23">
         <v>11</v>
       </c>
-      <c r="BK23">
-        <v>7</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>5.1</v>
-      </c>
-      <c r="BN23">
-        <v>5.5</v>
-      </c>
-      <c r="BO23">
-        <v>3.75</v>
-      </c>
-      <c r="BP23">
-        <v>17</v>
-      </c>
-      <c r="BQ23">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BR23">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BS23">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT23">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BU23">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW23">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="BX23">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BY23">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BZ23">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CA23">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="CB23" t="s">
         <v>177</v>
@@ -6465,31 +6465,31 @@
         <v>165</v>
       </c>
       <c r="F24">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G24">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H24">
         <v>3.7</v>
       </c>
       <c r="I24">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J24">
+        <v>3.55</v>
+      </c>
+      <c r="K24">
         <v>3.6</v>
       </c>
-      <c r="K24">
-        <v>3.65</v>
-      </c>
       <c r="L24">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M24">
         <v>1.07</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O24">
         <v>1.32</v>
@@ -6513,13 +6513,13 @@
         <v>2.2</v>
       </c>
       <c r="V24">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y24">
         <v>14.5</v>
@@ -6543,10 +6543,10 @@
         <v>44</v>
       </c>
       <c r="AF24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG24">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH24">
         <v>17</v>
@@ -6558,7 +6558,7 @@
         <v>27</v>
       </c>
       <c r="AK24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL24">
         <v>38</v>
@@ -6567,7 +6567,7 @@
         <v>95</v>
       </c>
       <c r="AN24">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO24">
         <v>42</v>
@@ -6579,7 +6579,7 @@
         <v>13</v>
       </c>
       <c r="AR24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS24">
         <v>60</v>
@@ -6591,25 +6591,25 @@
         <v>7.4</v>
       </c>
       <c r="AV24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW24">
         <v>38</v>
       </c>
       <c r="AX24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY24">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ24">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA24">
         <v>46</v>
       </c>
       <c r="BB24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC24">
         <v>20</v>
@@ -6618,73 +6618,73 @@
         <v>32</v>
       </c>
       <c r="BE24">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF24">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG24">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BH24">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BI24">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ24">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK24">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BL24">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM24">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BN24">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BO24">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP24">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BQ24">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BR24">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BS24">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="BT24">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BU24">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV24">
+        <v>30</v>
+      </c>
+      <c r="BW24">
+        <v>12</v>
+      </c>
+      <c r="BX24">
         <v>40</v>
       </c>
-      <c r="BW24">
-        <v>5.2</v>
-      </c>
-      <c r="BX24">
-        <v>55</v>
-      </c>
       <c r="BY24">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="BZ24">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="CA24">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="CB24" t="s">
         <v>177</v>
@@ -6710,13 +6710,13 @@
         <v>3.15</v>
       </c>
       <c r="G25">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H25">
         <v>2.44</v>
       </c>
       <c r="I25">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J25">
         <v>3.55</v>
@@ -6731,22 +6731,22 @@
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O25">
         <v>1.31</v>
       </c>
       <c r="P25">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q25">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R25">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S25">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T25">
         <v>1.74</v>
@@ -6755,19 +6755,19 @@
         <v>2.28</v>
       </c>
       <c r="V25">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W25">
         <v>1.45</v>
       </c>
       <c r="X25">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y25">
         <v>11</v>
       </c>
       <c r="Z25">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA25">
         <v>34</v>
@@ -6779,16 +6779,16 @@
         <v>8</v>
       </c>
       <c r="AD25">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE25">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF25">
         <v>22</v>
       </c>
       <c r="AG25">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH25">
         <v>16.5</v>
@@ -6800,13 +6800,13 @@
         <v>55</v>
       </c>
       <c r="AK25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL25">
         <v>44</v>
       </c>
       <c r="AM25">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN25">
         <v>32</v>
@@ -6815,7 +6815,7 @@
         <v>19.5</v>
       </c>
       <c r="AP25">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ25">
         <v>10</v>
@@ -6830,10 +6830,10 @@
         <v>12</v>
       </c>
       <c r="AU25">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV25">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW25">
         <v>23</v>
@@ -6845,88 +6845,88 @@
         <v>12</v>
       </c>
       <c r="AZ25">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA25">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB25">
         <v>46</v>
       </c>
       <c r="BC25">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BD25">
         <v>40</v>
       </c>
       <c r="BE25">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BF25">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BG25">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH25">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BI25">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ25">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK25">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL25">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM25">
-        <v>4.7</v>
+        <v>28</v>
       </c>
       <c r="BN25">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO25">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BP25">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BQ25">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BR25">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BS25">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="BT25">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BU25">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV25">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BW25">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX25">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BY25">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BZ25">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="CA25">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="CB25" t="s">
         <v>177</v>
@@ -6949,25 +6949,25 @@
         <v>167</v>
       </c>
       <c r="F26">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="G26">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H26">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I26">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="J26">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K26">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L26">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M26">
         <v>1.05</v>
@@ -6976,13 +6976,13 @@
         <v>5.2</v>
       </c>
       <c r="O26">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P26">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q26">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R26">
         <v>1.56</v>
@@ -6994,28 +6994,28 @@
         <v>1.6</v>
       </c>
       <c r="U26">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W26">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="X26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y26">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z26">
         <v>28</v>
       </c>
       <c r="AA26">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB26">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -7027,7 +7027,7 @@
         <v>36</v>
       </c>
       <c r="AF26">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG26">
         <v>11</v>
@@ -7039,64 +7039,64 @@
         <v>40</v>
       </c>
       <c r="AJ26">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL26">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM26">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO26">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AP26">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ26">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS26">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT26">
         <v>12</v>
       </c>
       <c r="AU26">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV26">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW26">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AX26">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY26">
         <v>10</v>
       </c>
       <c r="AZ26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA26">
         <v>34</v>
       </c>
       <c r="BB26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC26">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD26">
         <v>26</v>
@@ -7108,67 +7108,67 @@
         <v>11</v>
       </c>
       <c r="BG26">
+        <v>24</v>
+      </c>
+      <c r="BH26">
+        <v>4.1</v>
+      </c>
+      <c r="BI26">
+        <v>3.8</v>
+      </c>
+      <c r="BJ26">
+        <v>8.6</v>
+      </c>
+      <c r="BK26">
+        <v>7.6</v>
+      </c>
+      <c r="BL26">
+        <v>100</v>
+      </c>
+      <c r="BM26">
         <v>22</v>
       </c>
-      <c r="BH26">
-        <v>1000</v>
-      </c>
-      <c r="BI26">
-        <v>3.45</v>
-      </c>
-      <c r="BJ26">
-        <v>1000</v>
-      </c>
-      <c r="BK26">
-        <v>5.3</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>2.26</v>
-      </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO26">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ26">
         <v>8</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS26">
-        <v>2.26</v>
+        <v>10</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU26">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW26">
-        <v>2.26</v>
+        <v>10.5</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY26">
-        <v>2.26</v>
+        <v>10.5</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA26">
-        <v>2.26</v>
+        <v>8.6</v>
       </c>
       <c r="CB26" t="s">
         <v>177</v>
@@ -7191,25 +7191,25 @@
         <v>168</v>
       </c>
       <c r="F27">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G27">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H27">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I27">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J27">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K27">
         <v>3.8</v>
       </c>
       <c r="L27">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M27">
         <v>1.07</v>
@@ -7221,28 +7221,28 @@
         <v>1.32</v>
       </c>
       <c r="P27">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q27">
         <v>1.99</v>
       </c>
       <c r="R27">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S27">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T27">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U27">
         <v>2.18</v>
       </c>
       <c r="V27">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W27">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X27">
         <v>15</v>
@@ -7257,7 +7257,7 @@
         <v>80</v>
       </c>
       <c r="AB27">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -7266,16 +7266,16 @@
         <v>15.5</v>
       </c>
       <c r="AE27">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF27">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG27">
         <v>10.5</v>
       </c>
       <c r="AH27">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI27">
         <v>55</v>
@@ -7287,10 +7287,10 @@
         <v>22</v>
       </c>
       <c r="AL27">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM27">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN27">
         <v>16</v>
@@ -7299,16 +7299,16 @@
         <v>48</v>
       </c>
       <c r="AP27">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ27">
         <v>13</v>
       </c>
       <c r="AR27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS27">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT27">
         <v>8.800000000000001</v>
@@ -7320,25 +7320,25 @@
         <v>14.5</v>
       </c>
       <c r="AW27">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX27">
         <v>12</v>
       </c>
       <c r="AY27">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ27">
         <v>16</v>
       </c>
       <c r="BA27">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC27">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD27">
         <v>32</v>
@@ -7347,70 +7347,70 @@
         <v>75</v>
       </c>
       <c r="BF27">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG27">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH27">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="BI27">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ27">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BK27">
+        <v>8.4</v>
+      </c>
+      <c r="BL27">
+        <v>140</v>
+      </c>
+      <c r="BM27">
+        <v>26</v>
+      </c>
+      <c r="BN27">
+        <v>4.9</v>
+      </c>
+      <c r="BO27">
+        <v>4.4</v>
+      </c>
+      <c r="BP27">
+        <v>15.5</v>
+      </c>
+      <c r="BQ27">
+        <v>7.8</v>
+      </c>
+      <c r="BR27">
+        <v>29</v>
+      </c>
+      <c r="BS27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT27">
         <v>7.2</v>
       </c>
-      <c r="BL27">
-        <v>1000</v>
-      </c>
-      <c r="BM27">
-        <v>4.4</v>
-      </c>
-      <c r="BN27">
-        <v>5.6</v>
-      </c>
-      <c r="BO27">
-        <v>3.95</v>
-      </c>
-      <c r="BP27">
-        <v>21</v>
-      </c>
-      <c r="BQ27">
+      <c r="BU27">
+        <v>6.2</v>
+      </c>
+      <c r="BV27">
+        <v>32</v>
+      </c>
+      <c r="BW27">
+        <v>10</v>
+      </c>
+      <c r="BX27">
+        <v>42</v>
+      </c>
+      <c r="BY27">
         <v>11</v>
       </c>
-      <c r="BR27">
-        <v>40</v>
-      </c>
-      <c r="BS27">
-        <v>4</v>
-      </c>
-      <c r="BT27">
-        <v>8.6</v>
-      </c>
-      <c r="BU27">
-        <v>5.4</v>
-      </c>
-      <c r="BV27">
-        <v>44</v>
-      </c>
-      <c r="BW27">
-        <v>4</v>
-      </c>
-      <c r="BX27">
-        <v>55</v>
-      </c>
-      <c r="BY27">
-        <v>4</v>
-      </c>
       <c r="BZ27">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="CA27">
-        <v>3.9</v>
+        <v>9.4</v>
       </c>
       <c r="CB27" t="s">
         <v>177</v>
@@ -7433,31 +7433,31 @@
         <v>169</v>
       </c>
       <c r="F28">
+        <v>5.8</v>
+      </c>
+      <c r="G28">
         <v>5.9</v>
       </c>
-      <c r="G28">
-        <v>6</v>
-      </c>
       <c r="H28">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="I28">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="J28">
+        <v>4.4</v>
+      </c>
+      <c r="K28">
         <v>4.5</v>
       </c>
-      <c r="K28">
-        <v>4.6</v>
-      </c>
       <c r="L28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M28">
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O28">
         <v>1.19</v>
@@ -7469,10 +7469,10 @@
         <v>1.59</v>
       </c>
       <c r="R28">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S28">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T28">
         <v>1.69</v>
@@ -7481,13 +7481,13 @@
         <v>2.38</v>
       </c>
       <c r="V28">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="W28">
         <v>1.2</v>
       </c>
       <c r="X28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y28">
         <v>12.5</v>
@@ -7496,7 +7496,7 @@
         <v>11.5</v>
       </c>
       <c r="AA28">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB28">
         <v>28</v>
@@ -7514,16 +7514,16 @@
         <v>50</v>
       </c>
       <c r="AG28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH28">
         <v>17</v>
       </c>
       <c r="AI28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ28">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="AK28">
         <v>65</v>
@@ -7532,10 +7532,10 @@
         <v>60</v>
       </c>
       <c r="AM28">
-        <v>310</v>
+        <v>75</v>
       </c>
       <c r="AN28">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AO28">
         <v>6.4</v>
@@ -7553,7 +7553,7 @@
         <v>14.5</v>
       </c>
       <c r="AT28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU28">
         <v>9.800000000000001</v>
@@ -7562,10 +7562,10 @@
         <v>9.4</v>
       </c>
       <c r="AW28">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX28">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AY28">
         <v>19.5</v>
@@ -7592,67 +7592,67 @@
         <v>48</v>
       </c>
       <c r="BG28">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH28">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BI28">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BJ28">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK28">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM28">
-        <v>5.7</v>
+        <v>23</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO28">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BP28">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BQ28">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="BR28">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BS28">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="BT28">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BU28">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BV28">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BW28">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX28">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BY28">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="BZ28">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA28">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB28" t="s">
         <v>177</v>
@@ -7675,16 +7675,16 @@
         <v>170</v>
       </c>
       <c r="F29">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="G29">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="H29">
+        <v>4.3</v>
+      </c>
+      <c r="I29">
         <v>4.4</v>
-      </c>
-      <c r="I29">
-        <v>4.5</v>
       </c>
       <c r="J29">
         <v>4.2</v>
@@ -7693,40 +7693,40 @@
         <v>4.3</v>
       </c>
       <c r="L29">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M29">
         <v>1.03</v>
       </c>
       <c r="N29">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O29">
         <v>1.16</v>
       </c>
       <c r="P29">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q29">
         <v>1.51</v>
       </c>
       <c r="R29">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S29">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T29">
         <v>1.53</v>
       </c>
       <c r="U29">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="V29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W29">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X29">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>26</v>
       </c>
       <c r="Z29">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA29">
         <v>85</v>
@@ -7744,7 +7744,7 @@
         <v>15</v>
       </c>
       <c r="AC29">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD29">
         <v>17.5</v>
@@ -7756,40 +7756,40 @@
         <v>15.5</v>
       </c>
       <c r="AG29">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH29">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI29">
         <v>40</v>
       </c>
       <c r="AJ29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK29">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM29">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN29">
         <v>7.4</v>
       </c>
       <c r="AO29">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP29">
         <v>26</v>
       </c>
       <c r="AQ29">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR29">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS29">
         <v>70</v>
@@ -7798,7 +7798,7 @@
         <v>13.5</v>
       </c>
       <c r="AU29">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV29">
         <v>16.5</v>
@@ -7807,34 +7807,34 @@
         <v>38</v>
       </c>
       <c r="AX29">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY29">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA29">
         <v>36</v>
       </c>
       <c r="BB29">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC29">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD29">
         <v>22</v>
       </c>
       <c r="BE29">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF29">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG29">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BH29">
         <v>4.7</v>
@@ -7849,22 +7849,22 @@
         <v>7.8</v>
       </c>
       <c r="BL29">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BM29">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BN29">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO29">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP29">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ29">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR29">
         <v>19.5</v>
@@ -7873,22 +7873,22 @@
         <v>16.5</v>
       </c>
       <c r="BT29">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU29">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BV29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW29">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BX29">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY29">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BZ29">
         <v>13</v>
@@ -7917,22 +7917,22 @@
         <v>171</v>
       </c>
       <c r="F30">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G30">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="H30">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="I30">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="J30">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K30">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L30">
         <v>1.34</v>
@@ -7941,109 +7941,109 @@
         <v>1.05</v>
       </c>
       <c r="N30">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O30">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P30">
+        <v>2.38</v>
+      </c>
+      <c r="Q30">
+        <v>1.71</v>
+      </c>
+      <c r="R30">
+        <v>1.55</v>
+      </c>
+      <c r="S30">
+        <v>2.78</v>
+      </c>
+      <c r="T30">
+        <v>1.73</v>
+      </c>
+      <c r="U30">
         <v>2.32</v>
       </c>
-      <c r="Q30">
-        <v>1.73</v>
-      </c>
-      <c r="R30">
-        <v>1.51</v>
-      </c>
-      <c r="S30">
-        <v>2.84</v>
-      </c>
-      <c r="T30">
-        <v>1.74</v>
-      </c>
-      <c r="U30">
-        <v>2.26</v>
-      </c>
       <c r="V30">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="W30">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X30">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y30">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z30">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA30">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB30">
         <v>21</v>
       </c>
       <c r="AC30">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD30">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE30">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF30">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AG30">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH30">
         <v>17.5</v>
       </c>
       <c r="AI30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ30">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK30">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL30">
         <v>60</v>
       </c>
       <c r="AM30">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN30">
-        <v>280</v>
+        <v>60</v>
       </c>
       <c r="AO30">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AP30">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AQ30">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS30">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU30">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV30">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW30">
         <v>15</v>
@@ -8052,19 +8052,19 @@
         <v>38</v>
       </c>
       <c r="AY30">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AZ30">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA30">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB30">
         <v>100</v>
       </c>
       <c r="BC30">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD30">
         <v>50</v>
@@ -8076,13 +8076,13 @@
         <v>50</v>
       </c>
       <c r="BG30">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH30">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI30">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ30">
         <v>9.6</v>
@@ -8091,28 +8091,28 @@
         <v>8.4</v>
       </c>
       <c r="BL30">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM30">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BN30">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BO30">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BP30">
         <v>40</v>
       </c>
       <c r="BQ30">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BR30">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BS30">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="BT30">
         <v>4.5</v>
@@ -8130,13 +8130,13 @@
         <v>23</v>
       </c>
       <c r="BY30">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BZ30">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA30">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB30" t="s">
         <v>177</v>
@@ -8159,19 +8159,19 @@
         <v>172</v>
       </c>
       <c r="F31">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G31">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H31">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I31">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J31">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K31">
         <v>3.65</v>
@@ -8180,43 +8180,43 @@
         <v>1.39</v>
       </c>
       <c r="M31">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N31">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O31">
         <v>1.29</v>
       </c>
       <c r="P31">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q31">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="R31">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S31">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T31">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U31">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W31">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="X31">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y31">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z31">
         <v>24</v>
@@ -8228,19 +8228,19 @@
         <v>11</v>
       </c>
       <c r="AC31">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD31">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF31">
         <v>14.5</v>
       </c>
       <c r="AG31">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH31">
         <v>15.5</v>
@@ -8249,37 +8249,37 @@
         <v>44</v>
       </c>
       <c r="AJ31">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK31">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL31">
         <v>34</v>
       </c>
       <c r="AM31">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN31">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AO31">
         <v>34</v>
       </c>
       <c r="AP31">
+        <v>14.5</v>
+      </c>
+      <c r="AQ31">
         <v>14</v>
       </c>
-      <c r="AQ31">
-        <v>13</v>
-      </c>
       <c r="AR31">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS31">
         <v>55</v>
       </c>
       <c r="AT31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU31">
         <v>7.6</v>
@@ -8291,7 +8291,7 @@
         <v>34</v>
       </c>
       <c r="AX31">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY31">
         <v>10.5</v>
@@ -8300,7 +8300,7 @@
         <v>15</v>
       </c>
       <c r="BA31">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB31">
         <v>27</v>
@@ -8312,19 +8312,19 @@
         <v>30</v>
       </c>
       <c r="BE31">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF31">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH31">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI31">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ31">
         <v>9</v>
@@ -8333,10 +8333,10 @@
         <v>8</v>
       </c>
       <c r="BL31">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM31">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BN31">
         <v>5.2</v>
@@ -8345,40 +8345,40 @@
         <v>4.8</v>
       </c>
       <c r="BP31">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ31">
         <v>14</v>
       </c>
       <c r="BR31">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS31">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT31">
         <v>6.6</v>
       </c>
       <c r="BU31">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV31">
         <v>25</v>
       </c>
       <c r="BW31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY31">
         <v>13</v>
       </c>
       <c r="BZ31">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CA31">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="CB31" t="s">
         <v>177</v>
@@ -8401,16 +8401,16 @@
         <v>173</v>
       </c>
       <c r="F32">
+        <v>1.64</v>
+      </c>
+      <c r="G32">
         <v>1.65</v>
       </c>
-      <c r="G32">
-        <v>1.66</v>
-      </c>
       <c r="H32">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I32">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J32">
         <v>4.6</v>
@@ -8419,7 +8419,7 @@
         <v>4.7</v>
       </c>
       <c r="L32">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M32">
         <v>1.03</v>
@@ -8431,43 +8431,43 @@
         <v>1.14</v>
       </c>
       <c r="P32">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q32">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R32">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S32">
         <v>2.14</v>
       </c>
       <c r="T32">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U32">
         <v>2.76</v>
       </c>
       <c r="V32">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W32">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X32">
         <v>34</v>
       </c>
       <c r="Y32">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z32">
         <v>55</v>
       </c>
       <c r="AA32">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB32">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC32">
         <v>11.5</v>
@@ -8479,7 +8479,7 @@
         <v>55</v>
       </c>
       <c r="AF32">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG32">
         <v>9.800000000000001</v>
@@ -8503,7 +8503,7 @@
         <v>55</v>
       </c>
       <c r="AN32">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AO32">
         <v>44</v>
@@ -8512,16 +8512,16 @@
         <v>32</v>
       </c>
       <c r="AQ32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR32">
         <v>48</v>
       </c>
       <c r="AS32">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AT32">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU32">
         <v>10.5</v>
@@ -8566,7 +8566,7 @@
         <v>4.9</v>
       </c>
       <c r="BI32">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ32">
         <v>8.800000000000001</v>
@@ -8578,43 +8578,43 @@
         <v>70</v>
       </c>
       <c r="BM32">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN32">
         <v>4.8</v>
       </c>
       <c r="BO32">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP32">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BQ32">
         <v>8.800000000000001</v>
       </c>
       <c r="BR32">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BS32">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BT32">
         <v>9</v>
       </c>
       <c r="BU32">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BV32">
         <v>34</v>
       </c>
       <c r="BW32">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="BX32">
         <v>34</v>
       </c>
       <c r="BY32">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="BZ32">
         <v>11.5</v>
@@ -8643,16 +8643,16 @@
         <v>174</v>
       </c>
       <c r="F33">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G33">
         <v>2.48</v>
       </c>
       <c r="H33">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I33">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J33">
         <v>3.2</v>
@@ -8667,7 +8667,7 @@
         <v>1.1</v>
       </c>
       <c r="N33">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O33">
         <v>1.43</v>
@@ -8676,7 +8676,7 @@
         <v>1.69</v>
       </c>
       <c r="Q33">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R33">
         <v>1.25</v>
@@ -8694,7 +8694,7 @@
         <v>1.38</v>
       </c>
       <c r="W33">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X33">
         <v>12.5</v>
@@ -8748,7 +8748,7 @@
         <v>30</v>
       </c>
       <c r="AO33">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AP33">
         <v>9</v>
@@ -8757,7 +8757,7 @@
         <v>9.4</v>
       </c>
       <c r="AR33">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS33">
         <v>6</v>
@@ -8766,7 +8766,7 @@
         <v>7.4</v>
       </c>
       <c r="AU33">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV33">
         <v>12.5</v>
@@ -8793,76 +8793,76 @@
         <v>5.4</v>
       </c>
       <c r="BD33">
-        <v>40</v>
+        <v>5.9</v>
       </c>
       <c r="BE33">
         <v>6.2</v>
       </c>
       <c r="BF33">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG33">
         <v>6</v>
       </c>
       <c r="BH33">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI33">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BJ33">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK33">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BN33">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO33">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP33">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ33">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR33">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS33">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BT33">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU33">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV33">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW33">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BX33">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY33">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BZ33">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA33">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="CB33" t="s">
         <v>177</v>
@@ -8885,76 +8885,76 @@
         <v>175</v>
       </c>
       <c r="F34">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="G34">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="H34">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I34">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K34">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L34">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="M34">
         <v>1.14</v>
       </c>
       <c r="N34">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="O34">
+        <v>1.63</v>
+      </c>
+      <c r="P34">
+        <v>1.5</v>
+      </c>
+      <c r="Q34">
+        <v>2.96</v>
+      </c>
+      <c r="R34">
+        <v>1.17</v>
+      </c>
+      <c r="S34">
+        <v>6.4</v>
+      </c>
+      <c r="T34">
+        <v>2.62</v>
+      </c>
+      <c r="U34">
         <v>1.58</v>
       </c>
-      <c r="P34">
-        <v>1.54</v>
-      </c>
-      <c r="Q34">
-        <v>2.8</v>
-      </c>
-      <c r="R34">
-        <v>1.19</v>
-      </c>
-      <c r="S34">
-        <v>5.8</v>
-      </c>
-      <c r="T34">
-        <v>2.56</v>
-      </c>
-      <c r="U34">
-        <v>1.57</v>
-      </c>
       <c r="V34">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W34">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X34">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y34">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z34">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AA34">
         <v>900</v>
       </c>
       <c r="AB34">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AC34">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD34">
         <v>34</v>
@@ -8963,46 +8963,46 @@
         <v>700</v>
       </c>
       <c r="AF34">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG34">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH34">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AI34">
         <v>700</v>
       </c>
       <c r="AJ34">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AK34">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AL34">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM34">
         <v>580</v>
       </c>
       <c r="AN34">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AO34">
         <v>700</v>
       </c>
       <c r="AP34">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AQ34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR34">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="AS34">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT34">
         <v>5.2</v>
@@ -9011,52 +9011,52 @@
         <v>7.6</v>
       </c>
       <c r="AV34">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AW34">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX34">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY34">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ34">
         <v>30</v>
       </c>
       <c r="BA34">
+        <v>12</v>
+      </c>
+      <c r="BB34">
+        <v>15</v>
+      </c>
+      <c r="BC34">
+        <v>22</v>
+      </c>
+      <c r="BD34">
+        <v>12</v>
+      </c>
+      <c r="BE34">
+        <v>13.5</v>
+      </c>
+      <c r="BF34">
+        <v>17</v>
+      </c>
+      <c r="BG34">
+        <v>12.5</v>
+      </c>
+      <c r="BH34">
+        <v>2.56</v>
+      </c>
+      <c r="BI34">
+        <v>2.4</v>
+      </c>
+      <c r="BJ34">
+        <v>14</v>
+      </c>
+      <c r="BK34">
         <v>11.5</v>
-      </c>
-      <c r="BB34">
-        <v>14.5</v>
-      </c>
-      <c r="BC34">
-        <v>20</v>
-      </c>
-      <c r="BD34">
-        <v>11</v>
-      </c>
-      <c r="BE34">
-        <v>12</v>
-      </c>
-      <c r="BF34">
-        <v>15.5</v>
-      </c>
-      <c r="BG34">
-        <v>12</v>
-      </c>
-      <c r="BH34">
-        <v>1000</v>
-      </c>
-      <c r="BI34">
-        <v>2.34</v>
-      </c>
-      <c r="BJ34">
-        <v>20</v>
-      </c>
-      <c r="BK34">
-        <v>8.4</v>
       </c>
       <c r="BL34">
         <v>1000</v>
@@ -9065,28 +9065,28 @@
         <v>21</v>
       </c>
       <c r="BN34">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BO34">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="BP34">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BQ34">
+        <v>12</v>
+      </c>
+      <c r="BR34">
+        <v>48</v>
+      </c>
+      <c r="BS34">
+        <v>36</v>
+      </c>
+      <c r="BT34">
+        <v>10</v>
+      </c>
+      <c r="BU34">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BR34">
-        <v>1000</v>
-      </c>
-      <c r="BS34">
-        <v>21</v>
-      </c>
-      <c r="BT34">
-        <v>14.5</v>
-      </c>
-      <c r="BU34">
-        <v>6.8</v>
       </c>
       <c r="BV34">
         <v>1000</v>
@@ -9104,7 +9104,7 @@
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="CB34" t="s">
         <v>177</v>
@@ -9127,13 +9127,13 @@
         <v>176</v>
       </c>
       <c r="F35">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G35">
         <v>2</v>
       </c>
       <c r="H35">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I35">
         <v>5.4</v>
@@ -9151,7 +9151,7 @@
         <v>1.13</v>
       </c>
       <c r="N35">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O35">
         <v>1.58</v>
@@ -9166,7 +9166,7 @@
         <v>1.19</v>
       </c>
       <c r="S35">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T35">
         <v>2.3</v>
@@ -9208,7 +9208,7 @@
         <v>10.5</v>
       </c>
       <c r="AG35">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AH35">
         <v>28</v>
@@ -9226,13 +9226,13 @@
         <v>75</v>
       </c>
       <c r="AM35">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN35">
         <v>25</v>
       </c>
       <c r="AO35">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP35">
         <v>7.6</v>
@@ -9241,10 +9241,10 @@
         <v>11</v>
       </c>
       <c r="AR35">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS35">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AT35">
         <v>5.8</v>
@@ -9256,7 +9256,7 @@
         <v>19.5</v>
       </c>
       <c r="AW35">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX35">
         <v>9</v>
@@ -9265,88 +9265,88 @@
         <v>10</v>
       </c>
       <c r="AZ35">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="BA35">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB35">
         <v>20</v>
       </c>
       <c r="BC35">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="BD35">
+        <v>11</v>
+      </c>
+      <c r="BE35">
         <v>12.5</v>
-      </c>
-      <c r="BE35">
-        <v>15</v>
       </c>
       <c r="BF35">
         <v>17.5</v>
       </c>
       <c r="BG35">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BH35">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="BI35">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="BJ35">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="BK35">
-        <v>1.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.76</v>
+        <v>18</v>
       </c>
       <c r="BN35">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BO35">
-        <v>1.29</v>
+        <v>3.9</v>
       </c>
       <c r="BP35">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BQ35">
-        <v>1.63</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR35">
         <v>1000</v>
       </c>
       <c r="BS35">
-        <v>1.71</v>
+        <v>13.5</v>
       </c>
       <c r="BT35">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="BU35">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="BV35">
         <v>1000</v>
       </c>
       <c r="BW35">
-        <v>1.73</v>
+        <v>14.5</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>1.76</v>
+        <v>15.5</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>1.71</v>
+        <v>13.5</v>
       </c>
       <c r="CB35" t="s">
         <v>177</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -547,7 +547,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-09-08 04:08:25</t>
+    <t>2026-09-08 06:20:18</t>
   </si>
 </sst>
 </file>
@@ -1141,58 +1141,58 @@
         <v>143</v>
       </c>
       <c r="F2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G2">
         <v>4.1</v>
       </c>
       <c r="H2">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="I2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O2">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P2">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q2">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R2">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S2">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U2">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V2">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="W2">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X2">
         <v>22</v>
@@ -1216,82 +1216,82 @@
         <v>10.5</v>
       </c>
       <c r="AE2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AF2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ2">
         <v>75</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL2">
         <v>42</v>
       </c>
       <c r="AM2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN2">
         <v>32</v>
       </c>
       <c r="AO2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AP2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR2">
         <v>13</v>
       </c>
       <c r="AS2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU2">
         <v>8.4</v>
       </c>
       <c r="AV2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BC2">
+        <v>34</v>
+      </c>
+      <c r="BD2">
         <v>36</v>
-      </c>
-      <c r="BD2">
-        <v>38</v>
       </c>
       <c r="BE2">
         <v>50</v>
@@ -1300,67 +1300,67 @@
         <v>28</v>
       </c>
       <c r="BG2">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BH2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BI2">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BJ2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK2">
         <v>8</v>
       </c>
       <c r="BL2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM2">
+        <v>65</v>
+      </c>
+      <c r="BN2">
+        <v>7.2</v>
+      </c>
+      <c r="BO2">
+        <v>6.4</v>
+      </c>
+      <c r="BP2">
+        <v>25</v>
+      </c>
+      <c r="BQ2">
+        <v>10.5</v>
+      </c>
+      <c r="BR2">
+        <v>32</v>
+      </c>
+      <c r="BS2">
+        <v>11.5</v>
+      </c>
+      <c r="BT2">
+        <v>5.2</v>
+      </c>
+      <c r="BU2">
+        <v>4.8</v>
+      </c>
+      <c r="BV2">
         <v>14</v>
       </c>
-      <c r="BN2">
-        <v>7.4</v>
-      </c>
-      <c r="BO2">
-        <v>6.6</v>
-      </c>
-      <c r="BP2">
-        <v>27</v>
-      </c>
-      <c r="BQ2">
-        <v>10</v>
-      </c>
-      <c r="BR2">
-        <v>34</v>
-      </c>
-      <c r="BS2">
-        <v>11</v>
-      </c>
-      <c r="BT2">
-        <v>5.1</v>
-      </c>
-      <c r="BU2">
-        <v>4.6</v>
-      </c>
-      <c r="BV2">
-        <v>13.5</v>
-      </c>
       <c r="BW2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX2">
         <v>23</v>
       </c>
       <c r="BY2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="s">
         <v>177</v>
@@ -1383,226 +1383,226 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="G3">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="H3">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O3">
         <v>1.42</v>
       </c>
       <c r="P3">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T3">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="X3">
         <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB3">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
+        <v>17.5</v>
+      </c>
+      <c r="AE3">
+        <v>65</v>
+      </c>
+      <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
+        <v>11</v>
+      </c>
+      <c r="AH3">
+        <v>21</v>
+      </c>
+      <c r="AI3">
+        <v>75</v>
+      </c>
+      <c r="AJ3">
+        <v>23</v>
+      </c>
+      <c r="AK3">
+        <v>24</v>
+      </c>
+      <c r="AL3">
+        <v>44</v>
+      </c>
+      <c r="AM3">
+        <v>130</v>
+      </c>
+      <c r="AN3">
         <v>19</v>
       </c>
-      <c r="AE3">
-        <v>80</v>
-      </c>
-      <c r="AF3">
-        <v>10.5</v>
-      </c>
-      <c r="AG3">
-        <v>10.5</v>
-      </c>
-      <c r="AH3">
-        <v>22</v>
-      </c>
-      <c r="AI3">
-        <v>85</v>
-      </c>
-      <c r="AJ3">
-        <v>22</v>
-      </c>
-      <c r="AK3">
-        <v>23</v>
-      </c>
-      <c r="AL3">
-        <v>48</v>
-      </c>
-      <c r="AM3">
-        <v>160</v>
-      </c>
-      <c r="AN3">
-        <v>17.5</v>
-      </c>
       <c r="AO3">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AP3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
         <v>12.5</v>
       </c>
       <c r="AR3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AS3">
+        <v>65</v>
+      </c>
+      <c r="AT3">
+        <v>7.4</v>
+      </c>
+      <c r="AU3">
+        <v>7</v>
+      </c>
+      <c r="AV3">
+        <v>16</v>
+      </c>
+      <c r="AW3">
+        <v>55</v>
+      </c>
+      <c r="AX3">
+        <v>10.5</v>
+      </c>
+      <c r="AY3">
+        <v>10</v>
+      </c>
+      <c r="AZ3">
+        <v>18.5</v>
+      </c>
+      <c r="BA3">
+        <v>60</v>
+      </c>
+      <c r="BB3">
+        <v>21</v>
+      </c>
+      <c r="BC3">
+        <v>21</v>
+      </c>
+      <c r="BD3">
         <v>40</v>
       </c>
-      <c r="AT3">
-        <v>7</v>
-      </c>
-      <c r="AU3">
-        <v>7.2</v>
-      </c>
-      <c r="AV3">
+      <c r="BE3">
+        <v>120</v>
+      </c>
+      <c r="BF3">
         <v>17</v>
       </c>
-      <c r="AW3">
-        <v>50</v>
-      </c>
-      <c r="AX3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY3">
-        <v>9.6</v>
-      </c>
-      <c r="AZ3">
-        <v>19</v>
-      </c>
-      <c r="BA3">
-        <v>65</v>
-      </c>
-      <c r="BB3">
-        <v>19.5</v>
-      </c>
-      <c r="BC3">
-        <v>20</v>
-      </c>
-      <c r="BD3">
-        <v>38</v>
-      </c>
-      <c r="BE3">
-        <v>80</v>
-      </c>
-      <c r="BF3">
-        <v>16</v>
-      </c>
       <c r="BG3">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BH3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BI3">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="BJ3">
         <v>11</v>
       </c>
       <c r="BK3">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM3">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="BN3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BR3">
         <v>34</v>
       </c>
       <c r="BS3">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="BT3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BV3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BW3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BX3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY3">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="BZ3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA3">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1625,25 +1625,25 @@
         <v>145</v>
       </c>
       <c r="F4">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="H4">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="I4">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="J4">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K4">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M4">
         <v>1.04</v>
@@ -1655,139 +1655,139 @@
         <v>1.22</v>
       </c>
       <c r="P4">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q4">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="R4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S4">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="T4">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V4">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="W4">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y4">
         <v>11</v>
       </c>
       <c r="Z4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA4">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AB4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AC4">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AD4">
         <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ4">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AK4">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AN4">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AO4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP4">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AQ4">
+        <v>9.4</v>
+      </c>
+      <c r="AR4">
         <v>9.199999999999999</v>
       </c>
-      <c r="AR4">
-        <v>10</v>
-      </c>
       <c r="AS4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AT4">
         <v>20</v>
       </c>
       <c r="AU4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4">
         <v>9</v>
       </c>
       <c r="AW4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX4">
         <v>36</v>
       </c>
       <c r="AY4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>23</v>
+        <v>6.4</v>
       </c>
       <c r="BB4">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BC4">
-        <v>48</v>
+        <v>6.8</v>
       </c>
       <c r="BD4">
-        <v>40</v>
+        <v>6.6</v>
       </c>
       <c r="BE4">
-        <v>60</v>
+        <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>36</v>
+        <v>6.8</v>
       </c>
       <c r="BG4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BH4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI4">
         <v>3.7</v>
@@ -1796,55 +1796,55 @@
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BN4">
         <v>11</v>
       </c>
       <c r="BO4">
-        <v>7</v>
+        <v>3.65</v>
       </c>
       <c r="BP4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BQ4">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BT4">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BU4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BV4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BW4">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BX4">
         <v>26</v>
       </c>
       <c r="BY4">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BZ4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CA4">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1867,25 +1867,25 @@
         <v>146</v>
       </c>
       <c r="F5">
+        <v>1.45</v>
+      </c>
+      <c r="G5">
         <v>1.47</v>
       </c>
-      <c r="G5">
-        <v>1.5</v>
-      </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="L5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M5">
         <v>1.03</v>
@@ -1897,16 +1897,16 @@
         <v>1.15</v>
       </c>
       <c r="P5">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q5">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R5">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="S5">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T5">
         <v>1.64</v>
@@ -1915,40 +1915,40 @@
         <v>2.4</v>
       </c>
       <c r="V5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="X5">
         <v>32</v>
       </c>
       <c r="Y5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z5">
         <v>80</v>
       </c>
       <c r="AA5">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AB5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD5">
         <v>29</v>
       </c>
       <c r="AE5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH5">
         <v>18.5</v>
@@ -1969,10 +1969,10 @@
         <v>90</v>
       </c>
       <c r="AN5">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AO5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP5">
         <v>26</v>
@@ -1984,7 +1984,7 @@
         <v>55</v>
       </c>
       <c r="AS5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AT5">
         <v>12</v>
@@ -1993,7 +1993,7 @@
         <v>11</v>
       </c>
       <c r="AV5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW5">
         <v>55</v>
@@ -2011,7 +2011,7 @@
         <v>42</v>
       </c>
       <c r="BB5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC5">
         <v>12</v>
@@ -2020,13 +2020,13 @@
         <v>21</v>
       </c>
       <c r="BE5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF5">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH5">
         <v>5.7</v>
@@ -2038,22 +2038,22 @@
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="BL5">
         <v>95</v>
       </c>
       <c r="BM5">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN5">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO5">
         <v>4</v>
       </c>
       <c r="BP5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BQ5">
         <v>6.8</v>
@@ -2062,7 +2062,7 @@
         <v>21</v>
       </c>
       <c r="BS5">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BT5">
         <v>11</v>
@@ -2074,19 +2074,19 @@
         <v>55</v>
       </c>
       <c r="BW5">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BX5">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BY5">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BZ5">
         <v>12</v>
       </c>
       <c r="CA5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="s">
         <v>177</v>
@@ -2109,22 +2109,22 @@
         <v>147</v>
       </c>
       <c r="F6">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="G6">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="H6">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="I6">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="J6">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K6">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
         <v>1.36</v>
@@ -2139,7 +2139,7 @@
         <v>1.26</v>
       </c>
       <c r="P6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q6">
         <v>1.78</v>
@@ -2148,28 +2148,28 @@
         <v>1.48</v>
       </c>
       <c r="S6">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T6">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U6">
         <v>2.42</v>
       </c>
       <c r="V6">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y6">
         <v>13.5</v>
       </c>
       <c r="Z6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA6">
         <v>38</v>
@@ -2178,7 +2178,7 @@
         <v>14</v>
       </c>
       <c r="AC6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD6">
         <v>12</v>
@@ -2187,22 +2187,22 @@
         <v>27</v>
       </c>
       <c r="AF6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH6">
         <v>15.5</v>
       </c>
       <c r="AI6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ6">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AK6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6">
         <v>36</v>
@@ -2211,25 +2211,25 @@
         <v>70</v>
       </c>
       <c r="AN6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO6">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AP6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ6">
+        <v>12.5</v>
+      </c>
+      <c r="AR6">
+        <v>17.5</v>
+      </c>
+      <c r="AS6">
+        <v>36</v>
+      </c>
+      <c r="AT6">
         <v>12</v>
-      </c>
-      <c r="AR6">
-        <v>17</v>
-      </c>
-      <c r="AS6">
-        <v>32</v>
-      </c>
-      <c r="AT6">
-        <v>13</v>
       </c>
       <c r="AU6">
         <v>7.8</v>
@@ -2238,25 +2238,25 @@
         <v>11</v>
       </c>
       <c r="AW6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY6">
         <v>11.5</v>
       </c>
       <c r="AZ6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA6">
         <v>30</v>
       </c>
       <c r="BB6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BC6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD6">
         <v>32</v>
@@ -2265,16 +2265,16 @@
         <v>60</v>
       </c>
       <c r="BF6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BH6">
         <v>3.85</v>
       </c>
       <c r="BI6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ6">
         <v>8.800000000000001</v>
@@ -2283,46 +2283,46 @@
         <v>7.8</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN6">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BO6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ6">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BR6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS6">
         <v>11</v>
       </c>
       <c r="BT6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BU6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BW6">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX6">
         <v>28</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
         <v>21</v>
@@ -2354,7 +2354,7 @@
         <v>2.16</v>
       </c>
       <c r="G7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H7">
         <v>3.8</v>
@@ -2393,19 +2393,19 @@
         <v>3.8</v>
       </c>
       <c r="T7">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U7">
         <v>2.1</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y7">
         <v>13.5</v>
@@ -2432,16 +2432,16 @@
         <v>13.5</v>
       </c>
       <c r="AG7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH7">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK7">
         <v>25</v>
@@ -2450,7 +2450,7 @@
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
         <v>18.5</v>
@@ -2459,7 +2459,7 @@
         <v>55</v>
       </c>
       <c r="AP7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7">
         <v>12</v>
@@ -2483,7 +2483,7 @@
         <v>40</v>
       </c>
       <c r="AX7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY7">
         <v>10</v>
@@ -2492,16 +2492,16 @@
         <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC7">
         <v>20</v>
       </c>
       <c r="BD7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE7">
         <v>65</v>
@@ -2519,34 +2519,34 @@
         <v>3</v>
       </c>
       <c r="BJ7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL7">
         <v>140</v>
       </c>
       <c r="BM7">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN7">
         <v>4.9</v>
       </c>
       <c r="BO7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP7">
         <v>16</v>
       </c>
       <c r="BQ7">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BR7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT7">
         <v>7</v>
@@ -2555,22 +2555,22 @@
         <v>6.2</v>
       </c>
       <c r="BV7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW7">
+        <v>11</v>
+      </c>
+      <c r="BX7">
+        <v>46</v>
+      </c>
+      <c r="BY7">
         <v>12</v>
-      </c>
-      <c r="BX7">
-        <v>44</v>
-      </c>
-      <c r="BY7">
-        <v>13</v>
       </c>
       <c r="BZ7">
         <v>30</v>
       </c>
       <c r="CA7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="s">
         <v>177</v>
@@ -2593,22 +2593,22 @@
         <v>149</v>
       </c>
       <c r="F8">
+        <v>1.65</v>
+      </c>
+      <c r="G8">
         <v>1.67</v>
       </c>
-      <c r="G8">
-        <v>1.7</v>
-      </c>
       <c r="H8">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I8">
         <v>5.7</v>
       </c>
       <c r="J8">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L8">
         <v>1.32</v>
@@ -2617,7 +2617,7 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O8">
         <v>1.22</v>
@@ -2629,13 +2629,13 @@
         <v>1.68</v>
       </c>
       <c r="R8">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S8">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T8">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U8">
         <v>2.26</v>
@@ -2644,7 +2644,7 @@
         <v>1.21</v>
       </c>
       <c r="W8">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="X8">
         <v>22</v>
@@ -2653,28 +2653,28 @@
         <v>24</v>
       </c>
       <c r="Z8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AA8">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
+        <v>10.5</v>
+      </c>
+      <c r="AC8">
+        <v>10.5</v>
+      </c>
+      <c r="AD8">
+        <v>22</v>
+      </c>
+      <c r="AE8">
+        <v>65</v>
+      </c>
+      <c r="AF8">
         <v>11</v>
       </c>
-      <c r="AC8">
-        <v>10</v>
-      </c>
-      <c r="AD8">
-        <v>21</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>11.5</v>
-      </c>
       <c r="AG8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH8">
         <v>18.5</v>
@@ -2683,7 +2683,7 @@
         <v>65</v>
       </c>
       <c r="AJ8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK8">
         <v>16</v>
@@ -2695,10 +2695,10 @@
         <v>85</v>
       </c>
       <c r="AN8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP8">
         <v>19.5</v>
@@ -2707,25 +2707,25 @@
         <v>21</v>
       </c>
       <c r="AR8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AT8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU8">
+        <v>9.4</v>
+      </c>
+      <c r="AV8">
+        <v>19</v>
+      </c>
+      <c r="AW8">
+        <v>55</v>
+      </c>
+      <c r="AX8">
         <v>10</v>
-      </c>
-      <c r="AU8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV8">
-        <v>18.5</v>
-      </c>
-      <c r="AW8">
-        <v>50</v>
-      </c>
-      <c r="AX8">
-        <v>10.5</v>
       </c>
       <c r="AY8">
         <v>9.199999999999999</v>
@@ -2737,13 +2737,13 @@
         <v>50</v>
       </c>
       <c r="BB8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC8">
         <v>14.5</v>
       </c>
       <c r="BD8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE8">
         <v>65</v>
@@ -2758,61 +2758,61 @@
         <v>4.1</v>
       </c>
       <c r="BI8">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL8">
         <v>120</v>
       </c>
       <c r="BM8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN8">
         <v>4.5</v>
       </c>
       <c r="BO8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ8">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8">
         <v>27</v>
       </c>
       <c r="BS8">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BT8">
         <v>11</v>
       </c>
       <c r="BU8">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BV8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BW8">
         <v>6.2</v>
       </c>
       <c r="BX8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY8">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BZ8">
         <v>18.5</v>
       </c>
       <c r="CA8">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="s">
         <v>177</v>
@@ -2853,13 +2853,13 @@
         <v>4.6</v>
       </c>
       <c r="L9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M9">
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O9">
         <v>1.25</v>
@@ -2868,25 +2868,25 @@
         <v>2.26</v>
       </c>
       <c r="Q9">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R9">
         <v>1.49</v>
       </c>
       <c r="S9">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T9">
         <v>1.84</v>
       </c>
       <c r="U9">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W9">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X9">
         <v>19</v>
@@ -2898,7 +2898,7 @@
         <v>55</v>
       </c>
       <c r="AA9">
-        <v>930</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
         <v>10</v>
@@ -2916,7 +2916,7 @@
         <v>10.5</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH9">
         <v>21</v>
@@ -2925,7 +2925,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK9">
         <v>16</v>
@@ -2940,7 +2940,7 @@
         <v>7.6</v>
       </c>
       <c r="AO9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP9">
         <v>16.5</v>
@@ -2952,7 +2952,7 @@
         <v>44</v>
       </c>
       <c r="AS9">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="AT9">
         <v>9</v>
@@ -2964,7 +2964,7 @@
         <v>20</v>
       </c>
       <c r="AW9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AX9">
         <v>9.4</v>
@@ -2985,34 +2985,34 @@
         <v>14.5</v>
       </c>
       <c r="BD9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE9">
         <v>65</v>
       </c>
       <c r="BF9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG9">
         <v>65</v>
       </c>
       <c r="BH9">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI9">
         <v>3.6</v>
       </c>
       <c r="BJ9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK9">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BN9">
         <v>4.2</v>
@@ -3021,40 +3021,40 @@
         <v>3.9</v>
       </c>
       <c r="BP9">
+        <v>10.5</v>
+      </c>
+      <c r="BQ9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR9">
+        <v>25</v>
+      </c>
+      <c r="BS9">
+        <v>9</v>
+      </c>
+      <c r="BT9">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BQ9">
-        <v>6.4</v>
-      </c>
-      <c r="BR9">
-        <v>24</v>
-      </c>
-      <c r="BS9">
-        <v>10</v>
-      </c>
-      <c r="BT9">
-        <v>9.6</v>
       </c>
       <c r="BU9">
         <v>8.6</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW9">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BX9">
         <v>55</v>
       </c>
       <c r="BY9">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA9">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="s">
         <v>177</v>
@@ -3077,16 +3077,16 @@
         <v>151</v>
       </c>
       <c r="F10">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="G10">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I10">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3104,31 +3104,31 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S10">
         <v>2.78</v>
       </c>
       <c r="T10">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U10">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V10">
         <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X10">
         <v>20</v>
@@ -3140,7 +3140,7 @@
         <v>32</v>
       </c>
       <c r="AA10">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB10">
         <v>12.5</v>
@@ -3149,10 +3149,10 @@
         <v>9.4</v>
       </c>
       <c r="AD10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF10">
         <v>14.5</v>
@@ -3161,7 +3161,7 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI10">
         <v>44</v>
@@ -3185,7 +3185,7 @@
         <v>34</v>
       </c>
       <c r="AP10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ10">
         <v>17.5</v>
@@ -3197,7 +3197,7 @@
         <v>50</v>
       </c>
       <c r="AT10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU10">
         <v>8.4</v>
@@ -3212,13 +3212,13 @@
         <v>12.5</v>
       </c>
       <c r="AY10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10">
         <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB10">
         <v>21</v>
@@ -3233,10 +3233,10 @@
         <v>55</v>
       </c>
       <c r="BF10">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BH10">
         <v>4.1</v>
@@ -3260,28 +3260,28 @@
         <v>5.1</v>
       </c>
       <c r="BO10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP10">
         <v>14</v>
       </c>
       <c r="BQ10">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BR10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS10">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU10">
         <v>6.4</v>
       </c>
       <c r="BV10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BW10">
         <v>8.199999999999999</v>
@@ -3293,7 +3293,7 @@
         <v>8.6</v>
       </c>
       <c r="BZ10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA10">
         <v>7.6</v>
@@ -3319,22 +3319,22 @@
         <v>152</v>
       </c>
       <c r="F11">
+        <v>3.9</v>
+      </c>
+      <c r="G11">
         <v>4.2</v>
       </c>
-      <c r="G11">
-        <v>4.5</v>
-      </c>
       <c r="H11">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="I11">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="J11">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K11">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L11">
         <v>1.47</v>
@@ -3343,16 +3343,16 @@
         <v>1.09</v>
       </c>
       <c r="N11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O11">
         <v>1.4</v>
       </c>
       <c r="P11">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R11">
         <v>1.28</v>
@@ -3361,16 +3361,16 @@
         <v>4.1</v>
       </c>
       <c r="T11">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U11">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V11">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="W11">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X11">
         <v>12</v>
@@ -3379,28 +3379,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
         <v>11</v>
       </c>
       <c r="AE11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH11">
         <v>21</v>
@@ -3412,7 +3412,7 @@
         <v>900</v>
       </c>
       <c r="AK11">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AL11">
         <v>260</v>
@@ -3424,7 +3424,7 @@
         <v>600</v>
       </c>
       <c r="AO11">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AP11">
         <v>10.5</v>
@@ -3439,22 +3439,22 @@
         <v>21</v>
       </c>
       <c r="AT11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW11">
         <v>21</v>
       </c>
       <c r="AX11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ11">
         <v>18</v>
@@ -3472,10 +3472,10 @@
         <v>30</v>
       </c>
       <c r="BE11">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BF11">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BG11">
         <v>16</v>
@@ -3496,34 +3496,34 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO11">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS11">
         <v>11.5</v>
       </c>
       <c r="BT11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW11">
         <v>7.4</v>
@@ -3561,10 +3561,10 @@
         <v>153</v>
       </c>
       <c r="F12">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G12">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H12">
         <v>5.1</v>
@@ -3573,16 +3573,16 @@
         <v>5.5</v>
       </c>
       <c r="J12">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K12">
         <v>3.9</v>
       </c>
       <c r="L12">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N12">
         <v>3.5</v>
@@ -3591,7 +3591,7 @@
         <v>1.36</v>
       </c>
       <c r="P12">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q12">
         <v>2.06</v>
@@ -3612,7 +3612,7 @@
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X12">
         <v>13.5</v>
@@ -3636,7 +3636,7 @@
         <v>22</v>
       </c>
       <c r="AE12">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF12">
         <v>11</v>
@@ -3678,7 +3678,7 @@
         <v>29</v>
       </c>
       <c r="AS12">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AT12">
         <v>6.8</v>
@@ -3693,7 +3693,7 @@
         <v>46</v>
       </c>
       <c r="AX12">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY12">
         <v>9</v>
@@ -3714,7 +3714,7 @@
         <v>27</v>
       </c>
       <c r="BE12">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF12">
         <v>12</v>
@@ -3803,16 +3803,16 @@
         <v>154</v>
       </c>
       <c r="F13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="H13">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I13">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J13">
         <v>3.6</v>
@@ -3824,7 +3824,7 @@
         <v>1.4</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N13">
         <v>4.1</v>
@@ -3833,28 +3833,28 @@
         <v>1.3</v>
       </c>
       <c r="P13">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q13">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R13">
         <v>1.4</v>
       </c>
       <c r="S13">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T13">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V13">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W13">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X13">
         <v>15.5</v>
@@ -3866,10 +3866,10 @@
         <v>14</v>
       </c>
       <c r="AA13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC13">
         <v>8.199999999999999</v>
@@ -3881,7 +3881,7 @@
         <v>22</v>
       </c>
       <c r="AF13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG13">
         <v>16</v>
@@ -3890,13 +3890,13 @@
         <v>17.5</v>
       </c>
       <c r="AI13">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ13">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK13">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL13">
         <v>55</v>
@@ -3908,7 +3908,7 @@
         <v>44</v>
       </c>
       <c r="AO13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP13">
         <v>13.5</v>
@@ -3917,25 +3917,25 @@
         <v>9.4</v>
       </c>
       <c r="AR13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU13">
         <v>7.4</v>
       </c>
       <c r="AV13">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW13">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY13">
         <v>14</v>
@@ -3944,7 +3944,7 @@
         <v>15</v>
       </c>
       <c r="BA13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB13">
         <v>55</v>
@@ -3959,22 +3959,22 @@
         <v>65</v>
       </c>
       <c r="BF13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BG13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH13">
         <v>3.55</v>
       </c>
       <c r="BI13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13">
         <v>9.4</v>
       </c>
       <c r="BK13">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -3983,22 +3983,22 @@
         <v>14.5</v>
       </c>
       <c r="BN13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO13">
         <v>6.2</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ13">
         <v>10.5</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT13">
         <v>5</v>
@@ -4010,19 +4010,19 @@
         <v>15</v>
       </c>
       <c r="BW13">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY13">
         <v>10.5</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="s">
         <v>177</v>
@@ -4045,19 +4045,19 @@
         <v>155</v>
       </c>
       <c r="F14">
+        <v>3.8</v>
+      </c>
+      <c r="G14">
         <v>3.9</v>
       </c>
-      <c r="G14">
+      <c r="H14">
+        <v>2.02</v>
+      </c>
+      <c r="I14">
+        <v>2.04</v>
+      </c>
+      <c r="J14">
         <v>4</v>
-      </c>
-      <c r="H14">
-        <v>2</v>
-      </c>
-      <c r="I14">
-        <v>2.02</v>
-      </c>
-      <c r="J14">
-        <v>3.9</v>
       </c>
       <c r="K14">
         <v>4.1</v>
@@ -4093,13 +4093,13 @@
         <v>2.48</v>
       </c>
       <c r="V14">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W14">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y14">
         <v>12.5</v>
@@ -4111,7 +4111,7 @@
         <v>24</v>
       </c>
       <c r="AB14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC14">
         <v>9</v>
@@ -4120,13 +4120,13 @@
         <v>10.5</v>
       </c>
       <c r="AE14">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF14">
         <v>32</v>
       </c>
       <c r="AG14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH14">
         <v>15.5</v>
@@ -4138,16 +4138,16 @@
         <v>75</v>
       </c>
       <c r="AK14">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL14">
         <v>44</v>
       </c>
       <c r="AM14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO14">
         <v>10.5</v>
@@ -4168,19 +4168,19 @@
         <v>17</v>
       </c>
       <c r="AU14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW14">
         <v>17</v>
       </c>
       <c r="AX14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ14">
         <v>14</v>
@@ -4189,10 +4189,10 @@
         <v>25</v>
       </c>
       <c r="BB14">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BC14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD14">
         <v>38</v>
@@ -4201,16 +4201,16 @@
         <v>55</v>
       </c>
       <c r="BF14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BG14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH14">
         <v>4.1</v>
       </c>
       <c r="BI14">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ14">
         <v>8.800000000000001</v>
@@ -4225,7 +4225,7 @@
         <v>14.5</v>
       </c>
       <c r="BN14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BO14">
         <v>6.6</v>
@@ -4243,10 +4243,10 @@
         <v>11.5</v>
       </c>
       <c r="BT14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU14">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV14">
         <v>13.5</v>
@@ -4255,16 +4255,16 @@
         <v>7.8</v>
       </c>
       <c r="BX14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY14">
         <v>10</v>
       </c>
       <c r="BZ14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA14">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB14" t="s">
         <v>177</v>
@@ -4287,88 +4287,88 @@
         <v>156</v>
       </c>
       <c r="F15">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="G15">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="H15">
+        <v>5.1</v>
+      </c>
+      <c r="I15">
         <v>5.3</v>
       </c>
-      <c r="I15">
-        <v>5.5</v>
-      </c>
       <c r="J15">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K15">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M15">
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="O15">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="Q15">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="R15">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="S15">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="T15">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U15">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V15">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W15">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="X15">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y15">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Z15">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AA15">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB15">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC15">
         <v>11</v>
       </c>
       <c r="AD15">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE15">
         <v>55</v>
       </c>
       <c r="AF15">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH15">
         <v>16</v>
@@ -4386,46 +4386,46 @@
         <v>24</v>
       </c>
       <c r="AM15">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN15">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO15">
+        <v>38</v>
+      </c>
+      <c r="AP15">
+        <v>26</v>
+      </c>
+      <c r="AQ15">
+        <v>24</v>
+      </c>
+      <c r="AR15">
         <v>40</v>
-      </c>
-      <c r="AP15">
-        <v>27</v>
-      </c>
-      <c r="AQ15">
-        <v>28</v>
-      </c>
-      <c r="AR15">
-        <v>46</v>
       </c>
       <c r="AS15">
         <v>80</v>
       </c>
       <c r="AT15">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV15">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW15">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA15">
         <v>42</v>
@@ -4434,79 +4434,79 @@
         <v>16.5</v>
       </c>
       <c r="BC15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE15">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF15">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BH15">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BI15">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BJ15">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BK15">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BM15">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN15">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO15">
         <v>4.4</v>
       </c>
       <c r="BP15">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BQ15">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR15">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BS15">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="BT15">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BU15">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BV15">
         <v>34</v>
       </c>
       <c r="BW15">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BX15">
         <v>34</v>
       </c>
       <c r="BY15">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BZ15">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA15">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="CB15" t="s">
         <v>177</v>
@@ -4529,16 +4529,16 @@
         <v>157</v>
       </c>
       <c r="F16">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="G16">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H16">
+        <v>2.78</v>
+      </c>
+      <c r="I16">
         <v>2.8</v>
-      </c>
-      <c r="I16">
-        <v>2.82</v>
       </c>
       <c r="J16">
         <v>3.75</v>
@@ -4553,7 +4553,7 @@
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>1.24</v>
@@ -4562,37 +4562,37 @@
         <v>2.34</v>
       </c>
       <c r="Q16">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R16">
         <v>1.53</v>
       </c>
       <c r="S16">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T16">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U16">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V16">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X16">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y16">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z16">
         <v>20</v>
       </c>
       <c r="AA16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB16">
         <v>14</v>
@@ -4601,7 +4601,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD16">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE16">
         <v>27</v>
@@ -4616,7 +4616,7 @@
         <v>14.5</v>
       </c>
       <c r="AI16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ16">
         <v>36</v>
@@ -4631,7 +4631,7 @@
         <v>65</v>
       </c>
       <c r="AN16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO16">
         <v>19</v>
@@ -4655,13 +4655,13 @@
         <v>8</v>
       </c>
       <c r="AV16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY16">
         <v>11.5</v>
@@ -4670,7 +4670,7 @@
         <v>14</v>
       </c>
       <c r="BA16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB16">
         <v>34</v>
@@ -4679,10 +4679,10 @@
         <v>24</v>
       </c>
       <c r="BD16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF16">
         <v>15.5</v>
@@ -4697,7 +4697,7 @@
         <v>3.6</v>
       </c>
       <c r="BJ16">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK16">
         <v>8</v>
@@ -4709,22 +4709,22 @@
         <v>70</v>
       </c>
       <c r="BN16">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO16">
         <v>5.4</v>
       </c>
       <c r="BP16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ16">
         <v>16</v>
       </c>
       <c r="BR16">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BS16">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="BT16">
         <v>6</v>
@@ -4733,13 +4733,13 @@
         <v>5.6</v>
       </c>
       <c r="BV16">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BX16">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BY16">
         <v>25</v>
@@ -4777,10 +4777,10 @@
         <v>1.84</v>
       </c>
       <c r="H17">
+        <v>4.5</v>
+      </c>
+      <c r="I17">
         <v>4.6</v>
-      </c>
-      <c r="I17">
-        <v>4.7</v>
       </c>
       <c r="J17">
         <v>4.1</v>
@@ -4795,28 +4795,28 @@
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O17">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P17">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q17">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S17">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T17">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U17">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V17">
         <v>1.27</v>
@@ -4825,7 +4825,7 @@
         <v>2.18</v>
       </c>
       <c r="X17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y17">
         <v>25</v>
@@ -4834,19 +4834,19 @@
         <v>38</v>
       </c>
       <c r="AA17">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17">
         <v>17.5</v>
       </c>
       <c r="AE17">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF17">
         <v>14</v>
@@ -4855,31 +4855,31 @@
         <v>10</v>
       </c>
       <c r="AH17">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI17">
         <v>42</v>
       </c>
       <c r="AJ17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM17">
         <v>60</v>
       </c>
       <c r="AN17">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ17">
         <v>23</v>
@@ -4888,52 +4888,52 @@
         <v>34</v>
       </c>
       <c r="AS17">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AT17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU17">
         <v>9.4</v>
       </c>
       <c r="AV17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW17">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA17">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB17">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC17">
         <v>15.5</v>
       </c>
       <c r="BD17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE17">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG17">
         <v>30</v>
       </c>
       <c r="BH17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI17">
         <v>4</v>
@@ -4948,13 +4948,13 @@
         <v>80</v>
       </c>
       <c r="BM17">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="BN17">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP17">
         <v>11.5</v>
@@ -4975,22 +4975,22 @@
         <v>7.4</v>
       </c>
       <c r="BV17">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BW17">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BX17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY17">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BZ17">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CB17" t="s">
         <v>177</v>
@@ -5013,13 +5013,13 @@
         <v>159</v>
       </c>
       <c r="F18">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G18">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H18">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -5040,19 +5040,19 @@
         <v>4</v>
       </c>
       <c r="O18">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P18">
         <v>2.04</v>
       </c>
       <c r="Q18">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R18">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T18">
         <v>2.16</v>
@@ -5064,7 +5064,7 @@
         <v>1.11</v>
       </c>
       <c r="W18">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X18">
         <v>21</v>
@@ -5097,13 +5097,13 @@
         <v>11</v>
       </c>
       <c r="AH18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI18">
         <v>160</v>
       </c>
       <c r="AJ18">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK18">
         <v>18.5</v>
@@ -5115,7 +5115,7 @@
         <v>200</v>
       </c>
       <c r="AN18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO18">
         <v>240</v>
@@ -5124,25 +5124,25 @@
         <v>14.5</v>
       </c>
       <c r="AQ18">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR18">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AS18">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AT18">
         <v>7</v>
       </c>
       <c r="AU18">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV18">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW18">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AX18">
         <v>7.2</v>
@@ -5154,7 +5154,7 @@
         <v>25</v>
       </c>
       <c r="BA18">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB18">
         <v>10.5</v>
@@ -5172,25 +5172,25 @@
         <v>6.8</v>
       </c>
       <c r="BG18">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BH18">
         <v>4.3</v>
       </c>
       <c r="BI18">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ18">
         <v>14.5</v>
       </c>
       <c r="BK18">
-        <v>3.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN18">
         <v>4.4</v>
@@ -5202,7 +5202,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ18">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BR18">
         <v>32</v>
@@ -5214,25 +5214,25 @@
         <v>15</v>
       </c>
       <c r="BU18">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV18">
         <v>110</v>
       </c>
       <c r="BW18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX18">
         <v>110</v>
       </c>
       <c r="BY18">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ18">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA18">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="CB18" t="s">
         <v>177</v>
@@ -5255,97 +5255,97 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G19">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H19">
         <v>2.54</v>
       </c>
       <c r="I19">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J19">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K19">
         <v>2.84</v>
       </c>
       <c r="L19">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="M19">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="N19">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="O19">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="P19">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="Q19">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R19">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S19">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="U19">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V19">
         <v>1.6</v>
       </c>
       <c r="W19">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X19">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y19">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z19">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AA19">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB19">
-        <v>8.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD19">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE19">
         <v>500</v>
       </c>
       <c r="AF19">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AG19">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AH19">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AI19">
         <v>500</v>
       </c>
       <c r="AJ19">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK19">
         <v>500</v>
@@ -5357,124 +5357,124 @@
         <v>500</v>
       </c>
       <c r="AN19">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AQ19">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="AR19">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS19">
-        <v>11.5</v>
+        <v>2.34</v>
       </c>
       <c r="AT19">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU19">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="AV19">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AW19">
-        <v>16.5</v>
+        <v>2.34</v>
       </c>
       <c r="AX19">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="AY19">
-        <v>16.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19">
-        <v>10</v>
+        <v>2.44</v>
       </c>
       <c r="BA19">
-        <v>13</v>
+        <v>2.36</v>
       </c>
       <c r="BB19">
-        <v>13</v>
+        <v>2.36</v>
       </c>
       <c r="BC19">
-        <v>12.5</v>
+        <v>2.36</v>
       </c>
       <c r="BD19">
-        <v>13.5</v>
+        <v>2.36</v>
       </c>
       <c r="BE19">
-        <v>14.5</v>
+        <v>2.38</v>
       </c>
       <c r="BF19">
-        <v>12.5</v>
+        <v>2.38</v>
       </c>
       <c r="BG19">
-        <v>12</v>
+        <v>2.34</v>
       </c>
       <c r="BH19">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.24</v>
+        <v>1.36</v>
       </c>
       <c r="BJ19">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>7.4</v>
+        <v>1.12</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="BN19">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>12.5</v>
+        <v>3.45</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="BT19">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>4.6</v>
+        <v>1.93</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>10.5</v>
+        <v>2.22</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>13.5</v>
+        <v>3.55</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>6.6</v>
+        <v>3.6</v>
       </c>
       <c r="CB19" t="s">
         <v>177</v>
@@ -5497,43 +5497,43 @@
         <v>161</v>
       </c>
       <c r="F20">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G20">
         <v>2.16</v>
       </c>
       <c r="H20">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I20">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J20">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K20">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L20">
         <v>1.37</v>
       </c>
       <c r="M20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O20">
         <v>1.27</v>
       </c>
       <c r="P20">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q20">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R20">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S20">
         <v>3</v>
@@ -5542,10 +5542,10 @@
         <v>1.69</v>
       </c>
       <c r="U20">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W20">
         <v>1.86</v>
@@ -5554,58 +5554,58 @@
         <v>20</v>
       </c>
       <c r="Y20">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z20">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AA20">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD20">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE20">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF20">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH20">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AI20">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ20">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AK20">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL20">
         <v>40</v>
       </c>
       <c r="AM20">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AN20">
         <v>13.5</v>
       </c>
       <c r="AO20">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AP20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ20">
         <v>14</v>
@@ -5614,58 +5614,58 @@
         <v>21</v>
       </c>
       <c r="AS20">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="AT20">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU20">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV20">
         <v>13.5</v>
       </c>
       <c r="AW20">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AX20">
         <v>12.5</v>
       </c>
       <c r="AY20">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB20">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC20">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD20">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BE20">
-        <v>55</v>
+        <v>7.2</v>
       </c>
       <c r="BF20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG20">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BH20">
         <v>4.4</v>
       </c>
       <c r="BI20">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK20">
         <v>3.4</v>
@@ -5674,19 +5674,19 @@
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BN20">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BO20">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP20">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ20">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BR20">
         <v>32</v>
@@ -5695,28 +5695,28 @@
         <v>4.1</v>
       </c>
       <c r="BT20">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BU20">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BV20">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW20">
         <v>4.2</v>
       </c>
       <c r="BX20">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BZ20">
         <v>25</v>
       </c>
       <c r="CA20">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="CB20" t="s">
         <v>177</v>
@@ -5739,22 +5739,22 @@
         <v>162</v>
       </c>
       <c r="F21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G21">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H21">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I21">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J21">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="K21">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L21">
         <v>1.27</v>
@@ -5766,22 +5766,22 @@
         <v>6.2</v>
       </c>
       <c r="O21">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P21">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q21">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R21">
         <v>1.73</v>
       </c>
       <c r="S21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T21">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U21">
         <v>2.18</v>
@@ -5790,13 +5790,13 @@
         <v>1.13</v>
       </c>
       <c r="W21">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X21">
         <v>32</v>
       </c>
       <c r="Y21">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Z21">
         <v>170</v>
@@ -5808,13 +5808,13 @@
         <v>12.5</v>
       </c>
       <c r="AC21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD21">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AE21">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF21">
         <v>11</v>
@@ -5823,13 +5823,13 @@
         <v>10.5</v>
       </c>
       <c r="AH21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI21">
         <v>85</v>
       </c>
       <c r="AJ21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK21">
         <v>14</v>
@@ -5838,16 +5838,16 @@
         <v>28</v>
       </c>
       <c r="AM21">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN21">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AO21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ21">
         <v>30</v>
@@ -5856,7 +5856,7 @@
         <v>55</v>
       </c>
       <c r="AS21">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="AT21">
         <v>11</v>
@@ -5865,37 +5865,37 @@
         <v>11.5</v>
       </c>
       <c r="AV21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW21">
         <v>60</v>
       </c>
       <c r="AX21">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY21">
         <v>9.4</v>
       </c>
       <c r="AZ21">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA21">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD21">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE21">
         <v>55</v>
       </c>
       <c r="BF21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG21">
         <v>50</v>
@@ -5913,10 +5913,10 @@
         <v>7.4</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM21">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BN21">
         <v>4.3</v>
@@ -5925,40 +5925,40 @@
         <v>3.85</v>
       </c>
       <c r="BP21">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BQ21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR21">
         <v>19.5</v>
       </c>
       <c r="BS21">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BT21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU21">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BX21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY21">
+        <v>11</v>
+      </c>
+      <c r="BZ21">
+        <v>10.5</v>
+      </c>
+      <c r="CA21">
         <v>8</v>
-      </c>
-      <c r="BZ21">
-        <v>12.5</v>
-      </c>
-      <c r="CA21">
-        <v>5.5</v>
       </c>
       <c r="CB21" t="s">
         <v>177</v>
@@ -5981,22 +5981,22 @@
         <v>163</v>
       </c>
       <c r="F22">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G22">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H22">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I22">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J22">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L22">
         <v>1.31</v>
@@ -6005,7 +6005,7 @@
         <v>1.04</v>
       </c>
       <c r="N22">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O22">
         <v>1.19</v>
@@ -6014,7 +6014,7 @@
         <v>2.62</v>
       </c>
       <c r="Q22">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R22">
         <v>1.64</v>
@@ -6023,22 +6023,22 @@
         <v>2.48</v>
       </c>
       <c r="T22">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="U22">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V22">
         <v>1.37</v>
       </c>
       <c r="W22">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z22">
         <v>32</v>
@@ -6047,109 +6047,109 @@
         <v>70</v>
       </c>
       <c r="AB22">
+        <v>14.5</v>
+      </c>
+      <c r="AC22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD22">
         <v>15.5</v>
-      </c>
-      <c r="AC22">
-        <v>9.4</v>
-      </c>
-      <c r="AD22">
-        <v>15</v>
       </c>
       <c r="AE22">
         <v>36</v>
       </c>
       <c r="AF22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG22">
         <v>11</v>
       </c>
       <c r="AH22">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI22">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ22">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK22">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL22">
         <v>27</v>
       </c>
       <c r="AM22">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN22">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ22">
         <v>18.5</v>
       </c>
       <c r="AR22">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AS22">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AT22">
         <v>13</v>
       </c>
       <c r="AU22">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW22">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AX22">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY22">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA22">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BB22">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BC22">
         <v>16.5</v>
       </c>
       <c r="BD22">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE22">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF22">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG22">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH22">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI22">
         <v>3.9</v>
       </c>
       <c r="BJ22">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK22">
         <v>7.6</v>
@@ -6158,10 +6158,10 @@
         <v>80</v>
       </c>
       <c r="BM22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN22">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO22">
         <v>4.8</v>
@@ -6176,13 +6176,13 @@
         <v>24</v>
       </c>
       <c r="BS22">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT22">
         <v>7.2</v>
       </c>
       <c r="BU22">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV22">
         <v>25</v>
@@ -6200,7 +6200,7 @@
         <v>16.5</v>
       </c>
       <c r="CA22">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB22" t="s">
         <v>177</v>
@@ -6226,7 +6226,7 @@
         <v>1.91</v>
       </c>
       <c r="G23">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H23">
         <v>4.4</v>
@@ -6235,76 +6235,76 @@
         <v>4.5</v>
       </c>
       <c r="J23">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K23">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L23">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M23">
         <v>1.06</v>
       </c>
       <c r="N23">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O23">
         <v>1.27</v>
       </c>
       <c r="P23">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q23">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R23">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S23">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T23">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U23">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
         <v>1.28</v>
       </c>
       <c r="W23">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X23">
         <v>17</v>
       </c>
       <c r="Y23">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z23">
         <v>34</v>
       </c>
       <c r="AA23">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC23">
         <v>8.4</v>
       </c>
       <c r="AD23">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE23">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF23">
         <v>12.5</v>
       </c>
       <c r="AG23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH23">
         <v>17</v>
@@ -6316,7 +6316,7 @@
         <v>21</v>
       </c>
       <c r="AK23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL23">
         <v>32</v>
@@ -6325,7 +6325,7 @@
         <v>85</v>
       </c>
       <c r="AN23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO23">
         <v>50</v>
@@ -6361,10 +6361,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ23">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA23">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB23">
         <v>19.5</v>
@@ -6382,10 +6382,10 @@
         <v>10.5</v>
       </c>
       <c r="BG23">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH23">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BI23">
         <v>3.4</v>
@@ -6400,7 +6400,7 @@
         <v>110</v>
       </c>
       <c r="BM23">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="BN23">
         <v>4.7</v>
@@ -6418,7 +6418,7 @@
         <v>26</v>
       </c>
       <c r="BS23">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT23">
         <v>8</v>
@@ -6427,10 +6427,10 @@
         <v>6.8</v>
       </c>
       <c r="BV23">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BW23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX23">
         <v>42</v>
@@ -6439,10 +6439,10 @@
         <v>11</v>
       </c>
       <c r="BZ23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA23">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB23" t="s">
         <v>177</v>
@@ -6492,13 +6492,13 @@
         <v>3.95</v>
       </c>
       <c r="O24">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P24">
         <v>2</v>
       </c>
       <c r="Q24">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R24">
         <v>1.38</v>
@@ -6507,7 +6507,7 @@
         <v>3.45</v>
       </c>
       <c r="T24">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U24">
         <v>2.2</v>
@@ -6519,7 +6519,7 @@
         <v>1.81</v>
       </c>
       <c r="X24">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y24">
         <v>14.5</v>
@@ -6537,16 +6537,16 @@
         <v>8</v>
       </c>
       <c r="AD24">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE24">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF24">
         <v>14</v>
       </c>
       <c r="AG24">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH24">
         <v>17</v>
@@ -6558,7 +6558,7 @@
         <v>27</v>
       </c>
       <c r="AK24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL24">
         <v>38</v>
@@ -6567,7 +6567,7 @@
         <v>95</v>
       </c>
       <c r="AN24">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO24">
         <v>42</v>
@@ -6594,7 +6594,7 @@
         <v>13.5</v>
       </c>
       <c r="AW24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX24">
         <v>13</v>
@@ -6609,7 +6609,7 @@
         <v>46</v>
       </c>
       <c r="BB24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC24">
         <v>20</v>
@@ -6639,10 +6639,10 @@
         <v>8.4</v>
       </c>
       <c r="BL24">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM24">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="BN24">
         <v>4.9</v>
@@ -6654,16 +6654,16 @@
         <v>15.5</v>
       </c>
       <c r="BQ24">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BR24">
         <v>29</v>
       </c>
       <c r="BS24">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT24">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU24">
         <v>6.2</v>
@@ -6672,19 +6672,19 @@
         <v>30</v>
       </c>
       <c r="BW24">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BX24">
         <v>40</v>
       </c>
       <c r="BY24">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ24">
         <v>25</v>
       </c>
       <c r="CA24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CB24" t="s">
         <v>177</v>
@@ -6731,7 +6731,7 @@
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O25">
         <v>1.31</v>
@@ -6740,7 +6740,7 @@
         <v>2.04</v>
       </c>
       <c r="Q25">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R25">
         <v>1.39</v>
@@ -6749,7 +6749,7 @@
         <v>3.4</v>
       </c>
       <c r="T25">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U25">
         <v>2.28</v>
@@ -6761,13 +6761,13 @@
         <v>1.45</v>
       </c>
       <c r="X25">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y25">
         <v>11</v>
       </c>
       <c r="Z25">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA25">
         <v>34</v>
@@ -6791,7 +6791,7 @@
         <v>13</v>
       </c>
       <c r="AH25">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI25">
         <v>38</v>
@@ -6806,7 +6806,7 @@
         <v>44</v>
       </c>
       <c r="AM25">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN25">
         <v>32</v>
@@ -6833,7 +6833,7 @@
         <v>7.6</v>
       </c>
       <c r="AV25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW25">
         <v>23</v>
@@ -6842,16 +6842,16 @@
         <v>20</v>
       </c>
       <c r="AY25">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ25">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA25">
         <v>34</v>
       </c>
       <c r="BB25">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC25">
         <v>30</v>
@@ -6863,10 +6863,10 @@
         <v>60</v>
       </c>
       <c r="BF25">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG25">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH25">
         <v>3.5</v>
@@ -6884,7 +6884,7 @@
         <v>130</v>
       </c>
       <c r="BM25">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="BN25">
         <v>6.2</v>
@@ -6973,13 +6973,13 @@
         <v>1.05</v>
       </c>
       <c r="N26">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O26">
         <v>1.23</v>
       </c>
       <c r="P26">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q26">
         <v>1.68</v>
@@ -6988,10 +6988,10 @@
         <v>1.56</v>
       </c>
       <c r="S26">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T26">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U26">
         <v>2.58</v>
@@ -7006,7 +7006,7 @@
         <v>21</v>
       </c>
       <c r="Y26">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z26">
         <v>28</v>
@@ -7021,19 +7021,19 @@
         <v>9</v>
       </c>
       <c r="AD26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF26">
         <v>15.5</v>
       </c>
       <c r="AG26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI26">
         <v>40</v>
@@ -7042,7 +7042,7 @@
         <v>27</v>
       </c>
       <c r="AK26">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL26">
         <v>28</v>
@@ -7057,7 +7057,7 @@
         <v>28</v>
       </c>
       <c r="AP26">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ26">
         <v>17</v>
@@ -7066,7 +7066,7 @@
         <v>25</v>
       </c>
       <c r="AS26">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT26">
         <v>12</v>
@@ -7105,7 +7105,7 @@
         <v>55</v>
       </c>
       <c r="BF26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG26">
         <v>24</v>
@@ -7120,13 +7120,13 @@
         <v>8.6</v>
       </c>
       <c r="BK26">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL26">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BM26">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="BN26">
         <v>5.2</v>
@@ -7138,7 +7138,7 @@
         <v>14.5</v>
       </c>
       <c r="BQ26">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BR26">
         <v>25</v>
@@ -7156,19 +7156,19 @@
         <v>26</v>
       </c>
       <c r="BW26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX26">
         <v>32</v>
       </c>
       <c r="BY26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ26">
         <v>18</v>
       </c>
       <c r="CA26">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB26" t="s">
         <v>177</v>
@@ -7191,49 +7191,49 @@
         <v>168</v>
       </c>
       <c r="F27">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G27">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H27">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I27">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J27">
         <v>3.7</v>
       </c>
       <c r="K27">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L27">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M27">
         <v>1.07</v>
       </c>
       <c r="N27">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O27">
         <v>1.32</v>
       </c>
       <c r="P27">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q27">
         <v>1.99</v>
       </c>
       <c r="R27">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S27">
         <v>3.55</v>
       </c>
       <c r="T27">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U27">
         <v>2.18</v>
@@ -7242,7 +7242,7 @@
         <v>1.34</v>
       </c>
       <c r="W27">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X27">
         <v>15</v>
@@ -7260,13 +7260,13 @@
         <v>9.4</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE27">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF27">
         <v>13</v>
@@ -7275,7 +7275,7 @@
         <v>10.5</v>
       </c>
       <c r="AH27">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI27">
         <v>55</v>
@@ -7287,19 +7287,19 @@
         <v>22</v>
       </c>
       <c r="AL27">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN27">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO27">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP27">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ27">
         <v>13</v>
@@ -7314,7 +7314,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU27">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV27">
         <v>14.5</v>
@@ -7326,16 +7326,16 @@
         <v>12</v>
       </c>
       <c r="AY27">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ27">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA27">
         <v>48</v>
       </c>
       <c r="BB27">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC27">
         <v>20</v>
@@ -7350,10 +7350,10 @@
         <v>15</v>
       </c>
       <c r="BG27">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH27">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI27">
         <v>3.2</v>
@@ -7368,7 +7368,7 @@
         <v>140</v>
       </c>
       <c r="BM27">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="BN27">
         <v>4.9</v>
@@ -7380,7 +7380,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ27">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BR27">
         <v>29</v>
@@ -7392,7 +7392,7 @@
         <v>7.2</v>
       </c>
       <c r="BU27">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV27">
         <v>32</v>
@@ -7433,16 +7433,16 @@
         <v>169</v>
       </c>
       <c r="F28">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="G28">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="H28">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I28">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="J28">
         <v>4.4</v>
@@ -7451,13 +7451,13 @@
         <v>4.5</v>
       </c>
       <c r="L28">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M28">
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O28">
         <v>1.19</v>
@@ -7466,55 +7466,55 @@
         <v>2.64</v>
       </c>
       <c r="Q28">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R28">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S28">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T28">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U28">
+        <v>2.4</v>
+      </c>
+      <c r="V28">
         <v>2.38</v>
       </c>
-      <c r="V28">
-        <v>2.5</v>
-      </c>
       <c r="W28">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA28">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB28">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AC28">
         <v>10.5</v>
       </c>
       <c r="AD28">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE28">
         <v>15</v>
       </c>
       <c r="AF28">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AG28">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AH28">
         <v>17</v>
@@ -7523,43 +7523,43 @@
         <v>27</v>
       </c>
       <c r="AJ28">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AK28">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL28">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM28">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN28">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="AO28">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AP28">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ28">
         <v>11.5</v>
       </c>
       <c r="AR28">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS28">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU28">
         <v>9.800000000000001</v>
       </c>
       <c r="AV28">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW28">
         <v>14</v>
@@ -7568,7 +7568,7 @@
         <v>42</v>
       </c>
       <c r="AY28">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AZ28">
         <v>16.5</v>
@@ -7577,10 +7577,10 @@
         <v>25</v>
       </c>
       <c r="BB28">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="BC28">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BD28">
         <v>50</v>
@@ -7589,16 +7589,16 @@
         <v>65</v>
       </c>
       <c r="BF28">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BG28">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH28">
         <v>4.3</v>
       </c>
       <c r="BI28">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ28">
         <v>9.4</v>
@@ -7607,40 +7607,40 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BL28">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM28">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="BN28">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BO28">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BP28">
+        <v>38</v>
+      </c>
+      <c r="BQ28">
+        <v>10</v>
+      </c>
+      <c r="BR28">
         <v>40</v>
       </c>
-      <c r="BQ28">
-        <v>12.5</v>
-      </c>
-      <c r="BR28">
-        <v>42</v>
-      </c>
       <c r="BS28">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BT28">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU28">
         <v>4.1</v>
       </c>
       <c r="BV28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BW28">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX28">
         <v>21</v>
@@ -7649,10 +7649,10 @@
         <v>13.5</v>
       </c>
       <c r="BZ28">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA28">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB28" t="s">
         <v>177</v>
@@ -7675,10 +7675,10 @@
         <v>170</v>
       </c>
       <c r="F29">
+        <v>1.87</v>
+      </c>
+      <c r="G29">
         <v>1.88</v>
-      </c>
-      <c r="G29">
-        <v>1.89</v>
       </c>
       <c r="H29">
         <v>4.3</v>
@@ -7699,7 +7699,7 @@
         <v>1.03</v>
       </c>
       <c r="N29">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O29">
         <v>1.16</v>
@@ -7711,13 +7711,13 @@
         <v>1.51</v>
       </c>
       <c r="R29">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S29">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T29">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U29">
         <v>2.84</v>
@@ -7735,16 +7735,16 @@
         <v>26</v>
       </c>
       <c r="Z29">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA29">
         <v>85</v>
       </c>
       <c r="AB29">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC29">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD29">
         <v>17.5</v>
@@ -7762,10 +7762,10 @@
         <v>14</v>
       </c>
       <c r="AI29">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ29">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK29">
         <v>16.5</v>
@@ -7783,13 +7783,13 @@
         <v>29</v>
       </c>
       <c r="AP29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ29">
         <v>24</v>
       </c>
       <c r="AR29">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS29">
         <v>70</v>
@@ -7798,7 +7798,7 @@
         <v>13.5</v>
       </c>
       <c r="AU29">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV29">
         <v>16.5</v>
@@ -7807,22 +7807,22 @@
         <v>38</v>
       </c>
       <c r="AX29">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY29">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA29">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB29">
         <v>20</v>
       </c>
       <c r="BC29">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD29">
         <v>22</v>
@@ -7843,7 +7843,7 @@
         <v>4.3</v>
       </c>
       <c r="BJ29">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK29">
         <v>7.8</v>
@@ -7852,7 +7852,7 @@
         <v>65</v>
       </c>
       <c r="BM29">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BN29">
         <v>5.1</v>
@@ -7870,25 +7870,25 @@
         <v>19.5</v>
       </c>
       <c r="BS29">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BT29">
         <v>7.8</v>
       </c>
       <c r="BU29">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV29">
         <v>27</v>
       </c>
       <c r="BW29">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="BX29">
         <v>29</v>
       </c>
       <c r="BY29">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ29">
         <v>13</v>
@@ -7917,22 +7917,22 @@
         <v>171</v>
       </c>
       <c r="F30">
+        <v>5.2</v>
+      </c>
+      <c r="G30">
         <v>5.3</v>
       </c>
-      <c r="G30">
-        <v>5.4</v>
-      </c>
       <c r="H30">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I30">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="J30">
+        <v>4.2</v>
+      </c>
+      <c r="K30">
         <v>4.3</v>
-      </c>
-      <c r="K30">
-        <v>4.4</v>
       </c>
       <c r="L30">
         <v>1.34</v>
@@ -7941,34 +7941,34 @@
         <v>1.05</v>
       </c>
       <c r="N30">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>1.23</v>
       </c>
       <c r="P30">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q30">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R30">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S30">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T30">
         <v>1.73</v>
       </c>
       <c r="U30">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V30">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="W30">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X30">
         <v>21</v>
@@ -7980,10 +7980,10 @@
         <v>11</v>
       </c>
       <c r="AA30">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AB30">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC30">
         <v>9.6</v>
@@ -7992,7 +7992,7 @@
         <v>9.6</v>
       </c>
       <c r="AE30">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AF30">
         <v>42</v>
@@ -8001,7 +8001,7 @@
         <v>19.5</v>
       </c>
       <c r="AH30">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI30">
         <v>28</v>
@@ -8010,7 +8010,7 @@
         <v>130</v>
       </c>
       <c r="AK30">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL30">
         <v>60</v>
@@ -8022,10 +8022,10 @@
         <v>60</v>
       </c>
       <c r="AO30">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP30">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ30">
         <v>10</v>
@@ -8034,7 +8034,7 @@
         <v>10.5</v>
       </c>
       <c r="AS30">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT30">
         <v>20</v>
@@ -8043,16 +8043,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV30">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW30">
         <v>15</v>
       </c>
       <c r="AX30">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY30">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ30">
         <v>17</v>
@@ -8070,7 +8070,7 @@
         <v>50</v>
       </c>
       <c r="BE30">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF30">
         <v>50</v>
@@ -8079,40 +8079,40 @@
         <v>7.8</v>
       </c>
       <c r="BH30">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI30">
         <v>3.75</v>
       </c>
       <c r="BJ30">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL30">
         <v>120</v>
       </c>
       <c r="BM30">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="BN30">
         <v>8.4</v>
       </c>
       <c r="BO30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BP30">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ30">
-        <v>13.5</v>
+        <v>32</v>
       </c>
       <c r="BR30">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BS30">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BT30">
         <v>4.5</v>
@@ -8133,10 +8133,10 @@
         <v>20</v>
       </c>
       <c r="BZ30">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CB30" t="s">
         <v>177</v>
@@ -8165,10 +8165,10 @@
         <v>2.26</v>
       </c>
       <c r="H31">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I31">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J31">
         <v>3.6</v>
@@ -8177,7 +8177,7 @@
         <v>3.65</v>
       </c>
       <c r="L31">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M31">
         <v>1.06</v>
@@ -8207,7 +8207,7 @@
         <v>2.34</v>
       </c>
       <c r="V31">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W31">
         <v>1.79</v>
@@ -8216,10 +8216,10 @@
         <v>16</v>
       </c>
       <c r="Y31">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA31">
         <v>65</v>
@@ -8231,10 +8231,10 @@
         <v>8</v>
       </c>
       <c r="AD31">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE31">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF31">
         <v>14.5</v>
@@ -8282,7 +8282,7 @@
         <v>10.5</v>
       </c>
       <c r="AU31">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV31">
         <v>13.5</v>
@@ -8336,7 +8336,7 @@
         <v>100</v>
       </c>
       <c r="BM31">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BN31">
         <v>5.2</v>
@@ -8345,7 +8345,7 @@
         <v>4.8</v>
       </c>
       <c r="BP31">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ31">
         <v>14</v>
@@ -8354,19 +8354,19 @@
         <v>27</v>
       </c>
       <c r="BS31">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT31">
         <v>6.6</v>
       </c>
       <c r="BU31">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV31">
         <v>25</v>
       </c>
       <c r="BW31">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX31">
         <v>34</v>
@@ -8401,13 +8401,13 @@
         <v>173</v>
       </c>
       <c r="F32">
+        <v>1.63</v>
+      </c>
+      <c r="G32">
         <v>1.64</v>
       </c>
-      <c r="G32">
-        <v>1.65</v>
-      </c>
       <c r="H32">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I32">
         <v>5.8</v>
@@ -8419,13 +8419,13 @@
         <v>4.7</v>
       </c>
       <c r="L32">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M32">
         <v>1.03</v>
       </c>
       <c r="N32">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O32">
         <v>1.14</v>
@@ -8443,7 +8443,7 @@
         <v>2.14</v>
       </c>
       <c r="T32">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U32">
         <v>2.76</v>
@@ -8452,7 +8452,7 @@
         <v>1.2</v>
       </c>
       <c r="W32">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="X32">
         <v>34</v>
@@ -8467,7 +8467,7 @@
         <v>150</v>
       </c>
       <c r="AB32">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC32">
         <v>11.5</v>
@@ -8491,13 +8491,13 @@
         <v>46</v>
       </c>
       <c r="AJ32">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK32">
         <v>13.5</v>
       </c>
       <c r="AL32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM32">
         <v>55</v>
@@ -8509,19 +8509,19 @@
         <v>44</v>
       </c>
       <c r="AP32">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ32">
         <v>30</v>
       </c>
       <c r="AR32">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS32">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AT32">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU32">
         <v>10.5</v>
@@ -8545,7 +8545,7 @@
         <v>42</v>
       </c>
       <c r="BB32">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC32">
         <v>13</v>
@@ -8578,7 +8578,7 @@
         <v>70</v>
       </c>
       <c r="BM32">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BN32">
         <v>4.8</v>
@@ -8587,7 +8587,7 @@
         <v>4.5</v>
       </c>
       <c r="BP32">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ32">
         <v>8.800000000000001</v>
@@ -8599,7 +8599,7 @@
         <v>16</v>
       </c>
       <c r="BT32">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU32">
         <v>8.4</v>
@@ -8614,13 +8614,13 @@
         <v>34</v>
       </c>
       <c r="BY32">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="BZ32">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA32">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB32" t="s">
         <v>177</v>
@@ -8643,22 +8643,22 @@
         <v>174</v>
       </c>
       <c r="F33">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G33">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H33">
         <v>3.35</v>
       </c>
       <c r="I33">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J33">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K33">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L33">
         <v>1.49</v>
@@ -8670,10 +8670,10 @@
         <v>3.1</v>
       </c>
       <c r="O33">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P33">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8697,19 +8697,19 @@
         <v>1.68</v>
       </c>
       <c r="X33">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y33">
         <v>12</v>
       </c>
       <c r="Z33">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AA33">
         <v>90</v>
       </c>
       <c r="AB33">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC33">
         <v>7.8</v>
@@ -8727,7 +8727,7 @@
         <v>12.5</v>
       </c>
       <c r="AH33">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI33">
         <v>75</v>
@@ -8736,7 +8736,7 @@
         <v>85</v>
       </c>
       <c r="AK33">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AL33">
         <v>60</v>
@@ -8760,7 +8760,7 @@
         <v>20</v>
       </c>
       <c r="AS33">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AT33">
         <v>7.4</v>
@@ -8772,7 +8772,7 @@
         <v>12.5</v>
       </c>
       <c r="AW33">
-        <v>5.9</v>
+        <v>40</v>
       </c>
       <c r="AX33">
         <v>12</v>
@@ -8784,25 +8784,25 @@
         <v>16.5</v>
       </c>
       <c r="BA33">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BB33">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC33">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="BD33">
-        <v>5.9</v>
+        <v>40</v>
       </c>
       <c r="BE33">
+        <v>6.6</v>
+      </c>
+      <c r="BF33">
         <v>6.2</v>
       </c>
-      <c r="BF33">
-        <v>5.5</v>
-      </c>
       <c r="BG33">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BH33">
         <v>3.45</v>
@@ -8814,13 +8814,13 @@
         <v>12.5</v>
       </c>
       <c r="BK33">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN33">
         <v>6</v>
@@ -8832,13 +8832,13 @@
         <v>24</v>
       </c>
       <c r="BQ33">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR33">
         <v>46</v>
       </c>
       <c r="BS33">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT33">
         <v>7.8</v>
@@ -8850,19 +8850,19 @@
         <v>38</v>
       </c>
       <c r="BW33">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BX33">
         <v>60</v>
       </c>
       <c r="BY33">
+        <v>4.7</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
         <v>4.5</v>
-      </c>
-      <c r="BZ33">
-        <v>46</v>
-      </c>
-      <c r="CA33">
-        <v>4.4</v>
       </c>
       <c r="CB33" t="s">
         <v>177</v>
@@ -8885,61 +8885,61 @@
         <v>175</v>
       </c>
       <c r="F34">
+        <v>1.75</v>
+      </c>
+      <c r="G34">
         <v>1.77</v>
       </c>
-      <c r="G34">
-        <v>1.81</v>
-      </c>
       <c r="H34">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I34">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J34">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K34">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L34">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="M34">
         <v>1.14</v>
       </c>
       <c r="N34">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O34">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="P34">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q34">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="R34">
         <v>1.17</v>
       </c>
       <c r="S34">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T34">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="U34">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V34">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W34">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X34">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>14.5</v>
@@ -8948,73 +8948,73 @@
         <v>55</v>
       </c>
       <c r="AA34">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="AB34">
         <v>5.7</v>
       </c>
       <c r="AC34">
+        <v>8.6</v>
+      </c>
+      <c r="AD34">
+        <v>32</v>
+      </c>
+      <c r="AE34">
+        <v>170</v>
+      </c>
+      <c r="AF34">
         <v>8.4</v>
       </c>
-      <c r="AD34">
-        <v>34</v>
-      </c>
-      <c r="AE34">
-        <v>700</v>
-      </c>
-      <c r="AF34">
-        <v>8.6</v>
-      </c>
       <c r="AG34">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH34">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI34">
-        <v>700</v>
+        <v>210</v>
       </c>
       <c r="AJ34">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK34">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL34">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM34">
-        <v>580</v>
+        <v>400</v>
       </c>
       <c r="AN34">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AO34">
-        <v>700</v>
+        <v>380</v>
       </c>
       <c r="AP34">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ34">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR34">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AS34">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT34">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU34">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV34">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW34">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AX34">
         <v>7.6</v>
@@ -9023,34 +9023,34 @@
         <v>11</v>
       </c>
       <c r="AZ34">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA34">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BB34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC34">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD34">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="BE34">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BF34">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG34">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BH34">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BI34">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ34">
         <v>14</v>
@@ -9068,22 +9068,22 @@
         <v>3.95</v>
       </c>
       <c r="BO34">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BP34">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ34">
         <v>12</v>
       </c>
       <c r="BR34">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS34">
         <v>36</v>
       </c>
       <c r="BT34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BU34">
         <v>8.199999999999999</v>
@@ -9127,10 +9127,10 @@
         <v>176</v>
       </c>
       <c r="F35">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -9148,40 +9148,40 @@
         <v>1.61</v>
       </c>
       <c r="M35">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N35">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="O35">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P35">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q35">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R35">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S35">
         <v>6</v>
       </c>
       <c r="T35">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="U35">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V35">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W35">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X35">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y35">
         <v>12.5</v>
@@ -9190,49 +9190,49 @@
         <v>38</v>
       </c>
       <c r="AA35">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB35">
         <v>6.2</v>
       </c>
       <c r="AC35">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD35">
         <v>22</v>
       </c>
       <c r="AE35">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF35">
         <v>10.5</v>
       </c>
       <c r="AG35">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH35">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AI35">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ35">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK35">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AL35">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM35">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN35">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO35">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP35">
         <v>7.6</v>
@@ -9241,31 +9241,31 @@
         <v>11</v>
       </c>
       <c r="AR35">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS35">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT35">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU35">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV35">
-        <v>19.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW35">
         <v>12</v>
       </c>
       <c r="AX35">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY35">
         <v>10</v>
       </c>
       <c r="AZ35">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BA35">
         <v>11.5</v>
@@ -9274,13 +9274,13 @@
         <v>20</v>
       </c>
       <c r="BC35">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BD35">
         <v>11</v>
       </c>
       <c r="BE35">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF35">
         <v>17.5</v>
@@ -9289,22 +9289,22 @@
         <v>12</v>
       </c>
       <c r="BH35">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BI35">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ35">
         <v>12.5</v>
       </c>
       <c r="BK35">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BN35">
         <v>4.3</v>
@@ -9316,37 +9316,37 @@
         <v>16</v>
       </c>
       <c r="BQ35">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR35">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS35">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BT35">
         <v>8.6</v>
       </c>
       <c r="BU35">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BV35">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW35">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CB35" t="s">
         <v>177</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-08.xlsx
@@ -547,7 +547,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-09-08 06:20:18</t>
+    <t>2026-09-08 08:32:26</t>
   </si>
 </sst>
 </file>
@@ -1141,226 +1141,226 @@
         <v>143</v>
       </c>
       <c r="F2">
+        <v>3.85</v>
+      </c>
+      <c r="G2">
         <v>3.9</v>
       </c>
-      <c r="G2">
-        <v>4.1</v>
-      </c>
       <c r="H2">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="I2">
-        <v>2.04</v>
+        <v>2.64</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>2.78</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="L2">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="N2">
+        <v>1.88</v>
+      </c>
+      <c r="O2">
+        <v>2.08</v>
+      </c>
+      <c r="P2">
+        <v>1.25</v>
+      </c>
+      <c r="Q2">
+        <v>4.8</v>
+      </c>
+      <c r="R2">
+        <v>1.07</v>
+      </c>
+      <c r="S2">
+        <v>13.5</v>
+      </c>
+      <c r="T2">
+        <v>3.2</v>
+      </c>
+      <c r="U2">
+        <v>1.41</v>
+      </c>
+      <c r="V2">
+        <v>1.6</v>
+      </c>
+      <c r="W2">
+        <v>1.34</v>
+      </c>
+      <c r="X2">
+        <v>4.9</v>
+      </c>
+      <c r="Y2">
+        <v>5.6</v>
+      </c>
+      <c r="Z2">
+        <v>13</v>
+      </c>
+      <c r="AA2">
+        <v>46</v>
+      </c>
+      <c r="AB2">
+        <v>7.6</v>
+      </c>
+      <c r="AC2">
+        <v>7.8</v>
+      </c>
+      <c r="AD2">
+        <v>18.5</v>
+      </c>
+      <c r="AE2">
+        <v>85</v>
+      </c>
+      <c r="AF2">
+        <v>23</v>
+      </c>
+      <c r="AG2">
+        <v>25</v>
+      </c>
+      <c r="AH2">
+        <v>55</v>
+      </c>
+      <c r="AI2">
+        <v>250</v>
+      </c>
+      <c r="AJ2">
+        <v>120</v>
+      </c>
+      <c r="AK2">
+        <v>150</v>
+      </c>
+      <c r="AL2">
+        <v>330</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>270</v>
+      </c>
+      <c r="AO2">
+        <v>110</v>
+      </c>
+      <c r="AP2">
+        <v>4.6</v>
+      </c>
+      <c r="AQ2">
         <v>5.4</v>
       </c>
-      <c r="O2">
-        <v>1.21</v>
-      </c>
-      <c r="P2">
-        <v>2.5</v>
-      </c>
-      <c r="Q2">
-        <v>1.64</v>
-      </c>
-      <c r="R2">
-        <v>1.6</v>
-      </c>
-      <c r="S2">
-        <v>2.62</v>
-      </c>
-      <c r="T2">
-        <v>1.6</v>
-      </c>
-      <c r="U2">
-        <v>2.58</v>
-      </c>
-      <c r="V2">
-        <v>1.89</v>
-      </c>
-      <c r="W2">
-        <v>1.36</v>
-      </c>
-      <c r="X2">
-        <v>22</v>
-      </c>
-      <c r="Y2">
-        <v>13</v>
-      </c>
-      <c r="Z2">
+      <c r="AR2">
+        <v>11</v>
+      </c>
+      <c r="AS2">
+        <v>36</v>
+      </c>
+      <c r="AT2">
+        <v>7</v>
+      </c>
+      <c r="AU2">
+        <v>7</v>
+      </c>
+      <c r="AV2">
+        <v>16</v>
+      </c>
+      <c r="AW2">
+        <v>48</v>
+      </c>
+      <c r="AX2">
+        <v>20</v>
+      </c>
+      <c r="AY2">
+        <v>21</v>
+      </c>
+      <c r="AZ2">
+        <v>38</v>
+      </c>
+      <c r="BA2">
+        <v>32</v>
+      </c>
+      <c r="BB2">
         <v>14.5</v>
       </c>
-      <c r="AA2">
-        <v>24</v>
-      </c>
-      <c r="AB2">
-        <v>20</v>
-      </c>
-      <c r="AC2">
-        <v>9</v>
-      </c>
-      <c r="AD2">
-        <v>10.5</v>
-      </c>
-      <c r="AE2">
-        <v>18</v>
-      </c>
-      <c r="AF2">
-        <v>34</v>
-      </c>
-      <c r="AG2">
-        <v>16.5</v>
-      </c>
-      <c r="AH2">
-        <v>15</v>
-      </c>
-      <c r="AI2">
-        <v>27</v>
-      </c>
-      <c r="AJ2">
-        <v>75</v>
-      </c>
-      <c r="AK2">
-        <v>40</v>
-      </c>
-      <c r="AL2">
-        <v>42</v>
-      </c>
-      <c r="AM2">
+      <c r="BC2">
+        <v>90</v>
+      </c>
+      <c r="BD2">
+        <v>55</v>
+      </c>
+      <c r="BE2">
+        <v>120</v>
+      </c>
+      <c r="BF2">
+        <v>15.5</v>
+      </c>
+      <c r="BG2">
         <v>60</v>
       </c>
-      <c r="AN2">
-        <v>32</v>
-      </c>
-      <c r="AO2">
-        <v>9.6</v>
-      </c>
-      <c r="AP2">
-        <v>19.5</v>
-      </c>
-      <c r="AQ2">
-        <v>12</v>
-      </c>
-      <c r="AR2">
-        <v>13</v>
-      </c>
-      <c r="AS2">
-        <v>21</v>
-      </c>
-      <c r="AT2">
-        <v>18.5</v>
-      </c>
-      <c r="AU2">
-        <v>8.4</v>
-      </c>
-      <c r="AV2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW2">
-        <v>16.5</v>
-      </c>
-      <c r="AX2">
-        <v>30</v>
-      </c>
-      <c r="AY2">
-        <v>15</v>
-      </c>
-      <c r="AZ2">
-        <v>13.5</v>
-      </c>
-      <c r="BA2">
-        <v>24</v>
-      </c>
-      <c r="BB2">
-        <v>65</v>
-      </c>
-      <c r="BC2">
-        <v>34</v>
-      </c>
-      <c r="BD2">
-        <v>36</v>
-      </c>
-      <c r="BE2">
-        <v>50</v>
-      </c>
-      <c r="BF2">
-        <v>28</v>
-      </c>
-      <c r="BG2">
-        <v>9</v>
-      </c>
       <c r="BH2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>177</v>
@@ -1383,226 +1383,226 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="G3">
-        <v>2.08</v>
+        <v>2.54</v>
       </c>
       <c r="H3">
+        <v>4.7</v>
+      </c>
+      <c r="I3">
+        <v>4.8</v>
+      </c>
+      <c r="J3">
+        <v>2.52</v>
+      </c>
+      <c r="K3">
+        <v>2.56</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>3.95</v>
+      </c>
+      <c r="Q3">
+        <v>1.33</v>
+      </c>
+      <c r="R3">
+        <v>1.63</v>
+      </c>
+      <c r="S3">
+        <v>2.52</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>1.26</v>
+      </c>
+      <c r="W3">
+        <v>1.64</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>4.1</v>
+      </c>
+      <c r="AD3">
+        <v>7.8</v>
+      </c>
+      <c r="AE3">
+        <v>34</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>4.7</v>
+      </c>
+      <c r="AH3">
+        <v>8</v>
+      </c>
+      <c r="AI3">
+        <v>36</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>13</v>
+      </c>
+      <c r="AL3">
+        <v>23</v>
+      </c>
+      <c r="AM3">
+        <v>95</v>
+      </c>
+      <c r="AN3">
+        <v>28</v>
+      </c>
+      <c r="AO3">
+        <v>100</v>
+      </c>
+      <c r="AP3">
+        <v>1000</v>
+      </c>
+      <c r="AQ3">
+        <v>18</v>
+      </c>
+      <c r="AR3">
+        <v>18</v>
+      </c>
+      <c r="AS3">
+        <v>18</v>
+      </c>
+      <c r="AT3">
+        <v>1000</v>
+      </c>
+      <c r="AU3">
+        <v>3.85</v>
+      </c>
+      <c r="AV3">
+        <v>7</v>
+      </c>
+      <c r="AW3">
+        <v>30</v>
+      </c>
+      <c r="AX3">
+        <v>1000</v>
+      </c>
+      <c r="AY3">
         <v>4.3</v>
       </c>
-      <c r="I3">
-        <v>4.5</v>
-      </c>
-      <c r="J3">
-        <v>3.4</v>
-      </c>
-      <c r="K3">
-        <v>3.5</v>
-      </c>
-      <c r="L3">
-        <v>1.51</v>
-      </c>
-      <c r="M3">
-        <v>1.1</v>
-      </c>
-      <c r="N3">
-        <v>3.25</v>
-      </c>
-      <c r="O3">
-        <v>1.42</v>
-      </c>
-      <c r="P3">
-        <v>1.76</v>
-      </c>
-      <c r="Q3">
-        <v>2.28</v>
-      </c>
-      <c r="R3">
-        <v>1.28</v>
-      </c>
-      <c r="S3">
-        <v>4.3</v>
-      </c>
-      <c r="T3">
-        <v>2.02</v>
-      </c>
-      <c r="U3">
-        <v>1.95</v>
-      </c>
-      <c r="V3">
-        <v>1.28</v>
-      </c>
-      <c r="W3">
-        <v>1.92</v>
-      </c>
-      <c r="X3">
+      <c r="AZ3">
+        <v>7.2</v>
+      </c>
+      <c r="BA3">
+        <v>32</v>
+      </c>
+      <c r="BB3">
+        <v>1000</v>
+      </c>
+      <c r="BC3">
         <v>11.5</v>
       </c>
-      <c r="Y3">
-        <v>13</v>
-      </c>
-      <c r="Z3">
-        <v>34</v>
-      </c>
-      <c r="AA3">
-        <v>110</v>
-      </c>
-      <c r="AB3">
-        <v>8</v>
-      </c>
-      <c r="AC3">
-        <v>7.6</v>
-      </c>
-      <c r="AD3">
-        <v>17.5</v>
-      </c>
-      <c r="AE3">
+      <c r="BD3">
+        <v>20</v>
+      </c>
+      <c r="BE3">
         <v>65</v>
       </c>
-      <c r="AF3">
-        <v>11.5</v>
-      </c>
-      <c r="AG3">
-        <v>11</v>
-      </c>
-      <c r="AH3">
-        <v>21</v>
-      </c>
-      <c r="AI3">
-        <v>75</v>
-      </c>
-      <c r="AJ3">
-        <v>23</v>
-      </c>
-      <c r="AK3">
+      <c r="BF3">
         <v>24</v>
       </c>
-      <c r="AL3">
-        <v>44</v>
-      </c>
-      <c r="AM3">
-        <v>130</v>
-      </c>
-      <c r="AN3">
-        <v>19</v>
-      </c>
-      <c r="AO3">
-        <v>90</v>
-      </c>
-      <c r="AP3">
-        <v>10</v>
-      </c>
-      <c r="AQ3">
-        <v>12.5</v>
-      </c>
-      <c r="AR3">
-        <v>29</v>
-      </c>
-      <c r="AS3">
-        <v>65</v>
-      </c>
-      <c r="AT3">
-        <v>7.4</v>
-      </c>
-      <c r="AU3">
-        <v>7</v>
-      </c>
-      <c r="AV3">
-        <v>16</v>
-      </c>
-      <c r="AW3">
+      <c r="BG3">
         <v>55</v>
       </c>
-      <c r="AX3">
-        <v>10.5</v>
-      </c>
-      <c r="AY3">
-        <v>10</v>
-      </c>
-      <c r="AZ3">
-        <v>18.5</v>
-      </c>
-      <c r="BA3">
-        <v>60</v>
-      </c>
-      <c r="BB3">
-        <v>21</v>
-      </c>
-      <c r="BC3">
-        <v>21</v>
-      </c>
-      <c r="BD3">
-        <v>40</v>
-      </c>
-      <c r="BE3">
-        <v>120</v>
-      </c>
-      <c r="BF3">
-        <v>17</v>
-      </c>
-      <c r="BG3">
-        <v>48</v>
-      </c>
       <c r="BH3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1625,22 +1625,22 @@
         <v>145</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H4">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J4">
         <v>4.5</v>
       </c>
       <c r="K4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L4">
         <v>1.31</v>
@@ -1649,52 +1649,52 @@
         <v>1.04</v>
       </c>
       <c r="N4">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R4">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S4">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="T4">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="U4">
         <v>2.2</v>
       </c>
       <c r="V4">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="W4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X4">
         <v>23</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB4">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AC4">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AD4">
         <v>10.5</v>
@@ -1703,148 +1703,148 @@
         <v>16</v>
       </c>
       <c r="AF4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG4">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI4">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AJ4">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AK4">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AL4">
         <v>70</v>
       </c>
       <c r="AM4">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AN4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AO4">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AP4">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="AQ4">
+        <v>9</v>
+      </c>
+      <c r="AR4">
+        <v>9</v>
+      </c>
+      <c r="AS4">
+        <v>13.5</v>
+      </c>
+      <c r="AT4">
+        <v>23</v>
+      </c>
+      <c r="AU4">
         <v>9.4</v>
       </c>
-      <c r="AR4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS4">
-        <v>13</v>
-      </c>
-      <c r="AT4">
+      <c r="AV4">
+        <v>8.6</v>
+      </c>
+      <c r="AW4">
+        <v>12.5</v>
+      </c>
+      <c r="AX4">
+        <v>44</v>
+      </c>
+      <c r="AY4">
         <v>20</v>
       </c>
-      <c r="AU4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV4">
-        <v>9</v>
-      </c>
-      <c r="AW4">
-        <v>13.5</v>
-      </c>
-      <c r="AX4">
-        <v>36</v>
-      </c>
-      <c r="AY4">
-        <v>18.5</v>
-      </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="BB4">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="BC4">
-        <v>6.8</v>
+        <v>48</v>
       </c>
       <c r="BD4">
-        <v>6.6</v>
+        <v>46</v>
       </c>
       <c r="BE4">
-        <v>6.8</v>
+        <v>60</v>
       </c>
       <c r="BF4">
-        <v>6.8</v>
+        <v>44</v>
       </c>
       <c r="BG4">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BH4">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI4">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
+        <v>5.5</v>
+      </c>
+      <c r="BN4">
+        <v>12</v>
+      </c>
+      <c r="BO4">
+        <v>7</v>
+      </c>
+      <c r="BP4">
+        <v>50</v>
+      </c>
+      <c r="BQ4">
         <v>5.2</v>
-      </c>
-      <c r="BN4">
-        <v>11</v>
-      </c>
-      <c r="BO4">
-        <v>3.65</v>
-      </c>
-      <c r="BP4">
-        <v>60</v>
-      </c>
-      <c r="BQ4">
-        <v>5</v>
       </c>
       <c r="BR4">
         <v>55</v>
       </c>
       <c r="BS4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BT4">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BU4">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BV4">
         <v>11.5</v>
       </c>
       <c r="BW4">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BX4">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
+        <v>4.6</v>
+      </c>
+      <c r="BZ4">
+        <v>17.5</v>
+      </c>
+      <c r="CA4">
         <v>4.5</v>
-      </c>
-      <c r="BZ4">
-        <v>17</v>
-      </c>
-      <c r="CA4">
-        <v>4.1</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1867,22 +1867,22 @@
         <v>146</v>
       </c>
       <c r="F5">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="G5">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="K5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="L5">
         <v>1.24</v>
@@ -1891,10 +1891,10 @@
         <v>1.03</v>
       </c>
       <c r="N5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P5">
         <v>3</v>
@@ -1903,46 +1903,46 @@
         <v>1.45</v>
       </c>
       <c r="R5">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="S5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T5">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="U5">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W5">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="X5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Y5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Z5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA5">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="AB5">
         <v>14.5</v>
       </c>
       <c r="AC5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD5">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AE5">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AF5">
         <v>12</v>
@@ -1951,142 +1951,142 @@
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL5">
         <v>26</v>
       </c>
       <c r="AM5">
+        <v>85</v>
+      </c>
+      <c r="AN5">
+        <v>4.5</v>
+      </c>
+      <c r="AO5">
         <v>90</v>
       </c>
-      <c r="AN5">
-        <v>4.8</v>
-      </c>
-      <c r="AO5">
-        <v>75</v>
-      </c>
       <c r="AP5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AR5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AS5">
-        <v>120</v>
+        <v>15.5</v>
       </c>
       <c r="AT5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE5">
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BG5">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BH5">
         <v>5.7</v>
       </c>
       <c r="BI5">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BL5">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BM5">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BN5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP5">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BQ5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BS5">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BT5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BU5">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV5">
         <v>55</v>
       </c>
       <c r="BW5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX5">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BY5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BZ5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA5">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="CB5" t="s">
         <v>177</v>
@@ -2115,67 +2115,67 @@
         <v>2.76</v>
       </c>
       <c r="H6">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="I6">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="J6">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O6">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P6">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q6">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T6">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U6">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
         <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y6">
+        <v>13</v>
+      </c>
+      <c r="Z6">
+        <v>19</v>
+      </c>
+      <c r="AA6">
+        <v>40</v>
+      </c>
+      <c r="AB6">
         <v>13.5</v>
-      </c>
-      <c r="Z6">
-        <v>19.5</v>
-      </c>
-      <c r="AA6">
-        <v>38</v>
-      </c>
-      <c r="AB6">
-        <v>14</v>
       </c>
       <c r="AC6">
         <v>8.4</v>
@@ -2184,13 +2184,13 @@
         <v>12</v>
       </c>
       <c r="AE6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF6">
         <v>19.5</v>
       </c>
       <c r="AG6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH6">
         <v>15.5</v>
@@ -2202,7 +2202,7 @@
         <v>40</v>
       </c>
       <c r="AK6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL6">
         <v>36</v>
@@ -2211,22 +2211,22 @@
         <v>70</v>
       </c>
       <c r="AN6">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO6">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AP6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR6">
         <v>17.5</v>
       </c>
       <c r="AS6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT6">
         <v>12</v>
@@ -2235,7 +2235,7 @@
         <v>7.8</v>
       </c>
       <c r="AV6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW6">
         <v>24</v>
@@ -2250,10 +2250,10 @@
         <v>14</v>
       </c>
       <c r="BA6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC6">
         <v>24</v>
@@ -2265,28 +2265,28 @@
         <v>60</v>
       </c>
       <c r="BF6">
+        <v>18.5</v>
+      </c>
+      <c r="BG6">
         <v>18</v>
       </c>
-      <c r="BG6">
-        <v>17</v>
-      </c>
       <c r="BH6">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BI6">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6">
         <v>8.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BN6">
         <v>5.9</v>
@@ -2298,16 +2298,16 @@
         <v>19.5</v>
       </c>
       <c r="BQ6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BR6">
         <v>29</v>
       </c>
       <c r="BS6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU6">
         <v>5.3</v>
@@ -2316,19 +2316,19 @@
         <v>19</v>
       </c>
       <c r="BW6">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ6">
         <v>21</v>
       </c>
       <c r="CA6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="s">
         <v>177</v>
@@ -2351,10 +2351,10 @@
         <v>148</v>
       </c>
       <c r="F7">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H7">
         <v>3.8</v>
@@ -2363,10 +2363,10 @@
         <v>3.95</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
         <v>1.45</v>
@@ -2375,7 +2375,7 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
         <v>1.36</v>
@@ -2399,46 +2399,46 @@
         <v>2.1</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X7">
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z7">
         <v>27</v>
       </c>
       <c r="AA7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC7">
         <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE7">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
         <v>18.5</v>
       </c>
       <c r="AI7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ7">
         <v>28</v>
@@ -2447,13 +2447,13 @@
         <v>25</v>
       </c>
       <c r="AL7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO7">
         <v>55</v>
@@ -2465,13 +2465,13 @@
         <v>12</v>
       </c>
       <c r="AR7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS7">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU7">
         <v>7</v>
@@ -2489,46 +2489,46 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA7">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BB7">
         <v>23</v>
       </c>
       <c r="BC7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD7">
         <v>32</v>
       </c>
       <c r="BE7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG7">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BH7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI7">
         <v>3</v>
       </c>
       <c r="BJ7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BL7">
         <v>140</v>
       </c>
       <c r="BM7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN7">
         <v>4.9</v>
@@ -2537,16 +2537,16 @@
         <v>4.4</v>
       </c>
       <c r="BP7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ7">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BR7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT7">
         <v>7</v>
@@ -2555,22 +2555,22 @@
         <v>6.2</v>
       </c>
       <c r="BV7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX7">
         <v>46</v>
       </c>
       <c r="BY7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="CA7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="s">
         <v>177</v>
@@ -2593,16 +2593,16 @@
         <v>149</v>
       </c>
       <c r="F8">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G8">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H8">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J8">
         <v>4.5</v>
@@ -2626,16 +2626,16 @@
         <v>2.4</v>
       </c>
       <c r="Q8">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R8">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S8">
         <v>2.74</v>
       </c>
       <c r="T8">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U8">
         <v>2.26</v>
@@ -2644,13 +2644,13 @@
         <v>1.21</v>
       </c>
       <c r="W8">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X8">
         <v>22</v>
       </c>
       <c r="Y8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z8">
         <v>48</v>
@@ -2668,22 +2668,22 @@
         <v>22</v>
       </c>
       <c r="AE8">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF8">
         <v>11</v>
       </c>
       <c r="AG8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI8">
         <v>65</v>
       </c>
       <c r="AJ8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK8">
         <v>16</v>
@@ -2704,16 +2704,16 @@
         <v>19.5</v>
       </c>
       <c r="AQ8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR8">
         <v>42</v>
       </c>
       <c r="AS8">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AT8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU8">
         <v>9.4</v>
@@ -2722,7 +2722,7 @@
         <v>19</v>
       </c>
       <c r="AW8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX8">
         <v>10</v>
@@ -2734,7 +2734,7 @@
         <v>17</v>
       </c>
       <c r="BA8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB8">
         <v>15</v>
@@ -2746,13 +2746,13 @@
         <v>25</v>
       </c>
       <c r="BE8">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF8">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH8">
         <v>4.1</v>
@@ -2770,10 +2770,10 @@
         <v>120</v>
       </c>
       <c r="BM8">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BN8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO8">
         <v>4</v>
@@ -2788,7 +2788,7 @@
         <v>27</v>
       </c>
       <c r="BS8">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BT8">
         <v>11</v>
@@ -2797,22 +2797,22 @@
         <v>8</v>
       </c>
       <c r="BV8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW8">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX8">
         <v>55</v>
       </c>
       <c r="BY8">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BZ8">
         <v>18.5</v>
       </c>
       <c r="CA8">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="CB8" t="s">
         <v>177</v>
@@ -2835,22 +2835,22 @@
         <v>150</v>
       </c>
       <c r="F9">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="G9">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I9">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K9">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L9">
         <v>1.35</v>
@@ -2865,55 +2865,55 @@
         <v>1.25</v>
       </c>
       <c r="P9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q9">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R9">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S9">
         <v>2.9</v>
       </c>
       <c r="T9">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U9">
         <v>2.1</v>
       </c>
       <c r="V9">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W9">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="X9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z9">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG9">
         <v>9.6</v>
@@ -2922,13 +2922,13 @@
         <v>21</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL9">
         <v>32</v>
@@ -2937,82 +2937,82 @@
         <v>110</v>
       </c>
       <c r="AN9">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO9">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP9">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR9">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AS9">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AT9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9">
+        <v>9.4</v>
+      </c>
+      <c r="AV9">
+        <v>23</v>
+      </c>
+      <c r="AW9">
+        <v>55</v>
+      </c>
+      <c r="AX9">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AV9">
-        <v>20</v>
-      </c>
-      <c r="AW9">
-        <v>50</v>
-      </c>
-      <c r="AX9">
-        <v>9.4</v>
       </c>
       <c r="AY9">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA9">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BB9">
         <v>13.5</v>
       </c>
       <c r="BC9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE9">
         <v>65</v>
       </c>
       <c r="BF9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH9">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI9">
         <v>3.6</v>
       </c>
       <c r="BJ9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN9">
         <v>4.2</v>
@@ -3021,40 +3021,40 @@
         <v>3.9</v>
       </c>
       <c r="BP9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ9">
+        <v>8.6</v>
+      </c>
+      <c r="BR9">
+        <v>24</v>
+      </c>
+      <c r="BS9">
+        <v>10</v>
+      </c>
+      <c r="BT9">
+        <v>10</v>
+      </c>
+      <c r="BU9">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BR9">
-        <v>25</v>
-      </c>
-      <c r="BS9">
-        <v>9</v>
-      </c>
-      <c r="BT9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU9">
-        <v>8.6</v>
       </c>
       <c r="BV9">
         <v>55</v>
       </c>
       <c r="BW9">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BX9">
         <v>55</v>
       </c>
       <c r="BY9">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BZ9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CA9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="s">
         <v>177</v>
@@ -3077,16 +3077,16 @@
         <v>151</v>
       </c>
       <c r="F10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H10">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3095,7 +3095,7 @@
         <v>4.2</v>
       </c>
       <c r="L10">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M10">
         <v>1.05</v>
@@ -3104,16 +3104,16 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P10">
         <v>2.38</v>
       </c>
       <c r="Q10">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R10">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S10">
         <v>2.78</v>
@@ -3131,7 +3131,7 @@
         <v>2</v>
       </c>
       <c r="X10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y10">
         <v>19.5</v>
@@ -3140,7 +3140,7 @@
         <v>32</v>
       </c>
       <c r="AA10">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB10">
         <v>12.5</v>
@@ -3155,7 +3155,7 @@
         <v>42</v>
       </c>
       <c r="AF10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG10">
         <v>10.5</v>
@@ -3167,13 +3167,13 @@
         <v>44</v>
       </c>
       <c r="AJ10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK10">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM10">
         <v>70</v>
@@ -3191,22 +3191,22 @@
         <v>17.5</v>
       </c>
       <c r="AR10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS10">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AT10">
         <v>11</v>
       </c>
       <c r="AU10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV10">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX10">
         <v>12.5</v>
@@ -3215,7 +3215,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA10">
         <v>38</v>
@@ -3227,73 +3227,73 @@
         <v>16.5</v>
       </c>
       <c r="BD10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE10">
         <v>55</v>
       </c>
       <c r="BF10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG10">
         <v>28</v>
       </c>
       <c r="BH10">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BI10">
         <v>3.6</v>
       </c>
       <c r="BJ10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK10">
         <v>7.8</v>
       </c>
       <c r="BL10">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BM10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP10">
         <v>14</v>
       </c>
       <c r="BQ10">
+        <v>8.6</v>
+      </c>
+      <c r="BR10">
+        <v>25</v>
+      </c>
+      <c r="BS10">
+        <v>8.4</v>
+      </c>
+      <c r="BT10">
+        <v>7.4</v>
+      </c>
+      <c r="BU10">
         <v>6.6</v>
-      </c>
-      <c r="BR10">
-        <v>24</v>
-      </c>
-      <c r="BS10">
-        <v>8.6</v>
-      </c>
-      <c r="BT10">
-        <v>7.6</v>
-      </c>
-      <c r="BU10">
-        <v>6.4</v>
       </c>
       <c r="BV10">
         <v>30</v>
       </c>
       <c r="BW10">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BY10">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CA10">
         <v>7.6</v>
@@ -3322,19 +3322,19 @@
         <v>3.9</v>
       </c>
       <c r="G11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H11">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="I11">
         <v>2.14</v>
       </c>
       <c r="J11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L11">
         <v>1.47</v>
@@ -3343,37 +3343,37 @@
         <v>1.09</v>
       </c>
       <c r="N11">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O11">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P11">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q11">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T11">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U11">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V11">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W11">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X11">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y11">
         <v>8.199999999999999</v>
@@ -3394,7 +3394,7 @@
         <v>11</v>
       </c>
       <c r="AE11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF11">
         <v>29</v>
@@ -3406,13 +3406,13 @@
         <v>21</v>
       </c>
       <c r="AI11">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AJ11">
         <v>900</v>
       </c>
       <c r="AK11">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AL11">
         <v>260</v>
@@ -3421,37 +3421,37 @@
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="AO11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ11">
         <v>7.2</v>
       </c>
       <c r="AR11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AT11">
         <v>11</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY11">
         <v>14.5</v>
@@ -3460,16 +3460,16 @@
         <v>18</v>
       </c>
       <c r="BA11">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BB11">
+        <v>55</v>
+      </c>
+      <c r="BC11">
+        <v>36</v>
+      </c>
+      <c r="BD11">
         <v>42</v>
-      </c>
-      <c r="BC11">
-        <v>27</v>
-      </c>
-      <c r="BD11">
-        <v>30</v>
       </c>
       <c r="BE11">
         <v>55</v>
@@ -3484,7 +3484,7 @@
         <v>3.15</v>
       </c>
       <c r="BI11">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
@@ -3496,7 +3496,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN11">
         <v>7.6</v>
@@ -3505,7 +3505,7 @@
         <v>5.6</v>
       </c>
       <c r="BP11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ11">
         <v>10.5</v>
@@ -3526,7 +3526,7 @@
         <v>15.5</v>
       </c>
       <c r="BW11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX11">
         <v>34</v>
@@ -3561,7 +3561,7 @@
         <v>153</v>
       </c>
       <c r="F12">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="G12">
         <v>1.87</v>
@@ -3570,7 +3570,7 @@
         <v>5.1</v>
       </c>
       <c r="I12">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J12">
         <v>3.65</v>
@@ -3582,7 +3582,7 @@
         <v>1.43</v>
       </c>
       <c r="M12">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N12">
         <v>3.5</v>
@@ -3612,16 +3612,16 @@
         <v>1.22</v>
       </c>
       <c r="W12">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X12">
         <v>13.5</v>
       </c>
       <c r="Y12">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA12">
         <v>900</v>
@@ -3633,43 +3633,43 @@
         <v>8.6</v>
       </c>
       <c r="AD12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE12">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG12">
         <v>10.5</v>
       </c>
       <c r="AH12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI12">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="AJ12">
         <v>20</v>
       </c>
       <c r="AK12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM12">
         <v>580</v>
       </c>
       <c r="AN12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO12">
-        <v>600</v>
+        <v>130</v>
       </c>
       <c r="AP12">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ12">
         <v>14</v>
@@ -3678,13 +3678,13 @@
         <v>29</v>
       </c>
       <c r="AS12">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AT12">
         <v>6.8</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV12">
         <v>17.5</v>
@@ -3693,13 +3693,13 @@
         <v>46</v>
       </c>
       <c r="AX12">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY12">
         <v>9</v>
       </c>
       <c r="AZ12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA12">
         <v>50</v>
@@ -3708,7 +3708,7 @@
         <v>16.5</v>
       </c>
       <c r="BC12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD12">
         <v>27</v>
@@ -3717,7 +3717,7 @@
         <v>85</v>
       </c>
       <c r="BF12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG12">
         <v>55</v>
@@ -3803,7 +3803,7 @@
         <v>154</v>
       </c>
       <c r="F13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G13">
         <v>3.9</v>
@@ -3812,46 +3812,46 @@
         <v>2.12</v>
       </c>
       <c r="I13">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L13">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M13">
         <v>1.07</v>
       </c>
       <c r="N13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O13">
         <v>1.3</v>
       </c>
       <c r="P13">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q13">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="R13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T13">
         <v>1.74</v>
       </c>
       <c r="U13">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V13">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W13">
         <v>1.34</v>
@@ -3860,16 +3860,16 @@
         <v>15.5</v>
       </c>
       <c r="Y13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA13">
         <v>26</v>
       </c>
       <c r="AB13">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC13">
         <v>8.199999999999999</v>
@@ -3884,16 +3884,16 @@
         <v>28</v>
       </c>
       <c r="AG13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH13">
         <v>17.5</v>
       </c>
       <c r="AI13">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ13">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK13">
         <v>44</v>
@@ -3902,13 +3902,13 @@
         <v>55</v>
       </c>
       <c r="AM13">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN13">
         <v>44</v>
       </c>
       <c r="AO13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP13">
         <v>13.5</v>
@@ -3932,55 +3932,55 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY13">
         <v>14</v>
       </c>
       <c r="AZ13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA13">
         <v>30</v>
       </c>
       <c r="BB13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC13">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE13">
         <v>65</v>
       </c>
       <c r="BF13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG13">
         <v>13</v>
       </c>
       <c r="BH13">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BI13">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK13">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN13">
         <v>7</v>
@@ -3992,37 +3992,37 @@
         <v>30</v>
       </c>
       <c r="BQ13">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR13">
         <v>40</v>
       </c>
       <c r="BS13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU13">
         <v>4.5</v>
       </c>
       <c r="BV13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW13">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BX13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY13">
+        <v>11</v>
+      </c>
+      <c r="BZ13">
+        <v>25</v>
+      </c>
+      <c r="CA13">
         <v>10.5</v>
-      </c>
-      <c r="BZ13">
-        <v>24</v>
-      </c>
-      <c r="CA13">
-        <v>10</v>
       </c>
       <c r="CB13" t="s">
         <v>177</v>
@@ -4045,19 +4045,19 @@
         <v>155</v>
       </c>
       <c r="F14">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G14">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H14">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I14">
         <v>2.04</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K14">
         <v>4.1</v>
@@ -4069,16 +4069,16 @@
         <v>1.05</v>
       </c>
       <c r="N14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O14">
         <v>1.23</v>
       </c>
       <c r="P14">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q14">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R14">
         <v>1.55</v>
@@ -4087,7 +4087,7 @@
         <v>2.72</v>
       </c>
       <c r="T14">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U14">
         <v>2.48</v>
@@ -4096,10 +4096,10 @@
         <v>1.96</v>
       </c>
       <c r="W14">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y14">
         <v>12.5</v>
@@ -4111,22 +4111,22 @@
         <v>24</v>
       </c>
       <c r="AB14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
       </c>
       <c r="AE14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF14">
         <v>32</v>
       </c>
       <c r="AG14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH14">
         <v>15.5</v>
@@ -4141,7 +4141,7 @@
         <v>40</v>
       </c>
       <c r="AL14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM14">
         <v>65</v>
@@ -4153,7 +4153,7 @@
         <v>10.5</v>
       </c>
       <c r="AP14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ14">
         <v>11</v>
@@ -4162,7 +4162,7 @@
         <v>13</v>
       </c>
       <c r="AS14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT14">
         <v>17</v>
@@ -4177,10 +4177,10 @@
         <v>17</v>
       </c>
       <c r="AX14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ14">
         <v>14</v>
@@ -4192,7 +4192,7 @@
         <v>60</v>
       </c>
       <c r="BC14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD14">
         <v>38</v>
@@ -4201,10 +4201,10 @@
         <v>55</v>
       </c>
       <c r="BF14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG14">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH14">
         <v>4.1</v>
@@ -4216,52 +4216,52 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK14">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL14">
         <v>85</v>
       </c>
       <c r="BM14">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN14">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO14">
         <v>6.6</v>
       </c>
       <c r="BP14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BQ14">
         <v>10.5</v>
       </c>
       <c r="BR14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS14">
+        <v>11</v>
+      </c>
+      <c r="BT14">
+        <v>5</v>
+      </c>
+      <c r="BU14">
+        <v>4.6</v>
+      </c>
+      <c r="BV14">
+        <v>13</v>
+      </c>
+      <c r="BW14">
         <v>11.5</v>
-      </c>
-      <c r="BT14">
-        <v>5.1</v>
-      </c>
-      <c r="BU14">
-        <v>4.7</v>
-      </c>
-      <c r="BV14">
-        <v>13.5</v>
-      </c>
-      <c r="BW14">
-        <v>7.8</v>
       </c>
       <c r="BX14">
         <v>23</v>
       </c>
       <c r="BY14">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA14">
         <v>8.800000000000001</v>
@@ -4287,13 +4287,13 @@
         <v>156</v>
       </c>
       <c r="F15">
+        <v>1.68</v>
+      </c>
+      <c r="G15">
         <v>1.7</v>
       </c>
-      <c r="G15">
-        <v>1.72</v>
-      </c>
       <c r="H15">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I15">
         <v>5.3</v>
@@ -4305,43 +4305,43 @@
         <v>4.6</v>
       </c>
       <c r="L15">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M15">
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O15">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P15">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="Q15">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R15">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S15">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="T15">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U15">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V15">
         <v>1.23</v>
       </c>
       <c r="W15">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Y15">
         <v>28</v>
@@ -4353,13 +4353,13 @@
         <v>110</v>
       </c>
       <c r="AB15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC15">
         <v>11</v>
       </c>
       <c r="AD15">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE15">
         <v>55</v>
@@ -4380,7 +4380,7 @@
         <v>17.5</v>
       </c>
       <c r="AK15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL15">
         <v>24</v>
@@ -4389,22 +4389,22 @@
         <v>60</v>
       </c>
       <c r="AN15">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AO15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP15">
         <v>26</v>
       </c>
       <c r="AQ15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR15">
         <v>40</v>
       </c>
       <c r="AS15">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AT15">
         <v>12.5</v>
@@ -4413,10 +4413,10 @@
         <v>10</v>
       </c>
       <c r="AV15">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW15">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX15">
         <v>12.5</v>
@@ -4428,13 +4428,13 @@
         <v>15</v>
       </c>
       <c r="BA15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB15">
         <v>16.5</v>
       </c>
       <c r="BC15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD15">
         <v>22</v>
@@ -4443,70 +4443,70 @@
         <v>48</v>
       </c>
       <c r="BF15">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG15">
         <v>32</v>
       </c>
       <c r="BH15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI15">
         <v>4.3</v>
       </c>
       <c r="BJ15">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BK15">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL15">
         <v>80</v>
       </c>
       <c r="BM15">
-        <v>17.5</v>
+        <v>7.6</v>
       </c>
       <c r="BN15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO15">
         <v>4.4</v>
       </c>
       <c r="BP15">
+        <v>12</v>
+      </c>
+      <c r="BQ15">
+        <v>5.8</v>
+      </c>
+      <c r="BR15">
+        <v>22</v>
+      </c>
+      <c r="BS15">
+        <v>6.4</v>
+      </c>
+      <c r="BT15">
         <v>10.5</v>
-      </c>
-      <c r="BQ15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BR15">
-        <v>19.5</v>
-      </c>
-      <c r="BS15">
-        <v>16.5</v>
-      </c>
-      <c r="BT15">
-        <v>8.6</v>
       </c>
       <c r="BU15">
         <v>8</v>
       </c>
       <c r="BV15">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BW15">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="BX15">
         <v>34</v>
       </c>
       <c r="BY15">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="BZ15">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="CA15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CB15" t="s">
         <v>177</v>
@@ -4529,16 +4529,16 @@
         <v>157</v>
       </c>
       <c r="F16">
+        <v>2.64</v>
+      </c>
+      <c r="G16">
         <v>2.66</v>
       </c>
-      <c r="G16">
-        <v>2.68</v>
-      </c>
       <c r="H16">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I16">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="J16">
         <v>3.75</v>
@@ -4556,16 +4556,16 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P16">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q16">
         <v>1.72</v>
       </c>
       <c r="R16">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S16">
         <v>2.84</v>
@@ -4574,22 +4574,22 @@
         <v>1.61</v>
       </c>
       <c r="U16">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V16">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W16">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X16">
         <v>19.5</v>
       </c>
       <c r="Y16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z16">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA16">
         <v>40</v>
@@ -4604,7 +4604,7 @@
         <v>12.5</v>
       </c>
       <c r="AE16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF16">
         <v>19</v>
@@ -4622,7 +4622,7 @@
         <v>36</v>
       </c>
       <c r="AK16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL16">
         <v>32</v>
@@ -4649,7 +4649,7 @@
         <v>38</v>
       </c>
       <c r="AT16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU16">
         <v>8</v>
@@ -4658,7 +4658,7 @@
         <v>12</v>
       </c>
       <c r="AW16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX16">
         <v>18.5</v>
@@ -4676,22 +4676,22 @@
         <v>34</v>
       </c>
       <c r="BC16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE16">
         <v>55</v>
       </c>
       <c r="BF16">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG16">
         <v>18</v>
       </c>
       <c r="BH16">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI16">
         <v>3.6</v>
@@ -4703,19 +4703,19 @@
         <v>8</v>
       </c>
       <c r="BL16">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM16">
-        <v>70</v>
+        <v>15.5</v>
       </c>
       <c r="BN16">
         <v>5.9</v>
       </c>
       <c r="BO16">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP16">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ16">
         <v>16</v>
@@ -4724,25 +4724,25 @@
         <v>28</v>
       </c>
       <c r="BS16">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BT16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU16">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV16">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BX16">
         <v>29</v>
       </c>
       <c r="BY16">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BZ16">
         <v>19.5</v>
@@ -4771,22 +4771,22 @@
         <v>158</v>
       </c>
       <c r="F17">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="G17">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="H17">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I17">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.3</v>
@@ -4801,13 +4801,13 @@
         <v>1.18</v>
       </c>
       <c r="P17">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q17">
         <v>1.57</v>
       </c>
       <c r="R17">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S17">
         <v>2.4</v>
@@ -4816,13 +4816,13 @@
         <v>1.57</v>
       </c>
       <c r="U17">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V17">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="X17">
         <v>26</v>
@@ -4831,10 +4831,10 @@
         <v>25</v>
       </c>
       <c r="Z17">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA17">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AB17">
         <v>13.5</v>
@@ -4843,52 +4843,52 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD17">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE17">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AF17">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG17">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI17">
         <v>42</v>
       </c>
       <c r="AJ17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL17">
         <v>25</v>
       </c>
       <c r="AM17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN17">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AO17">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP17">
+        <v>23</v>
+      </c>
+      <c r="AQ17">
         <v>24</v>
       </c>
-      <c r="AQ17">
-        <v>23</v>
-      </c>
       <c r="AR17">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AS17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AT17">
         <v>13</v>
@@ -4897,28 +4897,28 @@
         <v>9.4</v>
       </c>
       <c r="AV17">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW17">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AX17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY17">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17">
         <v>14</v>
       </c>
       <c r="BA17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB17">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC17">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD17">
         <v>23</v>
@@ -4927,67 +4927,67 @@
         <v>48</v>
       </c>
       <c r="BF17">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG17">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BH17">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BI17">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ17">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK17">
         <v>8</v>
       </c>
       <c r="BL17">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BM17">
-        <v>60</v>
+        <v>13.5</v>
       </c>
       <c r="BN17">
         <v>4.9</v>
       </c>
       <c r="BO17">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP17">
         <v>11.5</v>
       </c>
       <c r="BQ17">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS17">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BT17">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BU17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV17">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BW17">
         <v>26</v>
       </c>
       <c r="BX17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY17">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BZ17">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA17">
         <v>11</v>
@@ -5019,46 +5019,46 @@
         <v>1.45</v>
       </c>
       <c r="H18">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J18">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K18">
         <v>5</v>
       </c>
       <c r="L18">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M18">
         <v>1.06</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O18">
         <v>1.3</v>
       </c>
       <c r="P18">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q18">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R18">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S18">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T18">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U18">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V18">
         <v>1.11</v>
@@ -5067,37 +5067,37 @@
         <v>3.2</v>
       </c>
       <c r="X18">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Y18">
         <v>28</v>
       </c>
       <c r="Z18">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA18">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AB18">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC18">
         <v>11.5</v>
       </c>
       <c r="AD18">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE18">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF18">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH18">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI18">
         <v>160</v>
@@ -5106,34 +5106,34 @@
         <v>11.5</v>
       </c>
       <c r="AK18">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL18">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM18">
         <v>200</v>
       </c>
       <c r="AN18">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO18">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AP18">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR18">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AS18">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="AT18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU18">
         <v>10.5</v>
@@ -5142,10 +5142,10 @@
         <v>30</v>
       </c>
       <c r="AW18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AX18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY18">
         <v>9.4</v>
@@ -5154,7 +5154,7 @@
         <v>25</v>
       </c>
       <c r="BA18">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BB18">
         <v>10.5</v>
@@ -5163,13 +5163,13 @@
         <v>15</v>
       </c>
       <c r="BD18">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BE18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BF18">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG18">
         <v>110</v>
@@ -5184,55 +5184,55 @@
         <v>14.5</v>
       </c>
       <c r="BK18">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BN18">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BO18">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP18">
         <v>10.5</v>
       </c>
       <c r="BQ18">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BR18">
         <v>32</v>
       </c>
       <c r="BS18">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BT18">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BU18">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BW18">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BX18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BY18">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BZ18">
         <v>19</v>
       </c>
       <c r="CA18">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="CB18" t="s">
         <v>177</v>
@@ -5255,31 +5255,31 @@
         <v>160</v>
       </c>
       <c r="F19">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H19">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="I19">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="J19">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="K19">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="L19">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M19">
         <v>1.18</v>
       </c>
       <c r="N19">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O19">
         <v>1.69</v>
@@ -5288,7 +5288,7 @@
         <v>1.43</v>
       </c>
       <c r="Q19">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R19">
         <v>1.15</v>
@@ -5297,22 +5297,22 @@
         <v>7</v>
       </c>
       <c r="T19">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U19">
         <v>1.59</v>
       </c>
       <c r="V19">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W19">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X19">
         <v>8.6</v>
       </c>
       <c r="Y19">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z19">
         <v>970</v>
@@ -5324,7 +5324,7 @@
         <v>22</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19">
         <v>970</v>
@@ -5369,64 +5369,64 @@
         <v>5.4</v>
       </c>
       <c r="AR19">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AS19">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AT19">
         <v>7.4</v>
       </c>
       <c r="AU19">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AV19">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AW19">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AX19">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AY19">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="BA19">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BB19">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BC19">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BD19">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BE19">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BF19">
         <v>2.38</v>
       </c>
       <c r="BG19">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BH19">
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="BL19">
         <v>1000</v>
@@ -5438,7 +5438,7 @@
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BP19">
         <v>1000</v>
@@ -5497,22 +5497,22 @@
         <v>161</v>
       </c>
       <c r="F20">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G20">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H20">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="I20">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J20">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K20">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L20">
         <v>1.37</v>
@@ -5521,7 +5521,7 @@
         <v>1.06</v>
       </c>
       <c r="N20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O20">
         <v>1.27</v>
@@ -5533,46 +5533,46 @@
         <v>1.81</v>
       </c>
       <c r="R20">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S20">
         <v>3</v>
       </c>
       <c r="T20">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U20">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V20">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="X20">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Y20">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z20">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AA20">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC20">
         <v>8.6</v>
       </c>
       <c r="AD20">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE20">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF20">
         <v>15.5</v>
@@ -5581,13 +5581,13 @@
         <v>11.5</v>
       </c>
       <c r="AH20">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI20">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ20">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AK20">
         <v>23</v>
@@ -5596,94 +5596,94 @@
         <v>40</v>
       </c>
       <c r="AM20">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AN20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO20">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP20">
         <v>14.5</v>
       </c>
       <c r="AQ20">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS20">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AT20">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU20">
         <v>7.4</v>
       </c>
       <c r="AV20">
+        <v>13</v>
+      </c>
+      <c r="AW20">
+        <v>27</v>
+      </c>
+      <c r="AX20">
+        <v>13</v>
+      </c>
+      <c r="AY20">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20">
         <v>13.5</v>
       </c>
-      <c r="AW20">
+      <c r="BA20">
         <v>30</v>
       </c>
-      <c r="AX20">
-        <v>12.5</v>
-      </c>
-      <c r="AY20">
-        <v>9.4</v>
-      </c>
-      <c r="AZ20">
-        <v>14</v>
-      </c>
-      <c r="BA20">
-        <v>32</v>
-      </c>
       <c r="BB20">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BC20">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BD20">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BE20">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BF20">
+        <v>11.5</v>
+      </c>
+      <c r="BG20">
+        <v>22</v>
+      </c>
+      <c r="BH20">
+        <v>4.5</v>
+      </c>
+      <c r="BI20">
+        <v>3.4</v>
+      </c>
+      <c r="BJ20">
         <v>11</v>
       </c>
-      <c r="BG20">
-        <v>28</v>
-      </c>
-      <c r="BH20">
-        <v>4.4</v>
-      </c>
-      <c r="BI20">
-        <v>3.35</v>
-      </c>
-      <c r="BJ20">
-        <v>11.5</v>
-      </c>
       <c r="BK20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN20">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BO20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP20">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ20">
         <v>3.65</v>
@@ -5692,22 +5692,22 @@
         <v>32</v>
       </c>
       <c r="BS20">
+        <v>4</v>
+      </c>
+      <c r="BT20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU20">
+        <v>5.5</v>
+      </c>
+      <c r="BV20">
+        <v>36</v>
+      </c>
+      <c r="BW20">
         <v>4.1</v>
       </c>
-      <c r="BT20">
-        <v>9</v>
-      </c>
-      <c r="BU20">
-        <v>5.6</v>
-      </c>
-      <c r="BV20">
-        <v>38</v>
-      </c>
-      <c r="BW20">
-        <v>4.2</v>
-      </c>
       <c r="BX20">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY20">
         <v>4.2</v>
@@ -5716,7 +5716,7 @@
         <v>25</v>
       </c>
       <c r="CA20">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="CB20" t="s">
         <v>177</v>
@@ -5739,22 +5739,22 @@
         <v>162</v>
       </c>
       <c r="F21">
+        <v>1.41</v>
+      </c>
+      <c r="G21">
         <v>1.43</v>
       </c>
-      <c r="G21">
-        <v>1.45</v>
-      </c>
       <c r="H21">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I21">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K21">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L21">
         <v>1.27</v>
@@ -5763,16 +5763,16 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O21">
         <v>1.17</v>
       </c>
       <c r="P21">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q21">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R21">
         <v>1.73</v>
@@ -5781,31 +5781,31 @@
         <v>2.3</v>
       </c>
       <c r="T21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U21">
         <v>2.18</v>
       </c>
       <c r="V21">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W21">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="X21">
         <v>32</v>
       </c>
       <c r="Y21">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z21">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AA21">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AB21">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC21">
         <v>13</v>
@@ -5814,13 +5814,13 @@
         <v>30</v>
       </c>
       <c r="AE21">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF21">
         <v>11</v>
       </c>
       <c r="AG21">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH21">
         <v>22</v>
@@ -5829,7 +5829,7 @@
         <v>85</v>
       </c>
       <c r="AJ21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK21">
         <v>14</v>
@@ -5838,25 +5838,25 @@
         <v>28</v>
       </c>
       <c r="AM21">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN21">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AO21">
         <v>90</v>
       </c>
       <c r="AP21">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AR21">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AS21">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="AT21">
         <v>11</v>
@@ -5865,7 +5865,7 @@
         <v>11.5</v>
       </c>
       <c r="AV21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW21">
         <v>60</v>
@@ -5877,13 +5877,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ21">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA21">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BB21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC21">
         <v>12.5</v>
@@ -5895,28 +5895,28 @@
         <v>55</v>
       </c>
       <c r="BF21">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG21">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BH21">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BI21">
         <v>4.3</v>
       </c>
       <c r="BJ21">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK21">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BL21">
         <v>120</v>
       </c>
       <c r="BM21">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BN21">
         <v>4.3</v>
@@ -5925,40 +5925,40 @@
         <v>3.85</v>
       </c>
       <c r="BP21">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ21">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR21">
         <v>19.5</v>
       </c>
       <c r="BS21">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BT21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU21">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW21">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="BX21">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BY21">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="BZ21">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA21">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="CB21" t="s">
         <v>177</v>
@@ -5981,31 +5981,31 @@
         <v>163</v>
       </c>
       <c r="F22">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G22">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H22">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I22">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J22">
         <v>3.95</v>
       </c>
       <c r="K22">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L22">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M22">
         <v>1.04</v>
       </c>
       <c r="N22">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O22">
         <v>1.19</v>
@@ -6017,22 +6017,22 @@
         <v>1.59</v>
       </c>
       <c r="R22">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S22">
         <v>2.48</v>
       </c>
       <c r="T22">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U22">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V22">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X22">
         <v>24</v>
@@ -6041,61 +6041,61 @@
         <v>21</v>
       </c>
       <c r="Z22">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB22">
         <v>14.5</v>
       </c>
       <c r="AC22">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD22">
         <v>15.5</v>
       </c>
       <c r="AE22">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG22">
         <v>11</v>
       </c>
       <c r="AH22">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI22">
         <v>38</v>
       </c>
       <c r="AJ22">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK22">
         <v>19</v>
       </c>
       <c r="AL22">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM22">
         <v>60</v>
       </c>
       <c r="AN22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO22">
         <v>24</v>
       </c>
       <c r="AP22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ22">
         <v>18.5</v>
       </c>
       <c r="AR22">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS22">
         <v>48</v>
@@ -6104,7 +6104,7 @@
         <v>13</v>
       </c>
       <c r="AU22">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV22">
         <v>13.5</v>
@@ -6113,10 +6113,10 @@
         <v>30</v>
       </c>
       <c r="AX22">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY22">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22">
         <v>13.5</v>
@@ -6128,25 +6128,25 @@
         <v>24</v>
       </c>
       <c r="BC22">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD22">
         <v>23</v>
       </c>
       <c r="BE22">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BF22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG22">
         <v>21</v>
       </c>
       <c r="BH22">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI22">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ22">
         <v>8.800000000000001</v>
@@ -6158,10 +6158,10 @@
         <v>80</v>
       </c>
       <c r="BM22">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN22">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO22">
         <v>4.8</v>
@@ -6170,37 +6170,37 @@
         <v>14.5</v>
       </c>
       <c r="BQ22">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BR22">
         <v>24</v>
       </c>
       <c r="BS22">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT22">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU22">
         <v>6.2</v>
       </c>
       <c r="BV22">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW22">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BX22">
         <v>32</v>
       </c>
       <c r="BY22">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ22">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA22">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB22" t="s">
         <v>177</v>
@@ -6223,22 +6223,22 @@
         <v>164</v>
       </c>
       <c r="F23">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="G23">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I23">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J23">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K23">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L23">
         <v>1.37</v>
@@ -6250,52 +6250,52 @@
         <v>4.6</v>
       </c>
       <c r="O23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P23">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q23">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R23">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S23">
         <v>3</v>
       </c>
       <c r="T23">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U23">
         <v>2.3</v>
       </c>
       <c r="V23">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y23">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z23">
         <v>34</v>
       </c>
       <c r="AA23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB23">
         <v>10.5</v>
       </c>
       <c r="AC23">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE23">
         <v>48</v>
@@ -6313,31 +6313,31 @@
         <v>55</v>
       </c>
       <c r="AJ23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK23">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM23">
         <v>85</v>
       </c>
       <c r="AN23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO23">
         <v>50</v>
       </c>
       <c r="AP23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR23">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS23">
         <v>75</v>
@@ -6346,13 +6346,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU23">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW23">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX23">
         <v>11.5</v>
@@ -6361,88 +6361,88 @@
         <v>9.6</v>
       </c>
       <c r="AZ23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA23">
         <v>48</v>
       </c>
       <c r="BB23">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC23">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD23">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE23">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG23">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH23">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BI23">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ23">
         <v>9.4</v>
       </c>
       <c r="BK23">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL23">
         <v>110</v>
       </c>
       <c r="BM23">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BN23">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO23">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP23">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ23">
         <v>11</v>
       </c>
       <c r="BR23">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS23">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT23">
         <v>8</v>
       </c>
       <c r="BU23">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV23">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX23">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY23">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ23">
         <v>20</v>
       </c>
       <c r="CA23">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB23" t="s">
         <v>177</v>
@@ -6465,37 +6465,37 @@
         <v>165</v>
       </c>
       <c r="F24">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G24">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H24">
+        <v>3.6</v>
+      </c>
+      <c r="I24">
         <v>3.7</v>
       </c>
-      <c r="I24">
-        <v>3.75</v>
-      </c>
       <c r="J24">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K24">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L24">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M24">
         <v>1.07</v>
       </c>
       <c r="N24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O24">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P24">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q24">
         <v>1.97</v>
@@ -6504,16 +6504,16 @@
         <v>1.38</v>
       </c>
       <c r="S24">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T24">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U24">
         <v>2.2</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
         <v>1.81</v>
@@ -6522,16 +6522,16 @@
         <v>14.5</v>
       </c>
       <c r="Y24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z24">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA24">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC24">
         <v>8</v>
@@ -6543,7 +6543,7 @@
         <v>40</v>
       </c>
       <c r="AF24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG24">
         <v>10.5</v>
@@ -6552,7 +6552,7 @@
         <v>17</v>
       </c>
       <c r="AI24">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ24">
         <v>27</v>
@@ -6561,16 +6561,16 @@
         <v>22</v>
       </c>
       <c r="AL24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM24">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO24">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP24">
         <v>13</v>
@@ -6582,19 +6582,19 @@
         <v>23</v>
       </c>
       <c r="AS24">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT24">
         <v>9.199999999999999</v>
       </c>
       <c r="AU24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV24">
         <v>13.5</v>
       </c>
       <c r="AW24">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX24">
         <v>13</v>
@@ -6612,7 +6612,7 @@
         <v>25</v>
       </c>
       <c r="BC24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD24">
         <v>32</v>
@@ -6642,16 +6642,16 @@
         <v>130</v>
       </c>
       <c r="BM24">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN24">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO24">
         <v>4.6</v>
       </c>
       <c r="BP24">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ24">
         <v>13.5</v>
@@ -6660,7 +6660,7 @@
         <v>29</v>
       </c>
       <c r="BS24">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BT24">
         <v>6.8</v>
@@ -6669,22 +6669,22 @@
         <v>6.2</v>
       </c>
       <c r="BV24">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BW24">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX24">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BY24">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ24">
         <v>25</v>
       </c>
       <c r="CA24">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="CB24" t="s">
         <v>177</v>
@@ -6707,7 +6707,7 @@
         <v>166</v>
       </c>
       <c r="F25">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G25">
         <v>3.25</v>
@@ -6716,7 +6716,7 @@
         <v>2.44</v>
       </c>
       <c r="I25">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J25">
         <v>3.55</v>
@@ -6755,13 +6755,13 @@
         <v>2.28</v>
       </c>
       <c r="V25">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W25">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X25">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y25">
         <v>11</v>
@@ -6806,7 +6806,7 @@
         <v>44</v>
       </c>
       <c r="AM25">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN25">
         <v>32</v>
@@ -6839,10 +6839,10 @@
         <v>23</v>
       </c>
       <c r="AX25">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ25">
         <v>15.5</v>
@@ -6851,16 +6851,16 @@
         <v>34</v>
       </c>
       <c r="BB25">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BC25">
         <v>30</v>
       </c>
       <c r="BD25">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE25">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF25">
         <v>28</v>
@@ -6869,7 +6869,7 @@
         <v>18</v>
       </c>
       <c r="BH25">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI25">
         <v>3.25</v>
@@ -6884,7 +6884,7 @@
         <v>130</v>
       </c>
       <c r="BM25">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BN25">
         <v>6.2</v>
@@ -6896,16 +6896,16 @@
         <v>24</v>
       </c>
       <c r="BQ25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR25">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BS25">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BT25">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU25">
         <v>4.9</v>
@@ -6914,19 +6914,19 @@
         <v>18</v>
       </c>
       <c r="BW25">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX25">
         <v>30</v>
       </c>
       <c r="BY25">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ25">
         <v>25</v>
       </c>
       <c r="CA25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB25" t="s">
         <v>177</v>
@@ -6949,16 +6949,16 @@
         <v>167</v>
       </c>
       <c r="F26">
+        <v>2.12</v>
+      </c>
+      <c r="G26">
         <v>2.14</v>
       </c>
-      <c r="G26">
-        <v>2.16</v>
-      </c>
       <c r="H26">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I26">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J26">
         <v>3.85</v>
@@ -6973,25 +6973,25 @@
         <v>1.05</v>
       </c>
       <c r="N26">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O26">
         <v>1.23</v>
       </c>
       <c r="P26">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q26">
         <v>1.68</v>
       </c>
       <c r="R26">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S26">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T26">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U26">
         <v>2.58</v>
@@ -7000,10 +7000,10 @@
         <v>1.37</v>
       </c>
       <c r="W26">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y26">
         <v>18</v>
@@ -7015,16 +7015,16 @@
         <v>65</v>
       </c>
       <c r="AB26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE26">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF26">
         <v>15.5</v>
@@ -7039,7 +7039,7 @@
         <v>40</v>
       </c>
       <c r="AJ26">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK26">
         <v>19.5</v>
@@ -7060,13 +7060,13 @@
         <v>19</v>
       </c>
       <c r="AQ26">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS26">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT26">
         <v>12</v>
@@ -7075,7 +7075,7 @@
         <v>8.6</v>
       </c>
       <c r="AV26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW26">
         <v>32</v>
@@ -7090,10 +7090,10 @@
         <v>14</v>
       </c>
       <c r="BA26">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC26">
         <v>18</v>
@@ -7108,7 +7108,7 @@
         <v>10.5</v>
       </c>
       <c r="BG26">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BH26">
         <v>4.1</v>
@@ -7120,13 +7120,13 @@
         <v>8.6</v>
       </c>
       <c r="BK26">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL26">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BM26">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN26">
         <v>5.2</v>
@@ -7135,16 +7135,16 @@
         <v>4.8</v>
       </c>
       <c r="BP26">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ26">
-        <v>12.5</v>
+        <v>7.4</v>
       </c>
       <c r="BR26">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BS26">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT26">
         <v>7</v>
@@ -7156,19 +7156,19 @@
         <v>26</v>
       </c>
       <c r="BW26">
+        <v>9.4</v>
+      </c>
+      <c r="BX26">
+        <v>34</v>
+      </c>
+      <c r="BY26">
         <v>10</v>
       </c>
-      <c r="BX26">
-        <v>32</v>
-      </c>
-      <c r="BY26">
-        <v>11</v>
-      </c>
       <c r="BZ26">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA26">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB26" t="s">
         <v>177</v>
@@ -7191,7 +7191,7 @@
         <v>168</v>
       </c>
       <c r="F27">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G27">
         <v>2.14</v>
@@ -7224,10 +7224,10 @@
         <v>1.98</v>
       </c>
       <c r="Q27">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R27">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S27">
         <v>3.55</v>
@@ -7236,7 +7236,7 @@
         <v>1.8</v>
       </c>
       <c r="U27">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V27">
         <v>1.34</v>
@@ -7260,13 +7260,13 @@
         <v>9.4</v>
       </c>
       <c r="AC27">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD27">
         <v>15</v>
       </c>
       <c r="AE27">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF27">
         <v>13</v>
@@ -7275,10 +7275,10 @@
         <v>10.5</v>
       </c>
       <c r="AH27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI27">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ27">
         <v>26</v>
@@ -7293,7 +7293,7 @@
         <v>95</v>
       </c>
       <c r="AN27">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO27">
         <v>46</v>
@@ -7329,10 +7329,10 @@
         <v>10</v>
       </c>
       <c r="AZ27">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA27">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB27">
         <v>24</v>
@@ -7347,13 +7347,13 @@
         <v>75</v>
       </c>
       <c r="BF27">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG27">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH27">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI27">
         <v>3.2</v>
@@ -7368,7 +7368,7 @@
         <v>140</v>
       </c>
       <c r="BM27">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="BN27">
         <v>4.9</v>
@@ -7377,40 +7377,40 @@
         <v>4.4</v>
       </c>
       <c r="BP27">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BQ27">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BR27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS27">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT27">
         <v>7.2</v>
       </c>
       <c r="BU27">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV27">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BX27">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY27">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BZ27">
         <v>26</v>
       </c>
       <c r="CA27">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="CB27" t="s">
         <v>177</v>
@@ -7433,16 +7433,16 @@
         <v>169</v>
       </c>
       <c r="F28">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="G28">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="H28">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="I28">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="J28">
         <v>4.4</v>
@@ -7457,7 +7457,7 @@
         <v>1.04</v>
       </c>
       <c r="N28">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O28">
         <v>1.19</v>
@@ -7475,16 +7475,16 @@
         <v>2.5</v>
       </c>
       <c r="T28">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U28">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V28">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="W28">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X28">
         <v>24</v>
@@ -7493,16 +7493,16 @@
         <v>12</v>
       </c>
       <c r="Z28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA28">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB28">
         <v>26</v>
       </c>
       <c r="AC28">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD28">
         <v>9.6</v>
@@ -7511,10 +7511,10 @@
         <v>15</v>
       </c>
       <c r="AF28">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG28">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH28">
         <v>17</v>
@@ -7523,37 +7523,37 @@
         <v>27</v>
       </c>
       <c r="AJ28">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK28">
+        <v>65</v>
+      </c>
+      <c r="AL28">
         <v>60</v>
-      </c>
-      <c r="AL28">
-        <v>55</v>
       </c>
       <c r="AM28">
         <v>70</v>
       </c>
       <c r="AN28">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO28">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AP28">
         <v>22</v>
       </c>
       <c r="AQ28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS28">
         <v>15</v>
       </c>
       <c r="AT28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU28">
         <v>9.800000000000001</v>
@@ -7565,13 +7565,13 @@
         <v>14</v>
       </c>
       <c r="AX28">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AY28">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AZ28">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA28">
         <v>25</v>
@@ -7580,7 +7580,7 @@
         <v>100</v>
       </c>
       <c r="BC28">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD28">
         <v>50</v>
@@ -7589,7 +7589,7 @@
         <v>65</v>
       </c>
       <c r="BF28">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BG28">
         <v>6.6</v>
@@ -7598,7 +7598,7 @@
         <v>4.3</v>
       </c>
       <c r="BI28">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ28">
         <v>9.4</v>
@@ -7610,13 +7610,13 @@
         <v>100</v>
       </c>
       <c r="BM28">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN28">
         <v>9</v>
       </c>
       <c r="BO28">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BP28">
         <v>38</v>
@@ -7634,7 +7634,7 @@
         <v>4.6</v>
       </c>
       <c r="BU28">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV28">
         <v>10.5</v>
@@ -7646,10 +7646,10 @@
         <v>21</v>
       </c>
       <c r="BY28">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BZ28">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA28">
         <v>7.8</v>
@@ -7675,67 +7675,67 @@
         <v>170</v>
       </c>
       <c r="F29">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G29">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="H29">
+        <v>4.2</v>
+      </c>
+      <c r="I29">
         <v>4.3</v>
       </c>
-      <c r="I29">
-        <v>4.4</v>
-      </c>
       <c r="J29">
+        <v>4.1</v>
+      </c>
+      <c r="K29">
         <v>4.2</v>
       </c>
-      <c r="K29">
-        <v>4.3</v>
-      </c>
       <c r="L29">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M29">
         <v>1.03</v>
       </c>
       <c r="N29">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O29">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P29">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q29">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R29">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="S29">
         <v>2.3</v>
       </c>
       <c r="T29">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U29">
         <v>2.84</v>
       </c>
       <c r="V29">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X29">
         <v>28</v>
       </c>
       <c r="Y29">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z29">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA29">
         <v>85</v>
@@ -7747,16 +7747,16 @@
         <v>10</v>
       </c>
       <c r="AD29">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE29">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF29">
         <v>15.5</v>
       </c>
       <c r="AG29">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH29">
         <v>14</v>
@@ -7765,13 +7765,13 @@
         <v>38</v>
       </c>
       <c r="AJ29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK29">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM29">
         <v>50</v>
@@ -7783,16 +7783,16 @@
         <v>29</v>
       </c>
       <c r="AP29">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ29">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AR29">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS29">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT29">
         <v>13.5</v>
@@ -7810,10 +7810,10 @@
         <v>14.5</v>
       </c>
       <c r="AY29">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA29">
         <v>34</v>
@@ -7822,19 +7822,19 @@
         <v>20</v>
       </c>
       <c r="BC29">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD29">
         <v>22</v>
       </c>
       <c r="BE29">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF29">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH29">
         <v>4.7</v>
@@ -7849,10 +7849,10 @@
         <v>7.8</v>
       </c>
       <c r="BL29">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="BM29">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BN29">
         <v>5.1</v>
@@ -7873,28 +7873,28 @@
         <v>17</v>
       </c>
       <c r="BT29">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU29">
         <v>7.2</v>
       </c>
       <c r="BV29">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW29">
         <v>24</v>
       </c>
       <c r="BX29">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY29">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="BZ29">
         <v>13</v>
       </c>
       <c r="CA29">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB29" t="s">
         <v>177</v>
@@ -7917,16 +7917,16 @@
         <v>171</v>
       </c>
       <c r="F30">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G30">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H30">
         <v>1.72</v>
       </c>
       <c r="I30">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="J30">
         <v>4.2</v>
@@ -7935,7 +7935,7 @@
         <v>4.3</v>
       </c>
       <c r="L30">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M30">
         <v>1.05</v>
@@ -7944,49 +7944,49 @@
         <v>5</v>
       </c>
       <c r="O30">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P30">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q30">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R30">
         <v>1.53</v>
       </c>
       <c r="S30">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T30">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U30">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V30">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="W30">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X30">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z30">
         <v>11</v>
       </c>
       <c r="AA30">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AB30">
         <v>22</v>
       </c>
       <c r="AC30">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD30">
         <v>9.6</v>
@@ -8007,7 +8007,7 @@
         <v>28</v>
       </c>
       <c r="AJ30">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK30">
         <v>60</v>
@@ -8022,10 +8022,10 @@
         <v>60</v>
       </c>
       <c r="AO30">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP30">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ30">
         <v>10</v>
@@ -8043,22 +8043,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV30">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW30">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX30">
         <v>40</v>
       </c>
       <c r="AY30">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AZ30">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB30">
         <v>100</v>
@@ -8070,25 +8070,25 @@
         <v>50</v>
       </c>
       <c r="BE30">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BF30">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BG30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH30">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI30">
         <v>3.75</v>
       </c>
       <c r="BJ30">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BK30">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL30">
         <v>120</v>
@@ -8097,19 +8097,19 @@
         <v>60</v>
       </c>
       <c r="BN30">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO30">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BP30">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ30">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BR30">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BS30">
         <v>36</v>
@@ -8121,10 +8121,10 @@
         <v>4.2</v>
       </c>
       <c r="BV30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BW30">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX30">
         <v>23</v>
@@ -8159,16 +8159,16 @@
         <v>172</v>
       </c>
       <c r="F31">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G31">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H31">
+        <v>3.5</v>
+      </c>
+      <c r="I31">
         <v>3.55</v>
-      </c>
-      <c r="I31">
-        <v>3.6</v>
       </c>
       <c r="J31">
         <v>3.6</v>
@@ -8177,7 +8177,7 @@
         <v>3.65</v>
       </c>
       <c r="L31">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M31">
         <v>1.06</v>
@@ -8186,16 +8186,16 @@
         <v>4.4</v>
       </c>
       <c r="O31">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P31">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q31">
         <v>1.87</v>
       </c>
       <c r="R31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S31">
         <v>3.15</v>
@@ -8204,19 +8204,19 @@
         <v>1.71</v>
       </c>
       <c r="U31">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V31">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W31">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X31">
         <v>16</v>
       </c>
       <c r="Y31">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z31">
         <v>25</v>
@@ -8231,7 +8231,7 @@
         <v>8</v>
       </c>
       <c r="AD31">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE31">
         <v>38</v>
@@ -8246,7 +8246,7 @@
         <v>15.5</v>
       </c>
       <c r="AI31">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ31">
         <v>29</v>
@@ -8261,19 +8261,19 @@
         <v>75</v>
       </c>
       <c r="AN31">
+        <v>14.5</v>
+      </c>
+      <c r="AO31">
+        <v>32</v>
+      </c>
+      <c r="AP31">
         <v>15</v>
-      </c>
-      <c r="AO31">
-        <v>34</v>
-      </c>
-      <c r="AP31">
-        <v>14.5</v>
       </c>
       <c r="AQ31">
         <v>14</v>
       </c>
       <c r="AR31">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS31">
         <v>55</v>
@@ -8297,7 +8297,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ31">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA31">
         <v>38</v>
@@ -8324,22 +8324,22 @@
         <v>3.6</v>
       </c>
       <c r="BI31">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ31">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK31">
         <v>8</v>
       </c>
       <c r="BL31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM31">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BN31">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO31">
         <v>4.8</v>
@@ -8348,31 +8348,31 @@
         <v>15.5</v>
       </c>
       <c r="BQ31">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BR31">
         <v>27</v>
       </c>
       <c r="BS31">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BT31">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU31">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV31">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW31">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="BX31">
         <v>34</v>
       </c>
       <c r="BY31">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BZ31">
         <v>22</v>
@@ -8401,82 +8401,82 @@
         <v>173</v>
       </c>
       <c r="F32">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G32">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H32">
+        <v>5.5</v>
+      </c>
+      <c r="I32">
         <v>5.6</v>
       </c>
-      <c r="I32">
-        <v>5.8</v>
-      </c>
       <c r="J32">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K32">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L32">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M32">
         <v>1.03</v>
       </c>
       <c r="N32">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O32">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P32">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q32">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R32">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="S32">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="T32">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U32">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V32">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W32">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X32">
         <v>34</v>
       </c>
       <c r="Y32">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z32">
         <v>55</v>
       </c>
       <c r="AA32">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB32">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC32">
         <v>11.5</v>
       </c>
       <c r="AD32">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF32">
         <v>13.5</v>
@@ -8488,7 +8488,7 @@
         <v>15.5</v>
       </c>
       <c r="AI32">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ32">
         <v>17.5</v>
@@ -8497,16 +8497,16 @@
         <v>13.5</v>
       </c>
       <c r="AL32">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM32">
         <v>55</v>
       </c>
       <c r="AN32">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AO32">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP32">
         <v>30</v>
@@ -8518,22 +8518,22 @@
         <v>50</v>
       </c>
       <c r="AS32">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AT32">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU32">
         <v>10.5</v>
       </c>
       <c r="AV32">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AW32">
         <v>50</v>
       </c>
       <c r="AX32">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY32">
         <v>9.6</v>
@@ -8551,13 +8551,13 @@
         <v>13</v>
       </c>
       <c r="BD32">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE32">
         <v>48</v>
       </c>
       <c r="BF32">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG32">
         <v>38</v>
@@ -8569,7 +8569,7 @@
         <v>4.6</v>
       </c>
       <c r="BJ32">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK32">
         <v>8</v>
@@ -8578,7 +8578,7 @@
         <v>70</v>
       </c>
       <c r="BM32">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="BN32">
         <v>4.8</v>
@@ -8587,13 +8587,13 @@
         <v>4.5</v>
       </c>
       <c r="BP32">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BQ32">
         <v>8.800000000000001</v>
       </c>
       <c r="BR32">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BS32">
         <v>16</v>
@@ -8605,22 +8605,22 @@
         <v>8.4</v>
       </c>
       <c r="BV32">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW32">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BX32">
         <v>34</v>
       </c>
       <c r="BY32">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="BZ32">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA32">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB32" t="s">
         <v>177</v>
@@ -8643,25 +8643,25 @@
         <v>174</v>
       </c>
       <c r="F33">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G33">
         <v>2.46</v>
       </c>
       <c r="H33">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I33">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J33">
         <v>3.25</v>
       </c>
       <c r="K33">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L33">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M33">
         <v>1.1</v>
@@ -8670,10 +8670,10 @@
         <v>3.1</v>
       </c>
       <c r="O33">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P33">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q33">
         <v>2.3</v>
@@ -8688,7 +8688,7 @@
         <v>1.89</v>
       </c>
       <c r="U33">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="V33">
         <v>1.38</v>
@@ -8697,16 +8697,16 @@
         <v>1.68</v>
       </c>
       <c r="X33">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Y33">
         <v>12</v>
       </c>
       <c r="Z33">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AA33">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB33">
         <v>9.199999999999999</v>
@@ -8727,16 +8727,16 @@
         <v>12.5</v>
       </c>
       <c r="AH33">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI33">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ33">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AK33">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AL33">
         <v>60</v>
@@ -8745,58 +8745,58 @@
         <v>580</v>
       </c>
       <c r="AN33">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO33">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="AP33">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ33">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AR33">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AS33">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AT33">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="AU33">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="AV33">
         <v>12.5</v>
       </c>
       <c r="AW33">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AX33">
         <v>12</v>
       </c>
       <c r="AY33">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AZ33">
         <v>16.5</v>
       </c>
       <c r="BA33">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BB33">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC33">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="BD33">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BE33">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF33">
         <v>6.2</v>
@@ -8814,31 +8814,31 @@
         <v>12.5</v>
       </c>
       <c r="BK33">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BN33">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BO33">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BP33">
         <v>24</v>
       </c>
       <c r="BQ33">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BR33">
         <v>46</v>
       </c>
       <c r="BS33">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BT33">
         <v>7.8</v>
@@ -8850,19 +8850,19 @@
         <v>38</v>
       </c>
       <c r="BW33">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BX33">
         <v>60</v>
       </c>
       <c r="BY33">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BZ33">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA33">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="CB33" t="s">
         <v>177</v>
@@ -8894,22 +8894,22 @@
         <v>6.6</v>
       </c>
       <c r="I34">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K34">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L34">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M34">
         <v>1.14</v>
       </c>
       <c r="N34">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O34">
         <v>1.61</v>
@@ -8918,31 +8918,31 @@
         <v>1.51</v>
       </c>
       <c r="Q34">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R34">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S34">
         <v>6.2</v>
       </c>
       <c r="T34">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="U34">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V34">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W34">
         <v>2.28</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y34">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z34">
         <v>55</v>
@@ -8954,13 +8954,13 @@
         <v>5.7</v>
       </c>
       <c r="AC34">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD34">
         <v>32</v>
       </c>
       <c r="AE34">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AF34">
         <v>8.4</v>
@@ -8972,13 +8972,13 @@
         <v>38</v>
       </c>
       <c r="AI34">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AJ34">
         <v>17.5</v>
       </c>
       <c r="AK34">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL34">
         <v>85</v>
@@ -8987,73 +8987,73 @@
         <v>400</v>
       </c>
       <c r="AN34">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO34">
         <v>380</v>
       </c>
       <c r="AP34">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ34">
         <v>13.5</v>
       </c>
       <c r="AR34">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AS34">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AT34">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU34">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV34">
         <v>27</v>
       </c>
       <c r="AW34">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX34">
         <v>7.6</v>
       </c>
       <c r="AY34">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ34">
         <v>32</v>
       </c>
       <c r="BA34">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BB34">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC34">
         <v>24</v>
       </c>
       <c r="BD34">
-        <v>65</v>
+        <v>17.5</v>
       </c>
       <c r="BE34">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BF34">
         <v>16.5</v>
       </c>
       <c r="BG34">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH34">
         <v>2.6</v>
       </c>
       <c r="BI34">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BJ34">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BK34">
         <v>11.5</v>
@@ -9065,28 +9065,28 @@
         <v>21</v>
       </c>
       <c r="BN34">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BO34">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP34">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ34">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BT34">
         <v>11</v>
       </c>
       <c r="BU34">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BV34">
         <v>1000</v>
@@ -9104,7 +9104,7 @@
         <v>1000</v>
       </c>
       <c r="CA34">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="CB34" t="s">
         <v>177</v>
@@ -9133,13 +9133,13 @@
         <v>2.02</v>
       </c>
       <c r="H35">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I35">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J35">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K35">
         <v>3.35</v>
@@ -9154,10 +9154,10 @@
         <v>2.58</v>
       </c>
       <c r="O35">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P35">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q35">
         <v>2.88</v>
@@ -9169,7 +9169,7 @@
         <v>6</v>
       </c>
       <c r="T35">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U35">
         <v>1.69</v>
@@ -9181,7 +9181,7 @@
         <v>1.98</v>
       </c>
       <c r="X35">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y35">
         <v>12.5</v>
@@ -9190,7 +9190,7 @@
         <v>38</v>
       </c>
       <c r="AA35">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB35">
         <v>6.2</v>
@@ -9199,10 +9199,10 @@
         <v>7.6</v>
       </c>
       <c r="AD35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE35">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF35">
         <v>10.5</v>
@@ -9211,79 +9211,79 @@
         <v>12</v>
       </c>
       <c r="AH35">
+        <v>34</v>
+      </c>
+      <c r="AI35">
+        <v>160</v>
+      </c>
+      <c r="AJ35">
+        <v>26</v>
+      </c>
+      <c r="AK35">
         <v>32</v>
       </c>
-      <c r="AI35">
-        <v>140</v>
-      </c>
-      <c r="AJ35">
-        <v>25</v>
-      </c>
-      <c r="AK35">
-        <v>36</v>
-      </c>
       <c r="AL35">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AM35">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="AN35">
         <v>27</v>
       </c>
       <c r="AO35">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AP35">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ35">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR35">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="AS35">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT35">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU35">
         <v>6.8</v>
       </c>
       <c r="AV35">
-        <v>8.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="AW35">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX35">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ35">
-        <v>9.4</v>
+        <v>25</v>
       </c>
       <c r="BA35">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BB35">
-        <v>20</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC35">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="BD35">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BE35">
         <v>12</v>
       </c>
       <c r="BF35">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BG35">
         <v>12</v>
@@ -9298,13 +9298,13 @@
         <v>12.5</v>
       </c>
       <c r="BK35">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BN35">
         <v>4.3</v>
@@ -9316,37 +9316,37 @@
         <v>16</v>
       </c>
       <c r="BQ35">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR35">
         <v>42</v>
       </c>
       <c r="BS35">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT35">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU35">
         <v>5.9</v>
       </c>
       <c r="BV35">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW35">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BX35">
         <v>1000</v>
       </c>
       <c r="BY35">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BZ35">
         <v>1000</v>
       </c>
       <c r="CA35">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB35" t="s">
         <v>177</v>
